--- a/data_fetching/Entsoe/Unintended_Deviation.xlsx
+++ b/data_fetching/Entsoe/Unintended_Deviation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="135">
   <si>
     <t>Timestamp</t>
   </si>
@@ -31,433 +31,394 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>03.09.20261</t>
-  </si>
-  <si>
-    <t>03.09.20262</t>
-  </si>
-  <si>
-    <t>03.09.20263</t>
-  </si>
-  <si>
-    <t>03.09.20264</t>
-  </si>
-  <si>
-    <t>03.09.20265</t>
-  </si>
-  <si>
-    <t>03.09.20266</t>
-  </si>
-  <si>
-    <t>03.09.20267</t>
-  </si>
-  <si>
-    <t>03.09.20268</t>
-  </si>
-  <si>
-    <t>03.09.20269</t>
-  </si>
-  <si>
-    <t>03.09.202610</t>
-  </si>
-  <si>
-    <t>03.09.202611</t>
-  </si>
-  <si>
-    <t>03.09.202612</t>
-  </si>
-  <si>
-    <t>03.09.202613</t>
-  </si>
-  <si>
-    <t>03.09.202614</t>
-  </si>
-  <si>
-    <t>03.09.202615</t>
-  </si>
-  <si>
-    <t>03.09.202616</t>
-  </si>
-  <si>
-    <t>03.09.202617</t>
-  </si>
-  <si>
-    <t>03.09.202618</t>
-  </si>
-  <si>
-    <t>03.09.202619</t>
-  </si>
-  <si>
-    <t>03.09.202620</t>
-  </si>
-  <si>
-    <t>03.09.202621</t>
-  </si>
-  <si>
-    <t>03.09.202622</t>
-  </si>
-  <si>
-    <t>03.09.202623</t>
-  </si>
-  <si>
-    <t>03.09.202624</t>
-  </si>
-  <si>
-    <t>03.09.202625</t>
-  </si>
-  <si>
-    <t>03.09.202626</t>
-  </si>
-  <si>
-    <t>03.09.202627</t>
-  </si>
-  <si>
-    <t>03.09.202628</t>
-  </si>
-  <si>
-    <t>03.09.202629</t>
-  </si>
-  <si>
-    <t>03.09.202630</t>
-  </si>
-  <si>
-    <t>03.09.202631</t>
-  </si>
-  <si>
-    <t>03.09.202632</t>
-  </si>
-  <si>
-    <t>03.09.202633</t>
-  </si>
-  <si>
-    <t>03.09.202634</t>
-  </si>
-  <si>
-    <t>03.09.202635</t>
-  </si>
-  <si>
-    <t>03.09.202636</t>
-  </si>
-  <si>
-    <t>03.09.202637</t>
-  </si>
-  <si>
-    <t>03.09.202638</t>
-  </si>
-  <si>
-    <t>03.09.202639</t>
-  </si>
-  <si>
-    <t>03.09.202640</t>
-  </si>
-  <si>
-    <t>03.09.202641</t>
-  </si>
-  <si>
-    <t>03.09.202642</t>
-  </si>
-  <si>
-    <t>03.09.202643</t>
-  </si>
-  <si>
-    <t>03.09.202644</t>
-  </si>
-  <si>
-    <t>03.09.202645</t>
-  </si>
-  <si>
-    <t>03.09.202646</t>
-  </si>
-  <si>
-    <t>03.09.202647</t>
-  </si>
-  <si>
-    <t>03.09.202648</t>
-  </si>
-  <si>
-    <t>03.09.202649</t>
-  </si>
-  <si>
-    <t>03.09.202650</t>
-  </si>
-  <si>
-    <t>03.09.202651</t>
-  </si>
-  <si>
-    <t>03.09.202652</t>
-  </si>
-  <si>
-    <t>03.09.202653</t>
-  </si>
-  <si>
-    <t>03.09.202654</t>
-  </si>
-  <si>
-    <t>03.09.202655</t>
-  </si>
-  <si>
-    <t>03.09.202656</t>
-  </si>
-  <si>
-    <t>03.09.202657</t>
-  </si>
-  <si>
-    <t>03.09.202658</t>
-  </si>
-  <si>
-    <t>03.09.202659</t>
-  </si>
-  <si>
-    <t>03.09.202660</t>
-  </si>
-  <si>
-    <t>03.09.202661</t>
-  </si>
-  <si>
-    <t>03.09.202662</t>
-  </si>
-  <si>
-    <t>03.09.202663</t>
-  </si>
-  <si>
-    <t>03.09.202664</t>
-  </si>
-  <si>
-    <t>03.09.202665</t>
-  </si>
-  <si>
-    <t>03.09.202666</t>
-  </si>
-  <si>
-    <t>03.09.202667</t>
-  </si>
-  <si>
-    <t>03.09.202668</t>
-  </si>
-  <si>
-    <t>03.09.202669</t>
-  </si>
-  <si>
-    <t>03.09.202670</t>
-  </si>
-  <si>
-    <t>03.09.202671</t>
-  </si>
-  <si>
-    <t>03.09.202672</t>
-  </si>
-  <si>
-    <t>03.09.202673</t>
-  </si>
-  <si>
-    <t>03.09.202674</t>
-  </si>
-  <si>
-    <t>03.09.202675</t>
-  </si>
-  <si>
-    <t>03.09.202676</t>
-  </si>
-  <si>
-    <t>03.09.202677</t>
-  </si>
-  <si>
-    <t>03.09.202678</t>
-  </si>
-  <si>
-    <t>03.09.202679</t>
-  </si>
-  <si>
-    <t>03.09.202680</t>
-  </si>
-  <si>
-    <t>03.09.202681</t>
-  </si>
-  <si>
-    <t>03.09.202682</t>
-  </si>
-  <si>
-    <t>03.09.202683</t>
-  </si>
-  <si>
-    <t>03.09.202684</t>
-  </si>
-  <si>
-    <t>03.09.202685</t>
-  </si>
-  <si>
-    <t>03.09.202686</t>
-  </si>
-  <si>
-    <t>03.09.202687</t>
-  </si>
-  <si>
-    <t>03.09.202688</t>
-  </si>
-  <si>
-    <t>03.09.202689</t>
-  </si>
-  <si>
-    <t>03.09.202690</t>
-  </si>
-  <si>
-    <t>03.09.202691</t>
-  </si>
-  <si>
-    <t>03.09.202692</t>
-  </si>
-  <si>
-    <t>03.09.202693</t>
-  </si>
-  <si>
-    <t>03.09.202694</t>
-  </si>
-  <si>
-    <t>03.09.202695</t>
-  </si>
-  <si>
-    <t>03.09.202696</t>
-  </si>
-  <si>
-    <t>04.09.20261</t>
-  </si>
-  <si>
-    <t>04.09.20262</t>
-  </si>
-  <si>
-    <t>04.09.20263</t>
-  </si>
-  <si>
-    <t>04.09.20264</t>
-  </si>
-  <si>
-    <t>04.09.20265</t>
-  </si>
-  <si>
-    <t>04.09.20266</t>
-  </si>
-  <si>
-    <t>04.09.20267</t>
-  </si>
-  <si>
-    <t>04.09.20268</t>
-  </si>
-  <si>
-    <t>04.09.20269</t>
-  </si>
-  <si>
-    <t>04.09.202610</t>
-  </si>
-  <si>
-    <t>04.09.202611</t>
-  </si>
-  <si>
-    <t>04.09.202612</t>
-  </si>
-  <si>
-    <t>04.09.202613</t>
-  </si>
-  <si>
-    <t>04.09.202614</t>
-  </si>
-  <si>
-    <t>04.09.202615</t>
-  </si>
-  <si>
-    <t>04.09.202616</t>
-  </si>
-  <si>
-    <t>04.09.202617</t>
-  </si>
-  <si>
-    <t>04.09.202618</t>
-  </si>
-  <si>
-    <t>04.09.202619</t>
-  </si>
-  <si>
-    <t>04.09.202620</t>
-  </si>
-  <si>
-    <t>04.09.202621</t>
-  </si>
-  <si>
-    <t>04.09.202622</t>
-  </si>
-  <si>
-    <t>04.09.202623</t>
-  </si>
-  <si>
-    <t>04.09.202624</t>
-  </si>
-  <si>
-    <t>04.09.202625</t>
-  </si>
-  <si>
-    <t>04.09.202626</t>
-  </si>
-  <si>
-    <t>04.09.202627</t>
-  </si>
-  <si>
-    <t>04.09.202628</t>
-  </si>
-  <si>
-    <t>04.09.202629</t>
-  </si>
-  <si>
-    <t>04.09.202630</t>
-  </si>
-  <si>
-    <t>04.09.202631</t>
-  </si>
-  <si>
-    <t>04.09.202632</t>
-  </si>
-  <si>
-    <t>04.09.202633</t>
-  </si>
-  <si>
-    <t>04.09.202634</t>
-  </si>
-  <si>
-    <t>04.09.202635</t>
-  </si>
-  <si>
-    <t>04.09.202636</t>
-  </si>
-  <si>
-    <t>04.09.202637</t>
-  </si>
-  <si>
-    <t>04.09.202638</t>
-  </si>
-  <si>
-    <t>04.09.202639</t>
-  </si>
-  <si>
-    <t>04.09.202640</t>
-  </si>
-  <si>
-    <t>04.09.202641</t>
-  </si>
-  <si>
-    <t>04.09.202642</t>
-  </si>
-  <si>
-    <t>04.09.202643</t>
-  </si>
-  <si>
-    <t>04.09.202644</t>
-  </si>
-  <si>
-    <t>04.09.202645</t>
-  </si>
-  <si>
-    <t>04.09.202646</t>
-  </si>
-  <si>
-    <t>04.09.202647</t>
+    <t>12.09.20261</t>
+  </si>
+  <si>
+    <t>12.09.20262</t>
+  </si>
+  <si>
+    <t>12.09.20263</t>
+  </si>
+  <si>
+    <t>12.09.20264</t>
+  </si>
+  <si>
+    <t>12.09.20265</t>
+  </si>
+  <si>
+    <t>12.09.20266</t>
+  </si>
+  <si>
+    <t>12.09.20267</t>
+  </si>
+  <si>
+    <t>12.09.20268</t>
+  </si>
+  <si>
+    <t>12.09.20269</t>
+  </si>
+  <si>
+    <t>12.09.202610</t>
+  </si>
+  <si>
+    <t>12.09.202611</t>
+  </si>
+  <si>
+    <t>12.09.202612</t>
+  </si>
+  <si>
+    <t>12.09.202613</t>
+  </si>
+  <si>
+    <t>12.09.202614</t>
+  </si>
+  <si>
+    <t>12.09.202615</t>
+  </si>
+  <si>
+    <t>12.09.202616</t>
+  </si>
+  <si>
+    <t>12.09.202617</t>
+  </si>
+  <si>
+    <t>12.09.202618</t>
+  </si>
+  <si>
+    <t>12.09.202619</t>
+  </si>
+  <si>
+    <t>12.09.202620</t>
+  </si>
+  <si>
+    <t>12.09.202621</t>
+  </si>
+  <si>
+    <t>12.09.202622</t>
+  </si>
+  <si>
+    <t>12.09.202623</t>
+  </si>
+  <si>
+    <t>12.09.202624</t>
+  </si>
+  <si>
+    <t>12.09.202625</t>
+  </si>
+  <si>
+    <t>12.09.202626</t>
+  </si>
+  <si>
+    <t>12.09.202627</t>
+  </si>
+  <si>
+    <t>12.09.202628</t>
+  </si>
+  <si>
+    <t>12.09.202629</t>
+  </si>
+  <si>
+    <t>12.09.202630</t>
+  </si>
+  <si>
+    <t>12.09.202631</t>
+  </si>
+  <si>
+    <t>12.09.202632</t>
+  </si>
+  <si>
+    <t>12.09.202633</t>
+  </si>
+  <si>
+    <t>12.09.202634</t>
+  </si>
+  <si>
+    <t>12.09.202635</t>
+  </si>
+  <si>
+    <t>12.09.202636</t>
+  </si>
+  <si>
+    <t>12.09.202637</t>
+  </si>
+  <si>
+    <t>12.09.202638</t>
+  </si>
+  <si>
+    <t>12.09.202639</t>
+  </si>
+  <si>
+    <t>12.09.202640</t>
+  </si>
+  <si>
+    <t>12.09.202641</t>
+  </si>
+  <si>
+    <t>12.09.202642</t>
+  </si>
+  <si>
+    <t>12.09.202643</t>
+  </si>
+  <si>
+    <t>12.09.202644</t>
+  </si>
+  <si>
+    <t>12.09.202645</t>
+  </si>
+  <si>
+    <t>12.09.202646</t>
+  </si>
+  <si>
+    <t>12.09.202647</t>
+  </si>
+  <si>
+    <t>12.09.202648</t>
+  </si>
+  <si>
+    <t>12.09.202649</t>
+  </si>
+  <si>
+    <t>12.09.202650</t>
+  </si>
+  <si>
+    <t>12.09.202651</t>
+  </si>
+  <si>
+    <t>12.09.202652</t>
+  </si>
+  <si>
+    <t>12.09.202653</t>
+  </si>
+  <si>
+    <t>12.09.202654</t>
+  </si>
+  <si>
+    <t>12.09.202655</t>
+  </si>
+  <si>
+    <t>12.09.202656</t>
+  </si>
+  <si>
+    <t>12.09.202657</t>
+  </si>
+  <si>
+    <t>12.09.202658</t>
+  </si>
+  <si>
+    <t>12.09.202659</t>
+  </si>
+  <si>
+    <t>12.09.202660</t>
+  </si>
+  <si>
+    <t>12.09.202661</t>
+  </si>
+  <si>
+    <t>12.09.202662</t>
+  </si>
+  <si>
+    <t>12.09.202663</t>
+  </si>
+  <si>
+    <t>12.09.202664</t>
+  </si>
+  <si>
+    <t>12.09.202665</t>
+  </si>
+  <si>
+    <t>12.09.202666</t>
+  </si>
+  <si>
+    <t>12.09.202667</t>
+  </si>
+  <si>
+    <t>12.09.202668</t>
+  </si>
+  <si>
+    <t>12.09.202669</t>
+  </si>
+  <si>
+    <t>12.09.202670</t>
+  </si>
+  <si>
+    <t>12.09.202671</t>
+  </si>
+  <si>
+    <t>12.09.202672</t>
+  </si>
+  <si>
+    <t>12.09.202673</t>
+  </si>
+  <si>
+    <t>12.09.202674</t>
+  </si>
+  <si>
+    <t>12.09.202675</t>
+  </si>
+  <si>
+    <t>12.09.202676</t>
+  </si>
+  <si>
+    <t>12.09.202677</t>
+  </si>
+  <si>
+    <t>12.09.202678</t>
+  </si>
+  <si>
+    <t>12.09.202679</t>
+  </si>
+  <si>
+    <t>12.09.202680</t>
+  </si>
+  <si>
+    <t>12.09.202681</t>
+  </si>
+  <si>
+    <t>12.09.202682</t>
+  </si>
+  <si>
+    <t>12.09.202683</t>
+  </si>
+  <si>
+    <t>12.09.202684</t>
+  </si>
+  <si>
+    <t>12.09.202685</t>
+  </si>
+  <si>
+    <t>12.09.202686</t>
+  </si>
+  <si>
+    <t>12.09.202687</t>
+  </si>
+  <si>
+    <t>12.09.202688</t>
+  </si>
+  <si>
+    <t>12.09.202689</t>
+  </si>
+  <si>
+    <t>12.09.202690</t>
+  </si>
+  <si>
+    <t>12.09.202691</t>
+  </si>
+  <si>
+    <t>12.09.202692</t>
+  </si>
+  <si>
+    <t>12.09.202693</t>
+  </si>
+  <si>
+    <t>12.09.202694</t>
+  </si>
+  <si>
+    <t>12.09.202695</t>
+  </si>
+  <si>
+    <t>12.09.202696</t>
+  </si>
+  <si>
+    <t>13.09.20261</t>
+  </si>
+  <si>
+    <t>13.09.20262</t>
+  </si>
+  <si>
+    <t>13.09.20263</t>
+  </si>
+  <si>
+    <t>13.09.20264</t>
+  </si>
+  <si>
+    <t>13.09.20265</t>
+  </si>
+  <si>
+    <t>13.09.20266</t>
+  </si>
+  <si>
+    <t>13.09.20267</t>
+  </si>
+  <si>
+    <t>13.09.20268</t>
+  </si>
+  <si>
+    <t>13.09.20269</t>
+  </si>
+  <si>
+    <t>13.09.202610</t>
+  </si>
+  <si>
+    <t>13.09.202611</t>
+  </si>
+  <si>
+    <t>13.09.202612</t>
+  </si>
+  <si>
+    <t>13.09.202613</t>
+  </si>
+  <si>
+    <t>13.09.202614</t>
+  </si>
+  <si>
+    <t>13.09.202615</t>
+  </si>
+  <si>
+    <t>13.09.202616</t>
+  </si>
+  <si>
+    <t>13.09.202617</t>
+  </si>
+  <si>
+    <t>13.09.202618</t>
+  </si>
+  <si>
+    <t>13.09.202619</t>
+  </si>
+  <si>
+    <t>13.09.202620</t>
+  </si>
+  <si>
+    <t>13.09.202621</t>
+  </si>
+  <si>
+    <t>13.09.202622</t>
+  </si>
+  <si>
+    <t>13.09.202623</t>
+  </si>
+  <si>
+    <t>13.09.202624</t>
+  </si>
+  <si>
+    <t>13.09.202625</t>
+  </si>
+  <si>
+    <t>13.09.202626</t>
+  </si>
+  <si>
+    <t>13.09.202627</t>
+  </si>
+  <si>
+    <t>13.09.202628</t>
+  </si>
+  <si>
+    <t>13.09.202629</t>
+  </si>
+  <si>
+    <t>13.09.202630</t>
+  </si>
+  <si>
+    <t>13.09.202631</t>
+  </si>
+  <si>
+    <t>13.09.202632</t>
+  </si>
+  <si>
+    <t>13.09.202633</t>
+  </si>
+  <si>
+    <t>13.09.202634</t>
   </si>
 </sst>
 </file>
@@ -819,7 +780,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E144"/>
+  <dimension ref="A1:E131"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -841,10 +802,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46268</v>
+        <v>46277</v>
       </c>
       <c r="B2">
-        <v>3.249</v>
+        <v>16.786</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -858,13 +819,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46268.01041666666</v>
+        <v>46277.01041666666</v>
       </c>
       <c r="B3">
-        <v>6.566</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>0.582</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -875,13 +836,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46268.02083333334</v>
+        <v>46277.02083333334</v>
       </c>
       <c r="B4">
-        <v>7.848</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>5.409</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -892,10 +853,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46268.03125</v>
+        <v>46277.03125</v>
       </c>
       <c r="B5">
-        <v>5.731</v>
+        <v>1.067</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -909,13 +870,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46268.04166666666</v>
+        <v>46277.04166666666</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>3.511</v>
       </c>
       <c r="C6">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -926,13 +887,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46268.05208333334</v>
+        <v>46277.05208333334</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>0.614</v>
       </c>
       <c r="C7">
-        <v>13.216</v>
+        <v>0</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -943,13 +904,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46268.0625</v>
+        <v>46277.0625</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>12.931</v>
       </c>
       <c r="C8">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -960,13 +921,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46268.07291666666</v>
+        <v>46277.07291666666</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>1.355</v>
       </c>
       <c r="C9">
-        <v>15.06</v>
+        <v>0</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -977,13 +938,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46268.08333333334</v>
+        <v>46277.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="C10">
-        <v>5.007</v>
+        <v>5.236</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -994,13 +955,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46268.09375</v>
+        <v>46277.09375</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>4.581</v>
       </c>
       <c r="C11">
-        <v>2.403</v>
+        <v>0</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1011,10 +972,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46268.10416666666</v>
+        <v>46277.10416666666</v>
       </c>
       <c r="B12">
-        <v>2.851</v>
+        <v>3.204</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1028,13 +989,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46268.11458333334</v>
+        <v>46277.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
       <c r="C13">
-        <v>5.217</v>
+        <v>3.097</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -1045,13 +1006,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46268.125</v>
+        <v>46277.125</v>
       </c>
       <c r="B14">
-        <v>0.621</v>
+        <v>0</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>20.87</v>
       </c>
       <c r="D14">
         <v>13</v>
@@ -1062,13 +1023,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46268.13541666666</v>
+        <v>46277.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
       </c>
       <c r="C15">
-        <v>3.547</v>
+        <v>24.018</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -1079,10 +1040,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46268.14583333334</v>
+        <v>46277.14583333334</v>
       </c>
       <c r="B16">
-        <v>1.313</v>
+        <v>1.767</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1096,10 +1057,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46268.15625</v>
+        <v>46277.15625</v>
       </c>
       <c r="B17">
-        <v>6.271</v>
+        <v>1.44</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1113,10 +1074,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46268.16666666666</v>
+        <v>46277.16666666666</v>
       </c>
       <c r="B18">
-        <v>7.51</v>
+        <v>3.052</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1130,13 +1091,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46268.17708333334</v>
+        <v>46277.17708333334</v>
       </c>
       <c r="B19">
-        <v>5.353</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>0.546</v>
       </c>
       <c r="D19">
         <v>18</v>
@@ -1147,13 +1108,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46268.1875</v>
+        <v>46277.1875</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>3.005</v>
       </c>
       <c r="C20">
-        <v>16.807</v>
+        <v>0</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1164,13 +1125,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46268.19791666666</v>
+        <v>46277.19791666666</v>
       </c>
       <c r="B21">
         <v>0</v>
       </c>
       <c r="C21">
-        <v>4.047</v>
+        <v>4.4</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1181,13 +1142,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46268.20833333334</v>
+        <v>46277.20833333334</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>17.007</v>
       </c>
       <c r="C22">
-        <v>1.458</v>
+        <v>0</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1198,13 +1159,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46268.21875</v>
+        <v>46277.21875</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>1.497</v>
       </c>
       <c r="C23">
-        <v>18.687</v>
+        <v>0</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1215,13 +1176,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46268.22916666666</v>
+        <v>46277.22916666666</v>
       </c>
       <c r="B24">
         <v>0</v>
       </c>
       <c r="C24">
-        <v>5.002</v>
+        <v>16.985</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1232,13 +1193,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46268.23958333334</v>
+        <v>46277.23958333334</v>
       </c>
       <c r="B25">
         <v>0</v>
       </c>
       <c r="C25">
-        <v>3.443</v>
+        <v>23.903</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1249,13 +1210,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46268.25</v>
+        <v>46277.25</v>
       </c>
       <c r="B26">
         <v>0</v>
       </c>
       <c r="C26">
-        <v>16.124</v>
+        <v>6.928</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1266,13 +1227,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46268.26041666666</v>
+        <v>46277.26041666666</v>
       </c>
       <c r="B27">
         <v>0</v>
       </c>
       <c r="C27">
-        <v>20.407</v>
+        <v>6.345</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1283,13 +1244,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46268.27083333334</v>
+        <v>46277.27083333334</v>
       </c>
       <c r="B28">
         <v>0</v>
       </c>
       <c r="C28">
-        <v>8.898999999999999</v>
+        <v>2.859</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1300,13 +1261,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46268.28125</v>
+        <v>46277.28125</v>
       </c>
       <c r="B29">
         <v>0</v>
       </c>
       <c r="C29">
-        <v>7.051</v>
+        <v>11.369</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1317,13 +1278,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46268.29166666666</v>
+        <v>46277.29166666666</v>
       </c>
       <c r="B30">
         <v>0</v>
       </c>
       <c r="C30">
-        <v>44.403</v>
+        <v>27.358</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1334,13 +1295,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46268.30208333334</v>
+        <v>46277.30208333334</v>
       </c>
       <c r="B31">
         <v>0</v>
       </c>
       <c r="C31">
-        <v>20.695</v>
+        <v>2.036</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1351,13 +1312,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46268.3125</v>
+        <v>46277.3125</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>12.18</v>
       </c>
       <c r="C32">
-        <v>14.833</v>
+        <v>0</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1368,13 +1329,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46268.32291666666</v>
+        <v>46277.32291666666</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>60.02</v>
       </c>
       <c r="C33">
-        <v>39.517</v>
+        <v>0</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1385,13 +1346,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46268.33333333334</v>
+        <v>46277.33333333334</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>33.676</v>
       </c>
       <c r="C34">
-        <v>81.008</v>
+        <v>0</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1402,13 +1363,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46268.34375</v>
+        <v>46277.34375</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>17.512</v>
       </c>
       <c r="C35">
-        <v>85.129</v>
+        <v>0</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1419,13 +1380,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46268.35416666666</v>
+        <v>46277.35416666666</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>34.231</v>
       </c>
       <c r="C36">
-        <v>2.523</v>
+        <v>0</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1436,13 +1397,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46268.36458333334</v>
+        <v>46277.36458333334</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>54.759</v>
       </c>
       <c r="C37">
-        <v>30.085</v>
+        <v>0</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1453,13 +1414,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46268.375</v>
+        <v>46277.375</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>15.018</v>
       </c>
       <c r="C38">
-        <v>8.257999999999999</v>
+        <v>0</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1470,13 +1431,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46268.38541666666</v>
+        <v>46277.38541666666</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>43.853</v>
       </c>
       <c r="C39">
-        <v>15.848</v>
+        <v>0</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1487,13 +1448,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46268.39583333334</v>
+        <v>46277.39583333334</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>49.424</v>
       </c>
       <c r="C40">
-        <v>5.315</v>
+        <v>0</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1504,10 +1465,10 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46268.40625</v>
+        <v>46277.40625</v>
       </c>
       <c r="B41">
-        <v>3.16</v>
+        <v>63.794</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -1521,10 +1482,10 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46268.41666666666</v>
+        <v>46277.41666666666</v>
       </c>
       <c r="B42">
-        <v>6.163</v>
+        <v>8.718999999999999</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -1538,10 +1499,10 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46268.42708333334</v>
+        <v>46277.42708333334</v>
       </c>
       <c r="B43">
-        <v>3.916</v>
+        <v>31.771</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -1555,13 +1516,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46268.4375</v>
+        <v>46277.4375</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>72.86799999999999</v>
       </c>
       <c r="C44">
-        <v>6.889</v>
+        <v>0</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1572,10 +1533,10 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46268.44791666666</v>
+        <v>46277.44791666666</v>
       </c>
       <c r="B45">
-        <v>14.314</v>
+        <v>72.458</v>
       </c>
       <c r="C45">
         <v>0</v>
@@ -1589,10 +1550,10 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46268.45833333334</v>
+        <v>46277.45833333334</v>
       </c>
       <c r="B46">
-        <v>40.718</v>
+        <v>43.248</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -1606,10 +1567,10 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46268.46875</v>
+        <v>46277.46875</v>
       </c>
       <c r="B47">
-        <v>42.627</v>
+        <v>67.294</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -1623,10 +1584,10 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46268.47916666666</v>
+        <v>46277.47916666666</v>
       </c>
       <c r="B48">
-        <v>45.345</v>
+        <v>46.044</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -1640,10 +1601,10 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46268.48958333334</v>
+        <v>46277.48958333334</v>
       </c>
       <c r="B49">
-        <v>16.536</v>
+        <v>46.575</v>
       </c>
       <c r="C49">
         <v>0</v>
@@ -1657,13 +1618,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46268.5</v>
+        <v>46277.5</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>41.981</v>
       </c>
       <c r="C50">
-        <v>15.278</v>
+        <v>0</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1674,13 +1635,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46268.51041666666</v>
+        <v>46277.51041666666</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>25.667</v>
       </c>
       <c r="C51">
-        <v>12.523</v>
+        <v>0</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1691,13 +1652,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46268.52083333334</v>
+        <v>46277.52083333334</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>13.279</v>
       </c>
       <c r="C52">
-        <v>10.562</v>
+        <v>0</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1708,13 +1669,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46268.53125</v>
+        <v>46277.53125</v>
       </c>
       <c r="B53">
-        <v>0</v>
+        <v>0.903</v>
       </c>
       <c r="C53">
-        <v>11.483</v>
+        <v>0</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1725,13 +1686,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46268.54166666666</v>
+        <v>46277.54166666666</v>
       </c>
       <c r="B54">
         <v>0</v>
       </c>
       <c r="C54">
-        <v>6.402</v>
+        <v>47.171</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1742,13 +1703,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46268.55208333334</v>
+        <v>46277.55208333334</v>
       </c>
       <c r="B55">
         <v>0</v>
       </c>
       <c r="C55">
-        <v>24.084</v>
+        <v>11.271</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1759,13 +1720,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46268.5625</v>
+        <v>46277.5625</v>
       </c>
       <c r="B56">
         <v>0</v>
       </c>
       <c r="C56">
-        <v>38.696</v>
+        <v>12.755</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1776,13 +1737,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46268.57291666666</v>
+        <v>46277.57291666666</v>
       </c>
       <c r="B57">
-        <v>0</v>
+        <v>1.317</v>
       </c>
       <c r="C57">
-        <v>13.824</v>
+        <v>0</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1793,13 +1754,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46268.58333333334</v>
+        <v>46277.58333333334</v>
       </c>
       <c r="B58">
-        <v>0</v>
+        <v>9.305</v>
       </c>
       <c r="C58">
-        <v>6.898</v>
+        <v>0</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1810,13 +1771,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46268.59375</v>
+        <v>46277.59375</v>
       </c>
       <c r="B59">
         <v>0</v>
       </c>
       <c r="C59">
-        <v>6.147</v>
+        <v>4.189</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1827,13 +1788,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46268.60416666666</v>
+        <v>46277.60416666666</v>
       </c>
       <c r="B60">
-        <v>1.309</v>
+        <v>0</v>
       </c>
       <c r="C60">
-        <v>0</v>
+        <v>79.846</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1844,13 +1805,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46268.61458333334</v>
+        <v>46277.61458333334</v>
       </c>
       <c r="B61">
         <v>0</v>
       </c>
       <c r="C61">
-        <v>8.919</v>
+        <v>71.925</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -1861,13 +1822,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46268.625</v>
+        <v>46277.625</v>
       </c>
       <c r="B62">
         <v>0</v>
       </c>
       <c r="C62">
-        <v>47.393</v>
+        <v>1.468</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -1878,13 +1839,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46268.63541666666</v>
+        <v>46277.63541666666</v>
       </c>
       <c r="B63">
-        <v>0</v>
+        <v>3.631</v>
       </c>
       <c r="C63">
-        <v>14.976</v>
+        <v>0</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -1895,13 +1856,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46268.64583333334</v>
+        <v>46277.64583333334</v>
       </c>
       <c r="B64">
-        <v>12.859</v>
+        <v>0</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>21.905</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -1912,10 +1873,10 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46268.65625</v>
+        <v>46277.65625</v>
       </c>
       <c r="B65">
-        <v>12.584</v>
+        <v>7.304</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -1929,10 +1890,10 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46268.66666666666</v>
+        <v>46277.66666666666</v>
       </c>
       <c r="B66">
-        <v>5.834</v>
+        <v>8.702</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -1946,13 +1907,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46268.67708333334</v>
+        <v>46277.67708333334</v>
       </c>
       <c r="B67">
-        <v>31.624</v>
+        <v>0</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>1.606</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -1963,10 +1924,10 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46268.6875</v>
+        <v>46277.6875</v>
       </c>
       <c r="B68">
-        <v>27.596</v>
+        <v>3.422</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -1980,13 +1941,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46268.69791666666</v>
+        <v>46277.69791666666</v>
       </c>
       <c r="B69">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="C69">
-        <v>1.159</v>
+        <v>0</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -1997,13 +1958,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46268.70833333334</v>
+        <v>46277.70833333334</v>
       </c>
       <c r="B70">
         <v>0</v>
       </c>
       <c r="C70">
-        <v>17.708</v>
+        <v>7.475</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2014,13 +1975,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46268.71875</v>
+        <v>46277.71875</v>
       </c>
       <c r="B71">
-        <v>0</v>
+        <v>5.663</v>
       </c>
       <c r="C71">
-        <v>1.635</v>
+        <v>0</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2031,13 +1992,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46268.72916666666</v>
+        <v>46277.72916666666</v>
       </c>
       <c r="B72">
-        <v>0.628</v>
+        <v>0</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>8.087</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2048,13 +2009,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46268.73958333334</v>
+        <v>46277.73958333334</v>
       </c>
       <c r="B73">
-        <v>5.254</v>
+        <v>0</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>3.657</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2065,13 +2026,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46268.75</v>
+        <v>46277.75</v>
       </c>
       <c r="B74">
-        <v>0</v>
+        <v>16.131</v>
       </c>
       <c r="C74">
-        <v>3.872</v>
+        <v>0</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2082,10 +2043,10 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46268.76041666666</v>
+        <v>46277.76041666666</v>
       </c>
       <c r="B75">
-        <v>1.165</v>
+        <v>9.215999999999999</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -2099,13 +2060,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46268.77083333334</v>
+        <v>46277.77083333334</v>
       </c>
       <c r="B76">
-        <v>0</v>
+        <v>9.067</v>
       </c>
       <c r="C76">
-        <v>4.235</v>
+        <v>0</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2116,13 +2077,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46268.78125</v>
+        <v>46277.78125</v>
       </c>
       <c r="B77">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>2.363</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2133,10 +2094,10 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46268.79166666666</v>
+        <v>46277.79166666666</v>
       </c>
       <c r="B78">
-        <v>0.746</v>
+        <v>1.574</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -2150,13 +2111,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46268.80208333334</v>
+        <v>46277.80208333334</v>
       </c>
       <c r="B79">
         <v>0</v>
       </c>
       <c r="C79">
-        <v>6.842</v>
+        <v>2.571</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2167,13 +2128,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46268.8125</v>
+        <v>46277.8125</v>
       </c>
       <c r="B80">
-        <v>1.741</v>
+        <v>0</v>
       </c>
       <c r="C80">
-        <v>0</v>
+        <v>4.737</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2184,13 +2145,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46268.82291666666</v>
+        <v>46277.82291666666</v>
       </c>
       <c r="B81">
-        <v>0.303</v>
+        <v>0</v>
       </c>
       <c r="C81">
-        <v>0</v>
+        <v>2.707</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2201,13 +2162,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46268.83333333334</v>
+        <v>46277.83333333334</v>
       </c>
       <c r="B82">
-        <v>0</v>
+        <v>1.482</v>
       </c>
       <c r="C82">
-        <v>6.224</v>
+        <v>0</v>
       </c>
       <c r="D82">
         <v>81</v>
@@ -2218,13 +2179,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46268.84375</v>
+        <v>46277.84375</v>
       </c>
       <c r="B83">
-        <v>0</v>
+        <v>11.334</v>
       </c>
       <c r="C83">
-        <v>16.919</v>
+        <v>0</v>
       </c>
       <c r="D83">
         <v>82</v>
@@ -2235,10 +2196,10 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46268.85416666666</v>
+        <v>46277.85416666666</v>
       </c>
       <c r="B84">
-        <v>0.07199999999999999</v>
+        <v>1.943</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -2252,13 +2213,13 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46268.86458333334</v>
+        <v>46277.86458333334</v>
       </c>
       <c r="B85">
         <v>0</v>
       </c>
       <c r="C85">
-        <v>4.371</v>
+        <v>5.271</v>
       </c>
       <c r="D85">
         <v>84</v>
@@ -2269,13 +2230,13 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46268.875</v>
+        <v>46277.875</v>
       </c>
       <c r="B86">
-        <v>17.604</v>
+        <v>0</v>
       </c>
       <c r="C86">
-        <v>0</v>
+        <v>10.952</v>
       </c>
       <c r="D86">
         <v>85</v>
@@ -2286,13 +2247,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46268.88541666666</v>
+        <v>46277.88541666666</v>
       </c>
       <c r="B87">
-        <v>0.423</v>
+        <v>0</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>3.463</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -2303,10 +2264,10 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46268.89583333334</v>
+        <v>46277.89583333334</v>
       </c>
       <c r="B88">
-        <v>2.76</v>
+        <v>6.645</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -2320,10 +2281,10 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46268.90625</v>
+        <v>46277.90625</v>
       </c>
       <c r="B89">
-        <v>8.307</v>
+        <v>3.269</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -2337,13 +2298,13 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46268.91666666666</v>
+        <v>46277.91666666666</v>
       </c>
       <c r="B90">
-        <v>2.675</v>
+        <v>0</v>
       </c>
       <c r="C90">
-        <v>0</v>
+        <v>0.227</v>
       </c>
       <c r="D90">
         <v>89</v>
@@ -2354,13 +2315,13 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46268.92708333334</v>
+        <v>46277.92708333334</v>
       </c>
       <c r="B91">
-        <v>0</v>
+        <v>1.773</v>
       </c>
       <c r="C91">
-        <v>8.926</v>
+        <v>0</v>
       </c>
       <c r="D91">
         <v>90</v>
@@ -2371,13 +2332,13 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46268.9375</v>
+        <v>46277.9375</v>
       </c>
       <c r="B92">
-        <v>0</v>
+        <v>3.333</v>
       </c>
       <c r="C92">
-        <v>13.338</v>
+        <v>0</v>
       </c>
       <c r="D92">
         <v>91</v>
@@ -2388,13 +2349,13 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46268.94791666666</v>
+        <v>46277.94791666666</v>
       </c>
       <c r="B93">
-        <v>0</v>
+        <v>2.921</v>
       </c>
       <c r="C93">
-        <v>12.602</v>
+        <v>0</v>
       </c>
       <c r="D93">
         <v>92</v>
@@ -2405,13 +2366,13 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46268.95833333334</v>
+        <v>46277.95833333334</v>
       </c>
       <c r="B94">
         <v>0</v>
       </c>
       <c r="C94">
-        <v>1.985</v>
+        <v>0.553</v>
       </c>
       <c r="D94">
         <v>93</v>
@@ -2422,13 +2383,13 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46268.96875</v>
+        <v>46277.96875</v>
       </c>
       <c r="B95">
-        <v>0</v>
+        <v>4.889</v>
       </c>
       <c r="C95">
-        <v>6.606</v>
+        <v>0</v>
       </c>
       <c r="D95">
         <v>94</v>
@@ -2439,13 +2400,13 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46268.97916666666</v>
+        <v>46277.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
       </c>
       <c r="C96">
-        <v>12.238</v>
+        <v>4.561</v>
       </c>
       <c r="D96">
         <v>95</v>
@@ -2456,10 +2417,10 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46268.98958333334</v>
+        <v>46277.98958333334</v>
       </c>
       <c r="B97">
-        <v>4.568</v>
+        <v>0.882</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -2473,10 +2434,10 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46269</v>
+        <v>46278</v>
       </c>
       <c r="B98">
-        <v>10.991</v>
+        <v>14.144</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -2490,10 +2451,10 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46269.01041666666</v>
+        <v>46278.01041666666</v>
       </c>
       <c r="B99">
-        <v>14.226</v>
+        <v>7.165</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -2507,13 +2468,13 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46269.02083333334</v>
+        <v>46278.02083333334</v>
       </c>
       <c r="B100">
-        <v>0</v>
+        <v>7.669</v>
       </c>
       <c r="C100">
-        <v>0.8080000000000001</v>
+        <v>0</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2524,10 +2485,10 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46269.03125</v>
+        <v>46278.03125</v>
       </c>
       <c r="B101">
-        <v>7.525</v>
+        <v>2.295</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -2541,13 +2502,13 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46269.04166666666</v>
+        <v>46278.04166666666</v>
       </c>
       <c r="B102">
-        <v>2.873</v>
+        <v>0</v>
       </c>
       <c r="C102">
-        <v>0</v>
+        <v>4.058</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -2558,13 +2519,13 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46269.05208333334</v>
+        <v>46278.05208333334</v>
       </c>
       <c r="B103">
-        <v>1.871</v>
+        <v>0</v>
       </c>
       <c r="C103">
-        <v>0</v>
+        <v>5.473</v>
       </c>
       <c r="D103">
         <v>6</v>
@@ -2575,13 +2536,13 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46269.0625</v>
+        <v>46278.0625</v>
       </c>
       <c r="B104">
-        <v>2.922</v>
+        <v>0</v>
       </c>
       <c r="C104">
-        <v>0</v>
+        <v>38.728</v>
       </c>
       <c r="D104">
         <v>7</v>
@@ -2592,13 +2553,13 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46269.07291666666</v>
+        <v>46278.07291666666</v>
       </c>
       <c r="B105">
         <v>0</v>
       </c>
       <c r="C105">
-        <v>2.041</v>
+        <v>23.476</v>
       </c>
       <c r="D105">
         <v>8</v>
@@ -2609,13 +2570,13 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46269.08333333334</v>
+        <v>46278.08333333334</v>
       </c>
       <c r="B106">
         <v>0</v>
       </c>
       <c r="C106">
-        <v>0.219</v>
+        <v>8.736000000000001</v>
       </c>
       <c r="D106">
         <v>9</v>
@@ -2626,13 +2587,13 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46269.09375</v>
+        <v>46278.09375</v>
       </c>
       <c r="B107">
-        <v>3.973</v>
+        <v>0</v>
       </c>
       <c r="C107">
-        <v>0</v>
+        <v>8.714</v>
       </c>
       <c r="D107">
         <v>10</v>
@@ -2643,13 +2604,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46269.10416666666</v>
+        <v>46278.10416666666</v>
       </c>
       <c r="B108">
         <v>0</v>
       </c>
       <c r="C108">
-        <v>3.201</v>
+        <v>5.517</v>
       </c>
       <c r="D108">
         <v>11</v>
@@ -2660,13 +2621,13 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46269.11458333334</v>
+        <v>46278.11458333334</v>
       </c>
       <c r="B109">
         <v>0</v>
       </c>
       <c r="C109">
-        <v>0.899</v>
+        <v>9.776999999999999</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -2677,10 +2638,10 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46269.125</v>
+        <v>46278.125</v>
       </c>
       <c r="B110">
-        <v>10.363</v>
+        <v>3.366</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -2694,10 +2655,10 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46269.13541666666</v>
+        <v>46278.13541666666</v>
       </c>
       <c r="B111">
-        <v>10.72</v>
+        <v>3.34</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -2711,10 +2672,10 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46269.14583333334</v>
+        <v>46278.14583333334</v>
       </c>
       <c r="B112">
-        <v>1.254</v>
+        <v>3.597</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -2728,10 +2689,10 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46269.15625</v>
+        <v>46278.15625</v>
       </c>
       <c r="B113">
-        <v>1.182</v>
+        <v>8.346</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -2745,13 +2706,13 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46269.16666666666</v>
+        <v>46278.16666666666</v>
       </c>
       <c r="B114">
-        <v>9.952</v>
+        <v>0</v>
       </c>
       <c r="C114">
-        <v>0</v>
+        <v>0.819</v>
       </c>
       <c r="D114">
         <v>17</v>
@@ -2762,10 +2723,10 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46269.17708333334</v>
+        <v>46278.17708333334</v>
       </c>
       <c r="B115">
-        <v>2.493</v>
+        <v>4.67</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -2779,13 +2740,13 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46269.1875</v>
+        <v>46278.1875</v>
       </c>
       <c r="B116">
-        <v>0</v>
+        <v>0.994</v>
       </c>
       <c r="C116">
-        <v>9.273</v>
+        <v>0</v>
       </c>
       <c r="D116">
         <v>19</v>
@@ -2796,13 +2757,13 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46269.19791666666</v>
+        <v>46278.19791666666</v>
       </c>
       <c r="B117">
-        <v>0</v>
+        <v>7.743</v>
       </c>
       <c r="C117">
-        <v>0.522</v>
+        <v>0</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -2813,10 +2774,10 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46269.20833333334</v>
+        <v>46278.20833333334</v>
       </c>
       <c r="B118">
-        <v>2.224</v>
+        <v>8.481999999999999</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -2830,13 +2791,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46269.21875</v>
+        <v>46278.21875</v>
       </c>
       <c r="B119">
-        <v>0</v>
+        <v>0.643</v>
       </c>
       <c r="C119">
-        <v>1.935</v>
+        <v>0</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -2847,13 +2808,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46269.22916666666</v>
+        <v>46278.22916666666</v>
       </c>
       <c r="B120">
-        <v>0.423</v>
+        <v>0</v>
       </c>
       <c r="C120">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -2864,13 +2825,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46269.23958333334</v>
+        <v>46278.23958333334</v>
       </c>
       <c r="B121">
-        <v>2.777</v>
+        <v>0</v>
       </c>
       <c r="C121">
-        <v>0</v>
+        <v>0.861</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -2881,13 +2842,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46269.25</v>
+        <v>46278.25</v>
       </c>
       <c r="B122">
         <v>0</v>
       </c>
       <c r="C122">
-        <v>8.313000000000001</v>
+        <v>16.903</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -2898,13 +2859,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46269.26041666666</v>
+        <v>46278.26041666666</v>
       </c>
       <c r="B123">
         <v>0</v>
       </c>
       <c r="C123">
-        <v>1.617</v>
+        <v>29.896</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -2915,13 +2876,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46269.27083333334</v>
+        <v>46278.27083333334</v>
       </c>
       <c r="B124">
-        <v>1.247</v>
+        <v>0</v>
       </c>
       <c r="C124">
-        <v>0</v>
+        <v>26.432</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -2932,13 +2893,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46269.28125</v>
+        <v>46278.28125</v>
       </c>
       <c r="B125">
-        <v>5.252</v>
+        <v>0</v>
       </c>
       <c r="C125">
-        <v>0</v>
+        <v>42.847</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -2949,13 +2910,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46269.29166666666</v>
+        <v>46278.29166666666</v>
       </c>
       <c r="B126">
         <v>0</v>
       </c>
       <c r="C126">
-        <v>12.904</v>
+        <v>4.14</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -2966,13 +2927,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46269.30208333334</v>
+        <v>46278.30208333334</v>
       </c>
       <c r="B127">
         <v>0</v>
       </c>
       <c r="C127">
-        <v>12.314</v>
+        <v>4.703</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -2983,13 +2944,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46269.3125</v>
+        <v>46278.3125</v>
       </c>
       <c r="B128">
         <v>0</v>
       </c>
       <c r="C128">
-        <v>14.31</v>
+        <v>19.301</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3000,13 +2961,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46269.32291666666</v>
+        <v>46278.32291666666</v>
       </c>
       <c r="B129">
         <v>0</v>
       </c>
       <c r="C129">
-        <v>58.069</v>
+        <v>9.19</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3017,13 +2978,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46269.33333333334</v>
+        <v>46278.33333333334</v>
       </c>
       <c r="B130">
         <v>0</v>
       </c>
       <c r="C130">
-        <v>75.86499999999999</v>
+        <v>10.971</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3034,240 +2995,19 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46269.34375</v>
+        <v>46278.34375</v>
       </c>
       <c r="B131">
         <v>0</v>
       </c>
       <c r="C131">
-        <v>44.141</v>
+        <v>18.278</v>
       </c>
       <c r="D131">
         <v>34</v>
       </c>
       <c r="E131" t="s">
         <v>134</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5">
-      <c r="A132" s="2">
-        <v>46269.35416666666</v>
-      </c>
-      <c r="B132">
-        <v>10.828</v>
-      </c>
-      <c r="C132">
-        <v>0</v>
-      </c>
-      <c r="D132">
-        <v>35</v>
-      </c>
-      <c r="E132" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5">
-      <c r="A133" s="2">
-        <v>46269.36458333334</v>
-      </c>
-      <c r="B133">
-        <v>0</v>
-      </c>
-      <c r="C133">
-        <v>10.209</v>
-      </c>
-      <c r="D133">
-        <v>36</v>
-      </c>
-      <c r="E133" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5">
-      <c r="A134" s="2">
-        <v>46269.375</v>
-      </c>
-      <c r="B134">
-        <v>41.402</v>
-      </c>
-      <c r="C134">
-        <v>0</v>
-      </c>
-      <c r="D134">
-        <v>37</v>
-      </c>
-      <c r="E134" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5">
-      <c r="A135" s="2">
-        <v>46269.38541666666</v>
-      </c>
-      <c r="B135">
-        <v>0.844</v>
-      </c>
-      <c r="C135">
-        <v>0</v>
-      </c>
-      <c r="D135">
-        <v>38</v>
-      </c>
-      <c r="E135" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5">
-      <c r="A136" s="2">
-        <v>46269.39583333334</v>
-      </c>
-      <c r="B136">
-        <v>0</v>
-      </c>
-      <c r="C136">
-        <v>16.224</v>
-      </c>
-      <c r="D136">
-        <v>39</v>
-      </c>
-      <c r="E136" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5">
-      <c r="A137" s="2">
-        <v>46269.40625</v>
-      </c>
-      <c r="B137">
-        <v>0</v>
-      </c>
-      <c r="C137">
-        <v>35.098</v>
-      </c>
-      <c r="D137">
-        <v>40</v>
-      </c>
-      <c r="E137" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5">
-      <c r="A138" s="2">
-        <v>46269.41666666666</v>
-      </c>
-      <c r="B138">
-        <v>0</v>
-      </c>
-      <c r="C138">
-        <v>34.507</v>
-      </c>
-      <c r="D138">
-        <v>41</v>
-      </c>
-      <c r="E138" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5">
-      <c r="A139" s="2">
-        <v>46269.42708333334</v>
-      </c>
-      <c r="B139">
-        <v>0</v>
-      </c>
-      <c r="C139">
-        <v>31.455</v>
-      </c>
-      <c r="D139">
-        <v>42</v>
-      </c>
-      <c r="E139" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5">
-      <c r="A140" s="2">
-        <v>46269.4375</v>
-      </c>
-      <c r="B140">
-        <v>0</v>
-      </c>
-      <c r="C140">
-        <v>23.153</v>
-      </c>
-      <c r="D140">
-        <v>43</v>
-      </c>
-      <c r="E140" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5">
-      <c r="A141" s="2">
-        <v>46269.44791666666</v>
-      </c>
-      <c r="B141">
-        <v>0</v>
-      </c>
-      <c r="C141">
-        <v>15.207</v>
-      </c>
-      <c r="D141">
-        <v>44</v>
-      </c>
-      <c r="E141" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5">
-      <c r="A142" s="2">
-        <v>46269.45833333334</v>
-      </c>
-      <c r="B142">
-        <v>0</v>
-      </c>
-      <c r="C142">
-        <v>11.071</v>
-      </c>
-      <c r="D142">
-        <v>45</v>
-      </c>
-      <c r="E142" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5">
-      <c r="A143" s="2">
-        <v>46269.46875</v>
-      </c>
-      <c r="B143">
-        <v>0</v>
-      </c>
-      <c r="C143">
-        <v>6.459</v>
-      </c>
-      <c r="D143">
-        <v>46</v>
-      </c>
-      <c r="E143" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5">
-      <c r="A144" s="2">
-        <v>46269.47916666666</v>
-      </c>
-      <c r="B144">
-        <v>0</v>
-      </c>
-      <c r="C144">
-        <v>8.048</v>
-      </c>
-      <c r="D144">
-        <v>47</v>
-      </c>
-      <c r="E144" t="s">
-        <v>147</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Unintended_Deviation.xlsx
+++ b/data_fetching/Entsoe/Unintended_Deviation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="236">
   <si>
     <t>Timestamp</t>
   </si>
@@ -31,694 +31,697 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>18.09.20261</t>
-  </si>
-  <si>
-    <t>18.09.20262</t>
-  </si>
-  <si>
-    <t>18.09.20263</t>
-  </si>
-  <si>
-    <t>18.09.20264</t>
-  </si>
-  <si>
-    <t>18.09.20265</t>
-  </si>
-  <si>
-    <t>18.09.20266</t>
-  </si>
-  <si>
-    <t>18.09.20267</t>
-  </si>
-  <si>
-    <t>18.09.20268</t>
-  </si>
-  <si>
-    <t>18.09.20269</t>
-  </si>
-  <si>
-    <t>18.09.202610</t>
-  </si>
-  <si>
-    <t>18.09.202611</t>
-  </si>
-  <si>
-    <t>18.09.202612</t>
-  </si>
-  <si>
-    <t>18.09.202613</t>
-  </si>
-  <si>
-    <t>18.09.202614</t>
-  </si>
-  <si>
-    <t>18.09.202615</t>
-  </si>
-  <si>
-    <t>18.09.202616</t>
-  </si>
-  <si>
-    <t>18.09.202617</t>
-  </si>
-  <si>
-    <t>18.09.202618</t>
-  </si>
-  <si>
-    <t>18.09.202619</t>
-  </si>
-  <si>
-    <t>18.09.202620</t>
-  </si>
-  <si>
-    <t>18.09.202621</t>
-  </si>
-  <si>
-    <t>18.09.202622</t>
-  </si>
-  <si>
-    <t>18.09.202623</t>
-  </si>
-  <si>
-    <t>18.09.202624</t>
-  </si>
-  <si>
-    <t>18.09.202625</t>
-  </si>
-  <si>
-    <t>18.09.202626</t>
-  </si>
-  <si>
-    <t>18.09.202627</t>
-  </si>
-  <si>
-    <t>18.09.202628</t>
-  </si>
-  <si>
-    <t>18.09.202629</t>
-  </si>
-  <si>
-    <t>18.09.202630</t>
-  </si>
-  <si>
-    <t>18.09.202631</t>
-  </si>
-  <si>
-    <t>18.09.202632</t>
-  </si>
-  <si>
-    <t>18.09.202633</t>
-  </si>
-  <si>
-    <t>18.09.202634</t>
-  </si>
-  <si>
-    <t>18.09.202635</t>
-  </si>
-  <si>
-    <t>18.09.202636</t>
-  </si>
-  <si>
-    <t>18.09.202637</t>
-  </si>
-  <si>
-    <t>18.09.202638</t>
-  </si>
-  <si>
-    <t>18.09.202639</t>
-  </si>
-  <si>
-    <t>18.09.202640</t>
-  </si>
-  <si>
-    <t>18.09.202641</t>
-  </si>
-  <si>
-    <t>18.09.202642</t>
-  </si>
-  <si>
-    <t>18.09.202643</t>
-  </si>
-  <si>
-    <t>18.09.202644</t>
-  </si>
-  <si>
-    <t>18.09.202645</t>
-  </si>
-  <si>
-    <t>18.09.202646</t>
-  </si>
-  <si>
-    <t>18.09.202647</t>
-  </si>
-  <si>
-    <t>18.09.202648</t>
-  </si>
-  <si>
-    <t>18.09.202649</t>
-  </si>
-  <si>
-    <t>18.09.202650</t>
-  </si>
-  <si>
-    <t>18.09.202651</t>
-  </si>
-  <si>
-    <t>18.09.202652</t>
-  </si>
-  <si>
-    <t>18.09.202653</t>
-  </si>
-  <si>
-    <t>18.09.202654</t>
-  </si>
-  <si>
-    <t>18.09.202655</t>
-  </si>
-  <si>
-    <t>18.09.202656</t>
-  </si>
-  <si>
-    <t>18.09.202657</t>
-  </si>
-  <si>
-    <t>18.09.202658</t>
-  </si>
-  <si>
-    <t>18.09.202659</t>
-  </si>
-  <si>
-    <t>18.09.202660</t>
-  </si>
-  <si>
-    <t>18.09.202661</t>
-  </si>
-  <si>
-    <t>18.09.202662</t>
-  </si>
-  <si>
-    <t>18.09.202663</t>
-  </si>
-  <si>
-    <t>18.09.202664</t>
-  </si>
-  <si>
-    <t>18.09.202665</t>
-  </si>
-  <si>
-    <t>18.09.202666</t>
-  </si>
-  <si>
-    <t>18.09.202667</t>
-  </si>
-  <si>
-    <t>18.09.202668</t>
-  </si>
-  <si>
-    <t>18.09.202669</t>
-  </si>
-  <si>
-    <t>18.09.202670</t>
-  </si>
-  <si>
-    <t>18.09.202671</t>
-  </si>
-  <si>
-    <t>18.09.202672</t>
-  </si>
-  <si>
-    <t>18.09.202673</t>
-  </si>
-  <si>
-    <t>18.09.202674</t>
-  </si>
-  <si>
-    <t>18.09.202675</t>
-  </si>
-  <si>
-    <t>18.09.202676</t>
-  </si>
-  <si>
-    <t>18.09.202677</t>
-  </si>
-  <si>
-    <t>18.09.202678</t>
-  </si>
-  <si>
-    <t>18.09.202679</t>
-  </si>
-  <si>
-    <t>18.09.202680</t>
-  </si>
-  <si>
-    <t>18.09.202681</t>
-  </si>
-  <si>
-    <t>18.09.202682</t>
-  </si>
-  <si>
-    <t>18.09.202683</t>
-  </si>
-  <si>
-    <t>18.09.202684</t>
-  </si>
-  <si>
-    <t>18.09.202685</t>
-  </si>
-  <si>
-    <t>18.09.202686</t>
-  </si>
-  <si>
-    <t>18.09.202687</t>
-  </si>
-  <si>
-    <t>18.09.202688</t>
-  </si>
-  <si>
-    <t>18.09.202689</t>
-  </si>
-  <si>
-    <t>18.09.202690</t>
-  </si>
-  <si>
-    <t>18.09.202691</t>
-  </si>
-  <si>
-    <t>18.09.202692</t>
-  </si>
-  <si>
-    <t>18.09.202693</t>
-  </si>
-  <si>
-    <t>18.09.202694</t>
-  </si>
-  <si>
-    <t>18.09.202695</t>
-  </si>
-  <si>
-    <t>18.09.202696</t>
-  </si>
-  <si>
-    <t>19.09.20261</t>
-  </si>
-  <si>
-    <t>19.09.20262</t>
-  </si>
-  <si>
-    <t>19.09.20263</t>
-  </si>
-  <si>
-    <t>19.09.20264</t>
-  </si>
-  <si>
-    <t>19.09.20265</t>
-  </si>
-  <si>
-    <t>19.09.20266</t>
-  </si>
-  <si>
-    <t>19.09.20267</t>
-  </si>
-  <si>
-    <t>19.09.20268</t>
-  </si>
-  <si>
-    <t>19.09.20269</t>
-  </si>
-  <si>
-    <t>19.09.202610</t>
-  </si>
-  <si>
-    <t>19.09.202611</t>
-  </si>
-  <si>
-    <t>19.09.202612</t>
-  </si>
-  <si>
-    <t>19.09.202613</t>
-  </si>
-  <si>
-    <t>19.09.202614</t>
-  </si>
-  <si>
-    <t>19.09.202615</t>
-  </si>
-  <si>
-    <t>19.09.202616</t>
-  </si>
-  <si>
-    <t>19.09.202617</t>
-  </si>
-  <si>
-    <t>19.09.202618</t>
-  </si>
-  <si>
-    <t>19.09.202619</t>
-  </si>
-  <si>
-    <t>19.09.202620</t>
-  </si>
-  <si>
-    <t>19.09.202621</t>
-  </si>
-  <si>
-    <t>19.09.202622</t>
-  </si>
-  <si>
-    <t>19.09.202623</t>
-  </si>
-  <si>
-    <t>19.09.202624</t>
-  </si>
-  <si>
-    <t>19.09.202625</t>
-  </si>
-  <si>
-    <t>19.09.202626</t>
-  </si>
-  <si>
-    <t>19.09.202627</t>
-  </si>
-  <si>
-    <t>19.09.202628</t>
-  </si>
-  <si>
-    <t>19.09.202629</t>
-  </si>
-  <si>
-    <t>19.09.202630</t>
-  </si>
-  <si>
-    <t>19.09.202631</t>
-  </si>
-  <si>
-    <t>19.09.202632</t>
-  </si>
-  <si>
-    <t>19.09.202633</t>
-  </si>
-  <si>
-    <t>19.09.202634</t>
-  </si>
-  <si>
-    <t>19.09.202635</t>
-  </si>
-  <si>
-    <t>19.09.202636</t>
-  </si>
-  <si>
-    <t>19.09.202637</t>
-  </si>
-  <si>
-    <t>19.09.202638</t>
-  </si>
-  <si>
-    <t>19.09.202639</t>
-  </si>
-  <si>
-    <t>19.09.202640</t>
-  </si>
-  <si>
-    <t>19.09.202641</t>
-  </si>
-  <si>
-    <t>19.09.202642</t>
-  </si>
-  <si>
-    <t>19.09.202643</t>
-  </si>
-  <si>
-    <t>19.09.202644</t>
-  </si>
-  <si>
-    <t>19.09.202645</t>
-  </si>
-  <si>
-    <t>19.09.202646</t>
-  </si>
-  <si>
-    <t>19.09.202647</t>
-  </si>
-  <si>
-    <t>19.09.202648</t>
-  </si>
-  <si>
-    <t>19.09.202649</t>
-  </si>
-  <si>
-    <t>19.09.202650</t>
-  </si>
-  <si>
-    <t>19.09.202651</t>
-  </si>
-  <si>
-    <t>19.09.202652</t>
-  </si>
-  <si>
-    <t>19.09.202653</t>
-  </si>
-  <si>
-    <t>19.09.202654</t>
-  </si>
-  <si>
-    <t>19.09.202655</t>
-  </si>
-  <si>
-    <t>19.09.202656</t>
-  </si>
-  <si>
-    <t>19.09.202657</t>
-  </si>
-  <si>
-    <t>19.09.202658</t>
-  </si>
-  <si>
-    <t>19.09.202659</t>
-  </si>
-  <si>
-    <t>19.09.202660</t>
-  </si>
-  <si>
-    <t>19.09.202661</t>
-  </si>
-  <si>
-    <t>19.09.202662</t>
-  </si>
-  <si>
-    <t>19.09.202663</t>
-  </si>
-  <si>
-    <t>19.09.202664</t>
-  </si>
-  <si>
-    <t>19.09.202665</t>
-  </si>
-  <si>
-    <t>19.09.202666</t>
-  </si>
-  <si>
-    <t>19.09.202667</t>
-  </si>
-  <si>
-    <t>19.09.202668</t>
-  </si>
-  <si>
-    <t>19.09.202669</t>
-  </si>
-  <si>
-    <t>19.09.202670</t>
-  </si>
-  <si>
-    <t>19.09.202671</t>
-  </si>
-  <si>
-    <t>19.09.202672</t>
-  </si>
-  <si>
-    <t>19.09.202673</t>
-  </si>
-  <si>
-    <t>19.09.202674</t>
-  </si>
-  <si>
-    <t>19.09.202675</t>
-  </si>
-  <si>
-    <t>19.09.202676</t>
-  </si>
-  <si>
-    <t>19.09.202677</t>
-  </si>
-  <si>
-    <t>19.09.202678</t>
-  </si>
-  <si>
-    <t>19.09.202679</t>
-  </si>
-  <si>
-    <t>19.09.202680</t>
-  </si>
-  <si>
-    <t>19.09.202681</t>
-  </si>
-  <si>
-    <t>19.09.202682</t>
-  </si>
-  <si>
-    <t>19.09.202683</t>
-  </si>
-  <si>
-    <t>19.09.202684</t>
-  </si>
-  <si>
-    <t>19.09.202685</t>
-  </si>
-  <si>
-    <t>19.09.202686</t>
-  </si>
-  <si>
-    <t>19.09.202687</t>
-  </si>
-  <si>
-    <t>19.09.202688</t>
-  </si>
-  <si>
-    <t>19.09.202689</t>
-  </si>
-  <si>
-    <t>19.09.202690</t>
-  </si>
-  <si>
-    <t>19.09.202691</t>
-  </si>
-  <si>
-    <t>19.09.202692</t>
-  </si>
-  <si>
-    <t>19.09.202693</t>
-  </si>
-  <si>
-    <t>19.09.202694</t>
-  </si>
-  <si>
-    <t>19.09.202695</t>
-  </si>
-  <si>
-    <t>19.09.202696</t>
-  </si>
-  <si>
-    <t>20.09.20261</t>
-  </si>
-  <si>
-    <t>20.09.20262</t>
-  </si>
-  <si>
-    <t>20.09.20263</t>
-  </si>
-  <si>
-    <t>20.09.20264</t>
-  </si>
-  <si>
-    <t>20.09.20265</t>
-  </si>
-  <si>
-    <t>20.09.20266</t>
-  </si>
-  <si>
-    <t>20.09.20267</t>
-  </si>
-  <si>
-    <t>20.09.20268</t>
-  </si>
-  <si>
-    <t>20.09.20269</t>
-  </si>
-  <si>
-    <t>20.09.202610</t>
-  </si>
-  <si>
-    <t>20.09.202611</t>
-  </si>
-  <si>
-    <t>20.09.202612</t>
-  </si>
-  <si>
-    <t>20.09.202613</t>
-  </si>
-  <si>
-    <t>20.09.202614</t>
-  </si>
-  <si>
-    <t>20.09.202615</t>
-  </si>
-  <si>
-    <t>20.09.202616</t>
-  </si>
-  <si>
-    <t>20.09.202617</t>
-  </si>
-  <si>
-    <t>20.09.202618</t>
-  </si>
-  <si>
-    <t>20.09.202619</t>
-  </si>
-  <si>
-    <t>20.09.202620</t>
-  </si>
-  <si>
-    <t>20.09.202621</t>
-  </si>
-  <si>
-    <t>20.09.202622</t>
-  </si>
-  <si>
-    <t>20.09.202623</t>
-  </si>
-  <si>
-    <t>20.09.202624</t>
-  </si>
-  <si>
-    <t>20.09.202625</t>
-  </si>
-  <si>
-    <t>20.09.202626</t>
-  </si>
-  <si>
-    <t>20.09.202627</t>
-  </si>
-  <si>
-    <t>20.09.202628</t>
-  </si>
-  <si>
-    <t>20.09.202629</t>
-  </si>
-  <si>
-    <t>20.09.202630</t>
-  </si>
-  <si>
-    <t>20.09.202631</t>
-  </si>
-  <si>
-    <t>20.09.202632</t>
-  </si>
-  <si>
-    <t>20.09.202633</t>
-  </si>
-  <si>
-    <t>20.09.202634</t>
-  </si>
-  <si>
-    <t>20.09.202635</t>
-  </si>
-  <si>
-    <t>20.09.202636</t>
-  </si>
-  <si>
-    <t>20.09.202637</t>
-  </si>
-  <si>
-    <t>20.09.202638</t>
+    <t>28.09.20261</t>
+  </si>
+  <si>
+    <t>28.09.20262</t>
+  </si>
+  <si>
+    <t>28.09.20263</t>
+  </si>
+  <si>
+    <t>28.09.20264</t>
+  </si>
+  <si>
+    <t>28.09.20265</t>
+  </si>
+  <si>
+    <t>28.09.20266</t>
+  </si>
+  <si>
+    <t>28.09.20267</t>
+  </si>
+  <si>
+    <t>28.09.20268</t>
+  </si>
+  <si>
+    <t>28.09.20269</t>
+  </si>
+  <si>
+    <t>28.09.202610</t>
+  </si>
+  <si>
+    <t>28.09.202611</t>
+  </si>
+  <si>
+    <t>28.09.202612</t>
+  </si>
+  <si>
+    <t>28.09.202613</t>
+  </si>
+  <si>
+    <t>28.09.202614</t>
+  </si>
+  <si>
+    <t>28.09.202615</t>
+  </si>
+  <si>
+    <t>28.09.202616</t>
+  </si>
+  <si>
+    <t>28.09.202617</t>
+  </si>
+  <si>
+    <t>28.09.202618</t>
+  </si>
+  <si>
+    <t>28.09.202619</t>
+  </si>
+  <si>
+    <t>28.09.202620</t>
+  </si>
+  <si>
+    <t>28.09.202621</t>
+  </si>
+  <si>
+    <t>28.09.202622</t>
+  </si>
+  <si>
+    <t>28.09.202623</t>
+  </si>
+  <si>
+    <t>28.09.202624</t>
+  </si>
+  <si>
+    <t>28.09.202625</t>
+  </si>
+  <si>
+    <t>28.09.202626</t>
+  </si>
+  <si>
+    <t>28.09.202627</t>
+  </si>
+  <si>
+    <t>28.09.202628</t>
+  </si>
+  <si>
+    <t>28.09.202629</t>
+  </si>
+  <si>
+    <t>28.09.202630</t>
+  </si>
+  <si>
+    <t>28.09.202631</t>
+  </si>
+  <si>
+    <t>28.09.202632</t>
+  </si>
+  <si>
+    <t>28.09.202633</t>
+  </si>
+  <si>
+    <t>28.09.202634</t>
+  </si>
+  <si>
+    <t>28.09.202635</t>
+  </si>
+  <si>
+    <t>28.09.202636</t>
+  </si>
+  <si>
+    <t>28.09.202637</t>
+  </si>
+  <si>
+    <t>28.09.202638</t>
+  </si>
+  <si>
+    <t>28.09.202639</t>
+  </si>
+  <si>
+    <t>28.09.202640</t>
+  </si>
+  <si>
+    <t>28.09.202641</t>
+  </si>
+  <si>
+    <t>28.09.202642</t>
+  </si>
+  <si>
+    <t>28.09.202643</t>
+  </si>
+  <si>
+    <t>28.09.202644</t>
+  </si>
+  <si>
+    <t>28.09.202645</t>
+  </si>
+  <si>
+    <t>28.09.202646</t>
+  </si>
+  <si>
+    <t>28.09.202647</t>
+  </si>
+  <si>
+    <t>28.09.202648</t>
+  </si>
+  <si>
+    <t>28.09.202649</t>
+  </si>
+  <si>
+    <t>28.09.202650</t>
+  </si>
+  <si>
+    <t>28.09.202651</t>
+  </si>
+  <si>
+    <t>28.09.202652</t>
+  </si>
+  <si>
+    <t>28.09.202653</t>
+  </si>
+  <si>
+    <t>28.09.202654</t>
+  </si>
+  <si>
+    <t>28.09.202655</t>
+  </si>
+  <si>
+    <t>28.09.202656</t>
+  </si>
+  <si>
+    <t>28.09.202657</t>
+  </si>
+  <si>
+    <t>28.09.202658</t>
+  </si>
+  <si>
+    <t>28.09.202659</t>
+  </si>
+  <si>
+    <t>28.09.202660</t>
+  </si>
+  <si>
+    <t>28.09.202661</t>
+  </si>
+  <si>
+    <t>28.09.202662</t>
+  </si>
+  <si>
+    <t>28.09.202663</t>
+  </si>
+  <si>
+    <t>28.09.202664</t>
+  </si>
+  <si>
+    <t>28.09.202665</t>
+  </si>
+  <si>
+    <t>28.09.202666</t>
+  </si>
+  <si>
+    <t>28.09.202667</t>
+  </si>
+  <si>
+    <t>28.09.202668</t>
+  </si>
+  <si>
+    <t>28.09.202669</t>
+  </si>
+  <si>
+    <t>28.09.202670</t>
+  </si>
+  <si>
+    <t>28.09.202671</t>
+  </si>
+  <si>
+    <t>28.09.202672</t>
+  </si>
+  <si>
+    <t>28.09.202673</t>
+  </si>
+  <si>
+    <t>28.09.202674</t>
+  </si>
+  <si>
+    <t>28.09.202675</t>
+  </si>
+  <si>
+    <t>28.09.202676</t>
+  </si>
+  <si>
+    <t>28.09.202677</t>
+  </si>
+  <si>
+    <t>28.09.202678</t>
+  </si>
+  <si>
+    <t>28.09.202679</t>
+  </si>
+  <si>
+    <t>28.09.202680</t>
+  </si>
+  <si>
+    <t>28.09.202681</t>
+  </si>
+  <si>
+    <t>28.09.202682</t>
+  </si>
+  <si>
+    <t>28.09.202683</t>
+  </si>
+  <si>
+    <t>28.09.202684</t>
+  </si>
+  <si>
+    <t>28.09.202685</t>
+  </si>
+  <si>
+    <t>28.09.202686</t>
+  </si>
+  <si>
+    <t>28.09.202687</t>
+  </si>
+  <si>
+    <t>28.09.202688</t>
+  </si>
+  <si>
+    <t>28.09.202689</t>
+  </si>
+  <si>
+    <t>28.09.202690</t>
+  </si>
+  <si>
+    <t>28.09.202691</t>
+  </si>
+  <si>
+    <t>28.09.202692</t>
+  </si>
+  <si>
+    <t>28.09.202693</t>
+  </si>
+  <si>
+    <t>28.09.202694</t>
+  </si>
+  <si>
+    <t>28.09.202695</t>
+  </si>
+  <si>
+    <t>28.09.202696</t>
+  </si>
+  <si>
+    <t>29.09.20261</t>
+  </si>
+  <si>
+    <t>29.09.20262</t>
+  </si>
+  <si>
+    <t>29.09.20263</t>
+  </si>
+  <si>
+    <t>29.09.20264</t>
+  </si>
+  <si>
+    <t>29.09.20265</t>
+  </si>
+  <si>
+    <t>29.09.20266</t>
+  </si>
+  <si>
+    <t>29.09.20267</t>
+  </si>
+  <si>
+    <t>29.09.20268</t>
+  </si>
+  <si>
+    <t>29.09.20269</t>
+  </si>
+  <si>
+    <t>29.09.202610</t>
+  </si>
+  <si>
+    <t>29.09.202611</t>
+  </si>
+  <si>
+    <t>29.09.202612</t>
+  </si>
+  <si>
+    <t>29.09.202613</t>
+  </si>
+  <si>
+    <t>29.09.202614</t>
+  </si>
+  <si>
+    <t>29.09.202615</t>
+  </si>
+  <si>
+    <t>29.09.202616</t>
+  </si>
+  <si>
+    <t>29.09.202617</t>
+  </si>
+  <si>
+    <t>29.09.202618</t>
+  </si>
+  <si>
+    <t>29.09.202619</t>
+  </si>
+  <si>
+    <t>29.09.202620</t>
+  </si>
+  <si>
+    <t>29.09.202621</t>
+  </si>
+  <si>
+    <t>29.09.202622</t>
+  </si>
+  <si>
+    <t>29.09.202623</t>
+  </si>
+  <si>
+    <t>29.09.202624</t>
+  </si>
+  <si>
+    <t>29.09.202625</t>
+  </si>
+  <si>
+    <t>29.09.202626</t>
+  </si>
+  <si>
+    <t>29.09.202627</t>
+  </si>
+  <si>
+    <t>29.09.202628</t>
+  </si>
+  <si>
+    <t>29.09.202629</t>
+  </si>
+  <si>
+    <t>29.09.202630</t>
+  </si>
+  <si>
+    <t>29.09.202631</t>
+  </si>
+  <si>
+    <t>29.09.202632</t>
+  </si>
+  <si>
+    <t>29.09.202633</t>
+  </si>
+  <si>
+    <t>29.09.202634</t>
+  </si>
+  <si>
+    <t>29.09.202635</t>
+  </si>
+  <si>
+    <t>29.09.202636</t>
+  </si>
+  <si>
+    <t>29.09.202637</t>
+  </si>
+  <si>
+    <t>29.09.202638</t>
+  </si>
+  <si>
+    <t>29.09.202639</t>
+  </si>
+  <si>
+    <t>29.09.202640</t>
+  </si>
+  <si>
+    <t>29.09.202641</t>
+  </si>
+  <si>
+    <t>29.09.202642</t>
+  </si>
+  <si>
+    <t>29.09.202643</t>
+  </si>
+  <si>
+    <t>29.09.202644</t>
+  </si>
+  <si>
+    <t>29.09.202645</t>
+  </si>
+  <si>
+    <t>29.09.202646</t>
+  </si>
+  <si>
+    <t>29.09.202647</t>
+  </si>
+  <si>
+    <t>29.09.202648</t>
+  </si>
+  <si>
+    <t>29.09.202649</t>
+  </si>
+  <si>
+    <t>29.09.202650</t>
+  </si>
+  <si>
+    <t>29.09.202651</t>
+  </si>
+  <si>
+    <t>29.09.202652</t>
+  </si>
+  <si>
+    <t>29.09.202653</t>
+  </si>
+  <si>
+    <t>29.09.202654</t>
+  </si>
+  <si>
+    <t>29.09.202655</t>
+  </si>
+  <si>
+    <t>29.09.202656</t>
+  </si>
+  <si>
+    <t>29.09.202657</t>
+  </si>
+  <si>
+    <t>29.09.202658</t>
+  </si>
+  <si>
+    <t>29.09.202659</t>
+  </si>
+  <si>
+    <t>29.09.202660</t>
+  </si>
+  <si>
+    <t>29.09.202661</t>
+  </si>
+  <si>
+    <t>29.09.202662</t>
+  </si>
+  <si>
+    <t>29.09.202663</t>
+  </si>
+  <si>
+    <t>29.09.202664</t>
+  </si>
+  <si>
+    <t>29.09.202665</t>
+  </si>
+  <si>
+    <t>29.09.202666</t>
+  </si>
+  <si>
+    <t>29.09.202667</t>
+  </si>
+  <si>
+    <t>29.09.202668</t>
+  </si>
+  <si>
+    <t>29.09.202669</t>
+  </si>
+  <si>
+    <t>29.09.202670</t>
+  </si>
+  <si>
+    <t>29.09.202671</t>
+  </si>
+  <si>
+    <t>29.09.202672</t>
+  </si>
+  <si>
+    <t>29.09.202673</t>
+  </si>
+  <si>
+    <t>29.09.202674</t>
+  </si>
+  <si>
+    <t>29.09.202675</t>
+  </si>
+  <si>
+    <t>29.09.202676</t>
+  </si>
+  <si>
+    <t>29.09.202677</t>
+  </si>
+  <si>
+    <t>29.09.202678</t>
+  </si>
+  <si>
+    <t>29.09.202679</t>
+  </si>
+  <si>
+    <t>29.09.202680</t>
+  </si>
+  <si>
+    <t>29.09.202681</t>
+  </si>
+  <si>
+    <t>29.09.202682</t>
+  </si>
+  <si>
+    <t>29.09.202683</t>
+  </si>
+  <si>
+    <t>29.09.202684</t>
+  </si>
+  <si>
+    <t>29.09.202685</t>
+  </si>
+  <si>
+    <t>29.09.202686</t>
+  </si>
+  <si>
+    <t>29.09.202687</t>
+  </si>
+  <si>
+    <t>29.09.202688</t>
+  </si>
+  <si>
+    <t>29.09.202689</t>
+  </si>
+  <si>
+    <t>29.09.202690</t>
+  </si>
+  <si>
+    <t>29.09.202691</t>
+  </si>
+  <si>
+    <t>29.09.202692</t>
+  </si>
+  <si>
+    <t>29.09.202693</t>
+  </si>
+  <si>
+    <t>29.09.202694</t>
+  </si>
+  <si>
+    <t>29.09.202695</t>
+  </si>
+  <si>
+    <t>29.09.202696</t>
+  </si>
+  <si>
+    <t>30.09.20261</t>
+  </si>
+  <si>
+    <t>30.09.20262</t>
+  </si>
+  <si>
+    <t>30.09.20263</t>
+  </si>
+  <si>
+    <t>30.09.20264</t>
+  </si>
+  <si>
+    <t>30.09.20265</t>
+  </si>
+  <si>
+    <t>30.09.20266</t>
+  </si>
+  <si>
+    <t>30.09.20267</t>
+  </si>
+  <si>
+    <t>30.09.20268</t>
+  </si>
+  <si>
+    <t>30.09.20269</t>
+  </si>
+  <si>
+    <t>30.09.202610</t>
+  </si>
+  <si>
+    <t>30.09.202611</t>
+  </si>
+  <si>
+    <t>30.09.202612</t>
+  </si>
+  <si>
+    <t>30.09.202613</t>
+  </si>
+  <si>
+    <t>30.09.202614</t>
+  </si>
+  <si>
+    <t>30.09.202615</t>
+  </si>
+  <si>
+    <t>30.09.202616</t>
+  </si>
+  <si>
+    <t>30.09.202617</t>
+  </si>
+  <si>
+    <t>30.09.202618</t>
+  </si>
+  <si>
+    <t>30.09.202619</t>
+  </si>
+  <si>
+    <t>30.09.202620</t>
+  </si>
+  <si>
+    <t>30.09.202621</t>
+  </si>
+  <si>
+    <t>30.09.202622</t>
+  </si>
+  <si>
+    <t>30.09.202623</t>
+  </si>
+  <si>
+    <t>30.09.202624</t>
+  </si>
+  <si>
+    <t>30.09.202625</t>
+  </si>
+  <si>
+    <t>30.09.202626</t>
+  </si>
+  <si>
+    <t>30.09.202627</t>
+  </si>
+  <si>
+    <t>30.09.202628</t>
+  </si>
+  <si>
+    <t>30.09.202629</t>
+  </si>
+  <si>
+    <t>30.09.202630</t>
+  </si>
+  <si>
+    <t>30.09.202631</t>
+  </si>
+  <si>
+    <t>30.09.202632</t>
+  </si>
+  <si>
+    <t>30.09.202633</t>
+  </si>
+  <si>
+    <t>30.09.202634</t>
+  </si>
+  <si>
+    <t>30.09.202635</t>
+  </si>
+  <si>
+    <t>30.09.202636</t>
+  </si>
+  <si>
+    <t>30.09.202637</t>
+  </si>
+  <si>
+    <t>30.09.202638</t>
+  </si>
+  <si>
+    <t>30.09.202639</t>
   </si>
 </sst>
 </file>
@@ -1080,7 +1083,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E231"/>
+  <dimension ref="A1:E232"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1102,13 +1105,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46283</v>
+        <v>46293</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>8.356</v>
+        <v>1.798</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1119,13 +1122,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46283.01041666666</v>
+        <v>46293.01041666666</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>1.409</v>
       </c>
       <c r="C3">
-        <v>2.351</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1136,13 +1139,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46283.02083333334</v>
+        <v>46293.02083333334</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>0.961</v>
       </c>
       <c r="C4">
-        <v>11.748</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1153,13 +1156,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46283.03125</v>
+        <v>46293.03125</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>10.579</v>
       </c>
       <c r="C5">
-        <v>13.68</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1170,10 +1173,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46283.04166666666</v>
+        <v>46293.04166666666</v>
       </c>
       <c r="B6">
-        <v>1.793</v>
+        <v>13.859</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1187,13 +1190,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46283.05208333334</v>
+        <v>46293.05208333334</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>15.555</v>
       </c>
       <c r="C7">
-        <v>3.215</v>
+        <v>0</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -1204,10 +1207,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46283.0625</v>
+        <v>46293.0625</v>
       </c>
       <c r="B8">
-        <v>4.923</v>
+        <v>13.645</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1221,10 +1224,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46283.07291666666</v>
+        <v>46293.07291666666</v>
       </c>
       <c r="B9">
-        <v>2.601</v>
+        <v>4.526</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1238,13 +1241,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46283.08333333334</v>
+        <v>46293.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="C10">
-        <v>8.111000000000001</v>
+        <v>3.359</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -1255,13 +1258,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46283.09375</v>
+        <v>46293.09375</v>
       </c>
       <c r="B11">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>6.666</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1272,13 +1275,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46283.10416666666</v>
+        <v>46293.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
       <c r="C12">
-        <v>1.959</v>
+        <v>3.275</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -1289,13 +1292,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46283.11458333334</v>
+        <v>46293.11458333334</v>
       </c>
       <c r="B13">
-        <v>0.462</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>8.061999999999999</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -1306,13 +1309,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46283.125</v>
+        <v>46293.125</v>
       </c>
       <c r="B14">
         <v>0</v>
       </c>
       <c r="C14">
-        <v>1.967</v>
+        <v>28.05</v>
       </c>
       <c r="D14">
         <v>13</v>
@@ -1323,13 +1326,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46283.13541666666</v>
+        <v>46293.13541666666</v>
       </c>
       <c r="B15">
-        <v>5.277</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>30.802</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -1340,13 +1343,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46283.14583333334</v>
+        <v>46293.14583333334</v>
       </c>
       <c r="B16">
-        <v>4.261</v>
+        <v>0</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>27.358</v>
       </c>
       <c r="D16">
         <v>15</v>
@@ -1357,13 +1360,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46283.15625</v>
+        <v>46293.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
       </c>
       <c r="C17">
-        <v>1.103</v>
+        <v>38.678</v>
       </c>
       <c r="D17">
         <v>16</v>
@@ -1374,13 +1377,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46283.16666666666</v>
+        <v>46293.16666666666</v>
       </c>
       <c r="B18">
-        <v>1.314</v>
+        <v>0</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>50.667</v>
       </c>
       <c r="D18">
         <v>17</v>
@@ -1391,10 +1394,10 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46283.17708333334</v>
+        <v>46293.17708333334</v>
       </c>
       <c r="B19">
-        <v>3.363</v>
+        <v>3.065</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1408,13 +1411,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46283.1875</v>
+        <v>46293.1875</v>
       </c>
       <c r="B20">
-        <v>3.752</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>6.456</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1425,10 +1428,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46283.19791666666</v>
+        <v>46293.19791666666</v>
       </c>
       <c r="B21">
-        <v>1.766</v>
+        <v>2.666</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1442,13 +1445,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46283.20833333334</v>
+        <v>46293.20833333334</v>
       </c>
       <c r="B22">
-        <v>22.149</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>10.816</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1459,10 +1462,10 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46283.21875</v>
+        <v>46293.21875</v>
       </c>
       <c r="B23">
-        <v>6.952</v>
+        <v>6.844</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1476,13 +1479,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46283.22916666666</v>
+        <v>46293.22916666666</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>6.292</v>
       </c>
       <c r="C24">
-        <v>0.075</v>
+        <v>0</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1493,13 +1496,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46283.23958333334</v>
+        <v>46293.23958333334</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>0.131</v>
       </c>
       <c r="C25">
-        <v>0.271</v>
+        <v>0</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1510,13 +1513,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46283.25</v>
+        <v>46293.25</v>
       </c>
       <c r="B26">
-        <v>0.949</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>3.254</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1527,13 +1530,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46283.26041666666</v>
+        <v>46293.26041666666</v>
       </c>
       <c r="B27">
         <v>0</v>
       </c>
       <c r="C27">
-        <v>0.443</v>
+        <v>4.113</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1544,13 +1547,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46283.27083333334</v>
+        <v>46293.27083333334</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>0.398</v>
       </c>
       <c r="C28">
-        <v>0.745</v>
+        <v>0</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1561,13 +1564,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46283.28125</v>
+        <v>46293.28125</v>
       </c>
       <c r="B29">
         <v>0</v>
       </c>
       <c r="C29">
-        <v>5.009</v>
+        <v>15.674</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1578,13 +1581,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46283.29166666666</v>
+        <v>46293.29166666666</v>
       </c>
       <c r="B30">
-        <v>16.399</v>
+        <v>0</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>9.18</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1595,13 +1598,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46283.30208333334</v>
+        <v>46293.30208333334</v>
       </c>
       <c r="B31">
-        <v>26.627</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>15.029</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1612,13 +1615,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46283.3125</v>
+        <v>46293.3125</v>
       </c>
       <c r="B32">
-        <v>1.411</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>33.922</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1629,13 +1632,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46283.32291666666</v>
+        <v>46293.32291666666</v>
       </c>
       <c r="B33">
         <v>0</v>
       </c>
       <c r="C33">
-        <v>43.594</v>
+        <v>84.81100000000001</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1646,13 +1649,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46283.33333333334</v>
+        <v>46293.33333333334</v>
       </c>
       <c r="B34">
         <v>0</v>
       </c>
       <c r="C34">
-        <v>33.775</v>
+        <v>63.084</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1663,13 +1666,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46283.34375</v>
+        <v>46293.34375</v>
       </c>
       <c r="B35">
         <v>0</v>
       </c>
       <c r="C35">
-        <v>61.152</v>
+        <v>28.023</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1680,13 +1683,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46283.35416666666</v>
+        <v>46293.35416666666</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>2.102</v>
       </c>
       <c r="C36">
-        <v>7.376</v>
+        <v>0</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1697,13 +1700,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46283.36458333334</v>
+        <v>46293.36458333334</v>
       </c>
       <c r="B37">
-        <v>11.259</v>
+        <v>0</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>45.248</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1714,13 +1717,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46283.375</v>
+        <v>46293.375</v>
       </c>
       <c r="B38">
-        <v>7.591</v>
+        <v>0</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>40.553</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1731,10 +1734,10 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46283.38541666666</v>
+        <v>46293.38541666666</v>
       </c>
       <c r="B39">
-        <v>5.023</v>
+        <v>6.82</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -1748,10 +1751,10 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46283.39583333334</v>
+        <v>46293.39583333334</v>
       </c>
       <c r="B40">
-        <v>18.253</v>
+        <v>1.555</v>
       </c>
       <c r="C40">
         <v>0</v>
@@ -1765,13 +1768,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46283.40625</v>
+        <v>46293.40625</v>
       </c>
       <c r="B41">
-        <v>16.643</v>
+        <v>0</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>0.313</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1782,10 +1785,10 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46283.41666666666</v>
+        <v>46293.41666666666</v>
       </c>
       <c r="B42">
-        <v>53.344</v>
+        <v>6.271</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -1799,10 +1802,10 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46283.42708333334</v>
+        <v>46293.42708333334</v>
       </c>
       <c r="B43">
-        <v>30.187</v>
+        <v>3.666</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -1816,13 +1819,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46283.4375</v>
+        <v>46293.4375</v>
       </c>
       <c r="B44">
-        <v>3.814</v>
+        <v>0</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>1.438</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1833,13 +1836,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46283.44791666666</v>
+        <v>46293.44791666666</v>
       </c>
       <c r="B45">
-        <v>12.808</v>
+        <v>0</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>3.065</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1850,13 +1853,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46283.45833333334</v>
+        <v>46293.45833333334</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>1.726</v>
       </c>
       <c r="C46">
-        <v>12.895</v>
+        <v>0</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1867,13 +1870,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46283.46875</v>
+        <v>46293.46875</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>8.055999999999999</v>
       </c>
       <c r="C47">
-        <v>5.883</v>
+        <v>0</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1884,13 +1887,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46283.47916666666</v>
+        <v>46293.47916666666</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>7.282</v>
       </c>
       <c r="C48">
-        <v>31.109</v>
+        <v>0</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1901,13 +1904,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46283.48958333334</v>
+        <v>46293.48958333334</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>1.903</v>
       </c>
       <c r="C49">
-        <v>6.885</v>
+        <v>0</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1918,13 +1921,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46283.5</v>
+        <v>46293.5</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>4.629</v>
       </c>
       <c r="C50">
-        <v>10.543</v>
+        <v>0</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1935,13 +1938,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46283.51041666666</v>
+        <v>46293.51041666666</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>6.961</v>
       </c>
       <c r="C51">
-        <v>28.97</v>
+        <v>0</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1952,13 +1955,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46283.52083333334</v>
+        <v>46293.52083333334</v>
       </c>
       <c r="B52">
         <v>0</v>
       </c>
       <c r="C52">
-        <v>10.314</v>
+        <v>31.715</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1969,13 +1972,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46283.53125</v>
+        <v>46293.53125</v>
       </c>
       <c r="B53">
-        <v>27.681</v>
+        <v>0</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>30.607</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1986,13 +1989,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46283.54166666666</v>
+        <v>46293.54166666666</v>
       </c>
       <c r="B54">
-        <v>76.825</v>
+        <v>0</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>10.989</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -2003,13 +2006,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46283.55208333334</v>
+        <v>46293.55208333334</v>
       </c>
       <c r="B55">
-        <v>28.628</v>
+        <v>0</v>
       </c>
       <c r="C55">
-        <v>0</v>
+        <v>2.561</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -2020,13 +2023,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46283.5625</v>
+        <v>46293.5625</v>
       </c>
       <c r="B56">
-        <v>15.983</v>
+        <v>0</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>26.777</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -2037,13 +2040,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46283.57291666666</v>
+        <v>46293.57291666666</v>
       </c>
       <c r="B57">
-        <v>19.113</v>
+        <v>0</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>13.412</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -2054,13 +2057,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46283.58333333334</v>
+        <v>46293.58333333334</v>
       </c>
       <c r="B58">
-        <v>24.869</v>
+        <v>0</v>
       </c>
       <c r="C58">
-        <v>0</v>
+        <v>10.266</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -2071,13 +2074,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46283.59375</v>
+        <v>46293.59375</v>
       </c>
       <c r="B59">
-        <v>0.527</v>
+        <v>0</v>
       </c>
       <c r="C59">
-        <v>0</v>
+        <v>18.765</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -2088,13 +2091,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46283.60416666666</v>
+        <v>46293.60416666666</v>
       </c>
       <c r="B60">
-        <v>0</v>
+        <v>2.908</v>
       </c>
       <c r="C60">
-        <v>1.918</v>
+        <v>0</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -2105,13 +2108,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46283.61458333334</v>
+        <v>46293.61458333334</v>
       </c>
       <c r="B61">
-        <v>1.748</v>
+        <v>0</v>
       </c>
       <c r="C61">
-        <v>0</v>
+        <v>14.509</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2122,10 +2125,10 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46283.625</v>
+        <v>46293.625</v>
       </c>
       <c r="B62">
-        <v>1.008</v>
+        <v>2.978</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -2139,10 +2142,10 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46283.63541666666</v>
+        <v>46293.63541666666</v>
       </c>
       <c r="B63">
-        <v>2.304</v>
+        <v>5.252</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -2156,13 +2159,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46283.64583333334</v>
+        <v>46293.64583333334</v>
       </c>
       <c r="B64">
-        <v>0</v>
+        <v>6.743</v>
       </c>
       <c r="C64">
-        <v>6.165</v>
+        <v>0</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2173,10 +2176,10 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46283.65625</v>
+        <v>46293.65625</v>
       </c>
       <c r="B65">
-        <v>5.568</v>
+        <v>8.433</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -2190,10 +2193,10 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46283.66666666666</v>
+        <v>46293.66666666666</v>
       </c>
       <c r="B66">
-        <v>4.075</v>
+        <v>9.037000000000001</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -2207,10 +2210,10 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46283.67708333334</v>
+        <v>46293.67708333334</v>
       </c>
       <c r="B67">
-        <v>12.843</v>
+        <v>8.708</v>
       </c>
       <c r="C67">
         <v>0</v>
@@ -2224,10 +2227,10 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46283.6875</v>
+        <v>46293.6875</v>
       </c>
       <c r="B68">
-        <v>9.98</v>
+        <v>4.397</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -2241,10 +2244,10 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46283.69791666666</v>
+        <v>46293.69791666666</v>
       </c>
       <c r="B69">
-        <v>6.344</v>
+        <v>5.307</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -2258,13 +2261,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46283.70833333334</v>
+        <v>46293.70833333334</v>
       </c>
       <c r="B70">
         <v>0</v>
       </c>
       <c r="C70">
-        <v>13.752</v>
+        <v>47.302</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2275,13 +2278,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46283.71875</v>
+        <v>46293.71875</v>
       </c>
       <c r="B71">
-        <v>6.442</v>
+        <v>0</v>
       </c>
       <c r="C71">
-        <v>0</v>
+        <v>25.027</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2292,13 +2295,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46283.72916666666</v>
+        <v>46293.72916666666</v>
       </c>
       <c r="B72">
         <v>0</v>
       </c>
       <c r="C72">
-        <v>1.726</v>
+        <v>5.766</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2309,13 +2312,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46283.73958333334</v>
+        <v>46293.73958333334</v>
       </c>
       <c r="B73">
-        <v>1.629</v>
+        <v>0</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>2.691</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2326,10 +2329,10 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46283.75</v>
+        <v>46293.75</v>
       </c>
       <c r="B74">
-        <v>6.007</v>
+        <v>12.517</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -2343,13 +2346,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46283.76041666666</v>
+        <v>46293.76041666666</v>
       </c>
       <c r="B75">
-        <v>0</v>
+        <v>2.664</v>
       </c>
       <c r="C75">
-        <v>4.145</v>
+        <v>0</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2360,10 +2363,10 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46283.77083333334</v>
+        <v>46293.77083333334</v>
       </c>
       <c r="B76">
-        <v>2.777</v>
+        <v>4.686</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -2377,13 +2380,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46283.78125</v>
+        <v>46293.78125</v>
       </c>
       <c r="B77">
         <v>0</v>
       </c>
       <c r="C77">
-        <v>21.764</v>
+        <v>6.003</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2394,13 +2397,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46283.79166666666</v>
+        <v>46293.79166666666</v>
       </c>
       <c r="B78">
         <v>0</v>
       </c>
       <c r="C78">
-        <v>1.352</v>
+        <v>0.771</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2411,13 +2414,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46283.80208333334</v>
+        <v>46293.80208333334</v>
       </c>
       <c r="B79">
         <v>0</v>
       </c>
       <c r="C79">
-        <v>16.039</v>
+        <v>1.714</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2428,13 +2431,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46283.8125</v>
+        <v>46293.8125</v>
       </c>
       <c r="B80">
         <v>0</v>
       </c>
       <c r="C80">
-        <v>21.396</v>
+        <v>11.644</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2445,13 +2448,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46283.82291666666</v>
+        <v>46293.82291666666</v>
       </c>
       <c r="B81">
         <v>0</v>
       </c>
       <c r="C81">
-        <v>28.766</v>
+        <v>13.082</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2462,13 +2465,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46283.83333333334</v>
+        <v>46293.83333333334</v>
       </c>
       <c r="B82">
         <v>0</v>
       </c>
       <c r="C82">
-        <v>28.425</v>
+        <v>4.347</v>
       </c>
       <c r="D82">
         <v>81</v>
@@ -2479,13 +2482,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46283.84375</v>
+        <v>46293.84375</v>
       </c>
       <c r="B83">
         <v>0</v>
       </c>
       <c r="C83">
-        <v>15.209</v>
+        <v>5.402</v>
       </c>
       <c r="D83">
         <v>82</v>
@@ -2496,13 +2499,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46283.85416666666</v>
+        <v>46293.85416666666</v>
       </c>
       <c r="B84">
         <v>0</v>
       </c>
       <c r="C84">
-        <v>3.617</v>
+        <v>7.037</v>
       </c>
       <c r="D84">
         <v>83</v>
@@ -2513,13 +2516,13 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46283.86458333334</v>
+        <v>46293.86458333334</v>
       </c>
       <c r="B85">
-        <v>11.287</v>
+        <v>0</v>
       </c>
       <c r="C85">
-        <v>0</v>
+        <v>1.256</v>
       </c>
       <c r="D85">
         <v>84</v>
@@ -2530,10 +2533,10 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46283.875</v>
+        <v>46293.875</v>
       </c>
       <c r="B86">
-        <v>4.738</v>
+        <v>11.536</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -2547,13 +2550,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46283.88541666666</v>
+        <v>46293.88541666666</v>
       </c>
       <c r="B87">
-        <v>8.422000000000001</v>
+        <v>0</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>3.719</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -2564,13 +2567,13 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46283.89583333334</v>
+        <v>46293.89583333334</v>
       </c>
       <c r="B88">
-        <v>8.289999999999999</v>
+        <v>0</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>14.448</v>
       </c>
       <c r="D88">
         <v>87</v>
@@ -2581,13 +2584,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46283.90625</v>
+        <v>46293.90625</v>
       </c>
       <c r="B89">
-        <v>12.073</v>
+        <v>0</v>
       </c>
       <c r="C89">
-        <v>0</v>
+        <v>16.027</v>
       </c>
       <c r="D89">
         <v>88</v>
@@ -2598,13 +2601,13 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46283.91666666666</v>
+        <v>46293.91666666666</v>
       </c>
       <c r="B90">
-        <v>19.454</v>
+        <v>0</v>
       </c>
       <c r="C90">
-        <v>0</v>
+        <v>2.664</v>
       </c>
       <c r="D90">
         <v>89</v>
@@ -2615,13 +2618,13 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46283.92708333334</v>
+        <v>46293.92708333334</v>
       </c>
       <c r="B91">
-        <v>10.539</v>
+        <v>0</v>
       </c>
       <c r="C91">
-        <v>0</v>
+        <v>7.384</v>
       </c>
       <c r="D91">
         <v>90</v>
@@ -2632,13 +2635,13 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46283.9375</v>
+        <v>46293.9375</v>
       </c>
       <c r="B92">
-        <v>7.859</v>
+        <v>0</v>
       </c>
       <c r="C92">
-        <v>0</v>
+        <v>3.563</v>
       </c>
       <c r="D92">
         <v>91</v>
@@ -2649,10 +2652,10 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46283.94791666666</v>
+        <v>46293.94791666666</v>
       </c>
       <c r="B93">
-        <v>14.685</v>
+        <v>4.269</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -2666,13 +2669,13 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46283.95833333334</v>
+        <v>46293.95833333334</v>
       </c>
       <c r="B94">
-        <v>12.438</v>
+        <v>0</v>
       </c>
       <c r="C94">
-        <v>0</v>
+        <v>0.803</v>
       </c>
       <c r="D94">
         <v>93</v>
@@ -2683,13 +2686,13 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46283.96875</v>
+        <v>46293.96875</v>
       </c>
       <c r="B95">
-        <v>5.19</v>
+        <v>0</v>
       </c>
       <c r="C95">
-        <v>0</v>
+        <v>1.261</v>
       </c>
       <c r="D95">
         <v>94</v>
@@ -2700,13 +2703,13 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46283.97916666666</v>
+        <v>46293.97916666666</v>
       </c>
       <c r="B96">
-        <v>0</v>
+        <v>1.297</v>
       </c>
       <c r="C96">
-        <v>4.627</v>
+        <v>0</v>
       </c>
       <c r="D96">
         <v>95</v>
@@ -2717,13 +2720,13 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46283.98958333334</v>
+        <v>46293.98958333334</v>
       </c>
       <c r="B97">
-        <v>0</v>
+        <v>8.444000000000001</v>
       </c>
       <c r="C97">
-        <v>17.959</v>
+        <v>0</v>
       </c>
       <c r="D97">
         <v>96</v>
@@ -2734,13 +2737,13 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46284</v>
+        <v>46294</v>
       </c>
       <c r="B98">
-        <v>0</v>
+        <v>7.175</v>
       </c>
       <c r="C98">
-        <v>20.048</v>
+        <v>0</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -2751,13 +2754,13 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46284.01041666666</v>
+        <v>46294.01041666666</v>
       </c>
       <c r="B99">
-        <v>0</v>
+        <v>3.201</v>
       </c>
       <c r="C99">
-        <v>31.634</v>
+        <v>0</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -2768,10 +2771,10 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46284.02083333334</v>
+        <v>46294.02083333334</v>
       </c>
       <c r="B100">
-        <v>3.321</v>
+        <v>0.208</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -2785,13 +2788,13 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46284.03125</v>
+        <v>46294.03125</v>
       </c>
       <c r="B101">
         <v>0</v>
       </c>
       <c r="C101">
-        <v>9.253</v>
+        <v>3.537</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -2802,13 +2805,13 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46284.04166666666</v>
+        <v>46294.04166666666</v>
       </c>
       <c r="B102">
         <v>0</v>
       </c>
       <c r="C102">
-        <v>8.541</v>
+        <v>4.233</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -2819,13 +2822,13 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46284.05208333334</v>
+        <v>46294.05208333334</v>
       </c>
       <c r="B103">
-        <v>0</v>
+        <v>4.737</v>
       </c>
       <c r="C103">
-        <v>2.677</v>
+        <v>0</v>
       </c>
       <c r="D103">
         <v>6</v>
@@ -2836,13 +2839,13 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46284.0625</v>
+        <v>46294.0625</v>
       </c>
       <c r="B104">
-        <v>0</v>
+        <v>0.036</v>
       </c>
       <c r="C104">
-        <v>5.515</v>
+        <v>0</v>
       </c>
       <c r="D104">
         <v>7</v>
@@ -2853,13 +2856,13 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46284.07291666666</v>
+        <v>46294.07291666666</v>
       </c>
       <c r="B105">
         <v>0</v>
       </c>
       <c r="C105">
-        <v>0.623</v>
+        <v>10.083</v>
       </c>
       <c r="D105">
         <v>8</v>
@@ -2870,13 +2873,13 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46284.08333333334</v>
+        <v>46294.08333333334</v>
       </c>
       <c r="B106">
         <v>0</v>
       </c>
       <c r="C106">
-        <v>17.52</v>
+        <v>0.113</v>
       </c>
       <c r="D106">
         <v>9</v>
@@ -2887,13 +2890,13 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46284.09375</v>
+        <v>46294.09375</v>
       </c>
       <c r="B107">
         <v>0</v>
       </c>
       <c r="C107">
-        <v>5.315</v>
+        <v>2.345</v>
       </c>
       <c r="D107">
         <v>10</v>
@@ -2904,13 +2907,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46284.10416666666</v>
+        <v>46294.10416666666</v>
       </c>
       <c r="B108">
-        <v>0</v>
+        <v>2.913</v>
       </c>
       <c r="C108">
-        <v>5.657</v>
+        <v>0</v>
       </c>
       <c r="D108">
         <v>11</v>
@@ -2921,13 +2924,13 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46284.11458333334</v>
+        <v>46294.11458333334</v>
       </c>
       <c r="B109">
-        <v>0</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="C109">
-        <v>4.251</v>
+        <v>0</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -2938,13 +2941,13 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46284.125</v>
+        <v>46294.125</v>
       </c>
       <c r="B110">
-        <v>0</v>
+        <v>8.323</v>
       </c>
       <c r="C110">
-        <v>5.653</v>
+        <v>0</v>
       </c>
       <c r="D110">
         <v>13</v>
@@ -2955,13 +2958,13 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46284.13541666666</v>
+        <v>46294.13541666666</v>
       </c>
       <c r="B111">
-        <v>0</v>
+        <v>2.534</v>
       </c>
       <c r="C111">
-        <v>3.072</v>
+        <v>0</v>
       </c>
       <c r="D111">
         <v>14</v>
@@ -2972,13 +2975,13 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46284.14583333334</v>
+        <v>46294.14583333334</v>
       </c>
       <c r="B112">
-        <v>0</v>
+        <v>0.272</v>
       </c>
       <c r="C112">
-        <v>5.009</v>
+        <v>0</v>
       </c>
       <c r="D112">
         <v>15</v>
@@ -2989,13 +2992,13 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46284.15625</v>
+        <v>46294.15625</v>
       </c>
       <c r="B113">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="C113">
-        <v>0</v>
+        <v>9.023999999999999</v>
       </c>
       <c r="D113">
         <v>16</v>
@@ -3006,13 +3009,13 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46284.16666666666</v>
+        <v>46294.16666666666</v>
       </c>
       <c r="B114">
-        <v>7.469</v>
+        <v>0</v>
       </c>
       <c r="C114">
-        <v>0</v>
+        <v>11.069</v>
       </c>
       <c r="D114">
         <v>17</v>
@@ -3023,13 +3026,13 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46284.17708333334</v>
+        <v>46294.17708333334</v>
       </c>
       <c r="B115">
         <v>0</v>
       </c>
       <c r="C115">
-        <v>0.592</v>
+        <v>5.772</v>
       </c>
       <c r="D115">
         <v>18</v>
@@ -3040,10 +3043,10 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46284.1875</v>
+        <v>46294.1875</v>
       </c>
       <c r="B116">
-        <v>0.424</v>
+        <v>2.496</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -3057,13 +3060,13 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46284.19791666666</v>
+        <v>46294.19791666666</v>
       </c>
       <c r="B117">
         <v>0</v>
       </c>
       <c r="C117">
-        <v>1.248</v>
+        <v>9.276999999999999</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -3074,13 +3077,13 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46284.20833333334</v>
+        <v>46294.20833333334</v>
       </c>
       <c r="B118">
-        <v>10.424</v>
+        <v>0</v>
       </c>
       <c r="C118">
-        <v>0</v>
+        <v>20.255</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -3091,13 +3094,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46284.21875</v>
+        <v>46294.21875</v>
       </c>
       <c r="B119">
-        <v>14.103</v>
+        <v>0</v>
       </c>
       <c r="C119">
-        <v>0</v>
+        <v>1.161</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -3108,10 +3111,10 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46284.22916666666</v>
+        <v>46294.22916666666</v>
       </c>
       <c r="B120">
-        <v>7.432</v>
+        <v>9.385</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -3125,13 +3128,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46284.23958333334</v>
+        <v>46294.23958333334</v>
       </c>
       <c r="B121">
-        <v>13.109</v>
+        <v>0</v>
       </c>
       <c r="C121">
-        <v>0</v>
+        <v>0.522</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3142,13 +3145,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46284.25</v>
+        <v>46294.25</v>
       </c>
       <c r="B122">
-        <v>1.167</v>
+        <v>0</v>
       </c>
       <c r="C122">
-        <v>0</v>
+        <v>4.927</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3159,10 +3162,10 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46284.26041666666</v>
+        <v>46294.26041666666</v>
       </c>
       <c r="B123">
-        <v>2.981</v>
+        <v>3.088</v>
       </c>
       <c r="C123">
         <v>0</v>
@@ -3176,10 +3179,10 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46284.27083333334</v>
+        <v>46294.27083333334</v>
       </c>
       <c r="B124">
-        <v>7.127</v>
+        <v>14.483</v>
       </c>
       <c r="C124">
         <v>0</v>
@@ -3193,13 +3196,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46284.28125</v>
+        <v>46294.28125</v>
       </c>
       <c r="B125">
-        <v>0</v>
+        <v>7.149</v>
       </c>
       <c r="C125">
-        <v>0.694</v>
+        <v>0</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3210,10 +3213,10 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46284.29166666666</v>
+        <v>46294.29166666666</v>
       </c>
       <c r="B126">
-        <v>15.682</v>
+        <v>0.643</v>
       </c>
       <c r="C126">
         <v>0</v>
@@ -3227,10 +3230,10 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46284.30208333334</v>
+        <v>46294.30208333334</v>
       </c>
       <c r="B127">
-        <v>31.555</v>
+        <v>2.957</v>
       </c>
       <c r="C127">
         <v>0</v>
@@ -3244,10 +3247,10 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46284.3125</v>
+        <v>46294.3125</v>
       </c>
       <c r="B128">
-        <v>12.208</v>
+        <v>2.305</v>
       </c>
       <c r="C128">
         <v>0</v>
@@ -3261,13 +3264,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46284.32291666666</v>
+        <v>46294.32291666666</v>
       </c>
       <c r="B129">
-        <v>4.815</v>
+        <v>0</v>
       </c>
       <c r="C129">
-        <v>0</v>
+        <v>19.333</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3278,13 +3281,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46284.33333333334</v>
+        <v>46294.33333333334</v>
       </c>
       <c r="B130">
-        <v>27.897</v>
+        <v>0</v>
       </c>
       <c r="C130">
-        <v>0</v>
+        <v>19.776</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3295,13 +3298,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46284.34375</v>
+        <v>46294.34375</v>
       </c>
       <c r="B131">
-        <v>20.017</v>
+        <v>0</v>
       </c>
       <c r="C131">
-        <v>0</v>
+        <v>27.251</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3312,13 +3315,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46284.35416666666</v>
+        <v>46294.35416666666</v>
       </c>
       <c r="B132">
-        <v>17.934</v>
+        <v>0</v>
       </c>
       <c r="C132">
-        <v>0</v>
+        <v>9.718999999999999</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3329,13 +3332,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46284.36458333334</v>
+        <v>46294.36458333334</v>
       </c>
       <c r="B133">
-        <v>5.106</v>
+        <v>0</v>
       </c>
       <c r="C133">
-        <v>0</v>
+        <v>49.831</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3346,13 +3349,13 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46284.375</v>
+        <v>46294.375</v>
       </c>
       <c r="B134">
         <v>0</v>
       </c>
       <c r="C134">
-        <v>10.875</v>
+        <v>20.582</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3363,13 +3366,13 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46284.38541666666</v>
+        <v>46294.38541666666</v>
       </c>
       <c r="B135">
-        <v>4.207</v>
+        <v>0</v>
       </c>
       <c r="C135">
-        <v>0</v>
+        <v>2.271</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3380,13 +3383,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46284.39583333334</v>
+        <v>46294.39583333334</v>
       </c>
       <c r="B136">
-        <v>1.976</v>
+        <v>0</v>
       </c>
       <c r="C136">
-        <v>0</v>
+        <v>6.438</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3397,13 +3400,13 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46284.40625</v>
+        <v>46294.40625</v>
       </c>
       <c r="B137">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="C137">
-        <v>0</v>
+        <v>61.842</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3414,13 +3417,13 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46284.41666666666</v>
+        <v>46294.41666666666</v>
       </c>
       <c r="B138">
         <v>0</v>
       </c>
       <c r="C138">
-        <v>14.199</v>
+        <v>31.1</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3431,13 +3434,13 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46284.42708333334</v>
+        <v>46294.42708333334</v>
       </c>
       <c r="B139">
         <v>0</v>
       </c>
       <c r="C139">
-        <v>5.445</v>
+        <v>27.518</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3448,13 +3451,13 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46284.4375</v>
+        <v>46294.4375</v>
       </c>
       <c r="B140">
-        <v>1.241</v>
+        <v>0</v>
       </c>
       <c r="C140">
-        <v>0</v>
+        <v>82.691</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3465,13 +3468,13 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46284.44791666666</v>
+        <v>46294.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
       </c>
       <c r="C141">
-        <v>2.082</v>
+        <v>16.543</v>
       </c>
       <c r="D141">
         <v>44</v>
@@ -3482,13 +3485,13 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46284.45833333334</v>
+        <v>46294.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
       </c>
       <c r="C142">
-        <v>3.554</v>
+        <v>11.256</v>
       </c>
       <c r="D142">
         <v>45</v>
@@ -3499,13 +3502,13 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46284.46875</v>
+        <v>46294.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
       </c>
       <c r="C143">
-        <v>2.677</v>
+        <v>18.409</v>
       </c>
       <c r="D143">
         <v>46</v>
@@ -3516,13 +3519,13 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46284.47916666666</v>
+        <v>46294.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
       </c>
       <c r="C144">
-        <v>8.563000000000001</v>
+        <v>52.001</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -3533,13 +3536,13 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46284.48958333334</v>
+        <v>46294.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
       </c>
       <c r="C145">
-        <v>3.231</v>
+        <v>51.361</v>
       </c>
       <c r="D145">
         <v>48</v>
@@ -3550,13 +3553,13 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46284.5</v>
+        <v>46294.5</v>
       </c>
       <c r="B146">
         <v>0</v>
       </c>
       <c r="C146">
-        <v>2.925</v>
+        <v>44.375</v>
       </c>
       <c r="D146">
         <v>49</v>
@@ -3567,13 +3570,13 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46284.51041666666</v>
+        <v>46294.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
       </c>
       <c r="C147">
-        <v>20.894</v>
+        <v>6.692</v>
       </c>
       <c r="D147">
         <v>50</v>
@@ -3584,13 +3587,13 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46284.52083333334</v>
+        <v>46294.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
       </c>
       <c r="C148">
-        <v>11.691</v>
+        <v>35.626</v>
       </c>
       <c r="D148">
         <v>51</v>
@@ -3601,10 +3604,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46284.53125</v>
+        <v>46294.53125</v>
       </c>
       <c r="B149">
-        <v>7.313</v>
+        <v>8.968999999999999</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -3618,13 +3621,13 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46284.54166666666</v>
+        <v>46294.54166666666</v>
       </c>
       <c r="B150">
-        <v>8.191000000000001</v>
+        <v>0</v>
       </c>
       <c r="C150">
-        <v>0</v>
+        <v>0.756</v>
       </c>
       <c r="D150">
         <v>53</v>
@@ -3635,13 +3638,13 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46284.55208333334</v>
+        <v>46294.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
       </c>
       <c r="C151">
-        <v>2.682</v>
+        <v>22.581</v>
       </c>
       <c r="D151">
         <v>54</v>
@@ -3652,13 +3655,13 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46284.5625</v>
+        <v>46294.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
       </c>
       <c r="C152">
-        <v>21.919</v>
+        <v>47.991</v>
       </c>
       <c r="D152">
         <v>55</v>
@@ -3669,13 +3672,13 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46284.57291666666</v>
+        <v>46294.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
       </c>
       <c r="C153">
-        <v>21.724</v>
+        <v>27.202</v>
       </c>
       <c r="D153">
         <v>56</v>
@@ -3686,13 +3689,13 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46284.58333333334</v>
+        <v>46294.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
       </c>
       <c r="C154">
-        <v>4.251</v>
+        <v>20.549</v>
       </c>
       <c r="D154">
         <v>57</v>
@@ -3703,13 +3706,13 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46284.59375</v>
+        <v>46294.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
       </c>
       <c r="C155">
-        <v>21.994</v>
+        <v>20.66</v>
       </c>
       <c r="D155">
         <v>58</v>
@@ -3720,13 +3723,13 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46284.60416666666</v>
+        <v>46294.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
       </c>
       <c r="C156">
-        <v>7.542</v>
+        <v>12.03</v>
       </c>
       <c r="D156">
         <v>59</v>
@@ -3737,13 +3740,13 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46284.61458333334</v>
+        <v>46294.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
       </c>
       <c r="C157">
-        <v>8.116</v>
+        <v>2.753</v>
       </c>
       <c r="D157">
         <v>60</v>
@@ -3754,13 +3757,13 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46284.625</v>
+        <v>46294.625</v>
       </c>
       <c r="B158">
         <v>0</v>
       </c>
       <c r="C158">
-        <v>34.976</v>
+        <v>14.989</v>
       </c>
       <c r="D158">
         <v>61</v>
@@ -3771,13 +3774,13 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46284.63541666666</v>
+        <v>46294.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
       </c>
       <c r="C159">
-        <v>11.294</v>
+        <v>28.564</v>
       </c>
       <c r="D159">
         <v>62</v>
@@ -3788,13 +3791,13 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46284.64583333334</v>
+        <v>46294.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
       </c>
       <c r="C160">
-        <v>27.599</v>
+        <v>34.086</v>
       </c>
       <c r="D160">
         <v>63</v>
@@ -3805,13 +3808,13 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46284.65625</v>
+        <v>46294.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
       </c>
       <c r="C161">
-        <v>44.524</v>
+        <v>9.089</v>
       </c>
       <c r="D161">
         <v>64</v>
@@ -3822,13 +3825,13 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46284.66666666666</v>
+        <v>46294.66666666666</v>
       </c>
       <c r="B162">
-        <v>0</v>
+        <v>37.003</v>
       </c>
       <c r="C162">
-        <v>13.312</v>
+        <v>0</v>
       </c>
       <c r="D162">
         <v>65</v>
@@ -3839,13 +3842,13 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46284.67708333334</v>
+        <v>46294.67708333334</v>
       </c>
       <c r="B163">
-        <v>0</v>
+        <v>25.691</v>
       </c>
       <c r="C163">
-        <v>14.221</v>
+        <v>0</v>
       </c>
       <c r="D163">
         <v>66</v>
@@ -3856,13 +3859,13 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46284.6875</v>
+        <v>46294.6875</v>
       </c>
       <c r="B164">
-        <v>0</v>
+        <v>3.393</v>
       </c>
       <c r="C164">
-        <v>26.87</v>
+        <v>0</v>
       </c>
       <c r="D164">
         <v>67</v>
@@ -3873,10 +3876,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46284.69791666666</v>
+        <v>46294.69791666666</v>
       </c>
       <c r="B165">
-        <v>1.749</v>
+        <v>12.344</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -3890,10 +3893,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46284.70833333334</v>
+        <v>46294.70833333334</v>
       </c>
       <c r="B166">
-        <v>2.814</v>
+        <v>48.067</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -3907,10 +3910,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46284.71875</v>
+        <v>46294.71875</v>
       </c>
       <c r="B167">
-        <v>11.098</v>
+        <v>7.625</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -3924,10 +3927,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46284.72916666666</v>
+        <v>46294.72916666666</v>
       </c>
       <c r="B168">
-        <v>12.228</v>
+        <v>13.88</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -3941,13 +3944,13 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46284.73958333334</v>
+        <v>46294.73958333334</v>
       </c>
       <c r="B169">
-        <v>6.646</v>
+        <v>0</v>
       </c>
       <c r="C169">
-        <v>0</v>
+        <v>10.918</v>
       </c>
       <c r="D169">
         <v>72</v>
@@ -3958,13 +3961,13 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46284.75</v>
+        <v>46294.75</v>
       </c>
       <c r="B170">
-        <v>5.253</v>
+        <v>0</v>
       </c>
       <c r="C170">
-        <v>0</v>
+        <v>44.821</v>
       </c>
       <c r="D170">
         <v>73</v>
@@ -3975,13 +3978,13 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46284.76041666666</v>
+        <v>46294.76041666666</v>
       </c>
       <c r="B171">
-        <v>5.805</v>
+        <v>0</v>
       </c>
       <c r="C171">
-        <v>0</v>
+        <v>20.493</v>
       </c>
       <c r="D171">
         <v>74</v>
@@ -3992,13 +3995,13 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46284.77083333334</v>
+        <v>46294.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
       </c>
       <c r="C172">
-        <v>6.704</v>
+        <v>39.863</v>
       </c>
       <c r="D172">
         <v>75</v>
@@ -4009,13 +4012,13 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46284.78125</v>
+        <v>46294.78125</v>
       </c>
       <c r="B173">
-        <v>3.911</v>
+        <v>0</v>
       </c>
       <c r="C173">
-        <v>0</v>
+        <v>37.749</v>
       </c>
       <c r="D173">
         <v>76</v>
@@ -4026,13 +4029,13 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46284.79166666666</v>
+        <v>46294.79166666666</v>
       </c>
       <c r="B174">
-        <v>2.086</v>
+        <v>0</v>
       </c>
       <c r="C174">
-        <v>0</v>
+        <v>10.802</v>
       </c>
       <c r="D174">
         <v>77</v>
@@ -4043,13 +4046,13 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46284.80208333334</v>
+        <v>46294.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
       </c>
       <c r="C175">
-        <v>11.589</v>
+        <v>31.764</v>
       </c>
       <c r="D175">
         <v>78</v>
@@ -4060,13 +4063,13 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46284.8125</v>
+        <v>46294.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
       </c>
       <c r="C176">
-        <v>20.059</v>
+        <v>34.344</v>
       </c>
       <c r="D176">
         <v>79</v>
@@ -4077,13 +4080,13 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46284.82291666666</v>
+        <v>46294.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
       </c>
       <c r="C177">
-        <v>17.918</v>
+        <v>44.453</v>
       </c>
       <c r="D177">
         <v>80</v>
@@ -4094,13 +4097,13 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46284.83333333334</v>
+        <v>46294.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
       </c>
       <c r="C178">
-        <v>11.062</v>
+        <v>59.814</v>
       </c>
       <c r="D178">
         <v>81</v>
@@ -4111,13 +4114,13 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46284.84375</v>
+        <v>46294.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
       </c>
       <c r="C179">
-        <v>4.498</v>
+        <v>86.893</v>
       </c>
       <c r="D179">
         <v>82</v>
@@ -4128,13 +4131,13 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46284.85416666666</v>
+        <v>46294.85416666666</v>
       </c>
       <c r="B180">
-        <v>1.074</v>
+        <v>0</v>
       </c>
       <c r="C180">
-        <v>0</v>
+        <v>58.984</v>
       </c>
       <c r="D180">
         <v>83</v>
@@ -4145,13 +4148,13 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46284.86458333334</v>
+        <v>46294.86458333334</v>
       </c>
       <c r="B181">
-        <v>2.774</v>
+        <v>0</v>
       </c>
       <c r="C181">
-        <v>0</v>
+        <v>22.102</v>
       </c>
       <c r="D181">
         <v>84</v>
@@ -4162,13 +4165,13 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46284.875</v>
+        <v>46294.875</v>
       </c>
       <c r="B182">
-        <v>0</v>
+        <v>5.096</v>
       </c>
       <c r="C182">
-        <v>1.826</v>
+        <v>0</v>
       </c>
       <c r="D182">
         <v>85</v>
@@ -4179,13 +4182,13 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46284.88541666666</v>
+        <v>46294.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
       </c>
       <c r="C183">
-        <v>5.863</v>
+        <v>3.546</v>
       </c>
       <c r="D183">
         <v>86</v>
@@ -4196,13 +4199,13 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46284.89583333334</v>
+        <v>46294.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
       </c>
       <c r="C184">
-        <v>3.687</v>
+        <v>6.07</v>
       </c>
       <c r="D184">
         <v>87</v>
@@ -4213,13 +4216,13 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46284.90625</v>
+        <v>46294.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
       </c>
       <c r="C185">
-        <v>1.524</v>
+        <v>22.177</v>
       </c>
       <c r="D185">
         <v>88</v>
@@ -4230,10 +4233,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46284.91666666666</v>
+        <v>46294.91666666666</v>
       </c>
       <c r="B186">
-        <v>2.257</v>
+        <v>9.994999999999999</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -4247,13 +4250,13 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46284.92708333334</v>
+        <v>46294.92708333334</v>
       </c>
       <c r="B187">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="C187">
-        <v>3.176</v>
+        <v>0</v>
       </c>
       <c r="D187">
         <v>90</v>
@@ -4264,13 +4267,13 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46284.9375</v>
+        <v>46294.9375</v>
       </c>
       <c r="B188">
-        <v>0</v>
+        <v>0.823</v>
       </c>
       <c r="C188">
-        <v>1.393</v>
+        <v>0</v>
       </c>
       <c r="D188">
         <v>91</v>
@@ -4281,13 +4284,13 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46284.94791666666</v>
+        <v>46294.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
       </c>
       <c r="C189">
-        <v>0.8100000000000001</v>
+        <v>11.721</v>
       </c>
       <c r="D189">
         <v>92</v>
@@ -4298,13 +4301,13 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46284.95833333334</v>
+        <v>46294.95833333334</v>
       </c>
       <c r="B190">
-        <v>4.629</v>
+        <v>0</v>
       </c>
       <c r="C190">
-        <v>0</v>
+        <v>20.128</v>
       </c>
       <c r="D190">
         <v>93</v>
@@ -4315,13 +4318,13 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46284.96875</v>
+        <v>46294.96875</v>
       </c>
       <c r="B191">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="C191">
-        <v>0</v>
+        <v>4.331</v>
       </c>
       <c r="D191">
         <v>94</v>
@@ -4332,10 +4335,10 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46284.97916666666</v>
+        <v>46294.97916666666</v>
       </c>
       <c r="B192">
-        <v>8.843</v>
+        <v>13.398</v>
       </c>
       <c r="C192">
         <v>0</v>
@@ -4349,10 +4352,10 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46284.98958333334</v>
+        <v>46294.98958333334</v>
       </c>
       <c r="B193">
-        <v>7.802</v>
+        <v>32.884</v>
       </c>
       <c r="C193">
         <v>0</v>
@@ -4366,13 +4369,13 @@
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="2">
-        <v>46285</v>
+        <v>46295</v>
       </c>
       <c r="B194">
-        <v>0</v>
+        <v>12.005</v>
       </c>
       <c r="C194">
-        <v>4.644</v>
+        <v>0</v>
       </c>
       <c r="D194">
         <v>1</v>
@@ -4383,13 +4386,13 @@
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="2">
-        <v>46285.01041666666</v>
+        <v>46295.01041666666</v>
       </c>
       <c r="B195">
-        <v>8.010999999999999</v>
+        <v>0</v>
       </c>
       <c r="C195">
-        <v>0</v>
+        <v>4.922</v>
       </c>
       <c r="D195">
         <v>2</v>
@@ -4400,13 +4403,13 @@
     </row>
     <row r="196" spans="1:5">
       <c r="A196" s="2">
-        <v>46285.02083333334</v>
+        <v>46295.02083333334</v>
       </c>
       <c r="B196">
-        <v>14.901</v>
+        <v>0</v>
       </c>
       <c r="C196">
-        <v>0</v>
+        <v>4.566</v>
       </c>
       <c r="D196">
         <v>3</v>
@@ -4417,13 +4420,13 @@
     </row>
     <row r="197" spans="1:5">
       <c r="A197" s="2">
-        <v>46285.03125</v>
+        <v>46295.03125</v>
       </c>
       <c r="B197">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="C197">
-        <v>0</v>
+        <v>1.837</v>
       </c>
       <c r="D197">
         <v>4</v>
@@ -4434,10 +4437,10 @@
     </row>
     <row r="198" spans="1:5">
       <c r="A198" s="2">
-        <v>46285.04166666666</v>
+        <v>46295.04166666666</v>
       </c>
       <c r="B198">
-        <v>11.151</v>
+        <v>9.066000000000001</v>
       </c>
       <c r="C198">
         <v>0</v>
@@ -4451,10 +4454,10 @@
     </row>
     <row r="199" spans="1:5">
       <c r="A199" s="2">
-        <v>46285.05208333334</v>
+        <v>46295.05208333334</v>
       </c>
       <c r="B199">
-        <v>2.933</v>
+        <v>2.044</v>
       </c>
       <c r="C199">
         <v>0</v>
@@ -4468,10 +4471,10 @@
     </row>
     <row r="200" spans="1:5">
       <c r="A200" s="2">
-        <v>46285.0625</v>
+        <v>46295.0625</v>
       </c>
       <c r="B200">
-        <v>12.009</v>
+        <v>17.834</v>
       </c>
       <c r="C200">
         <v>0</v>
@@ -4485,10 +4488,10 @@
     </row>
     <row r="201" spans="1:5">
       <c r="A201" s="2">
-        <v>46285.07291666666</v>
+        <v>46295.07291666666</v>
       </c>
       <c r="B201">
-        <v>16.324</v>
+        <v>23.524</v>
       </c>
       <c r="C201">
         <v>0</v>
@@ -4502,10 +4505,10 @@
     </row>
     <row r="202" spans="1:5">
       <c r="A202" s="2">
-        <v>46285.08333333334</v>
+        <v>46295.08333333334</v>
       </c>
       <c r="B202">
-        <v>16.389</v>
+        <v>5.653</v>
       </c>
       <c r="C202">
         <v>0</v>
@@ -4519,10 +4522,10 @@
     </row>
     <row r="203" spans="1:5">
       <c r="A203" s="2">
-        <v>46285.09375</v>
+        <v>46295.09375</v>
       </c>
       <c r="B203">
-        <v>17.187</v>
+        <v>9.419</v>
       </c>
       <c r="C203">
         <v>0</v>
@@ -4536,10 +4539,10 @@
     </row>
     <row r="204" spans="1:5">
       <c r="A204" s="2">
-        <v>46285.10416666666</v>
+        <v>46295.10416666666</v>
       </c>
       <c r="B204">
-        <v>3.812</v>
+        <v>35.878</v>
       </c>
       <c r="C204">
         <v>0</v>
@@ -4553,10 +4556,10 @@
     </row>
     <row r="205" spans="1:5">
       <c r="A205" s="2">
-        <v>46285.11458333334</v>
+        <v>46295.11458333334</v>
       </c>
       <c r="B205">
-        <v>3.125</v>
+        <v>18.523</v>
       </c>
       <c r="C205">
         <v>0</v>
@@ -4570,13 +4573,13 @@
     </row>
     <row r="206" spans="1:5">
       <c r="A206" s="2">
-        <v>46285.125</v>
+        <v>46295.125</v>
       </c>
       <c r="B206">
-        <v>0</v>
+        <v>13.924</v>
       </c>
       <c r="C206">
-        <v>5.607</v>
+        <v>0</v>
       </c>
       <c r="D206">
         <v>13</v>
@@ -4587,13 +4590,13 @@
     </row>
     <row r="207" spans="1:5">
       <c r="A207" s="2">
-        <v>46285.13541666666</v>
+        <v>46295.13541666666</v>
       </c>
       <c r="B207">
-        <v>0</v>
+        <v>20.929</v>
       </c>
       <c r="C207">
-        <v>9.601000000000001</v>
+        <v>0</v>
       </c>
       <c r="D207">
         <v>14</v>
@@ -4604,13 +4607,13 @@
     </row>
     <row r="208" spans="1:5">
       <c r="A208" s="2">
-        <v>46285.14583333334</v>
+        <v>46295.14583333334</v>
       </c>
       <c r="B208">
-        <v>0</v>
+        <v>27.199</v>
       </c>
       <c r="C208">
-        <v>21.253</v>
+        <v>0</v>
       </c>
       <c r="D208">
         <v>15</v>
@@ -4621,13 +4624,13 @@
     </row>
     <row r="209" spans="1:5">
       <c r="A209" s="2">
-        <v>46285.15625</v>
+        <v>46295.15625</v>
       </c>
       <c r="B209">
-        <v>0</v>
+        <v>35.969</v>
       </c>
       <c r="C209">
-        <v>13.347</v>
+        <v>0</v>
       </c>
       <c r="D209">
         <v>16</v>
@@ -4638,13 +4641,13 @@
     </row>
     <row r="210" spans="1:5">
       <c r="A210" s="2">
-        <v>46285.16666666666</v>
+        <v>46295.16666666666</v>
       </c>
       <c r="B210">
-        <v>0</v>
+        <v>16.028</v>
       </c>
       <c r="C210">
-        <v>22.021</v>
+        <v>0</v>
       </c>
       <c r="D210">
         <v>17</v>
@@ -4655,13 +4658,13 @@
     </row>
     <row r="211" spans="1:5">
       <c r="A211" s="2">
-        <v>46285.17708333334</v>
+        <v>46295.17708333334</v>
       </c>
       <c r="B211">
-        <v>0</v>
+        <v>10.285</v>
       </c>
       <c r="C211">
-        <v>21.721</v>
+        <v>0</v>
       </c>
       <c r="D211">
         <v>18</v>
@@ -4672,13 +4675,13 @@
     </row>
     <row r="212" spans="1:5">
       <c r="A212" s="2">
-        <v>46285.1875</v>
+        <v>46295.1875</v>
       </c>
       <c r="B212">
-        <v>0</v>
+        <v>3.602</v>
       </c>
       <c r="C212">
-        <v>10.623</v>
+        <v>0</v>
       </c>
       <c r="D212">
         <v>19</v>
@@ -4689,13 +4692,13 @@
     </row>
     <row r="213" spans="1:5">
       <c r="A213" s="2">
-        <v>46285.19791666666</v>
+        <v>46295.19791666666</v>
       </c>
       <c r="B213">
-        <v>0</v>
+        <v>3.992</v>
       </c>
       <c r="C213">
-        <v>12.304</v>
+        <v>0</v>
       </c>
       <c r="D213">
         <v>20</v>
@@ -4706,13 +4709,13 @@
     </row>
     <row r="214" spans="1:5">
       <c r="A214" s="2">
-        <v>46285.20833333334</v>
+        <v>46295.20833333334</v>
       </c>
       <c r="B214">
-        <v>1.932</v>
+        <v>0</v>
       </c>
       <c r="C214">
-        <v>0</v>
+        <v>20.169</v>
       </c>
       <c r="D214">
         <v>21</v>
@@ -4723,13 +4726,13 @@
     </row>
     <row r="215" spans="1:5">
       <c r="A215" s="2">
-        <v>46285.21875</v>
+        <v>46295.21875</v>
       </c>
       <c r="B215">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="C215">
-        <v>0</v>
+        <v>13.475</v>
       </c>
       <c r="D215">
         <v>22</v>
@@ -4740,10 +4743,10 @@
     </row>
     <row r="216" spans="1:5">
       <c r="A216" s="2">
-        <v>46285.22916666666</v>
+        <v>46295.22916666666</v>
       </c>
       <c r="B216">
-        <v>12.394</v>
+        <v>1.793</v>
       </c>
       <c r="C216">
         <v>0</v>
@@ -4757,10 +4760,10 @@
     </row>
     <row r="217" spans="1:5">
       <c r="A217" s="2">
-        <v>46285.23958333334</v>
+        <v>46295.23958333334</v>
       </c>
       <c r="B217">
-        <v>9.949999999999999</v>
+        <v>9.552</v>
       </c>
       <c r="C217">
         <v>0</v>
@@ -4774,13 +4777,13 @@
     </row>
     <row r="218" spans="1:5">
       <c r="A218" s="2">
-        <v>46285.25</v>
+        <v>46295.25</v>
       </c>
       <c r="B218">
-        <v>5.509</v>
+        <v>0</v>
       </c>
       <c r="C218">
-        <v>0</v>
+        <v>6.995</v>
       </c>
       <c r="D218">
         <v>25</v>
@@ -4791,10 +4794,10 @@
     </row>
     <row r="219" spans="1:5">
       <c r="A219" s="2">
-        <v>46285.26041666666</v>
+        <v>46295.26041666666</v>
       </c>
       <c r="B219">
-        <v>1.103</v>
+        <v>9.089</v>
       </c>
       <c r="C219">
         <v>0</v>
@@ -4808,13 +4811,13 @@
     </row>
     <row r="220" spans="1:5">
       <c r="A220" s="2">
-        <v>46285.27083333334</v>
+        <v>46295.27083333334</v>
       </c>
       <c r="B220">
-        <v>0</v>
+        <v>29.44</v>
       </c>
       <c r="C220">
-        <v>2.708</v>
+        <v>0</v>
       </c>
       <c r="D220">
         <v>27</v>
@@ -4825,13 +4828,13 @@
     </row>
     <row r="221" spans="1:5">
       <c r="A221" s="2">
-        <v>46285.28125</v>
+        <v>46295.28125</v>
       </c>
       <c r="B221">
-        <v>0</v>
+        <v>29.456</v>
       </c>
       <c r="C221">
-        <v>33.953</v>
+        <v>0</v>
       </c>
       <c r="D221">
         <v>28</v>
@@ -4842,10 +4845,10 @@
     </row>
     <row r="222" spans="1:5">
       <c r="A222" s="2">
-        <v>46285.29166666666</v>
+        <v>46295.29166666666</v>
       </c>
       <c r="B222">
-        <v>6.28</v>
+        <v>12.376</v>
       </c>
       <c r="C222">
         <v>0</v>
@@ -4859,13 +4862,13 @@
     </row>
     <row r="223" spans="1:5">
       <c r="A223" s="2">
-        <v>46285.30208333334</v>
+        <v>46295.30208333334</v>
       </c>
       <c r="B223">
-        <v>0</v>
+        <v>7.034</v>
       </c>
       <c r="C223">
-        <v>5.341</v>
+        <v>0</v>
       </c>
       <c r="D223">
         <v>30</v>
@@ -4876,13 +4879,13 @@
     </row>
     <row r="224" spans="1:5">
       <c r="A224" s="2">
-        <v>46285.3125</v>
+        <v>46295.3125</v>
       </c>
       <c r="B224">
-        <v>0</v>
+        <v>14.758</v>
       </c>
       <c r="C224">
-        <v>1.771</v>
+        <v>0</v>
       </c>
       <c r="D224">
         <v>31</v>
@@ -4893,13 +4896,13 @@
     </row>
     <row r="225" spans="1:5">
       <c r="A225" s="2">
-        <v>46285.32291666666</v>
+        <v>46295.32291666666</v>
       </c>
       <c r="B225">
-        <v>0</v>
+        <v>10.262</v>
       </c>
       <c r="C225">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="D225">
         <v>32</v>
@@ -4910,10 +4913,10 @@
     </row>
     <row r="226" spans="1:5">
       <c r="A226" s="2">
-        <v>46285.33333333334</v>
+        <v>46295.33333333334</v>
       </c>
       <c r="B226">
-        <v>0.801</v>
+        <v>23.969</v>
       </c>
       <c r="C226">
         <v>0</v>
@@ -4927,10 +4930,10 @@
     </row>
     <row r="227" spans="1:5">
       <c r="A227" s="2">
-        <v>46285.34375</v>
+        <v>46295.34375</v>
       </c>
       <c r="B227">
-        <v>16.142</v>
+        <v>21.047</v>
       </c>
       <c r="C227">
         <v>0</v>
@@ -4944,10 +4947,10 @@
     </row>
     <row r="228" spans="1:5">
       <c r="A228" s="2">
-        <v>46285.35416666666</v>
+        <v>46295.35416666666</v>
       </c>
       <c r="B228">
-        <v>25.537</v>
+        <v>5.191</v>
       </c>
       <c r="C228">
         <v>0</v>
@@ -4961,13 +4964,13 @@
     </row>
     <row r="229" spans="1:5">
       <c r="A229" s="2">
-        <v>46285.36458333334</v>
+        <v>46295.36458333334</v>
       </c>
       <c r="B229">
-        <v>7.372</v>
+        <v>0</v>
       </c>
       <c r="C229">
-        <v>0</v>
+        <v>12.896</v>
       </c>
       <c r="D229">
         <v>36</v>
@@ -4978,13 +4981,13 @@
     </row>
     <row r="230" spans="1:5">
       <c r="A230" s="2">
-        <v>46285.375</v>
+        <v>46295.375</v>
       </c>
       <c r="B230">
-        <v>0</v>
+        <v>8.518000000000001</v>
       </c>
       <c r="C230">
-        <v>0.448</v>
+        <v>0</v>
       </c>
       <c r="D230">
         <v>37</v>
@@ -4995,19 +4998,36 @@
     </row>
     <row r="231" spans="1:5">
       <c r="A231" s="2">
-        <v>46285.38541666666</v>
+        <v>46295.38541666666</v>
       </c>
       <c r="B231">
-        <v>12.991</v>
+        <v>0</v>
       </c>
       <c r="C231">
-        <v>0</v>
+        <v>15.181</v>
       </c>
       <c r="D231">
         <v>38</v>
       </c>
       <c r="E231" t="s">
         <v>234</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5">
+      <c r="A232" s="2">
+        <v>46295.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>0</v>
+      </c>
+      <c r="C232">
+        <v>14.198</v>
+      </c>
+      <c r="D232">
+        <v>39</v>
+      </c>
+      <c r="E232" t="s">
+        <v>235</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Unintended_Deviation.xlsx
+++ b/data_fetching/Entsoe/Unintended_Deviation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="230">
   <si>
     <t>Timestamp</t>
   </si>
@@ -31,697 +31,679 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>28.09.20261</t>
-  </si>
-  <si>
-    <t>28.09.20262</t>
-  </si>
-  <si>
-    <t>28.09.20263</t>
-  </si>
-  <si>
-    <t>28.09.20264</t>
-  </si>
-  <si>
-    <t>28.09.20265</t>
-  </si>
-  <si>
-    <t>28.09.20266</t>
-  </si>
-  <si>
-    <t>28.09.20267</t>
-  </si>
-  <si>
-    <t>28.09.20268</t>
-  </si>
-  <si>
-    <t>28.09.20269</t>
-  </si>
-  <si>
-    <t>28.09.202610</t>
-  </si>
-  <si>
-    <t>28.09.202611</t>
-  </si>
-  <si>
-    <t>28.09.202612</t>
-  </si>
-  <si>
-    <t>28.09.202613</t>
-  </si>
-  <si>
-    <t>28.09.202614</t>
-  </si>
-  <si>
-    <t>28.09.202615</t>
-  </si>
-  <si>
-    <t>28.09.202616</t>
-  </si>
-  <si>
-    <t>28.09.202617</t>
-  </si>
-  <si>
-    <t>28.09.202618</t>
-  </si>
-  <si>
-    <t>28.09.202619</t>
-  </si>
-  <si>
-    <t>28.09.202620</t>
-  </si>
-  <si>
-    <t>28.09.202621</t>
-  </si>
-  <si>
-    <t>28.09.202622</t>
-  </si>
-  <si>
-    <t>28.09.202623</t>
-  </si>
-  <si>
-    <t>28.09.202624</t>
-  </si>
-  <si>
-    <t>28.09.202625</t>
-  </si>
-  <si>
-    <t>28.09.202626</t>
-  </si>
-  <si>
-    <t>28.09.202627</t>
-  </si>
-  <si>
-    <t>28.09.202628</t>
-  </si>
-  <si>
-    <t>28.09.202629</t>
-  </si>
-  <si>
-    <t>28.09.202630</t>
-  </si>
-  <si>
-    <t>28.09.202631</t>
-  </si>
-  <si>
-    <t>28.09.202632</t>
-  </si>
-  <si>
-    <t>28.09.202633</t>
-  </si>
-  <si>
-    <t>28.09.202634</t>
-  </si>
-  <si>
-    <t>28.09.202635</t>
-  </si>
-  <si>
-    <t>28.09.202636</t>
-  </si>
-  <si>
-    <t>28.09.202637</t>
-  </si>
-  <si>
-    <t>28.09.202638</t>
-  </si>
-  <si>
-    <t>28.09.202639</t>
-  </si>
-  <si>
-    <t>28.09.202640</t>
-  </si>
-  <si>
-    <t>28.09.202641</t>
-  </si>
-  <si>
-    <t>28.09.202642</t>
-  </si>
-  <si>
-    <t>28.09.202643</t>
-  </si>
-  <si>
-    <t>28.09.202644</t>
-  </si>
-  <si>
-    <t>28.09.202645</t>
-  </si>
-  <si>
-    <t>28.09.202646</t>
-  </si>
-  <si>
-    <t>28.09.202647</t>
-  </si>
-  <si>
-    <t>28.09.202648</t>
-  </si>
-  <si>
-    <t>28.09.202649</t>
-  </si>
-  <si>
-    <t>28.09.202650</t>
-  </si>
-  <si>
-    <t>28.09.202651</t>
-  </si>
-  <si>
-    <t>28.09.202652</t>
-  </si>
-  <si>
-    <t>28.09.202653</t>
-  </si>
-  <si>
-    <t>28.09.202654</t>
-  </si>
-  <si>
-    <t>28.09.202655</t>
-  </si>
-  <si>
-    <t>28.09.202656</t>
-  </si>
-  <si>
-    <t>28.09.202657</t>
-  </si>
-  <si>
-    <t>28.09.202658</t>
-  </si>
-  <si>
-    <t>28.09.202659</t>
-  </si>
-  <si>
-    <t>28.09.202660</t>
-  </si>
-  <si>
-    <t>28.09.202661</t>
-  </si>
-  <si>
-    <t>28.09.202662</t>
-  </si>
-  <si>
-    <t>28.09.202663</t>
-  </si>
-  <si>
-    <t>28.09.202664</t>
-  </si>
-  <si>
-    <t>28.09.202665</t>
-  </si>
-  <si>
-    <t>28.09.202666</t>
-  </si>
-  <si>
-    <t>28.09.202667</t>
-  </si>
-  <si>
-    <t>28.09.202668</t>
-  </si>
-  <si>
-    <t>28.09.202669</t>
-  </si>
-  <si>
-    <t>28.09.202670</t>
-  </si>
-  <si>
-    <t>28.09.202671</t>
-  </si>
-  <si>
-    <t>28.09.202672</t>
-  </si>
-  <si>
-    <t>28.09.202673</t>
-  </si>
-  <si>
-    <t>28.09.202674</t>
-  </si>
-  <si>
-    <t>28.09.202675</t>
-  </si>
-  <si>
-    <t>28.09.202676</t>
-  </si>
-  <si>
-    <t>28.09.202677</t>
-  </si>
-  <si>
-    <t>28.09.202678</t>
-  </si>
-  <si>
-    <t>28.09.202679</t>
-  </si>
-  <si>
-    <t>28.09.202680</t>
-  </si>
-  <si>
-    <t>28.09.202681</t>
-  </si>
-  <si>
-    <t>28.09.202682</t>
-  </si>
-  <si>
-    <t>28.09.202683</t>
-  </si>
-  <si>
-    <t>28.09.202684</t>
-  </si>
-  <si>
-    <t>28.09.202685</t>
-  </si>
-  <si>
-    <t>28.09.202686</t>
-  </si>
-  <si>
-    <t>28.09.202687</t>
-  </si>
-  <si>
-    <t>28.09.202688</t>
-  </si>
-  <si>
-    <t>28.09.202689</t>
-  </si>
-  <si>
-    <t>28.09.202690</t>
-  </si>
-  <si>
-    <t>28.09.202691</t>
-  </si>
-  <si>
-    <t>28.09.202692</t>
-  </si>
-  <si>
-    <t>28.09.202693</t>
-  </si>
-  <si>
-    <t>28.09.202694</t>
-  </si>
-  <si>
-    <t>28.09.202695</t>
-  </si>
-  <si>
-    <t>28.09.202696</t>
-  </si>
-  <si>
-    <t>29.09.20261</t>
-  </si>
-  <si>
-    <t>29.09.20262</t>
-  </si>
-  <si>
-    <t>29.09.20263</t>
-  </si>
-  <si>
-    <t>29.09.20264</t>
-  </si>
-  <si>
-    <t>29.09.20265</t>
-  </si>
-  <si>
-    <t>29.09.20266</t>
-  </si>
-  <si>
-    <t>29.09.20267</t>
-  </si>
-  <si>
-    <t>29.09.20268</t>
-  </si>
-  <si>
-    <t>29.09.20269</t>
-  </si>
-  <si>
-    <t>29.09.202610</t>
-  </si>
-  <si>
-    <t>29.09.202611</t>
-  </si>
-  <si>
-    <t>29.09.202612</t>
-  </si>
-  <si>
-    <t>29.09.202613</t>
-  </si>
-  <si>
-    <t>29.09.202614</t>
-  </si>
-  <si>
-    <t>29.09.202615</t>
-  </si>
-  <si>
-    <t>29.09.202616</t>
-  </si>
-  <si>
-    <t>29.09.202617</t>
-  </si>
-  <si>
-    <t>29.09.202618</t>
-  </si>
-  <si>
-    <t>29.09.202619</t>
-  </si>
-  <si>
-    <t>29.09.202620</t>
-  </si>
-  <si>
-    <t>29.09.202621</t>
-  </si>
-  <si>
-    <t>29.09.202622</t>
-  </si>
-  <si>
-    <t>29.09.202623</t>
-  </si>
-  <si>
-    <t>29.09.202624</t>
-  </si>
-  <si>
-    <t>29.09.202625</t>
-  </si>
-  <si>
-    <t>29.09.202626</t>
-  </si>
-  <si>
-    <t>29.09.202627</t>
-  </si>
-  <si>
-    <t>29.09.202628</t>
-  </si>
-  <si>
-    <t>29.09.202629</t>
-  </si>
-  <si>
-    <t>29.09.202630</t>
-  </si>
-  <si>
-    <t>29.09.202631</t>
-  </si>
-  <si>
-    <t>29.09.202632</t>
-  </si>
-  <si>
-    <t>29.09.202633</t>
-  </si>
-  <si>
-    <t>29.09.202634</t>
-  </si>
-  <si>
-    <t>29.09.202635</t>
-  </si>
-  <si>
-    <t>29.09.202636</t>
-  </si>
-  <si>
-    <t>29.09.202637</t>
-  </si>
-  <si>
-    <t>29.09.202638</t>
-  </si>
-  <si>
-    <t>29.09.202639</t>
-  </si>
-  <si>
-    <t>29.09.202640</t>
-  </si>
-  <si>
-    <t>29.09.202641</t>
-  </si>
-  <si>
-    <t>29.09.202642</t>
-  </si>
-  <si>
-    <t>29.09.202643</t>
-  </si>
-  <si>
-    <t>29.09.202644</t>
-  </si>
-  <si>
-    <t>29.09.202645</t>
-  </si>
-  <si>
-    <t>29.09.202646</t>
-  </si>
-  <si>
-    <t>29.09.202647</t>
-  </si>
-  <si>
-    <t>29.09.202648</t>
-  </si>
-  <si>
-    <t>29.09.202649</t>
-  </si>
-  <si>
-    <t>29.09.202650</t>
-  </si>
-  <si>
-    <t>29.09.202651</t>
-  </si>
-  <si>
-    <t>29.09.202652</t>
-  </si>
-  <si>
-    <t>29.09.202653</t>
-  </si>
-  <si>
-    <t>29.09.202654</t>
-  </si>
-  <si>
-    <t>29.09.202655</t>
-  </si>
-  <si>
-    <t>29.09.202656</t>
-  </si>
-  <si>
-    <t>29.09.202657</t>
-  </si>
-  <si>
-    <t>29.09.202658</t>
-  </si>
-  <si>
-    <t>29.09.202659</t>
-  </si>
-  <si>
-    <t>29.09.202660</t>
-  </si>
-  <si>
-    <t>29.09.202661</t>
-  </si>
-  <si>
-    <t>29.09.202662</t>
-  </si>
-  <si>
-    <t>29.09.202663</t>
-  </si>
-  <si>
-    <t>29.09.202664</t>
-  </si>
-  <si>
-    <t>29.09.202665</t>
-  </si>
-  <si>
-    <t>29.09.202666</t>
-  </si>
-  <si>
-    <t>29.09.202667</t>
-  </si>
-  <si>
-    <t>29.09.202668</t>
-  </si>
-  <si>
-    <t>29.09.202669</t>
-  </si>
-  <si>
-    <t>29.09.202670</t>
-  </si>
-  <si>
-    <t>29.09.202671</t>
-  </si>
-  <si>
-    <t>29.09.202672</t>
-  </si>
-  <si>
-    <t>29.09.202673</t>
-  </si>
-  <si>
-    <t>29.09.202674</t>
-  </si>
-  <si>
-    <t>29.09.202675</t>
-  </si>
-  <si>
-    <t>29.09.202676</t>
-  </si>
-  <si>
-    <t>29.09.202677</t>
-  </si>
-  <si>
-    <t>29.09.202678</t>
-  </si>
-  <si>
-    <t>29.09.202679</t>
-  </si>
-  <si>
-    <t>29.09.202680</t>
-  </si>
-  <si>
-    <t>29.09.202681</t>
-  </si>
-  <si>
-    <t>29.09.202682</t>
-  </si>
-  <si>
-    <t>29.09.202683</t>
-  </si>
-  <si>
-    <t>29.09.202684</t>
-  </si>
-  <si>
-    <t>29.09.202685</t>
-  </si>
-  <si>
-    <t>29.09.202686</t>
-  </si>
-  <si>
-    <t>29.09.202687</t>
-  </si>
-  <si>
-    <t>29.09.202688</t>
-  </si>
-  <si>
-    <t>29.09.202689</t>
-  </si>
-  <si>
-    <t>29.09.202690</t>
-  </si>
-  <si>
-    <t>29.09.202691</t>
-  </si>
-  <si>
-    <t>29.09.202692</t>
-  </si>
-  <si>
-    <t>29.09.202693</t>
-  </si>
-  <si>
-    <t>29.09.202694</t>
-  </si>
-  <si>
-    <t>29.09.202695</t>
-  </si>
-  <si>
-    <t>29.09.202696</t>
-  </si>
-  <si>
-    <t>30.09.20261</t>
-  </si>
-  <si>
-    <t>30.09.20262</t>
-  </si>
-  <si>
-    <t>30.09.20263</t>
-  </si>
-  <si>
-    <t>30.09.20264</t>
-  </si>
-  <si>
-    <t>30.09.20265</t>
-  </si>
-  <si>
-    <t>30.09.20266</t>
-  </si>
-  <si>
-    <t>30.09.20267</t>
-  </si>
-  <si>
-    <t>30.09.20268</t>
-  </si>
-  <si>
-    <t>30.09.20269</t>
-  </si>
-  <si>
-    <t>30.09.202610</t>
-  </si>
-  <si>
-    <t>30.09.202611</t>
-  </si>
-  <si>
-    <t>30.09.202612</t>
-  </si>
-  <si>
-    <t>30.09.202613</t>
-  </si>
-  <si>
-    <t>30.09.202614</t>
-  </si>
-  <si>
-    <t>30.09.202615</t>
-  </si>
-  <si>
-    <t>30.09.202616</t>
-  </si>
-  <si>
-    <t>30.09.202617</t>
-  </si>
-  <si>
-    <t>30.09.202618</t>
-  </si>
-  <si>
-    <t>30.09.202619</t>
-  </si>
-  <si>
-    <t>30.09.202620</t>
-  </si>
-  <si>
-    <t>30.09.202621</t>
-  </si>
-  <si>
-    <t>30.09.202622</t>
-  </si>
-  <si>
-    <t>30.09.202623</t>
-  </si>
-  <si>
-    <t>30.09.202624</t>
-  </si>
-  <si>
-    <t>30.09.202625</t>
-  </si>
-  <si>
-    <t>30.09.202626</t>
-  </si>
-  <si>
-    <t>30.09.202627</t>
-  </si>
-  <si>
-    <t>30.09.202628</t>
-  </si>
-  <si>
-    <t>30.09.202629</t>
-  </si>
-  <si>
-    <t>30.09.202630</t>
-  </si>
-  <si>
-    <t>30.09.202631</t>
-  </si>
-  <si>
-    <t>30.09.202632</t>
-  </si>
-  <si>
-    <t>30.09.202633</t>
-  </si>
-  <si>
-    <t>30.09.202634</t>
-  </si>
-  <si>
-    <t>30.09.202635</t>
-  </si>
-  <si>
-    <t>30.09.202636</t>
-  </si>
-  <si>
-    <t>30.09.202637</t>
-  </si>
-  <si>
-    <t>30.09.202638</t>
-  </si>
-  <si>
-    <t>30.09.202639</t>
+    <t>01.10.20261</t>
+  </si>
+  <si>
+    <t>01.10.20262</t>
+  </si>
+  <si>
+    <t>01.10.20263</t>
+  </si>
+  <si>
+    <t>01.10.20264</t>
+  </si>
+  <si>
+    <t>01.10.20265</t>
+  </si>
+  <si>
+    <t>01.10.20266</t>
+  </si>
+  <si>
+    <t>01.10.20267</t>
+  </si>
+  <si>
+    <t>01.10.20268</t>
+  </si>
+  <si>
+    <t>01.10.20269</t>
+  </si>
+  <si>
+    <t>01.10.202610</t>
+  </si>
+  <si>
+    <t>01.10.202611</t>
+  </si>
+  <si>
+    <t>01.10.202612</t>
+  </si>
+  <si>
+    <t>01.10.202613</t>
+  </si>
+  <si>
+    <t>01.10.202614</t>
+  </si>
+  <si>
+    <t>01.10.202615</t>
+  </si>
+  <si>
+    <t>01.10.202616</t>
+  </si>
+  <si>
+    <t>01.10.202617</t>
+  </si>
+  <si>
+    <t>01.10.202618</t>
+  </si>
+  <si>
+    <t>01.10.202619</t>
+  </si>
+  <si>
+    <t>01.10.202620</t>
+  </si>
+  <si>
+    <t>01.10.202621</t>
+  </si>
+  <si>
+    <t>01.10.202622</t>
+  </si>
+  <si>
+    <t>01.10.202623</t>
+  </si>
+  <si>
+    <t>01.10.202624</t>
+  </si>
+  <si>
+    <t>01.10.202625</t>
+  </si>
+  <si>
+    <t>01.10.202626</t>
+  </si>
+  <si>
+    <t>01.10.202627</t>
+  </si>
+  <si>
+    <t>01.10.202628</t>
+  </si>
+  <si>
+    <t>01.10.202629</t>
+  </si>
+  <si>
+    <t>01.10.202630</t>
+  </si>
+  <si>
+    <t>01.10.202631</t>
+  </si>
+  <si>
+    <t>01.10.202632</t>
+  </si>
+  <si>
+    <t>01.10.202633</t>
+  </si>
+  <si>
+    <t>01.10.202634</t>
+  </si>
+  <si>
+    <t>01.10.202635</t>
+  </si>
+  <si>
+    <t>01.10.202636</t>
+  </si>
+  <si>
+    <t>01.10.202637</t>
+  </si>
+  <si>
+    <t>01.10.202638</t>
+  </si>
+  <si>
+    <t>01.10.202639</t>
+  </si>
+  <si>
+    <t>01.10.202640</t>
+  </si>
+  <si>
+    <t>01.10.202641</t>
+  </si>
+  <si>
+    <t>01.10.202642</t>
+  </si>
+  <si>
+    <t>01.10.202643</t>
+  </si>
+  <si>
+    <t>01.10.202644</t>
+  </si>
+  <si>
+    <t>01.10.202645</t>
+  </si>
+  <si>
+    <t>01.10.202646</t>
+  </si>
+  <si>
+    <t>01.10.202647</t>
+  </si>
+  <si>
+    <t>01.10.202648</t>
+  </si>
+  <si>
+    <t>01.10.202649</t>
+  </si>
+  <si>
+    <t>01.10.202650</t>
+  </si>
+  <si>
+    <t>01.10.202651</t>
+  </si>
+  <si>
+    <t>01.10.202652</t>
+  </si>
+  <si>
+    <t>01.10.202653</t>
+  </si>
+  <si>
+    <t>01.10.202654</t>
+  </si>
+  <si>
+    <t>01.10.202655</t>
+  </si>
+  <si>
+    <t>01.10.202656</t>
+  </si>
+  <si>
+    <t>01.10.202657</t>
+  </si>
+  <si>
+    <t>01.10.202658</t>
+  </si>
+  <si>
+    <t>01.10.202659</t>
+  </si>
+  <si>
+    <t>01.10.202660</t>
+  </si>
+  <si>
+    <t>01.10.202661</t>
+  </si>
+  <si>
+    <t>01.10.202662</t>
+  </si>
+  <si>
+    <t>01.10.202663</t>
+  </si>
+  <si>
+    <t>01.10.202664</t>
+  </si>
+  <si>
+    <t>01.10.202665</t>
+  </si>
+  <si>
+    <t>01.10.202666</t>
+  </si>
+  <si>
+    <t>01.10.202667</t>
+  </si>
+  <si>
+    <t>01.10.202668</t>
+  </si>
+  <si>
+    <t>01.10.202669</t>
+  </si>
+  <si>
+    <t>01.10.202670</t>
+  </si>
+  <si>
+    <t>01.10.202671</t>
+  </si>
+  <si>
+    <t>01.10.202672</t>
+  </si>
+  <si>
+    <t>01.10.202673</t>
+  </si>
+  <si>
+    <t>01.10.202674</t>
+  </si>
+  <si>
+    <t>01.10.202675</t>
+  </si>
+  <si>
+    <t>01.10.202676</t>
+  </si>
+  <si>
+    <t>01.10.202677</t>
+  </si>
+  <si>
+    <t>01.10.202678</t>
+  </si>
+  <si>
+    <t>01.10.202679</t>
+  </si>
+  <si>
+    <t>01.10.202680</t>
+  </si>
+  <si>
+    <t>01.10.202681</t>
+  </si>
+  <si>
+    <t>01.10.202682</t>
+  </si>
+  <si>
+    <t>01.10.202683</t>
+  </si>
+  <si>
+    <t>01.10.202684</t>
+  </si>
+  <si>
+    <t>01.10.202685</t>
+  </si>
+  <si>
+    <t>01.10.202686</t>
+  </si>
+  <si>
+    <t>01.10.202687</t>
+  </si>
+  <si>
+    <t>01.10.202688</t>
+  </si>
+  <si>
+    <t>01.10.202689</t>
+  </si>
+  <si>
+    <t>01.10.202690</t>
+  </si>
+  <si>
+    <t>01.10.202691</t>
+  </si>
+  <si>
+    <t>01.10.202692</t>
+  </si>
+  <si>
+    <t>01.10.202693</t>
+  </si>
+  <si>
+    <t>01.10.202694</t>
+  </si>
+  <si>
+    <t>01.10.202695</t>
+  </si>
+  <si>
+    <t>01.10.202696</t>
+  </si>
+  <si>
+    <t>02.10.20261</t>
+  </si>
+  <si>
+    <t>02.10.20262</t>
+  </si>
+  <si>
+    <t>02.10.20263</t>
+  </si>
+  <si>
+    <t>02.10.20264</t>
+  </si>
+  <si>
+    <t>02.10.20265</t>
+  </si>
+  <si>
+    <t>02.10.20266</t>
+  </si>
+  <si>
+    <t>02.10.20267</t>
+  </si>
+  <si>
+    <t>02.10.20268</t>
+  </si>
+  <si>
+    <t>02.10.20269</t>
+  </si>
+  <si>
+    <t>02.10.202610</t>
+  </si>
+  <si>
+    <t>02.10.202611</t>
+  </si>
+  <si>
+    <t>02.10.202612</t>
+  </si>
+  <si>
+    <t>02.10.202613</t>
+  </si>
+  <si>
+    <t>02.10.202614</t>
+  </si>
+  <si>
+    <t>02.10.202615</t>
+  </si>
+  <si>
+    <t>02.10.202616</t>
+  </si>
+  <si>
+    <t>02.10.202617</t>
+  </si>
+  <si>
+    <t>02.10.202618</t>
+  </si>
+  <si>
+    <t>02.10.202619</t>
+  </si>
+  <si>
+    <t>02.10.202620</t>
+  </si>
+  <si>
+    <t>02.10.202621</t>
+  </si>
+  <si>
+    <t>02.10.202622</t>
+  </si>
+  <si>
+    <t>02.10.202623</t>
+  </si>
+  <si>
+    <t>02.10.202624</t>
+  </si>
+  <si>
+    <t>02.10.202625</t>
+  </si>
+  <si>
+    <t>02.10.202626</t>
+  </si>
+  <si>
+    <t>02.10.202627</t>
+  </si>
+  <si>
+    <t>02.10.202628</t>
+  </si>
+  <si>
+    <t>02.10.202629</t>
+  </si>
+  <si>
+    <t>02.10.202630</t>
+  </si>
+  <si>
+    <t>02.10.202631</t>
+  </si>
+  <si>
+    <t>02.10.202632</t>
+  </si>
+  <si>
+    <t>02.10.202633</t>
+  </si>
+  <si>
+    <t>02.10.202634</t>
+  </si>
+  <si>
+    <t>02.10.202635</t>
+  </si>
+  <si>
+    <t>02.10.202636</t>
+  </si>
+  <si>
+    <t>02.10.202637</t>
+  </si>
+  <si>
+    <t>02.10.202638</t>
+  </si>
+  <si>
+    <t>02.10.202639</t>
+  </si>
+  <si>
+    <t>02.10.202640</t>
+  </si>
+  <si>
+    <t>02.10.202641</t>
+  </si>
+  <si>
+    <t>02.10.202642</t>
+  </si>
+  <si>
+    <t>02.10.202643</t>
+  </si>
+  <si>
+    <t>02.10.202644</t>
+  </si>
+  <si>
+    <t>02.10.202645</t>
+  </si>
+  <si>
+    <t>02.10.202646</t>
+  </si>
+  <si>
+    <t>02.10.202647</t>
+  </si>
+  <si>
+    <t>02.10.202648</t>
+  </si>
+  <si>
+    <t>02.10.202649</t>
+  </si>
+  <si>
+    <t>02.10.202650</t>
+  </si>
+  <si>
+    <t>02.10.202651</t>
+  </si>
+  <si>
+    <t>02.10.202652</t>
+  </si>
+  <si>
+    <t>02.10.202653</t>
+  </si>
+  <si>
+    <t>02.10.202654</t>
+  </si>
+  <si>
+    <t>02.10.202655</t>
+  </si>
+  <si>
+    <t>02.10.202656</t>
+  </si>
+  <si>
+    <t>02.10.202657</t>
+  </si>
+  <si>
+    <t>02.10.202658</t>
+  </si>
+  <si>
+    <t>02.10.202659</t>
+  </si>
+  <si>
+    <t>02.10.202660</t>
+  </si>
+  <si>
+    <t>02.10.202661</t>
+  </si>
+  <si>
+    <t>02.10.202662</t>
+  </si>
+  <si>
+    <t>02.10.202663</t>
+  </si>
+  <si>
+    <t>02.10.202664</t>
+  </si>
+  <si>
+    <t>02.10.202665</t>
+  </si>
+  <si>
+    <t>02.10.202666</t>
+  </si>
+  <si>
+    <t>02.10.202667</t>
+  </si>
+  <si>
+    <t>02.10.202668</t>
+  </si>
+  <si>
+    <t>02.10.202669</t>
+  </si>
+  <si>
+    <t>02.10.202670</t>
+  </si>
+  <si>
+    <t>02.10.202671</t>
+  </si>
+  <si>
+    <t>02.10.202672</t>
+  </si>
+  <si>
+    <t>02.10.202673</t>
+  </si>
+  <si>
+    <t>02.10.202674</t>
+  </si>
+  <si>
+    <t>02.10.202675</t>
+  </si>
+  <si>
+    <t>02.10.202676</t>
+  </si>
+  <si>
+    <t>02.10.202677</t>
+  </si>
+  <si>
+    <t>02.10.202678</t>
+  </si>
+  <si>
+    <t>02.10.202679</t>
+  </si>
+  <si>
+    <t>02.10.202680</t>
+  </si>
+  <si>
+    <t>02.10.202681</t>
+  </si>
+  <si>
+    <t>02.10.202682</t>
+  </si>
+  <si>
+    <t>02.10.202683</t>
+  </si>
+  <si>
+    <t>02.10.202684</t>
+  </si>
+  <si>
+    <t>02.10.202685</t>
+  </si>
+  <si>
+    <t>02.10.202686</t>
+  </si>
+  <si>
+    <t>02.10.202687</t>
+  </si>
+  <si>
+    <t>02.10.202688</t>
+  </si>
+  <si>
+    <t>02.10.202689</t>
+  </si>
+  <si>
+    <t>02.10.202690</t>
+  </si>
+  <si>
+    <t>02.10.202691</t>
+  </si>
+  <si>
+    <t>02.10.202692</t>
+  </si>
+  <si>
+    <t>02.10.202693</t>
+  </si>
+  <si>
+    <t>02.10.202694</t>
+  </si>
+  <si>
+    <t>02.10.202695</t>
+  </si>
+  <si>
+    <t>02.10.202696</t>
+  </si>
+  <si>
+    <t>03.10.20261</t>
+  </si>
+  <si>
+    <t>03.10.20262</t>
+  </si>
+  <si>
+    <t>03.10.20263</t>
+  </si>
+  <si>
+    <t>03.10.20264</t>
+  </si>
+  <si>
+    <t>03.10.20265</t>
+  </si>
+  <si>
+    <t>03.10.20266</t>
+  </si>
+  <si>
+    <t>03.10.20267</t>
+  </si>
+  <si>
+    <t>03.10.20268</t>
+  </si>
+  <si>
+    <t>03.10.20269</t>
+  </si>
+  <si>
+    <t>03.10.202610</t>
+  </si>
+  <si>
+    <t>03.10.202611</t>
+  </si>
+  <si>
+    <t>03.10.202612</t>
+  </si>
+  <si>
+    <t>03.10.202613</t>
+  </si>
+  <si>
+    <t>03.10.202614</t>
+  </si>
+  <si>
+    <t>03.10.202615</t>
+  </si>
+  <si>
+    <t>03.10.202616</t>
+  </si>
+  <si>
+    <t>03.10.202617</t>
+  </si>
+  <si>
+    <t>03.10.202618</t>
+  </si>
+  <si>
+    <t>03.10.202619</t>
+  </si>
+  <si>
+    <t>03.10.202620</t>
+  </si>
+  <si>
+    <t>03.10.202621</t>
+  </si>
+  <si>
+    <t>03.10.202622</t>
+  </si>
+  <si>
+    <t>03.10.202623</t>
+  </si>
+  <si>
+    <t>03.10.202624</t>
+  </si>
+  <si>
+    <t>03.10.202625</t>
+  </si>
+  <si>
+    <t>03.10.202626</t>
+  </si>
+  <si>
+    <t>03.10.202627</t>
+  </si>
+  <si>
+    <t>03.10.202628</t>
+  </si>
+  <si>
+    <t>03.10.202629</t>
+  </si>
+  <si>
+    <t>03.10.202630</t>
+  </si>
+  <si>
+    <t>03.10.202631</t>
+  </si>
+  <si>
+    <t>03.10.202632</t>
+  </si>
+  <si>
+    <t>03.10.202633</t>
   </si>
 </sst>
 </file>
@@ -1083,7 +1065,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E232"/>
+  <dimension ref="A1:E226"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1105,13 +1087,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46293</v>
+        <v>46296</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>1.798</v>
+        <v>0.714</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1122,10 +1104,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46293.01041666666</v>
+        <v>46296.01041666666</v>
       </c>
       <c r="B3">
-        <v>1.409</v>
+        <v>1.635</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1139,13 +1121,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46293.02083333334</v>
+        <v>46296.02083333334</v>
       </c>
       <c r="B4">
-        <v>0.961</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1156,13 +1138,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46293.03125</v>
+        <v>46296.03125</v>
       </c>
       <c r="B5">
-        <v>10.579</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1.707</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1173,13 +1155,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46293.04166666666</v>
+        <v>46296.04166666666</v>
       </c>
       <c r="B6">
-        <v>13.859</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>1.195</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1190,13 +1172,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46293.05208333334</v>
+        <v>46296.05208333334</v>
       </c>
       <c r="B7">
-        <v>15.555</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>6.476</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -1207,13 +1189,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46293.0625</v>
+        <v>46296.0625</v>
       </c>
       <c r="B8">
-        <v>13.645</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>5.051</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -1224,13 +1206,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46293.07291666666</v>
+        <v>46296.07291666666</v>
       </c>
       <c r="B9">
-        <v>4.526</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>2.482</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -1241,13 +1223,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46293.08333333334</v>
+        <v>46296.08333333334</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>10.891</v>
       </c>
       <c r="C10">
-        <v>3.359</v>
+        <v>0</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -1258,13 +1240,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46293.09375</v>
+        <v>46296.09375</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>8.689</v>
       </c>
       <c r="C11">
-        <v>6.666</v>
+        <v>0</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1275,13 +1257,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46293.10416666666</v>
+        <v>46296.10416666666</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>10.338</v>
       </c>
       <c r="C12">
-        <v>3.275</v>
+        <v>0</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -1292,13 +1274,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46293.11458333334</v>
+        <v>46296.11458333334</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="C13">
-        <v>8.061999999999999</v>
+        <v>0</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -1309,13 +1291,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46293.125</v>
+        <v>46296.125</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>0.899</v>
       </c>
       <c r="C14">
-        <v>28.05</v>
+        <v>0</v>
       </c>
       <c r="D14">
         <v>13</v>
@@ -1326,13 +1308,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46293.13541666666</v>
+        <v>46296.13541666666</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>1.861</v>
       </c>
       <c r="C15">
-        <v>30.802</v>
+        <v>0</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -1343,13 +1325,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46293.14583333334</v>
+        <v>46296.14583333334</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>16.045</v>
       </c>
       <c r="C16">
-        <v>27.358</v>
+        <v>0</v>
       </c>
       <c r="D16">
         <v>15</v>
@@ -1360,13 +1342,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46293.15625</v>
+        <v>46296.15625</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>6.257</v>
       </c>
       <c r="C17">
-        <v>38.678</v>
+        <v>0</v>
       </c>
       <c r="D17">
         <v>16</v>
@@ -1377,13 +1359,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46293.16666666666</v>
+        <v>46296.16666666666</v>
       </c>
       <c r="B18">
         <v>0</v>
       </c>
       <c r="C18">
-        <v>50.667</v>
+        <v>3.568</v>
       </c>
       <c r="D18">
         <v>17</v>
@@ -1394,13 +1376,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46293.17708333334</v>
+        <v>46296.17708333334</v>
       </c>
       <c r="B19">
-        <v>3.065</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>8.092000000000001</v>
       </c>
       <c r="D19">
         <v>18</v>
@@ -1411,13 +1393,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46293.1875</v>
+        <v>46296.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
       </c>
       <c r="C20">
-        <v>6.456</v>
+        <v>6.285</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1428,13 +1410,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46293.19791666666</v>
+        <v>46296.19791666666</v>
       </c>
       <c r="B21">
-        <v>2.666</v>
+        <v>0</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>20.104</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1445,13 +1427,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46293.20833333334</v>
+        <v>46296.20833333334</v>
       </c>
       <c r="B22">
         <v>0</v>
       </c>
       <c r="C22">
-        <v>10.816</v>
+        <v>29.654</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1462,13 +1444,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46293.21875</v>
+        <v>46296.21875</v>
       </c>
       <c r="B23">
-        <v>6.844</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>13.461</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1479,13 +1461,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46293.22916666666</v>
+        <v>46296.22916666666</v>
       </c>
       <c r="B24">
-        <v>6.292</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>11.109</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1496,13 +1478,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46293.23958333334</v>
+        <v>46296.23958333334</v>
       </c>
       <c r="B25">
-        <v>0.131</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>17.845</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1513,13 +1495,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46293.25</v>
+        <v>46296.25</v>
       </c>
       <c r="B26">
         <v>0</v>
       </c>
       <c r="C26">
-        <v>3.254</v>
+        <v>43.79</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1530,13 +1512,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46293.26041666666</v>
+        <v>46296.26041666666</v>
       </c>
       <c r="B27">
         <v>0</v>
       </c>
       <c r="C27">
-        <v>4.113</v>
+        <v>16.522</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1547,13 +1529,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46293.27083333334</v>
+        <v>46296.27083333334</v>
       </c>
       <c r="B28">
-        <v>0.398</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>32.223</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1564,13 +1546,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46293.28125</v>
+        <v>46296.28125</v>
       </c>
       <c r="B29">
         <v>0</v>
       </c>
       <c r="C29">
-        <v>15.674</v>
+        <v>41.228</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1581,13 +1563,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46293.29166666666</v>
+        <v>46296.29166666666</v>
       </c>
       <c r="B30">
         <v>0</v>
       </c>
       <c r="C30">
-        <v>9.18</v>
+        <v>18.649</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1598,13 +1580,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46293.30208333334</v>
+        <v>46296.30208333334</v>
       </c>
       <c r="B31">
         <v>0</v>
       </c>
       <c r="C31">
-        <v>15.029</v>
+        <v>20.509</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1615,13 +1597,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46293.3125</v>
+        <v>46296.3125</v>
       </c>
       <c r="B32">
         <v>0</v>
       </c>
       <c r="C32">
-        <v>33.922</v>
+        <v>24.979</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1632,13 +1614,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46293.32291666666</v>
+        <v>46296.32291666666</v>
       </c>
       <c r="B33">
         <v>0</v>
       </c>
       <c r="C33">
-        <v>84.81100000000001</v>
+        <v>59.945</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1649,13 +1631,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46293.33333333334</v>
+        <v>46296.33333333334</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>2.811</v>
       </c>
       <c r="C34">
-        <v>63.084</v>
+        <v>0</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1666,13 +1648,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46293.34375</v>
+        <v>46296.34375</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>19.77</v>
       </c>
       <c r="C35">
-        <v>28.023</v>
+        <v>0</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1683,13 +1665,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46293.35416666666</v>
+        <v>46296.35416666666</v>
       </c>
       <c r="B36">
-        <v>2.102</v>
+        <v>0</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>7.686</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1700,13 +1682,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46293.36458333334</v>
+        <v>46296.36458333334</v>
       </c>
       <c r="B37">
         <v>0</v>
       </c>
       <c r="C37">
-        <v>45.248</v>
+        <v>25.171</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1717,13 +1699,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46293.375</v>
+        <v>46296.375</v>
       </c>
       <c r="B38">
         <v>0</v>
       </c>
       <c r="C38">
-        <v>40.553</v>
+        <v>2.177</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1734,13 +1716,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46293.38541666666</v>
+        <v>46296.38541666666</v>
       </c>
       <c r="B39">
-        <v>6.82</v>
+        <v>0</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>22.141</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1751,13 +1733,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46293.39583333334</v>
+        <v>46296.39583333334</v>
       </c>
       <c r="B40">
-        <v>1.555</v>
+        <v>0</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>11.533</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1768,13 +1750,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46293.40625</v>
+        <v>46296.40625</v>
       </c>
       <c r="B41">
         <v>0</v>
       </c>
       <c r="C41">
-        <v>0.313</v>
+        <v>72.119</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1785,13 +1767,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46293.41666666666</v>
+        <v>46296.41666666666</v>
       </c>
       <c r="B42">
-        <v>6.271</v>
+        <v>0</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>13.946</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1802,10 +1784,10 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46293.42708333334</v>
+        <v>46296.42708333334</v>
       </c>
       <c r="B43">
-        <v>3.666</v>
+        <v>21.777</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -1819,13 +1801,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46293.4375</v>
+        <v>46296.4375</v>
       </c>
       <c r="B44">
         <v>0</v>
       </c>
       <c r="C44">
-        <v>1.438</v>
+        <v>23.009</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1836,13 +1818,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46293.44791666666</v>
+        <v>46296.44791666666</v>
       </c>
       <c r="B45">
         <v>0</v>
       </c>
       <c r="C45">
-        <v>3.065</v>
+        <v>18.721</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1853,10 +1835,10 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46293.45833333334</v>
+        <v>46296.45833333334</v>
       </c>
       <c r="B46">
-        <v>1.726</v>
+        <v>4.964</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -1870,13 +1852,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46293.46875</v>
+        <v>46296.46875</v>
       </c>
       <c r="B47">
-        <v>8.055999999999999</v>
+        <v>0</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>1.549</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1887,13 +1869,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46293.47916666666</v>
+        <v>46296.47916666666</v>
       </c>
       <c r="B48">
-        <v>7.282</v>
+        <v>0</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>3.234</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1904,10 +1886,10 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46293.48958333334</v>
+        <v>46296.48958333334</v>
       </c>
       <c r="B49">
-        <v>1.903</v>
+        <v>4.05</v>
       </c>
       <c r="C49">
         <v>0</v>
@@ -1921,13 +1903,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46293.5</v>
+        <v>46296.5</v>
       </c>
       <c r="B50">
-        <v>4.629</v>
+        <v>0</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>1.516</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1938,10 +1920,10 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46293.51041666666</v>
+        <v>46296.51041666666</v>
       </c>
       <c r="B51">
-        <v>6.961</v>
+        <v>5.952</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -1955,13 +1937,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46293.52083333334</v>
+        <v>46296.52083333334</v>
       </c>
       <c r="B52">
         <v>0</v>
       </c>
       <c r="C52">
-        <v>31.715</v>
+        <v>5.766</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1972,13 +1954,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46293.53125</v>
+        <v>46296.53125</v>
       </c>
       <c r="B53">
         <v>0</v>
       </c>
       <c r="C53">
-        <v>30.607</v>
+        <v>2.272</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1989,13 +1971,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46293.54166666666</v>
+        <v>46296.54166666666</v>
       </c>
       <c r="B54">
         <v>0</v>
       </c>
       <c r="C54">
-        <v>10.989</v>
+        <v>12.556</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -2006,13 +1988,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46293.55208333334</v>
+        <v>46296.55208333334</v>
       </c>
       <c r="B55">
         <v>0</v>
       </c>
       <c r="C55">
-        <v>2.561</v>
+        <v>13.519</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -2023,13 +2005,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46293.5625</v>
+        <v>46296.5625</v>
       </c>
       <c r="B56">
         <v>0</v>
       </c>
       <c r="C56">
-        <v>26.777</v>
+        <v>1.257</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -2040,13 +2022,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46293.57291666666</v>
+        <v>46296.57291666666</v>
       </c>
       <c r="B57">
         <v>0</v>
       </c>
       <c r="C57">
-        <v>13.412</v>
+        <v>8.186999999999999</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -2057,13 +2039,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46293.58333333334</v>
+        <v>46296.58333333334</v>
       </c>
       <c r="B58">
         <v>0</v>
       </c>
       <c r="C58">
-        <v>10.266</v>
+        <v>32.542</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -2074,13 +2056,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46293.59375</v>
+        <v>46296.59375</v>
       </c>
       <c r="B59">
         <v>0</v>
       </c>
       <c r="C59">
-        <v>18.765</v>
+        <v>3.705</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -2091,10 +2073,10 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46293.60416666666</v>
+        <v>46296.60416666666</v>
       </c>
       <c r="B60">
-        <v>2.908</v>
+        <v>5.774</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -2108,13 +2090,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46293.61458333334</v>
+        <v>46296.61458333334</v>
       </c>
       <c r="B61">
         <v>0</v>
       </c>
       <c r="C61">
-        <v>14.509</v>
+        <v>23.012</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2125,13 +2107,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46293.625</v>
+        <v>46296.625</v>
       </c>
       <c r="B62">
-        <v>2.978</v>
+        <v>0</v>
       </c>
       <c r="C62">
-        <v>0</v>
+        <v>7.797</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2142,13 +2124,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46293.63541666666</v>
+        <v>46296.63541666666</v>
       </c>
       <c r="B63">
-        <v>5.252</v>
+        <v>0</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>0.487</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2159,13 +2141,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46293.64583333334</v>
+        <v>46296.64583333334</v>
       </c>
       <c r="B64">
-        <v>6.743</v>
+        <v>0</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>26.207</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2176,13 +2158,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46293.65625</v>
+        <v>46296.65625</v>
       </c>
       <c r="B65">
-        <v>8.433</v>
+        <v>0</v>
       </c>
       <c r="C65">
-        <v>0</v>
+        <v>9.000999999999999</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2193,13 +2175,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46293.66666666666</v>
+        <v>46296.66666666666</v>
       </c>
       <c r="B66">
-        <v>9.037000000000001</v>
+        <v>0</v>
       </c>
       <c r="C66">
-        <v>0</v>
+        <v>68.749</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2210,13 +2192,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46293.67708333334</v>
+        <v>46296.67708333334</v>
       </c>
       <c r="B67">
-        <v>8.708</v>
+        <v>0</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>17.476</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2227,13 +2209,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46293.6875</v>
+        <v>46296.6875</v>
       </c>
       <c r="B68">
-        <v>4.397</v>
+        <v>0</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>16.104</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2244,10 +2226,10 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46293.69791666666</v>
+        <v>46296.69791666666</v>
       </c>
       <c r="B69">
-        <v>5.307</v>
+        <v>23.526</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -2261,13 +2243,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46293.70833333334</v>
+        <v>46296.70833333334</v>
       </c>
       <c r="B70">
-        <v>0</v>
+        <v>12.351</v>
       </c>
       <c r="C70">
-        <v>47.302</v>
+        <v>0</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2278,13 +2260,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46293.71875</v>
+        <v>46296.71875</v>
       </c>
       <c r="B71">
-        <v>0</v>
+        <v>41.527</v>
       </c>
       <c r="C71">
-        <v>25.027</v>
+        <v>0</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2295,13 +2277,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46293.72916666666</v>
+        <v>46296.72916666666</v>
       </c>
       <c r="B72">
         <v>0</v>
       </c>
       <c r="C72">
-        <v>5.766</v>
+        <v>1.568</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2312,13 +2294,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46293.73958333334</v>
+        <v>46296.73958333334</v>
       </c>
       <c r="B73">
-        <v>0</v>
+        <v>17.866</v>
       </c>
       <c r="C73">
-        <v>2.691</v>
+        <v>0</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2329,10 +2311,10 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46293.75</v>
+        <v>46296.75</v>
       </c>
       <c r="B74">
-        <v>12.517</v>
+        <v>3.875</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -2346,13 +2328,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46293.76041666666</v>
+        <v>46296.76041666666</v>
       </c>
       <c r="B75">
-        <v>2.664</v>
+        <v>0</v>
       </c>
       <c r="C75">
-        <v>0</v>
+        <v>4.454</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2363,10 +2345,10 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46293.77083333334</v>
+        <v>46296.77083333334</v>
       </c>
       <c r="B76">
-        <v>4.686</v>
+        <v>19.677</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -2380,13 +2362,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46293.78125</v>
+        <v>46296.78125</v>
       </c>
       <c r="B77">
         <v>0</v>
       </c>
       <c r="C77">
-        <v>6.003</v>
+        <v>0.187</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2397,13 +2379,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46293.79166666666</v>
+        <v>46296.79166666666</v>
       </c>
       <c r="B78">
         <v>0</v>
       </c>
       <c r="C78">
-        <v>0.771</v>
+        <v>25.846</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2414,13 +2396,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46293.80208333334</v>
+        <v>46296.80208333334</v>
       </c>
       <c r="B79">
-        <v>0</v>
+        <v>5.222</v>
       </c>
       <c r="C79">
-        <v>1.714</v>
+        <v>0</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2431,13 +2413,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46293.8125</v>
+        <v>46296.8125</v>
       </c>
       <c r="B80">
-        <v>0</v>
+        <v>10.019</v>
       </c>
       <c r="C80">
-        <v>11.644</v>
+        <v>0</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2448,13 +2430,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46293.82291666666</v>
+        <v>46296.82291666666</v>
       </c>
       <c r="B81">
-        <v>0</v>
+        <v>7.462</v>
       </c>
       <c r="C81">
-        <v>13.082</v>
+        <v>0</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2465,13 +2447,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46293.83333333334</v>
+        <v>46296.83333333334</v>
       </c>
       <c r="B82">
         <v>0</v>
       </c>
       <c r="C82">
-        <v>4.347</v>
+        <v>0.408</v>
       </c>
       <c r="D82">
         <v>81</v>
@@ -2482,13 +2464,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46293.84375</v>
+        <v>46296.84375</v>
       </c>
       <c r="B83">
-        <v>0</v>
+        <v>3.983</v>
       </c>
       <c r="C83">
-        <v>5.402</v>
+        <v>0</v>
       </c>
       <c r="D83">
         <v>82</v>
@@ -2499,13 +2481,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46293.85416666666</v>
+        <v>46296.85416666666</v>
       </c>
       <c r="B84">
         <v>0</v>
       </c>
       <c r="C84">
-        <v>7.037</v>
+        <v>2.949</v>
       </c>
       <c r="D84">
         <v>83</v>
@@ -2516,13 +2498,13 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46293.86458333334</v>
+        <v>46296.86458333334</v>
       </c>
       <c r="B85">
-        <v>0</v>
+        <v>8.534000000000001</v>
       </c>
       <c r="C85">
-        <v>1.256</v>
+        <v>0</v>
       </c>
       <c r="D85">
         <v>84</v>
@@ -2533,10 +2515,10 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46293.875</v>
+        <v>46296.875</v>
       </c>
       <c r="B86">
-        <v>11.536</v>
+        <v>23.849</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -2550,13 +2532,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46293.88541666666</v>
+        <v>46296.88541666666</v>
       </c>
       <c r="B87">
-        <v>0</v>
+        <v>15.839</v>
       </c>
       <c r="C87">
-        <v>3.719</v>
+        <v>0</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -2567,13 +2549,13 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46293.89583333334</v>
+        <v>46296.89583333334</v>
       </c>
       <c r="B88">
-        <v>0</v>
+        <v>0.694</v>
       </c>
       <c r="C88">
-        <v>14.448</v>
+        <v>0</v>
       </c>
       <c r="D88">
         <v>87</v>
@@ -2584,13 +2566,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46293.90625</v>
+        <v>46296.90625</v>
       </c>
       <c r="B89">
-        <v>0</v>
+        <v>0.755</v>
       </c>
       <c r="C89">
-        <v>16.027</v>
+        <v>0</v>
       </c>
       <c r="D89">
         <v>88</v>
@@ -2601,13 +2583,13 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46293.91666666666</v>
+        <v>46296.91666666666</v>
       </c>
       <c r="B90">
         <v>0</v>
       </c>
       <c r="C90">
-        <v>2.664</v>
+        <v>2.263</v>
       </c>
       <c r="D90">
         <v>89</v>
@@ -2618,13 +2600,13 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46293.92708333334</v>
+        <v>46296.92708333334</v>
       </c>
       <c r="B91">
         <v>0</v>
       </c>
       <c r="C91">
-        <v>7.384</v>
+        <v>4.816</v>
       </c>
       <c r="D91">
         <v>90</v>
@@ -2635,13 +2617,13 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46293.9375</v>
+        <v>46296.9375</v>
       </c>
       <c r="B92">
         <v>0</v>
       </c>
       <c r="C92">
-        <v>3.563</v>
+        <v>4.092</v>
       </c>
       <c r="D92">
         <v>91</v>
@@ -2652,13 +2634,13 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46293.94791666666</v>
+        <v>46296.94791666666</v>
       </c>
       <c r="B93">
-        <v>4.269</v>
+        <v>0</v>
       </c>
       <c r="C93">
-        <v>0</v>
+        <v>9.481999999999999</v>
       </c>
       <c r="D93">
         <v>92</v>
@@ -2669,13 +2651,13 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46293.95833333334</v>
+        <v>46296.95833333334</v>
       </c>
       <c r="B94">
         <v>0</v>
       </c>
       <c r="C94">
-        <v>0.803</v>
+        <v>15.69</v>
       </c>
       <c r="D94">
         <v>93</v>
@@ -2686,13 +2668,13 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46293.96875</v>
+        <v>46296.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
       </c>
       <c r="C95">
-        <v>1.261</v>
+        <v>17.871</v>
       </c>
       <c r="D95">
         <v>94</v>
@@ -2703,13 +2685,13 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46293.97916666666</v>
+        <v>46296.97916666666</v>
       </c>
       <c r="B96">
-        <v>1.297</v>
+        <v>0</v>
       </c>
       <c r="C96">
-        <v>0</v>
+        <v>9.842000000000001</v>
       </c>
       <c r="D96">
         <v>95</v>
@@ -2720,13 +2702,13 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46293.98958333334</v>
+        <v>46296.98958333334</v>
       </c>
       <c r="B97">
-        <v>8.444000000000001</v>
+        <v>0</v>
       </c>
       <c r="C97">
-        <v>0</v>
+        <v>10.764</v>
       </c>
       <c r="D97">
         <v>96</v>
@@ -2737,10 +2719,10 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46294</v>
+        <v>46297</v>
       </c>
       <c r="B98">
-        <v>7.175</v>
+        <v>3.686</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -2754,13 +2736,13 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46294.01041666666</v>
+        <v>46297.01041666666</v>
       </c>
       <c r="B99">
-        <v>3.201</v>
+        <v>0</v>
       </c>
       <c r="C99">
-        <v>0</v>
+        <v>10.227</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -2771,10 +2753,10 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46294.02083333334</v>
+        <v>46297.02083333334</v>
       </c>
       <c r="B100">
-        <v>0.208</v>
+        <v>2.537</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -2788,13 +2770,13 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46294.03125</v>
+        <v>46297.03125</v>
       </c>
       <c r="B101">
-        <v>0</v>
+        <v>3.314</v>
       </c>
       <c r="C101">
-        <v>3.537</v>
+        <v>0</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -2805,13 +2787,13 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46294.04166666666</v>
+        <v>46297.04166666666</v>
       </c>
       <c r="B102">
-        <v>0</v>
+        <v>2.298</v>
       </c>
       <c r="C102">
-        <v>4.233</v>
+        <v>0</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -2822,13 +2804,13 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46294.05208333334</v>
+        <v>46297.05208333334</v>
       </c>
       <c r="B103">
-        <v>4.737</v>
+        <v>0</v>
       </c>
       <c r="C103">
-        <v>0</v>
+        <v>6.91</v>
       </c>
       <c r="D103">
         <v>6</v>
@@ -2839,10 +2821,10 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46294.0625</v>
+        <v>46297.0625</v>
       </c>
       <c r="B104">
-        <v>0.036</v>
+        <v>1.865</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -2856,13 +2838,13 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46294.07291666666</v>
+        <v>46297.07291666666</v>
       </c>
       <c r="B105">
-        <v>0</v>
+        <v>5.411</v>
       </c>
       <c r="C105">
-        <v>10.083</v>
+        <v>0</v>
       </c>
       <c r="D105">
         <v>8</v>
@@ -2873,13 +2855,13 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46294.08333333334</v>
+        <v>46297.08333333334</v>
       </c>
       <c r="B106">
-        <v>0</v>
+        <v>18.74</v>
       </c>
       <c r="C106">
-        <v>0.113</v>
+        <v>0</v>
       </c>
       <c r="D106">
         <v>9</v>
@@ -2890,13 +2872,13 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46294.09375</v>
+        <v>46297.09375</v>
       </c>
       <c r="B107">
-        <v>0</v>
+        <v>14.354</v>
       </c>
       <c r="C107">
-        <v>2.345</v>
+        <v>0</v>
       </c>
       <c r="D107">
         <v>10</v>
@@ -2907,10 +2889,10 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46294.10416666666</v>
+        <v>46297.10416666666</v>
       </c>
       <c r="B108">
-        <v>2.913</v>
+        <v>0.736</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -2924,10 +2906,10 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46294.11458333334</v>
+        <v>46297.11458333334</v>
       </c>
       <c r="B109">
-        <v>8.710000000000001</v>
+        <v>16.484</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -2941,10 +2923,10 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46294.125</v>
+        <v>46297.125</v>
       </c>
       <c r="B110">
-        <v>8.323</v>
+        <v>4.719</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -2958,10 +2940,10 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46294.13541666666</v>
+        <v>46297.13541666666</v>
       </c>
       <c r="B111">
-        <v>2.534</v>
+        <v>14.029</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -2975,10 +2957,10 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46294.14583333334</v>
+        <v>46297.14583333334</v>
       </c>
       <c r="B112">
-        <v>0.272</v>
+        <v>0.956</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -2992,13 +2974,13 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46294.15625</v>
+        <v>46297.15625</v>
       </c>
       <c r="B113">
         <v>0</v>
       </c>
       <c r="C113">
-        <v>9.023999999999999</v>
+        <v>1.837</v>
       </c>
       <c r="D113">
         <v>16</v>
@@ -3009,13 +2991,13 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46294.16666666666</v>
+        <v>46297.16666666666</v>
       </c>
       <c r="B114">
         <v>0</v>
       </c>
       <c r="C114">
-        <v>11.069</v>
+        <v>22.878</v>
       </c>
       <c r="D114">
         <v>17</v>
@@ -3026,13 +3008,13 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46294.17708333334</v>
+        <v>46297.17708333334</v>
       </c>
       <c r="B115">
         <v>0</v>
       </c>
       <c r="C115">
-        <v>5.772</v>
+        <v>12.798</v>
       </c>
       <c r="D115">
         <v>18</v>
@@ -3043,13 +3025,13 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46294.1875</v>
+        <v>46297.1875</v>
       </c>
       <c r="B116">
-        <v>2.496</v>
+        <v>0</v>
       </c>
       <c r="C116">
-        <v>0</v>
+        <v>14.246</v>
       </c>
       <c r="D116">
         <v>19</v>
@@ -3060,13 +3042,13 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46294.19791666666</v>
+        <v>46297.19791666666</v>
       </c>
       <c r="B117">
-        <v>0</v>
+        <v>0.775</v>
       </c>
       <c r="C117">
-        <v>9.276999999999999</v>
+        <v>0</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -3077,13 +3059,13 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46294.20833333334</v>
+        <v>46297.20833333334</v>
       </c>
       <c r="B118">
-        <v>0</v>
+        <v>8.638</v>
       </c>
       <c r="C118">
-        <v>20.255</v>
+        <v>0</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -3094,13 +3076,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46294.21875</v>
+        <v>46297.21875</v>
       </c>
       <c r="B119">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="C119">
-        <v>1.161</v>
+        <v>0</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -3111,13 +3093,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46294.22916666666</v>
+        <v>46297.22916666666</v>
       </c>
       <c r="B120">
-        <v>9.385</v>
+        <v>0</v>
       </c>
       <c r="C120">
-        <v>0</v>
+        <v>30.33</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -3128,13 +3110,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46294.23958333334</v>
+        <v>46297.23958333334</v>
       </c>
       <c r="B121">
         <v>0</v>
       </c>
       <c r="C121">
-        <v>0.522</v>
+        <v>7.962</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3145,13 +3127,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46294.25</v>
+        <v>46297.25</v>
       </c>
       <c r="B122">
         <v>0</v>
       </c>
       <c r="C122">
-        <v>4.927</v>
+        <v>7.487</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3162,13 +3144,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46294.26041666666</v>
+        <v>46297.26041666666</v>
       </c>
       <c r="B123">
-        <v>3.088</v>
+        <v>0</v>
       </c>
       <c r="C123">
-        <v>0</v>
+        <v>7.198</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3179,13 +3161,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46294.27083333334</v>
+        <v>46297.27083333334</v>
       </c>
       <c r="B124">
-        <v>14.483</v>
+        <v>0</v>
       </c>
       <c r="C124">
-        <v>0</v>
+        <v>23.08</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3196,13 +3178,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46294.28125</v>
+        <v>46297.28125</v>
       </c>
       <c r="B125">
-        <v>7.149</v>
+        <v>0</v>
       </c>
       <c r="C125">
-        <v>0</v>
+        <v>21.177</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3213,13 +3195,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46294.29166666666</v>
+        <v>46297.29166666666</v>
       </c>
       <c r="B126">
-        <v>0.643</v>
+        <v>0</v>
       </c>
       <c r="C126">
-        <v>0</v>
+        <v>20.24</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3230,13 +3212,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46294.30208333334</v>
+        <v>46297.30208333334</v>
       </c>
       <c r="B127">
-        <v>2.957</v>
+        <v>0</v>
       </c>
       <c r="C127">
-        <v>0</v>
+        <v>13.301</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3247,13 +3229,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46294.3125</v>
+        <v>46297.3125</v>
       </c>
       <c r="B128">
-        <v>2.305</v>
+        <v>0</v>
       </c>
       <c r="C128">
-        <v>0</v>
+        <v>13.57</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3264,13 +3246,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46294.32291666666</v>
+        <v>46297.32291666666</v>
       </c>
       <c r="B129">
         <v>0</v>
       </c>
       <c r="C129">
-        <v>19.333</v>
+        <v>16.748</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3281,13 +3263,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46294.33333333334</v>
+        <v>46297.33333333334</v>
       </c>
       <c r="B130">
-        <v>0</v>
+        <v>2.029</v>
       </c>
       <c r="C130">
-        <v>19.776</v>
+        <v>0</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3298,13 +3280,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46294.34375</v>
+        <v>46297.34375</v>
       </c>
       <c r="B131">
         <v>0</v>
       </c>
       <c r="C131">
-        <v>27.251</v>
+        <v>16.945</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3315,13 +3297,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46294.35416666666</v>
+        <v>46297.35416666666</v>
       </c>
       <c r="B132">
         <v>0</v>
       </c>
       <c r="C132">
-        <v>9.718999999999999</v>
+        <v>26.229</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3332,13 +3314,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46294.36458333334</v>
+        <v>46297.36458333334</v>
       </c>
       <c r="B133">
         <v>0</v>
       </c>
       <c r="C133">
-        <v>49.831</v>
+        <v>21.414</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3349,13 +3331,13 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46294.375</v>
+        <v>46297.375</v>
       </c>
       <c r="B134">
-        <v>0</v>
+        <v>39.085</v>
       </c>
       <c r="C134">
-        <v>20.582</v>
+        <v>0</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3366,13 +3348,13 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46294.38541666666</v>
+        <v>46297.38541666666</v>
       </c>
       <c r="B135">
         <v>0</v>
       </c>
       <c r="C135">
-        <v>2.271</v>
+        <v>7.543</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3383,13 +3365,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46294.39583333334</v>
+        <v>46297.39583333334</v>
       </c>
       <c r="B136">
         <v>0</v>
       </c>
       <c r="C136">
-        <v>6.438</v>
+        <v>20.623</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3400,13 +3382,13 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46294.40625</v>
+        <v>46297.40625</v>
       </c>
       <c r="B137">
         <v>0</v>
       </c>
       <c r="C137">
-        <v>61.842</v>
+        <v>14.971</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3417,13 +3399,13 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46294.41666666666</v>
+        <v>46297.41666666666</v>
       </c>
       <c r="B138">
-        <v>0</v>
+        <v>14.117</v>
       </c>
       <c r="C138">
-        <v>31.1</v>
+        <v>0</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3434,13 +3416,13 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46294.42708333334</v>
+        <v>46297.42708333334</v>
       </c>
       <c r="B139">
-        <v>0</v>
+        <v>3.039</v>
       </c>
       <c r="C139">
-        <v>27.518</v>
+        <v>0</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3451,13 +3433,13 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46294.4375</v>
+        <v>46297.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
       </c>
       <c r="C140">
-        <v>82.691</v>
+        <v>34.874</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3468,13 +3450,13 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46294.44791666666</v>
+        <v>46297.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
       </c>
       <c r="C141">
-        <v>16.543</v>
+        <v>3.478</v>
       </c>
       <c r="D141">
         <v>44</v>
@@ -3485,13 +3467,13 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46294.45833333334</v>
+        <v>46297.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
       </c>
       <c r="C142">
-        <v>11.256</v>
+        <v>18.036</v>
       </c>
       <c r="D142">
         <v>45</v>
@@ -3502,13 +3484,13 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46294.46875</v>
+        <v>46297.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
       </c>
       <c r="C143">
-        <v>18.409</v>
+        <v>22.978</v>
       </c>
       <c r="D143">
         <v>46</v>
@@ -3519,13 +3501,13 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46294.47916666666</v>
+        <v>46297.47916666666</v>
       </c>
       <c r="B144">
-        <v>0</v>
+        <v>0.313</v>
       </c>
       <c r="C144">
-        <v>52.001</v>
+        <v>0</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -3536,13 +3518,13 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46294.48958333334</v>
+        <v>46297.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
       </c>
       <c r="C145">
-        <v>51.361</v>
+        <v>6.763</v>
       </c>
       <c r="D145">
         <v>48</v>
@@ -3553,13 +3535,13 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46294.5</v>
+        <v>46297.5</v>
       </c>
       <c r="B146">
         <v>0</v>
       </c>
       <c r="C146">
-        <v>44.375</v>
+        <v>1.572</v>
       </c>
       <c r="D146">
         <v>49</v>
@@ -3570,13 +3552,13 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46294.51041666666</v>
+        <v>46297.51041666666</v>
       </c>
       <c r="B147">
-        <v>0</v>
+        <v>25.132</v>
       </c>
       <c r="C147">
-        <v>6.692</v>
+        <v>0</v>
       </c>
       <c r="D147">
         <v>50</v>
@@ -3587,13 +3569,13 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46294.52083333334</v>
+        <v>46297.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
       </c>
       <c r="C148">
-        <v>35.626</v>
+        <v>11.114</v>
       </c>
       <c r="D148">
         <v>51</v>
@@ -3604,10 +3586,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46294.53125</v>
+        <v>46297.53125</v>
       </c>
       <c r="B149">
-        <v>8.968999999999999</v>
+        <v>2.36</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -3621,13 +3603,13 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46294.54166666666</v>
+        <v>46297.54166666666</v>
       </c>
       <c r="B150">
-        <v>0</v>
+        <v>13.532</v>
       </c>
       <c r="C150">
-        <v>0.756</v>
+        <v>0</v>
       </c>
       <c r="D150">
         <v>53</v>
@@ -3638,13 +3620,13 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46294.55208333334</v>
+        <v>46297.55208333334</v>
       </c>
       <c r="B151">
-        <v>0</v>
+        <v>5.515</v>
       </c>
       <c r="C151">
-        <v>22.581</v>
+        <v>0</v>
       </c>
       <c r="D151">
         <v>54</v>
@@ -3655,13 +3637,13 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46294.5625</v>
+        <v>46297.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
       </c>
       <c r="C152">
-        <v>47.991</v>
+        <v>2.321</v>
       </c>
       <c r="D152">
         <v>55</v>
@@ -3672,13 +3654,13 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46294.57291666666</v>
+        <v>46297.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
       </c>
       <c r="C153">
-        <v>27.202</v>
+        <v>2.687</v>
       </c>
       <c r="D153">
         <v>56</v>
@@ -3689,13 +3671,13 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46294.58333333334</v>
+        <v>46297.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
       </c>
       <c r="C154">
-        <v>20.549</v>
+        <v>11.145</v>
       </c>
       <c r="D154">
         <v>57</v>
@@ -3706,13 +3688,13 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46294.59375</v>
+        <v>46297.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
       </c>
       <c r="C155">
-        <v>20.66</v>
+        <v>13.806</v>
       </c>
       <c r="D155">
         <v>58</v>
@@ -3723,13 +3705,13 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46294.60416666666</v>
+        <v>46297.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
       </c>
       <c r="C156">
-        <v>12.03</v>
+        <v>17.542</v>
       </c>
       <c r="D156">
         <v>59</v>
@@ -3740,13 +3722,13 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46294.61458333334</v>
+        <v>46297.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
       </c>
       <c r="C157">
-        <v>2.753</v>
+        <v>19.674</v>
       </c>
       <c r="D157">
         <v>60</v>
@@ -3757,13 +3739,13 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46294.625</v>
+        <v>46297.625</v>
       </c>
       <c r="B158">
         <v>0</v>
       </c>
       <c r="C158">
-        <v>14.989</v>
+        <v>17.492</v>
       </c>
       <c r="D158">
         <v>61</v>
@@ -3774,13 +3756,13 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46294.63541666666</v>
+        <v>46297.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
       </c>
       <c r="C159">
-        <v>28.564</v>
+        <v>1.476</v>
       </c>
       <c r="D159">
         <v>62</v>
@@ -3791,13 +3773,13 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46294.64583333334</v>
+        <v>46297.64583333334</v>
       </c>
       <c r="B160">
-        <v>0</v>
+        <v>2.383</v>
       </c>
       <c r="C160">
-        <v>34.086</v>
+        <v>0</v>
       </c>
       <c r="D160">
         <v>63</v>
@@ -3808,13 +3790,13 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46294.65625</v>
+        <v>46297.65625</v>
       </c>
       <c r="B161">
-        <v>0</v>
+        <v>12.125</v>
       </c>
       <c r="C161">
-        <v>9.089</v>
+        <v>0</v>
       </c>
       <c r="D161">
         <v>64</v>
@@ -3825,10 +3807,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46294.66666666666</v>
+        <v>46297.66666666666</v>
       </c>
       <c r="B162">
-        <v>37.003</v>
+        <v>2.438</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -3842,10 +3824,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46294.67708333334</v>
+        <v>46297.67708333334</v>
       </c>
       <c r="B163">
-        <v>25.691</v>
+        <v>7.383</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -3859,10 +3841,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46294.6875</v>
+        <v>46297.6875</v>
       </c>
       <c r="B164">
-        <v>3.393</v>
+        <v>2.192</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -3876,10 +3858,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46294.69791666666</v>
+        <v>46297.69791666666</v>
       </c>
       <c r="B165">
-        <v>12.344</v>
+        <v>15.423</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -3893,13 +3875,13 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46294.70833333334</v>
+        <v>46297.70833333334</v>
       </c>
       <c r="B166">
-        <v>48.067</v>
+        <v>0</v>
       </c>
       <c r="C166">
-        <v>0</v>
+        <v>16.491</v>
       </c>
       <c r="D166">
         <v>69</v>
@@ -3910,10 +3892,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46294.71875</v>
+        <v>46297.71875</v>
       </c>
       <c r="B167">
-        <v>7.625</v>
+        <v>5.281</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -3927,13 +3909,13 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46294.72916666666</v>
+        <v>46297.72916666666</v>
       </c>
       <c r="B168">
-        <v>13.88</v>
+        <v>0</v>
       </c>
       <c r="C168">
-        <v>0</v>
+        <v>4.827</v>
       </c>
       <c r="D168">
         <v>71</v>
@@ -3944,13 +3926,13 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46294.73958333334</v>
+        <v>46297.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
       </c>
       <c r="C169">
-        <v>10.918</v>
+        <v>3.152</v>
       </c>
       <c r="D169">
         <v>72</v>
@@ -3961,13 +3943,13 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46294.75</v>
+        <v>46297.75</v>
       </c>
       <c r="B170">
         <v>0</v>
       </c>
       <c r="C170">
-        <v>44.821</v>
+        <v>22.643</v>
       </c>
       <c r="D170">
         <v>73</v>
@@ -3978,13 +3960,13 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46294.76041666666</v>
+        <v>46297.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
       </c>
       <c r="C171">
-        <v>20.493</v>
+        <v>32.922</v>
       </c>
       <c r="D171">
         <v>74</v>
@@ -3995,13 +3977,13 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46294.77083333334</v>
+        <v>46297.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
       </c>
       <c r="C172">
-        <v>39.863</v>
+        <v>27.799</v>
       </c>
       <c r="D172">
         <v>75</v>
@@ -4012,13 +3994,13 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46294.78125</v>
+        <v>46297.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
       </c>
       <c r="C173">
-        <v>37.749</v>
+        <v>43.302</v>
       </c>
       <c r="D173">
         <v>76</v>
@@ -4029,13 +4011,13 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46294.79166666666</v>
+        <v>46297.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
       </c>
       <c r="C174">
-        <v>10.802</v>
+        <v>34.84</v>
       </c>
       <c r="D174">
         <v>77</v>
@@ -4046,13 +4028,13 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46294.80208333334</v>
+        <v>46297.80208333334</v>
       </c>
       <c r="B175">
-        <v>0</v>
+        <v>3.717</v>
       </c>
       <c r="C175">
-        <v>31.764</v>
+        <v>0</v>
       </c>
       <c r="D175">
         <v>78</v>
@@ -4063,13 +4045,13 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46294.8125</v>
+        <v>46297.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
       </c>
       <c r="C176">
-        <v>34.344</v>
+        <v>10.695</v>
       </c>
       <c r="D176">
         <v>79</v>
@@ -4080,13 +4062,13 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46294.82291666666</v>
+        <v>46297.82291666666</v>
       </c>
       <c r="B177">
-        <v>0</v>
+        <v>5.126</v>
       </c>
       <c r="C177">
-        <v>44.453</v>
+        <v>0</v>
       </c>
       <c r="D177">
         <v>80</v>
@@ -4097,13 +4079,13 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46294.83333333334</v>
+        <v>46297.83333333334</v>
       </c>
       <c r="B178">
-        <v>0</v>
+        <v>4.568</v>
       </c>
       <c r="C178">
-        <v>59.814</v>
+        <v>0</v>
       </c>
       <c r="D178">
         <v>81</v>
@@ -4114,13 +4096,13 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46294.84375</v>
+        <v>46297.84375</v>
       </c>
       <c r="B179">
-        <v>0</v>
+        <v>12.865</v>
       </c>
       <c r="C179">
-        <v>86.893</v>
+        <v>0</v>
       </c>
       <c r="D179">
         <v>82</v>
@@ -4131,13 +4113,13 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46294.85416666666</v>
+        <v>46297.85416666666</v>
       </c>
       <c r="B180">
-        <v>0</v>
+        <v>12.649</v>
       </c>
       <c r="C180">
-        <v>58.984</v>
+        <v>0</v>
       </c>
       <c r="D180">
         <v>83</v>
@@ -4148,13 +4130,13 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46294.86458333334</v>
+        <v>46297.86458333334</v>
       </c>
       <c r="B181">
-        <v>0</v>
+        <v>5.262</v>
       </c>
       <c r="C181">
-        <v>22.102</v>
+        <v>0</v>
       </c>
       <c r="D181">
         <v>84</v>
@@ -4165,10 +4147,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46294.875</v>
+        <v>46297.875</v>
       </c>
       <c r="B182">
-        <v>5.096</v>
+        <v>18.496</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -4182,13 +4164,13 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46294.88541666666</v>
+        <v>46297.88541666666</v>
       </c>
       <c r="B183">
-        <v>0</v>
+        <v>22.915</v>
       </c>
       <c r="C183">
-        <v>3.546</v>
+        <v>0</v>
       </c>
       <c r="D183">
         <v>86</v>
@@ -4199,13 +4181,13 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46294.89583333334</v>
+        <v>46297.89583333334</v>
       </c>
       <c r="B184">
-        <v>0</v>
+        <v>9.013999999999999</v>
       </c>
       <c r="C184">
-        <v>6.07</v>
+        <v>0</v>
       </c>
       <c r="D184">
         <v>87</v>
@@ -4216,13 +4198,13 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46294.90625</v>
+        <v>46297.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
       </c>
       <c r="C185">
-        <v>22.177</v>
+        <v>3.636</v>
       </c>
       <c r="D185">
         <v>88</v>
@@ -4233,10 +4215,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46294.91666666666</v>
+        <v>46297.91666666666</v>
       </c>
       <c r="B186">
-        <v>9.994999999999999</v>
+        <v>19.138</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -4250,10 +4232,10 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46294.92708333334</v>
+        <v>46297.92708333334</v>
       </c>
       <c r="B187">
-        <v>5.95</v>
+        <v>3.566</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -4267,13 +4249,13 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46294.9375</v>
+        <v>46297.9375</v>
       </c>
       <c r="B188">
-        <v>0.823</v>
+        <v>0</v>
       </c>
       <c r="C188">
-        <v>0</v>
+        <v>6.532</v>
       </c>
       <c r="D188">
         <v>91</v>
@@ -4284,13 +4266,13 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46294.94791666666</v>
+        <v>46297.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
       </c>
       <c r="C189">
-        <v>11.721</v>
+        <v>5.567</v>
       </c>
       <c r="D189">
         <v>92</v>
@@ -4301,13 +4283,13 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46294.95833333334</v>
+        <v>46297.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
       </c>
       <c r="C190">
-        <v>20.128</v>
+        <v>3.456</v>
       </c>
       <c r="D190">
         <v>93</v>
@@ -4318,13 +4300,13 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46294.96875</v>
+        <v>46297.96875</v>
       </c>
       <c r="B191">
-        <v>0</v>
+        <v>2.292</v>
       </c>
       <c r="C191">
-        <v>4.331</v>
+        <v>0</v>
       </c>
       <c r="D191">
         <v>94</v>
@@ -4335,13 +4317,13 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46294.97916666666</v>
+        <v>46297.97916666666</v>
       </c>
       <c r="B192">
-        <v>13.398</v>
+        <v>0</v>
       </c>
       <c r="C192">
-        <v>0</v>
+        <v>13.131</v>
       </c>
       <c r="D192">
         <v>95</v>
@@ -4352,13 +4334,13 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46294.98958333334</v>
+        <v>46297.98958333334</v>
       </c>
       <c r="B193">
-        <v>32.884</v>
+        <v>0</v>
       </c>
       <c r="C193">
-        <v>0</v>
+        <v>5.163</v>
       </c>
       <c r="D193">
         <v>96</v>
@@ -4369,13 +4351,13 @@
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="2">
-        <v>46295</v>
+        <v>46298</v>
       </c>
       <c r="B194">
-        <v>12.005</v>
+        <v>0</v>
       </c>
       <c r="C194">
-        <v>0</v>
+        <v>17.117</v>
       </c>
       <c r="D194">
         <v>1</v>
@@ -4386,13 +4368,13 @@
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="2">
-        <v>46295.01041666666</v>
+        <v>46298.01041666666</v>
       </c>
       <c r="B195">
         <v>0</v>
       </c>
       <c r="C195">
-        <v>4.922</v>
+        <v>3.615</v>
       </c>
       <c r="D195">
         <v>2</v>
@@ -4403,13 +4385,13 @@
     </row>
     <row r="196" spans="1:5">
       <c r="A196" s="2">
-        <v>46295.02083333334</v>
+        <v>46298.02083333334</v>
       </c>
       <c r="B196">
         <v>0</v>
       </c>
       <c r="C196">
-        <v>4.566</v>
+        <v>7.913</v>
       </c>
       <c r="D196">
         <v>3</v>
@@ -4420,13 +4402,13 @@
     </row>
     <row r="197" spans="1:5">
       <c r="A197" s="2">
-        <v>46295.03125</v>
+        <v>46298.03125</v>
       </c>
       <c r="B197">
         <v>0</v>
       </c>
       <c r="C197">
-        <v>1.837</v>
+        <v>3.992</v>
       </c>
       <c r="D197">
         <v>4</v>
@@ -4437,13 +4419,13 @@
     </row>
     <row r="198" spans="1:5">
       <c r="A198" s="2">
-        <v>46295.04166666666</v>
+        <v>46298.04166666666</v>
       </c>
       <c r="B198">
-        <v>9.066000000000001</v>
+        <v>0</v>
       </c>
       <c r="C198">
-        <v>0</v>
+        <v>2.743</v>
       </c>
       <c r="D198">
         <v>5</v>
@@ -4454,10 +4436,10 @@
     </row>
     <row r="199" spans="1:5">
       <c r="A199" s="2">
-        <v>46295.05208333334</v>
+        <v>46298.05208333334</v>
       </c>
       <c r="B199">
-        <v>2.044</v>
+        <v>7.781</v>
       </c>
       <c r="C199">
         <v>0</v>
@@ -4471,10 +4453,10 @@
     </row>
     <row r="200" spans="1:5">
       <c r="A200" s="2">
-        <v>46295.0625</v>
+        <v>46298.0625</v>
       </c>
       <c r="B200">
-        <v>17.834</v>
+        <v>24.6</v>
       </c>
       <c r="C200">
         <v>0</v>
@@ -4488,13 +4470,13 @@
     </row>
     <row r="201" spans="1:5">
       <c r="A201" s="2">
-        <v>46295.07291666666</v>
+        <v>46298.07291666666</v>
       </c>
       <c r="B201">
-        <v>23.524</v>
+        <v>0</v>
       </c>
       <c r="C201">
-        <v>0</v>
+        <v>8.423999999999999</v>
       </c>
       <c r="D201">
         <v>8</v>
@@ -4505,10 +4487,10 @@
     </row>
     <row r="202" spans="1:5">
       <c r="A202" s="2">
-        <v>46295.08333333334</v>
+        <v>46298.08333333334</v>
       </c>
       <c r="B202">
-        <v>5.653</v>
+        <v>2.162</v>
       </c>
       <c r="C202">
         <v>0</v>
@@ -4522,10 +4504,10 @@
     </row>
     <row r="203" spans="1:5">
       <c r="A203" s="2">
-        <v>46295.09375</v>
+        <v>46298.09375</v>
       </c>
       <c r="B203">
-        <v>9.419</v>
+        <v>11.277</v>
       </c>
       <c r="C203">
         <v>0</v>
@@ -4539,10 +4521,10 @@
     </row>
     <row r="204" spans="1:5">
       <c r="A204" s="2">
-        <v>46295.10416666666</v>
+        <v>46298.10416666666</v>
       </c>
       <c r="B204">
-        <v>35.878</v>
+        <v>0.864</v>
       </c>
       <c r="C204">
         <v>0</v>
@@ -4556,13 +4538,13 @@
     </row>
     <row r="205" spans="1:5">
       <c r="A205" s="2">
-        <v>46295.11458333334</v>
+        <v>46298.11458333334</v>
       </c>
       <c r="B205">
-        <v>18.523</v>
+        <v>0</v>
       </c>
       <c r="C205">
-        <v>0</v>
+        <v>4.467</v>
       </c>
       <c r="D205">
         <v>12</v>
@@ -4573,10 +4555,10 @@
     </row>
     <row r="206" spans="1:5">
       <c r="A206" s="2">
-        <v>46295.125</v>
+        <v>46298.125</v>
       </c>
       <c r="B206">
-        <v>13.924</v>
+        <v>9.702</v>
       </c>
       <c r="C206">
         <v>0</v>
@@ -4590,10 +4572,10 @@
     </row>
     <row r="207" spans="1:5">
       <c r="A207" s="2">
-        <v>46295.13541666666</v>
+        <v>46298.13541666666</v>
       </c>
       <c r="B207">
-        <v>20.929</v>
+        <v>2.941</v>
       </c>
       <c r="C207">
         <v>0</v>
@@ -4607,10 +4589,10 @@
     </row>
     <row r="208" spans="1:5">
       <c r="A208" s="2">
-        <v>46295.14583333334</v>
+        <v>46298.14583333334</v>
       </c>
       <c r="B208">
-        <v>27.199</v>
+        <v>6.322</v>
       </c>
       <c r="C208">
         <v>0</v>
@@ -4624,10 +4606,10 @@
     </row>
     <row r="209" spans="1:5">
       <c r="A209" s="2">
-        <v>46295.15625</v>
+        <v>46298.15625</v>
       </c>
       <c r="B209">
-        <v>35.969</v>
+        <v>9.821</v>
       </c>
       <c r="C209">
         <v>0</v>
@@ -4641,10 +4623,10 @@
     </row>
     <row r="210" spans="1:5">
       <c r="A210" s="2">
-        <v>46295.16666666666</v>
+        <v>46298.16666666666</v>
       </c>
       <c r="B210">
-        <v>16.028</v>
+        <v>16.068</v>
       </c>
       <c r="C210">
         <v>0</v>
@@ -4658,13 +4640,13 @@
     </row>
     <row r="211" spans="1:5">
       <c r="A211" s="2">
-        <v>46295.17708333334</v>
+        <v>46298.17708333334</v>
       </c>
       <c r="B211">
-        <v>10.285</v>
+        <v>0</v>
       </c>
       <c r="C211">
-        <v>0</v>
+        <v>2.402</v>
       </c>
       <c r="D211">
         <v>18</v>
@@ -4675,10 +4657,10 @@
     </row>
     <row r="212" spans="1:5">
       <c r="A212" s="2">
-        <v>46295.1875</v>
+        <v>46298.1875</v>
       </c>
       <c r="B212">
-        <v>3.602</v>
+        <v>3.408</v>
       </c>
       <c r="C212">
         <v>0</v>
@@ -4692,10 +4674,10 @@
     </row>
     <row r="213" spans="1:5">
       <c r="A213" s="2">
-        <v>46295.19791666666</v>
+        <v>46298.19791666666</v>
       </c>
       <c r="B213">
-        <v>3.992</v>
+        <v>26.754</v>
       </c>
       <c r="C213">
         <v>0</v>
@@ -4709,13 +4691,13 @@
     </row>
     <row r="214" spans="1:5">
       <c r="A214" s="2">
-        <v>46295.20833333334</v>
+        <v>46298.20833333334</v>
       </c>
       <c r="B214">
-        <v>0</v>
+        <v>0.155</v>
       </c>
       <c r="C214">
-        <v>20.169</v>
+        <v>0</v>
       </c>
       <c r="D214">
         <v>21</v>
@@ -4726,13 +4708,13 @@
     </row>
     <row r="215" spans="1:5">
       <c r="A215" s="2">
-        <v>46295.21875</v>
+        <v>46298.21875</v>
       </c>
       <c r="B215">
-        <v>0</v>
+        <v>3.876</v>
       </c>
       <c r="C215">
-        <v>13.475</v>
+        <v>0</v>
       </c>
       <c r="D215">
         <v>22</v>
@@ -4743,13 +4725,13 @@
     </row>
     <row r="216" spans="1:5">
       <c r="A216" s="2">
-        <v>46295.22916666666</v>
+        <v>46298.22916666666</v>
       </c>
       <c r="B216">
-        <v>1.793</v>
+        <v>0</v>
       </c>
       <c r="C216">
-        <v>0</v>
+        <v>7.727</v>
       </c>
       <c r="D216">
         <v>23</v>
@@ -4760,13 +4742,13 @@
     </row>
     <row r="217" spans="1:5">
       <c r="A217" s="2">
-        <v>46295.23958333334</v>
+        <v>46298.23958333334</v>
       </c>
       <c r="B217">
-        <v>9.552</v>
+        <v>0</v>
       </c>
       <c r="C217">
-        <v>0</v>
+        <v>6.864</v>
       </c>
       <c r="D217">
         <v>24</v>
@@ -4777,13 +4759,13 @@
     </row>
     <row r="218" spans="1:5">
       <c r="A218" s="2">
-        <v>46295.25</v>
+        <v>46298.25</v>
       </c>
       <c r="B218">
-        <v>0</v>
+        <v>2.534</v>
       </c>
       <c r="C218">
-        <v>6.995</v>
+        <v>0</v>
       </c>
       <c r="D218">
         <v>25</v>
@@ -4794,13 +4776,13 @@
     </row>
     <row r="219" spans="1:5">
       <c r="A219" s="2">
-        <v>46295.26041666666</v>
+        <v>46298.26041666666</v>
       </c>
       <c r="B219">
-        <v>9.089</v>
+        <v>0</v>
       </c>
       <c r="C219">
-        <v>0</v>
+        <v>1.321</v>
       </c>
       <c r="D219">
         <v>26</v>
@@ -4811,10 +4793,10 @@
     </row>
     <row r="220" spans="1:5">
       <c r="A220" s="2">
-        <v>46295.27083333334</v>
+        <v>46298.27083333334</v>
       </c>
       <c r="B220">
-        <v>29.44</v>
+        <v>2.488</v>
       </c>
       <c r="C220">
         <v>0</v>
@@ -4828,13 +4810,13 @@
     </row>
     <row r="221" spans="1:5">
       <c r="A221" s="2">
-        <v>46295.28125</v>
+        <v>46298.28125</v>
       </c>
       <c r="B221">
-        <v>29.456</v>
+        <v>0</v>
       </c>
       <c r="C221">
-        <v>0</v>
+        <v>9.734999999999999</v>
       </c>
       <c r="D221">
         <v>28</v>
@@ -4845,13 +4827,13 @@
     </row>
     <row r="222" spans="1:5">
       <c r="A222" s="2">
-        <v>46295.29166666666</v>
+        <v>46298.29166666666</v>
       </c>
       <c r="B222">
-        <v>12.376</v>
+        <v>0</v>
       </c>
       <c r="C222">
-        <v>0</v>
+        <v>7.772</v>
       </c>
       <c r="D222">
         <v>29</v>
@@ -4862,13 +4844,13 @@
     </row>
     <row r="223" spans="1:5">
       <c r="A223" s="2">
-        <v>46295.30208333334</v>
+        <v>46298.30208333334</v>
       </c>
       <c r="B223">
-        <v>7.034</v>
+        <v>0</v>
       </c>
       <c r="C223">
-        <v>0</v>
+        <v>13.801</v>
       </c>
       <c r="D223">
         <v>30</v>
@@ -4879,13 +4861,13 @@
     </row>
     <row r="224" spans="1:5">
       <c r="A224" s="2">
-        <v>46295.3125</v>
+        <v>46298.3125</v>
       </c>
       <c r="B224">
-        <v>14.758</v>
+        <v>0</v>
       </c>
       <c r="C224">
-        <v>0</v>
+        <v>10.716</v>
       </c>
       <c r="D224">
         <v>31</v>
@@ -4896,10 +4878,10 @@
     </row>
     <row r="225" spans="1:5">
       <c r="A225" s="2">
-        <v>46295.32291666666</v>
+        <v>46298.32291666666</v>
       </c>
       <c r="B225">
-        <v>10.262</v>
+        <v>1.471</v>
       </c>
       <c r="C225">
         <v>0</v>
@@ -4913,121 +4895,19 @@
     </row>
     <row r="226" spans="1:5">
       <c r="A226" s="2">
-        <v>46295.33333333334</v>
+        <v>46298.33333333334</v>
       </c>
       <c r="B226">
-        <v>23.969</v>
+        <v>0</v>
       </c>
       <c r="C226">
-        <v>0</v>
+        <v>11.018</v>
       </c>
       <c r="D226">
         <v>33</v>
       </c>
       <c r="E226" t="s">
         <v>229</v>
-      </c>
-    </row>
-    <row r="227" spans="1:5">
-      <c r="A227" s="2">
-        <v>46295.34375</v>
-      </c>
-      <c r="B227">
-        <v>21.047</v>
-      </c>
-      <c r="C227">
-        <v>0</v>
-      </c>
-      <c r="D227">
-        <v>34</v>
-      </c>
-      <c r="E227" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="228" spans="1:5">
-      <c r="A228" s="2">
-        <v>46295.35416666666</v>
-      </c>
-      <c r="B228">
-        <v>5.191</v>
-      </c>
-      <c r="C228">
-        <v>0</v>
-      </c>
-      <c r="D228">
-        <v>35</v>
-      </c>
-      <c r="E228" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="229" spans="1:5">
-      <c r="A229" s="2">
-        <v>46295.36458333334</v>
-      </c>
-      <c r="B229">
-        <v>0</v>
-      </c>
-      <c r="C229">
-        <v>12.896</v>
-      </c>
-      <c r="D229">
-        <v>36</v>
-      </c>
-      <c r="E229" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="230" spans="1:5">
-      <c r="A230" s="2">
-        <v>46295.375</v>
-      </c>
-      <c r="B230">
-        <v>8.518000000000001</v>
-      </c>
-      <c r="C230">
-        <v>0</v>
-      </c>
-      <c r="D230">
-        <v>37</v>
-      </c>
-      <c r="E230" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="231" spans="1:5">
-      <c r="A231" s="2">
-        <v>46295.38541666666</v>
-      </c>
-      <c r="B231">
-        <v>0</v>
-      </c>
-      <c r="C231">
-        <v>15.181</v>
-      </c>
-      <c r="D231">
-        <v>38</v>
-      </c>
-      <c r="E231" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="232" spans="1:5">
-      <c r="A232" s="2">
-        <v>46295.39583333334</v>
-      </c>
-      <c r="B232">
-        <v>0</v>
-      </c>
-      <c r="C232">
-        <v>14.198</v>
-      </c>
-      <c r="D232">
-        <v>39</v>
-      </c>
-      <c r="E232" t="s">
-        <v>235</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Unintended_Deviation.xlsx
+++ b/data_fetching/Entsoe/Unintended_Deviation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="430">
   <si>
     <t>Timestamp</t>
   </si>
@@ -422,6 +422,888 @@
   </si>
   <si>
     <t>04.10.202635</t>
+  </si>
+  <si>
+    <t>04.10.202636</t>
+  </si>
+  <si>
+    <t>04.10.202637</t>
+  </si>
+  <si>
+    <t>04.10.202638</t>
+  </si>
+  <si>
+    <t>04.10.202639</t>
+  </si>
+  <si>
+    <t>04.10.202640</t>
+  </si>
+  <si>
+    <t>04.10.202641</t>
+  </si>
+  <si>
+    <t>04.10.202642</t>
+  </si>
+  <si>
+    <t>04.10.202643</t>
+  </si>
+  <si>
+    <t>04.10.202644</t>
+  </si>
+  <si>
+    <t>04.10.202645</t>
+  </si>
+  <si>
+    <t>04.10.202646</t>
+  </si>
+  <si>
+    <t>04.10.202647</t>
+  </si>
+  <si>
+    <t>04.10.202648</t>
+  </si>
+  <si>
+    <t>04.10.202649</t>
+  </si>
+  <si>
+    <t>04.10.202650</t>
+  </si>
+  <si>
+    <t>04.10.202651</t>
+  </si>
+  <si>
+    <t>04.10.202652</t>
+  </si>
+  <si>
+    <t>04.10.202653</t>
+  </si>
+  <si>
+    <t>04.10.202654</t>
+  </si>
+  <si>
+    <t>04.10.202655</t>
+  </si>
+  <si>
+    <t>04.10.202656</t>
+  </si>
+  <si>
+    <t>04.10.202657</t>
+  </si>
+  <si>
+    <t>04.10.202658</t>
+  </si>
+  <si>
+    <t>04.10.202659</t>
+  </si>
+  <si>
+    <t>04.10.202660</t>
+  </si>
+  <si>
+    <t>04.10.202661</t>
+  </si>
+  <si>
+    <t>04.10.202662</t>
+  </si>
+  <si>
+    <t>04.10.202663</t>
+  </si>
+  <si>
+    <t>04.10.202664</t>
+  </si>
+  <si>
+    <t>04.10.202665</t>
+  </si>
+  <si>
+    <t>04.10.202666</t>
+  </si>
+  <si>
+    <t>04.10.202667</t>
+  </si>
+  <si>
+    <t>04.10.202668</t>
+  </si>
+  <si>
+    <t>04.10.202669</t>
+  </si>
+  <si>
+    <t>04.10.202670</t>
+  </si>
+  <si>
+    <t>04.10.202671</t>
+  </si>
+  <si>
+    <t>04.10.202672</t>
+  </si>
+  <si>
+    <t>04.10.202673</t>
+  </si>
+  <si>
+    <t>04.10.202674</t>
+  </si>
+  <si>
+    <t>04.10.202675</t>
+  </si>
+  <si>
+    <t>04.10.202676</t>
+  </si>
+  <si>
+    <t>04.10.202677</t>
+  </si>
+  <si>
+    <t>04.10.202678</t>
+  </si>
+  <si>
+    <t>04.10.202679</t>
+  </si>
+  <si>
+    <t>04.10.202680</t>
+  </si>
+  <si>
+    <t>04.10.202681</t>
+  </si>
+  <si>
+    <t>04.10.202682</t>
+  </si>
+  <si>
+    <t>04.10.202683</t>
+  </si>
+  <si>
+    <t>04.10.202684</t>
+  </si>
+  <si>
+    <t>04.10.202685</t>
+  </si>
+  <si>
+    <t>04.10.202686</t>
+  </si>
+  <si>
+    <t>04.10.202687</t>
+  </si>
+  <si>
+    <t>04.10.202688</t>
+  </si>
+  <si>
+    <t>04.10.202689</t>
+  </si>
+  <si>
+    <t>04.10.202690</t>
+  </si>
+  <si>
+    <t>04.10.202691</t>
+  </si>
+  <si>
+    <t>04.10.202692</t>
+  </si>
+  <si>
+    <t>04.10.202693</t>
+  </si>
+  <si>
+    <t>04.10.202694</t>
+  </si>
+  <si>
+    <t>04.10.202695</t>
+  </si>
+  <si>
+    <t>04.10.202696</t>
+  </si>
+  <si>
+    <t>05.10.20261</t>
+  </si>
+  <si>
+    <t>05.10.20262</t>
+  </si>
+  <si>
+    <t>05.10.20263</t>
+  </si>
+  <si>
+    <t>05.10.20264</t>
+  </si>
+  <si>
+    <t>05.10.20265</t>
+  </si>
+  <si>
+    <t>05.10.20266</t>
+  </si>
+  <si>
+    <t>05.10.20267</t>
+  </si>
+  <si>
+    <t>05.10.20268</t>
+  </si>
+  <si>
+    <t>05.10.20269</t>
+  </si>
+  <si>
+    <t>05.10.202610</t>
+  </si>
+  <si>
+    <t>05.10.202611</t>
+  </si>
+  <si>
+    <t>05.10.202612</t>
+  </si>
+  <si>
+    <t>05.10.202613</t>
+  </si>
+  <si>
+    <t>05.10.202614</t>
+  </si>
+  <si>
+    <t>05.10.202615</t>
+  </si>
+  <si>
+    <t>05.10.202616</t>
+  </si>
+  <si>
+    <t>05.10.202617</t>
+  </si>
+  <si>
+    <t>05.10.202618</t>
+  </si>
+  <si>
+    <t>05.10.202619</t>
+  </si>
+  <si>
+    <t>05.10.202620</t>
+  </si>
+  <si>
+    <t>05.10.202621</t>
+  </si>
+  <si>
+    <t>05.10.202622</t>
+  </si>
+  <si>
+    <t>05.10.202623</t>
+  </si>
+  <si>
+    <t>05.10.202624</t>
+  </si>
+  <si>
+    <t>05.10.202625</t>
+  </si>
+  <si>
+    <t>05.10.202626</t>
+  </si>
+  <si>
+    <t>05.10.202627</t>
+  </si>
+  <si>
+    <t>05.10.202628</t>
+  </si>
+  <si>
+    <t>05.10.202629</t>
+  </si>
+  <si>
+    <t>05.10.202630</t>
+  </si>
+  <si>
+    <t>05.10.202631</t>
+  </si>
+  <si>
+    <t>05.10.202632</t>
+  </si>
+  <si>
+    <t>05.10.202633</t>
+  </si>
+  <si>
+    <t>05.10.202634</t>
+  </si>
+  <si>
+    <t>05.10.202635</t>
+  </si>
+  <si>
+    <t>05.10.202636</t>
+  </si>
+  <si>
+    <t>05.10.202637</t>
+  </si>
+  <si>
+    <t>05.10.202638</t>
+  </si>
+  <si>
+    <t>05.10.202639</t>
+  </si>
+  <si>
+    <t>05.10.202640</t>
+  </si>
+  <si>
+    <t>05.10.202641</t>
+  </si>
+  <si>
+    <t>05.10.202642</t>
+  </si>
+  <si>
+    <t>05.10.202643</t>
+  </si>
+  <si>
+    <t>05.10.202644</t>
+  </si>
+  <si>
+    <t>05.10.202645</t>
+  </si>
+  <si>
+    <t>05.10.202646</t>
+  </si>
+  <si>
+    <t>05.10.202647</t>
+  </si>
+  <si>
+    <t>05.10.202648</t>
+  </si>
+  <si>
+    <t>05.10.202649</t>
+  </si>
+  <si>
+    <t>05.10.202650</t>
+  </si>
+  <si>
+    <t>05.10.202651</t>
+  </si>
+  <si>
+    <t>05.10.202652</t>
+  </si>
+  <si>
+    <t>05.10.202653</t>
+  </si>
+  <si>
+    <t>05.10.202654</t>
+  </si>
+  <si>
+    <t>05.10.202655</t>
+  </si>
+  <si>
+    <t>05.10.202656</t>
+  </si>
+  <si>
+    <t>05.10.202657</t>
+  </si>
+  <si>
+    <t>05.10.202658</t>
+  </si>
+  <si>
+    <t>05.10.202659</t>
+  </si>
+  <si>
+    <t>05.10.202660</t>
+  </si>
+  <si>
+    <t>05.10.202661</t>
+  </si>
+  <si>
+    <t>05.10.202662</t>
+  </si>
+  <si>
+    <t>05.10.202663</t>
+  </si>
+  <si>
+    <t>05.10.202664</t>
+  </si>
+  <si>
+    <t>05.10.202665</t>
+  </si>
+  <si>
+    <t>05.10.202666</t>
+  </si>
+  <si>
+    <t>05.10.202667</t>
+  </si>
+  <si>
+    <t>05.10.202668</t>
+  </si>
+  <si>
+    <t>05.10.202669</t>
+  </si>
+  <si>
+    <t>05.10.202670</t>
+  </si>
+  <si>
+    <t>05.10.202671</t>
+  </si>
+  <si>
+    <t>05.10.202672</t>
+  </si>
+  <si>
+    <t>05.10.202673</t>
+  </si>
+  <si>
+    <t>05.10.202674</t>
+  </si>
+  <si>
+    <t>05.10.202675</t>
+  </si>
+  <si>
+    <t>05.10.202676</t>
+  </si>
+  <si>
+    <t>05.10.202677</t>
+  </si>
+  <si>
+    <t>05.10.202678</t>
+  </si>
+  <si>
+    <t>05.10.202679</t>
+  </si>
+  <si>
+    <t>05.10.202680</t>
+  </si>
+  <si>
+    <t>05.10.202681</t>
+  </si>
+  <si>
+    <t>05.10.202682</t>
+  </si>
+  <si>
+    <t>05.10.202683</t>
+  </si>
+  <si>
+    <t>05.10.202684</t>
+  </si>
+  <si>
+    <t>05.10.202685</t>
+  </si>
+  <si>
+    <t>05.10.202686</t>
+  </si>
+  <si>
+    <t>05.10.202687</t>
+  </si>
+  <si>
+    <t>05.10.202688</t>
+  </si>
+  <si>
+    <t>05.10.202689</t>
+  </si>
+  <si>
+    <t>05.10.202690</t>
+  </si>
+  <si>
+    <t>05.10.202691</t>
+  </si>
+  <si>
+    <t>05.10.202692</t>
+  </si>
+  <si>
+    <t>05.10.202693</t>
+  </si>
+  <si>
+    <t>05.10.202694</t>
+  </si>
+  <si>
+    <t>05.10.202695</t>
+  </si>
+  <si>
+    <t>05.10.202696</t>
+  </si>
+  <si>
+    <t>06.10.20261</t>
+  </si>
+  <si>
+    <t>06.10.20262</t>
+  </si>
+  <si>
+    <t>06.10.20263</t>
+  </si>
+  <si>
+    <t>06.10.20264</t>
+  </si>
+  <si>
+    <t>06.10.20265</t>
+  </si>
+  <si>
+    <t>06.10.20266</t>
+  </si>
+  <si>
+    <t>06.10.20267</t>
+  </si>
+  <si>
+    <t>06.10.20268</t>
+  </si>
+  <si>
+    <t>06.10.20269</t>
+  </si>
+  <si>
+    <t>06.10.202610</t>
+  </si>
+  <si>
+    <t>06.10.202611</t>
+  </si>
+  <si>
+    <t>06.10.202612</t>
+  </si>
+  <si>
+    <t>06.10.202613</t>
+  </si>
+  <si>
+    <t>06.10.202614</t>
+  </si>
+  <si>
+    <t>06.10.202615</t>
+  </si>
+  <si>
+    <t>06.10.202616</t>
+  </si>
+  <si>
+    <t>06.10.202617</t>
+  </si>
+  <si>
+    <t>06.10.202618</t>
+  </si>
+  <si>
+    <t>06.10.202619</t>
+  </si>
+  <si>
+    <t>06.10.202620</t>
+  </si>
+  <si>
+    <t>06.10.202621</t>
+  </si>
+  <si>
+    <t>06.10.202622</t>
+  </si>
+  <si>
+    <t>06.10.202623</t>
+  </si>
+  <si>
+    <t>06.10.202624</t>
+  </si>
+  <si>
+    <t>06.10.202625</t>
+  </si>
+  <si>
+    <t>06.10.202626</t>
+  </si>
+  <si>
+    <t>06.10.202627</t>
+  </si>
+  <si>
+    <t>06.10.202628</t>
+  </si>
+  <si>
+    <t>06.10.202629</t>
+  </si>
+  <si>
+    <t>06.10.202630</t>
+  </si>
+  <si>
+    <t>06.10.202631</t>
+  </si>
+  <si>
+    <t>06.10.202632</t>
+  </si>
+  <si>
+    <t>06.10.202633</t>
+  </si>
+  <si>
+    <t>06.10.202634</t>
+  </si>
+  <si>
+    <t>06.10.202635</t>
+  </si>
+  <si>
+    <t>06.10.202636</t>
+  </si>
+  <si>
+    <t>06.10.202637</t>
+  </si>
+  <si>
+    <t>06.10.202638</t>
+  </si>
+  <si>
+    <t>06.10.202639</t>
+  </si>
+  <si>
+    <t>06.10.202640</t>
+  </si>
+  <si>
+    <t>06.10.202641</t>
+  </si>
+  <si>
+    <t>06.10.202642</t>
+  </si>
+  <si>
+    <t>06.10.202643</t>
+  </si>
+  <si>
+    <t>06.10.202644</t>
+  </si>
+  <si>
+    <t>06.10.202645</t>
+  </si>
+  <si>
+    <t>06.10.202646</t>
+  </si>
+  <si>
+    <t>06.10.202647</t>
+  </si>
+  <si>
+    <t>06.10.202648</t>
+  </si>
+  <si>
+    <t>06.10.202649</t>
+  </si>
+  <si>
+    <t>06.10.202650</t>
+  </si>
+  <si>
+    <t>06.10.202651</t>
+  </si>
+  <si>
+    <t>06.10.202652</t>
+  </si>
+  <si>
+    <t>06.10.202653</t>
+  </si>
+  <si>
+    <t>06.10.202654</t>
+  </si>
+  <si>
+    <t>06.10.202655</t>
+  </si>
+  <si>
+    <t>06.10.202656</t>
+  </si>
+  <si>
+    <t>06.10.202657</t>
+  </si>
+  <si>
+    <t>06.10.202658</t>
+  </si>
+  <si>
+    <t>06.10.202659</t>
+  </si>
+  <si>
+    <t>06.10.202660</t>
+  </si>
+  <si>
+    <t>06.10.202661</t>
+  </si>
+  <si>
+    <t>06.10.202662</t>
+  </si>
+  <si>
+    <t>06.10.202663</t>
+  </si>
+  <si>
+    <t>06.10.202664</t>
+  </si>
+  <si>
+    <t>06.10.202665</t>
+  </si>
+  <si>
+    <t>06.10.202666</t>
+  </si>
+  <si>
+    <t>06.10.202667</t>
+  </si>
+  <si>
+    <t>06.10.202668</t>
+  </si>
+  <si>
+    <t>06.10.202669</t>
+  </si>
+  <si>
+    <t>06.10.202670</t>
+  </si>
+  <si>
+    <t>06.10.202671</t>
+  </si>
+  <si>
+    <t>06.10.202672</t>
+  </si>
+  <si>
+    <t>06.10.202673</t>
+  </si>
+  <si>
+    <t>06.10.202674</t>
+  </si>
+  <si>
+    <t>06.10.202675</t>
+  </si>
+  <si>
+    <t>06.10.202676</t>
+  </si>
+  <si>
+    <t>06.10.202677</t>
+  </si>
+  <si>
+    <t>06.10.202678</t>
+  </si>
+  <si>
+    <t>06.10.202679</t>
+  </si>
+  <si>
+    <t>06.10.202680</t>
+  </si>
+  <si>
+    <t>06.10.202681</t>
+  </si>
+  <si>
+    <t>06.10.202682</t>
+  </si>
+  <si>
+    <t>06.10.202683</t>
+  </si>
+  <si>
+    <t>06.10.202684</t>
+  </si>
+  <si>
+    <t>06.10.202685</t>
+  </si>
+  <si>
+    <t>06.10.202686</t>
+  </si>
+  <si>
+    <t>06.10.202687</t>
+  </si>
+  <si>
+    <t>06.10.202688</t>
+  </si>
+  <si>
+    <t>06.10.202689</t>
+  </si>
+  <si>
+    <t>06.10.202690</t>
+  </si>
+  <si>
+    <t>06.10.202691</t>
+  </si>
+  <si>
+    <t>06.10.202692</t>
+  </si>
+  <si>
+    <t>06.10.202693</t>
+  </si>
+  <si>
+    <t>06.10.202694</t>
+  </si>
+  <si>
+    <t>06.10.202695</t>
+  </si>
+  <si>
+    <t>06.10.202696</t>
+  </si>
+  <si>
+    <t>07.10.20261</t>
+  </si>
+  <si>
+    <t>07.10.20262</t>
+  </si>
+  <si>
+    <t>07.10.20263</t>
+  </si>
+  <si>
+    <t>07.10.20264</t>
+  </si>
+  <si>
+    <t>07.10.20265</t>
+  </si>
+  <si>
+    <t>07.10.20266</t>
+  </si>
+  <si>
+    <t>07.10.20267</t>
+  </si>
+  <si>
+    <t>07.10.20268</t>
+  </si>
+  <si>
+    <t>07.10.20269</t>
+  </si>
+  <si>
+    <t>07.10.202610</t>
+  </si>
+  <si>
+    <t>07.10.202611</t>
+  </si>
+  <si>
+    <t>07.10.202612</t>
+  </si>
+  <si>
+    <t>07.10.202613</t>
+  </si>
+  <si>
+    <t>07.10.202614</t>
+  </si>
+  <si>
+    <t>07.10.202615</t>
+  </si>
+  <si>
+    <t>07.10.202616</t>
+  </si>
+  <si>
+    <t>07.10.202617</t>
+  </si>
+  <si>
+    <t>07.10.202618</t>
+  </si>
+  <si>
+    <t>07.10.202619</t>
+  </si>
+  <si>
+    <t>07.10.202620</t>
+  </si>
+  <si>
+    <t>07.10.202621</t>
+  </si>
+  <si>
+    <t>07.10.202622</t>
+  </si>
+  <si>
+    <t>07.10.202623</t>
+  </si>
+  <si>
+    <t>07.10.202624</t>
+  </si>
+  <si>
+    <t>07.10.202625</t>
+  </si>
+  <si>
+    <t>07.10.202626</t>
+  </si>
+  <si>
+    <t>07.10.202627</t>
+  </si>
+  <si>
+    <t>07.10.202628</t>
+  </si>
+  <si>
+    <t>07.10.202629</t>
+  </si>
+  <si>
+    <t>07.10.202630</t>
+  </si>
+  <si>
+    <t>07.10.202631</t>
+  </si>
+  <si>
+    <t>07.10.202632</t>
+  </si>
+  <si>
+    <t>07.10.202633</t>
+  </si>
+  <si>
+    <t>07.10.202634</t>
+  </si>
+  <si>
+    <t>07.10.202635</t>
+  </si>
+  <si>
+    <t>07.10.202636</t>
+  </si>
+  <si>
+    <t>07.10.202637</t>
+  </si>
+  <si>
+    <t>07.10.202638</t>
+  </si>
+  <si>
+    <t>07.10.202639</t>
+  </si>
+  <si>
+    <t>07.10.202640</t>
+  </si>
+  <si>
+    <t>07.10.202641</t>
   </si>
 </sst>
 </file>
@@ -783,7 +1665,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E132"/>
+  <dimension ref="A1:E426"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -3030,6 +3912,5004 @@
         <v>135</v>
       </c>
     </row>
+    <row r="133" spans="1:5">
+      <c r="A133" s="2">
+        <v>46299.36458333334</v>
+      </c>
+      <c r="B133">
+        <v>2.719</v>
+      </c>
+      <c r="C133">
+        <v>0</v>
+      </c>
+      <c r="D133">
+        <v>36</v>
+      </c>
+      <c r="E133" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5">
+      <c r="A134" s="2">
+        <v>46299.375</v>
+      </c>
+      <c r="B134">
+        <v>30.795</v>
+      </c>
+      <c r="C134">
+        <v>0</v>
+      </c>
+      <c r="D134">
+        <v>37</v>
+      </c>
+      <c r="E134" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5">
+      <c r="A135" s="2">
+        <v>46299.38541666666</v>
+      </c>
+      <c r="B135">
+        <v>43.443</v>
+      </c>
+      <c r="C135">
+        <v>0</v>
+      </c>
+      <c r="D135">
+        <v>38</v>
+      </c>
+      <c r="E135" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5">
+      <c r="A136" s="2">
+        <v>46299.39583333334</v>
+      </c>
+      <c r="B136">
+        <v>41.745</v>
+      </c>
+      <c r="C136">
+        <v>0</v>
+      </c>
+      <c r="D136">
+        <v>39</v>
+      </c>
+      <c r="E136" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5">
+      <c r="A137" s="2">
+        <v>46299.40625</v>
+      </c>
+      <c r="B137">
+        <v>27.902</v>
+      </c>
+      <c r="C137">
+        <v>0</v>
+      </c>
+      <c r="D137">
+        <v>40</v>
+      </c>
+      <c r="E137" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5">
+      <c r="A138" s="2">
+        <v>46299.41666666666</v>
+      </c>
+      <c r="B138">
+        <v>25.427</v>
+      </c>
+      <c r="C138">
+        <v>0</v>
+      </c>
+      <c r="D138">
+        <v>41</v>
+      </c>
+      <c r="E138" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5">
+      <c r="A139" s="2">
+        <v>46299.42708333334</v>
+      </c>
+      <c r="B139">
+        <v>25.407</v>
+      </c>
+      <c r="C139">
+        <v>0</v>
+      </c>
+      <c r="D139">
+        <v>42</v>
+      </c>
+      <c r="E139" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5">
+      <c r="A140" s="2">
+        <v>46299.4375</v>
+      </c>
+      <c r="B140">
+        <v>13.978</v>
+      </c>
+      <c r="C140">
+        <v>0</v>
+      </c>
+      <c r="D140">
+        <v>43</v>
+      </c>
+      <c r="E140" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5">
+      <c r="A141" s="2">
+        <v>46299.44791666666</v>
+      </c>
+      <c r="B141">
+        <v>1.948</v>
+      </c>
+      <c r="C141">
+        <v>0</v>
+      </c>
+      <c r="D141">
+        <v>44</v>
+      </c>
+      <c r="E141" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
+      <c r="A142" s="2">
+        <v>46299.45833333334</v>
+      </c>
+      <c r="B142">
+        <v>2.541</v>
+      </c>
+      <c r="C142">
+        <v>0</v>
+      </c>
+      <c r="D142">
+        <v>45</v>
+      </c>
+      <c r="E142" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143" s="2">
+        <v>46299.46875</v>
+      </c>
+      <c r="B143">
+        <v>4.217</v>
+      </c>
+      <c r="C143">
+        <v>0</v>
+      </c>
+      <c r="D143">
+        <v>46</v>
+      </c>
+      <c r="E143" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="A144" s="2">
+        <v>46299.47916666666</v>
+      </c>
+      <c r="B144">
+        <v>0.769</v>
+      </c>
+      <c r="C144">
+        <v>0</v>
+      </c>
+      <c r="D144">
+        <v>47</v>
+      </c>
+      <c r="E144" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145" s="2">
+        <v>46299.48958333334</v>
+      </c>
+      <c r="B145">
+        <v>7.001</v>
+      </c>
+      <c r="C145">
+        <v>0</v>
+      </c>
+      <c r="D145">
+        <v>48</v>
+      </c>
+      <c r="E145" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5">
+      <c r="A146" s="2">
+        <v>46299.5</v>
+      </c>
+      <c r="B146">
+        <v>0</v>
+      </c>
+      <c r="C146">
+        <v>16.619</v>
+      </c>
+      <c r="D146">
+        <v>49</v>
+      </c>
+      <c r="E146" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5">
+      <c r="A147" s="2">
+        <v>46299.51041666666</v>
+      </c>
+      <c r="B147">
+        <v>0</v>
+      </c>
+      <c r="C147">
+        <v>4.043</v>
+      </c>
+      <c r="D147">
+        <v>50</v>
+      </c>
+      <c r="E147" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5">
+      <c r="A148" s="2">
+        <v>46299.52083333334</v>
+      </c>
+      <c r="B148">
+        <v>0</v>
+      </c>
+      <c r="C148">
+        <v>6.397</v>
+      </c>
+      <c r="D148">
+        <v>51</v>
+      </c>
+      <c r="E148" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5">
+      <c r="A149" s="2">
+        <v>46299.53125</v>
+      </c>
+      <c r="B149">
+        <v>0</v>
+      </c>
+      <c r="C149">
+        <v>12.974</v>
+      </c>
+      <c r="D149">
+        <v>52</v>
+      </c>
+      <c r="E149" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5">
+      <c r="A150" s="2">
+        <v>46299.54166666666</v>
+      </c>
+      <c r="B150">
+        <v>0</v>
+      </c>
+      <c r="C150">
+        <v>0.213</v>
+      </c>
+      <c r="D150">
+        <v>53</v>
+      </c>
+      <c r="E150" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5">
+      <c r="A151" s="2">
+        <v>46299.55208333334</v>
+      </c>
+      <c r="B151">
+        <v>0</v>
+      </c>
+      <c r="C151">
+        <v>3.358</v>
+      </c>
+      <c r="D151">
+        <v>54</v>
+      </c>
+      <c r="E151" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5">
+      <c r="A152" s="2">
+        <v>46299.5625</v>
+      </c>
+      <c r="B152">
+        <v>0</v>
+      </c>
+      <c r="C152">
+        <v>6.886</v>
+      </c>
+      <c r="D152">
+        <v>55</v>
+      </c>
+      <c r="E152" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5">
+      <c r="A153" s="2">
+        <v>46299.57291666666</v>
+      </c>
+      <c r="B153">
+        <v>0</v>
+      </c>
+      <c r="C153">
+        <v>3.113</v>
+      </c>
+      <c r="D153">
+        <v>56</v>
+      </c>
+      <c r="E153" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5">
+      <c r="A154" s="2">
+        <v>46299.58333333334</v>
+      </c>
+      <c r="B154">
+        <v>0</v>
+      </c>
+      <c r="C154">
+        <v>6.409</v>
+      </c>
+      <c r="D154">
+        <v>57</v>
+      </c>
+      <c r="E154" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5">
+      <c r="A155" s="2">
+        <v>46299.59375</v>
+      </c>
+      <c r="B155">
+        <v>0</v>
+      </c>
+      <c r="C155">
+        <v>9.065</v>
+      </c>
+      <c r="D155">
+        <v>58</v>
+      </c>
+      <c r="E155" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5">
+      <c r="A156" s="2">
+        <v>46299.60416666666</v>
+      </c>
+      <c r="B156">
+        <v>0</v>
+      </c>
+      <c r="C156">
+        <v>5.342</v>
+      </c>
+      <c r="D156">
+        <v>59</v>
+      </c>
+      <c r="E156" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5">
+      <c r="A157" s="2">
+        <v>46299.61458333334</v>
+      </c>
+      <c r="B157">
+        <v>0</v>
+      </c>
+      <c r="C157">
+        <v>4.577</v>
+      </c>
+      <c r="D157">
+        <v>60</v>
+      </c>
+      <c r="E157" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5">
+      <c r="A158" s="2">
+        <v>46299.625</v>
+      </c>
+      <c r="B158">
+        <v>0</v>
+      </c>
+      <c r="C158">
+        <v>16.643</v>
+      </c>
+      <c r="D158">
+        <v>61</v>
+      </c>
+      <c r="E158" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5">
+      <c r="A159" s="2">
+        <v>46299.63541666666</v>
+      </c>
+      <c r="B159">
+        <v>0</v>
+      </c>
+      <c r="C159">
+        <v>22.858</v>
+      </c>
+      <c r="D159">
+        <v>62</v>
+      </c>
+      <c r="E159" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5">
+      <c r="A160" s="2">
+        <v>46299.64583333334</v>
+      </c>
+      <c r="B160">
+        <v>0</v>
+      </c>
+      <c r="C160">
+        <v>19.063</v>
+      </c>
+      <c r="D160">
+        <v>63</v>
+      </c>
+      <c r="E160" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5">
+      <c r="A161" s="2">
+        <v>46299.65625</v>
+      </c>
+      <c r="B161">
+        <v>0</v>
+      </c>
+      <c r="C161">
+        <v>14.724</v>
+      </c>
+      <c r="D161">
+        <v>64</v>
+      </c>
+      <c r="E161" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5">
+      <c r="A162" s="2">
+        <v>46299.66666666666</v>
+      </c>
+      <c r="B162">
+        <v>0</v>
+      </c>
+      <c r="C162">
+        <v>6.38</v>
+      </c>
+      <c r="D162">
+        <v>65</v>
+      </c>
+      <c r="E162" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5">
+      <c r="A163" s="2">
+        <v>46299.67708333334</v>
+      </c>
+      <c r="B163">
+        <v>0</v>
+      </c>
+      <c r="C163">
+        <v>3.194</v>
+      </c>
+      <c r="D163">
+        <v>66</v>
+      </c>
+      <c r="E163" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5">
+      <c r="A164" s="2">
+        <v>46299.6875</v>
+      </c>
+      <c r="B164">
+        <v>0.897</v>
+      </c>
+      <c r="C164">
+        <v>0</v>
+      </c>
+      <c r="D164">
+        <v>67</v>
+      </c>
+      <c r="E164" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5">
+      <c r="A165" s="2">
+        <v>46299.69791666666</v>
+      </c>
+      <c r="B165">
+        <v>0</v>
+      </c>
+      <c r="C165">
+        <v>5.462</v>
+      </c>
+      <c r="D165">
+        <v>68</v>
+      </c>
+      <c r="E165" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5">
+      <c r="A166" s="2">
+        <v>46299.70833333334</v>
+      </c>
+      <c r="B166">
+        <v>0</v>
+      </c>
+      <c r="C166">
+        <v>24.315</v>
+      </c>
+      <c r="D166">
+        <v>69</v>
+      </c>
+      <c r="E166" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5">
+      <c r="A167" s="2">
+        <v>46299.71875</v>
+      </c>
+      <c r="B167">
+        <v>0</v>
+      </c>
+      <c r="C167">
+        <v>1.349</v>
+      </c>
+      <c r="D167">
+        <v>70</v>
+      </c>
+      <c r="E167" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5">
+      <c r="A168" s="2">
+        <v>46299.72916666666</v>
+      </c>
+      <c r="B168">
+        <v>0</v>
+      </c>
+      <c r="C168">
+        <v>5.743</v>
+      </c>
+      <c r="D168">
+        <v>71</v>
+      </c>
+      <c r="E168" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5">
+      <c r="A169" s="2">
+        <v>46299.73958333334</v>
+      </c>
+      <c r="B169">
+        <v>0</v>
+      </c>
+      <c r="C169">
+        <v>12.329</v>
+      </c>
+      <c r="D169">
+        <v>72</v>
+      </c>
+      <c r="E169" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5">
+      <c r="A170" s="2">
+        <v>46299.75</v>
+      </c>
+      <c r="B170">
+        <v>0</v>
+      </c>
+      <c r="C170">
+        <v>10.869</v>
+      </c>
+      <c r="D170">
+        <v>73</v>
+      </c>
+      <c r="E170" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5">
+      <c r="A171" s="2">
+        <v>46299.76041666666</v>
+      </c>
+      <c r="B171">
+        <v>0</v>
+      </c>
+      <c r="C171">
+        <v>9.646000000000001</v>
+      </c>
+      <c r="D171">
+        <v>74</v>
+      </c>
+      <c r="E171" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5">
+      <c r="A172" s="2">
+        <v>46299.77083333334</v>
+      </c>
+      <c r="B172">
+        <v>0</v>
+      </c>
+      <c r="C172">
+        <v>3.544</v>
+      </c>
+      <c r="D172">
+        <v>75</v>
+      </c>
+      <c r="E172" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5">
+      <c r="A173" s="2">
+        <v>46299.78125</v>
+      </c>
+      <c r="B173">
+        <v>0</v>
+      </c>
+      <c r="C173">
+        <v>18.909</v>
+      </c>
+      <c r="D173">
+        <v>76</v>
+      </c>
+      <c r="E173" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5">
+      <c r="A174" s="2">
+        <v>46299.79166666666</v>
+      </c>
+      <c r="B174">
+        <v>0</v>
+      </c>
+      <c r="C174">
+        <v>19.213</v>
+      </c>
+      <c r="D174">
+        <v>77</v>
+      </c>
+      <c r="E174" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5">
+      <c r="A175" s="2">
+        <v>46299.80208333334</v>
+      </c>
+      <c r="B175">
+        <v>0</v>
+      </c>
+      <c r="C175">
+        <v>29.264</v>
+      </c>
+      <c r="D175">
+        <v>78</v>
+      </c>
+      <c r="E175" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5">
+      <c r="A176" s="2">
+        <v>46299.8125</v>
+      </c>
+      <c r="B176">
+        <v>0</v>
+      </c>
+      <c r="C176">
+        <v>23.425</v>
+      </c>
+      <c r="D176">
+        <v>79</v>
+      </c>
+      <c r="E176" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5">
+      <c r="A177" s="2">
+        <v>46299.82291666666</v>
+      </c>
+      <c r="B177">
+        <v>0</v>
+      </c>
+      <c r="C177">
+        <v>29.795</v>
+      </c>
+      <c r="D177">
+        <v>80</v>
+      </c>
+      <c r="E177" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5">
+      <c r="A178" s="2">
+        <v>46299.83333333334</v>
+      </c>
+      <c r="B178">
+        <v>0</v>
+      </c>
+      <c r="C178">
+        <v>17.02</v>
+      </c>
+      <c r="D178">
+        <v>81</v>
+      </c>
+      <c r="E178" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5">
+      <c r="A179" s="2">
+        <v>46299.84375</v>
+      </c>
+      <c r="B179">
+        <v>0</v>
+      </c>
+      <c r="C179">
+        <v>22.425</v>
+      </c>
+      <c r="D179">
+        <v>82</v>
+      </c>
+      <c r="E179" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5">
+      <c r="A180" s="2">
+        <v>46299.85416666666</v>
+      </c>
+      <c r="B180">
+        <v>0</v>
+      </c>
+      <c r="C180">
+        <v>30.006</v>
+      </c>
+      <c r="D180">
+        <v>83</v>
+      </c>
+      <c r="E180" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5">
+      <c r="A181" s="2">
+        <v>46299.86458333334</v>
+      </c>
+      <c r="B181">
+        <v>0</v>
+      </c>
+      <c r="C181">
+        <v>16.211</v>
+      </c>
+      <c r="D181">
+        <v>84</v>
+      </c>
+      <c r="E181" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5">
+      <c r="A182" s="2">
+        <v>46299.875</v>
+      </c>
+      <c r="B182">
+        <v>0</v>
+      </c>
+      <c r="C182">
+        <v>1.141</v>
+      </c>
+      <c r="D182">
+        <v>85</v>
+      </c>
+      <c r="E182" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5">
+      <c r="A183" s="2">
+        <v>46299.88541666666</v>
+      </c>
+      <c r="B183">
+        <v>0</v>
+      </c>
+      <c r="C183">
+        <v>5.72</v>
+      </c>
+      <c r="D183">
+        <v>86</v>
+      </c>
+      <c r="E183" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5">
+      <c r="A184" s="2">
+        <v>46299.89583333334</v>
+      </c>
+      <c r="B184">
+        <v>0</v>
+      </c>
+      <c r="C184">
+        <v>3.704</v>
+      </c>
+      <c r="D184">
+        <v>87</v>
+      </c>
+      <c r="E184" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5">
+      <c r="A185" s="2">
+        <v>46299.90625</v>
+      </c>
+      <c r="B185">
+        <v>0</v>
+      </c>
+      <c r="C185">
+        <v>7.016</v>
+      </c>
+      <c r="D185">
+        <v>88</v>
+      </c>
+      <c r="E185" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5">
+      <c r="A186" s="2">
+        <v>46299.91666666666</v>
+      </c>
+      <c r="B186">
+        <v>0</v>
+      </c>
+      <c r="C186">
+        <v>21.127</v>
+      </c>
+      <c r="D186">
+        <v>89</v>
+      </c>
+      <c r="E186" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5">
+      <c r="A187" s="2">
+        <v>46299.92708333334</v>
+      </c>
+      <c r="B187">
+        <v>0</v>
+      </c>
+      <c r="C187">
+        <v>24.552</v>
+      </c>
+      <c r="D187">
+        <v>90</v>
+      </c>
+      <c r="E187" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5">
+      <c r="A188" s="2">
+        <v>46299.9375</v>
+      </c>
+      <c r="B188">
+        <v>0</v>
+      </c>
+      <c r="C188">
+        <v>15.112</v>
+      </c>
+      <c r="D188">
+        <v>91</v>
+      </c>
+      <c r="E188" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5">
+      <c r="A189" s="2">
+        <v>46299.94791666666</v>
+      </c>
+      <c r="B189">
+        <v>0</v>
+      </c>
+      <c r="C189">
+        <v>18.164</v>
+      </c>
+      <c r="D189">
+        <v>92</v>
+      </c>
+      <c r="E189" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5">
+      <c r="A190" s="2">
+        <v>46299.95833333334</v>
+      </c>
+      <c r="B190">
+        <v>0</v>
+      </c>
+      <c r="C190">
+        <v>45.307</v>
+      </c>
+      <c r="D190">
+        <v>93</v>
+      </c>
+      <c r="E190" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5">
+      <c r="A191" s="2">
+        <v>46299.96875</v>
+      </c>
+      <c r="B191">
+        <v>0</v>
+      </c>
+      <c r="C191">
+        <v>17.804</v>
+      </c>
+      <c r="D191">
+        <v>94</v>
+      </c>
+      <c r="E191" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5">
+      <c r="A192" s="2">
+        <v>46299.97916666666</v>
+      </c>
+      <c r="B192">
+        <v>5.859</v>
+      </c>
+      <c r="C192">
+        <v>0</v>
+      </c>
+      <c r="D192">
+        <v>95</v>
+      </c>
+      <c r="E192" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5">
+      <c r="A193" s="2">
+        <v>46299.98958333334</v>
+      </c>
+      <c r="B193">
+        <v>3.867</v>
+      </c>
+      <c r="C193">
+        <v>0</v>
+      </c>
+      <c r="D193">
+        <v>96</v>
+      </c>
+      <c r="E193" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5">
+      <c r="A194" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B194">
+        <v>2.312</v>
+      </c>
+      <c r="C194">
+        <v>0</v>
+      </c>
+      <c r="D194">
+        <v>1</v>
+      </c>
+      <c r="E194" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5">
+      <c r="A195" s="2">
+        <v>46300.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>21.938</v>
+      </c>
+      <c r="C195">
+        <v>0</v>
+      </c>
+      <c r="D195">
+        <v>2</v>
+      </c>
+      <c r="E195" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5">
+      <c r="A196" s="2">
+        <v>46300.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>29.429</v>
+      </c>
+      <c r="C196">
+        <v>0</v>
+      </c>
+      <c r="D196">
+        <v>3</v>
+      </c>
+      <c r="E196" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="A197" s="2">
+        <v>46300.03125</v>
+      </c>
+      <c r="B197">
+        <v>3.813</v>
+      </c>
+      <c r="C197">
+        <v>0</v>
+      </c>
+      <c r="D197">
+        <v>4</v>
+      </c>
+      <c r="E197" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="A198" s="2">
+        <v>46300.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>0</v>
+      </c>
+      <c r="C198">
+        <v>6.334</v>
+      </c>
+      <c r="D198">
+        <v>5</v>
+      </c>
+      <c r="E198" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5">
+      <c r="A199" s="2">
+        <v>46300.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>0</v>
+      </c>
+      <c r="C199">
+        <v>6.514</v>
+      </c>
+      <c r="D199">
+        <v>6</v>
+      </c>
+      <c r="E199" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="A200" s="2">
+        <v>46300.0625</v>
+      </c>
+      <c r="B200">
+        <v>0</v>
+      </c>
+      <c r="C200">
+        <v>5.71</v>
+      </c>
+      <c r="D200">
+        <v>7</v>
+      </c>
+      <c r="E200" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5">
+      <c r="A201" s="2">
+        <v>46300.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>0</v>
+      </c>
+      <c r="C201">
+        <v>0.606</v>
+      </c>
+      <c r="D201">
+        <v>8</v>
+      </c>
+      <c r="E201" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5">
+      <c r="A202" s="2">
+        <v>46300.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>0</v>
+      </c>
+      <c r="C202">
+        <v>2.824</v>
+      </c>
+      <c r="D202">
+        <v>9</v>
+      </c>
+      <c r="E202" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5">
+      <c r="A203" s="2">
+        <v>46300.09375</v>
+      </c>
+      <c r="B203">
+        <v>0</v>
+      </c>
+      <c r="C203">
+        <v>5.862</v>
+      </c>
+      <c r="D203">
+        <v>10</v>
+      </c>
+      <c r="E203" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5">
+      <c r="A204" s="2">
+        <v>46300.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>1.951</v>
+      </c>
+      <c r="C204">
+        <v>0</v>
+      </c>
+      <c r="D204">
+        <v>11</v>
+      </c>
+      <c r="E204" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5">
+      <c r="A205" s="2">
+        <v>46300.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>9.952</v>
+      </c>
+      <c r="C205">
+        <v>0</v>
+      </c>
+      <c r="D205">
+        <v>12</v>
+      </c>
+      <c r="E205" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5">
+      <c r="A206" s="2">
+        <v>46300.125</v>
+      </c>
+      <c r="B206">
+        <v>1.387</v>
+      </c>
+      <c r="C206">
+        <v>0</v>
+      </c>
+      <c r="D206">
+        <v>13</v>
+      </c>
+      <c r="E206" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5">
+      <c r="A207" s="2">
+        <v>46300.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>4.388</v>
+      </c>
+      <c r="C207">
+        <v>0</v>
+      </c>
+      <c r="D207">
+        <v>14</v>
+      </c>
+      <c r="E207" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5">
+      <c r="A208" s="2">
+        <v>46300.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>6.552</v>
+      </c>
+      <c r="C208">
+        <v>0</v>
+      </c>
+      <c r="D208">
+        <v>15</v>
+      </c>
+      <c r="E208" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5">
+      <c r="A209" s="2">
+        <v>46300.15625</v>
+      </c>
+      <c r="B209">
+        <v>8.225</v>
+      </c>
+      <c r="C209">
+        <v>0</v>
+      </c>
+      <c r="D209">
+        <v>16</v>
+      </c>
+      <c r="E209" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5">
+      <c r="A210" s="2">
+        <v>46300.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>0</v>
+      </c>
+      <c r="C210">
+        <v>2.892</v>
+      </c>
+      <c r="D210">
+        <v>17</v>
+      </c>
+      <c r="E210" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5">
+      <c r="A211" s="2">
+        <v>46300.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>4.122</v>
+      </c>
+      <c r="C211">
+        <v>0</v>
+      </c>
+      <c r="D211">
+        <v>18</v>
+      </c>
+      <c r="E211" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5">
+      <c r="A212" s="2">
+        <v>46300.1875</v>
+      </c>
+      <c r="B212">
+        <v>0</v>
+      </c>
+      <c r="C212">
+        <v>2.497</v>
+      </c>
+      <c r="D212">
+        <v>19</v>
+      </c>
+      <c r="E212" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5">
+      <c r="A213" s="2">
+        <v>46300.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>20.296</v>
+      </c>
+      <c r="C213">
+        <v>0</v>
+      </c>
+      <c r="D213">
+        <v>20</v>
+      </c>
+      <c r="E213" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5">
+      <c r="A214" s="2">
+        <v>46300.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>1.225</v>
+      </c>
+      <c r="C214">
+        <v>0</v>
+      </c>
+      <c r="D214">
+        <v>21</v>
+      </c>
+      <c r="E214" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5">
+      <c r="A215" s="2">
+        <v>46300.21875</v>
+      </c>
+      <c r="B215">
+        <v>0</v>
+      </c>
+      <c r="C215">
+        <v>0.47</v>
+      </c>
+      <c r="D215">
+        <v>22</v>
+      </c>
+      <c r="E215" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5">
+      <c r="A216" s="2">
+        <v>46300.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>0.96</v>
+      </c>
+      <c r="C216">
+        <v>0</v>
+      </c>
+      <c r="D216">
+        <v>23</v>
+      </c>
+      <c r="E216" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5">
+      <c r="A217" s="2">
+        <v>46300.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>3.577</v>
+      </c>
+      <c r="C217">
+        <v>0</v>
+      </c>
+      <c r="D217">
+        <v>24</v>
+      </c>
+      <c r="E217" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5">
+      <c r="A218" s="2">
+        <v>46300.25</v>
+      </c>
+      <c r="B218">
+        <v>0</v>
+      </c>
+      <c r="C218">
+        <v>20.909</v>
+      </c>
+      <c r="D218">
+        <v>25</v>
+      </c>
+      <c r="E218" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5">
+      <c r="A219" s="2">
+        <v>46300.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>0</v>
+      </c>
+      <c r="C219">
+        <v>19.216</v>
+      </c>
+      <c r="D219">
+        <v>26</v>
+      </c>
+      <c r="E219" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5">
+      <c r="A220" s="2">
+        <v>46300.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>0</v>
+      </c>
+      <c r="C220">
+        <v>12.568</v>
+      </c>
+      <c r="D220">
+        <v>27</v>
+      </c>
+      <c r="E220" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5">
+      <c r="A221" s="2">
+        <v>46300.28125</v>
+      </c>
+      <c r="B221">
+        <v>0</v>
+      </c>
+      <c r="C221">
+        <v>8.565</v>
+      </c>
+      <c r="D221">
+        <v>28</v>
+      </c>
+      <c r="E221" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5">
+      <c r="A222" s="2">
+        <v>46300.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>0</v>
+      </c>
+      <c r="C222">
+        <v>3.652</v>
+      </c>
+      <c r="D222">
+        <v>29</v>
+      </c>
+      <c r="E222" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5">
+      <c r="A223" s="2">
+        <v>46300.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>0</v>
+      </c>
+      <c r="C223">
+        <v>8.093</v>
+      </c>
+      <c r="D223">
+        <v>30</v>
+      </c>
+      <c r="E223" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5">
+      <c r="A224" s="2">
+        <v>46300.3125</v>
+      </c>
+      <c r="B224">
+        <v>0</v>
+      </c>
+      <c r="C224">
+        <v>10.069</v>
+      </c>
+      <c r="D224">
+        <v>31</v>
+      </c>
+      <c r="E224" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5">
+      <c r="A225" s="2">
+        <v>46300.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>0</v>
+      </c>
+      <c r="C225">
+        <v>8.965</v>
+      </c>
+      <c r="D225">
+        <v>32</v>
+      </c>
+      <c r="E225" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5">
+      <c r="A226" s="2">
+        <v>46300.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>0</v>
+      </c>
+      <c r="C226">
+        <v>20.905</v>
+      </c>
+      <c r="D226">
+        <v>33</v>
+      </c>
+      <c r="E226" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5">
+      <c r="A227" s="2">
+        <v>46300.34375</v>
+      </c>
+      <c r="B227">
+        <v>0</v>
+      </c>
+      <c r="C227">
+        <v>23.565</v>
+      </c>
+      <c r="D227">
+        <v>34</v>
+      </c>
+      <c r="E227" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5">
+      <c r="A228" s="2">
+        <v>46300.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>0</v>
+      </c>
+      <c r="C228">
+        <v>14.658</v>
+      </c>
+      <c r="D228">
+        <v>35</v>
+      </c>
+      <c r="E228" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5">
+      <c r="A229" s="2">
+        <v>46300.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>0</v>
+      </c>
+      <c r="C229">
+        <v>0.058</v>
+      </c>
+      <c r="D229">
+        <v>36</v>
+      </c>
+      <c r="E229" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5">
+      <c r="A230" s="2">
+        <v>46300.375</v>
+      </c>
+      <c r="B230">
+        <v>24.611</v>
+      </c>
+      <c r="C230">
+        <v>0</v>
+      </c>
+      <c r="D230">
+        <v>37</v>
+      </c>
+      <c r="E230" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5">
+      <c r="A231" s="2">
+        <v>46300.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>0</v>
+      </c>
+      <c r="C231">
+        <v>0.231</v>
+      </c>
+      <c r="D231">
+        <v>38</v>
+      </c>
+      <c r="E231" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5">
+      <c r="A232" s="2">
+        <v>46300.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>1.403</v>
+      </c>
+      <c r="C232">
+        <v>0</v>
+      </c>
+      <c r="D232">
+        <v>39</v>
+      </c>
+      <c r="E232" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5">
+      <c r="A233" s="2">
+        <v>46300.40625</v>
+      </c>
+      <c r="B233">
+        <v>8.010999999999999</v>
+      </c>
+      <c r="C233">
+        <v>0</v>
+      </c>
+      <c r="D233">
+        <v>40</v>
+      </c>
+      <c r="E233" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5">
+      <c r="A234" s="2">
+        <v>46300.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>23.825</v>
+      </c>
+      <c r="C234">
+        <v>0</v>
+      </c>
+      <c r="D234">
+        <v>41</v>
+      </c>
+      <c r="E234" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5">
+      <c r="A235" s="2">
+        <v>46300.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>16.474</v>
+      </c>
+      <c r="C235">
+        <v>0</v>
+      </c>
+      <c r="D235">
+        <v>42</v>
+      </c>
+      <c r="E235" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5">
+      <c r="A236" s="2">
+        <v>46300.4375</v>
+      </c>
+      <c r="B236">
+        <v>0</v>
+      </c>
+      <c r="C236">
+        <v>6.415</v>
+      </c>
+      <c r="D236">
+        <v>43</v>
+      </c>
+      <c r="E236" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5">
+      <c r="A237" s="2">
+        <v>46300.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>0</v>
+      </c>
+      <c r="C237">
+        <v>25.07</v>
+      </c>
+      <c r="D237">
+        <v>44</v>
+      </c>
+      <c r="E237" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5">
+      <c r="A238" s="2">
+        <v>46300.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>0</v>
+      </c>
+      <c r="C238">
+        <v>10.775</v>
+      </c>
+      <c r="D238">
+        <v>45</v>
+      </c>
+      <c r="E238" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5">
+      <c r="A239" s="2">
+        <v>46300.46875</v>
+      </c>
+      <c r="B239">
+        <v>0</v>
+      </c>
+      <c r="C239">
+        <v>11.276</v>
+      </c>
+      <c r="D239">
+        <v>46</v>
+      </c>
+      <c r="E239" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5">
+      <c r="A240" s="2">
+        <v>46300.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>0</v>
+      </c>
+      <c r="C240">
+        <v>5.172</v>
+      </c>
+      <c r="D240">
+        <v>47</v>
+      </c>
+      <c r="E240" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5">
+      <c r="A241" s="2">
+        <v>46300.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>0</v>
+      </c>
+      <c r="C241">
+        <v>1.729</v>
+      </c>
+      <c r="D241">
+        <v>48</v>
+      </c>
+      <c r="E241" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5">
+      <c r="A242" s="2">
+        <v>46300.5</v>
+      </c>
+      <c r="B242">
+        <v>0</v>
+      </c>
+      <c r="C242">
+        <v>1.53</v>
+      </c>
+      <c r="D242">
+        <v>49</v>
+      </c>
+      <c r="E242" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5">
+      <c r="A243" s="2">
+        <v>46300.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>0</v>
+      </c>
+      <c r="C243">
+        <v>12.458</v>
+      </c>
+      <c r="D243">
+        <v>50</v>
+      </c>
+      <c r="E243" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5">
+      <c r="A244" s="2">
+        <v>46300.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>0</v>
+      </c>
+      <c r="C244">
+        <v>2.05</v>
+      </c>
+      <c r="D244">
+        <v>51</v>
+      </c>
+      <c r="E244" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5">
+      <c r="A245" s="2">
+        <v>46300.53125</v>
+      </c>
+      <c r="B245">
+        <v>4.879</v>
+      </c>
+      <c r="C245">
+        <v>0</v>
+      </c>
+      <c r="D245">
+        <v>52</v>
+      </c>
+      <c r="E245" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5">
+      <c r="A246" s="2">
+        <v>46300.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>0.527</v>
+      </c>
+      <c r="C246">
+        <v>0</v>
+      </c>
+      <c r="D246">
+        <v>53</v>
+      </c>
+      <c r="E246" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5">
+      <c r="A247" s="2">
+        <v>46300.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>0</v>
+      </c>
+      <c r="C247">
+        <v>4.552</v>
+      </c>
+      <c r="D247">
+        <v>54</v>
+      </c>
+      <c r="E247" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5">
+      <c r="A248" s="2">
+        <v>46300.5625</v>
+      </c>
+      <c r="B248">
+        <v>0</v>
+      </c>
+      <c r="C248">
+        <v>5.231</v>
+      </c>
+      <c r="D248">
+        <v>55</v>
+      </c>
+      <c r="E248" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5">
+      <c r="A249" s="2">
+        <v>46300.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>0</v>
+      </c>
+      <c r="C249">
+        <v>4.835</v>
+      </c>
+      <c r="D249">
+        <v>56</v>
+      </c>
+      <c r="E249" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5">
+      <c r="A250" s="2">
+        <v>46300.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>0</v>
+      </c>
+      <c r="C250">
+        <v>20.812</v>
+      </c>
+      <c r="D250">
+        <v>57</v>
+      </c>
+      <c r="E250" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5">
+      <c r="A251" s="2">
+        <v>46300.59375</v>
+      </c>
+      <c r="B251">
+        <v>0</v>
+      </c>
+      <c r="C251">
+        <v>8.507</v>
+      </c>
+      <c r="D251">
+        <v>58</v>
+      </c>
+      <c r="E251" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5">
+      <c r="A252" s="2">
+        <v>46300.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>0</v>
+      </c>
+      <c r="C252">
+        <v>29.858</v>
+      </c>
+      <c r="D252">
+        <v>59</v>
+      </c>
+      <c r="E252" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5">
+      <c r="A253" s="2">
+        <v>46300.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>0</v>
+      </c>
+      <c r="C253">
+        <v>0.284</v>
+      </c>
+      <c r="D253">
+        <v>60</v>
+      </c>
+      <c r="E253" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5">
+      <c r="A254" s="2">
+        <v>46300.625</v>
+      </c>
+      <c r="B254">
+        <v>0</v>
+      </c>
+      <c r="C254">
+        <v>42.844</v>
+      </c>
+      <c r="D254">
+        <v>61</v>
+      </c>
+      <c r="E254" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5">
+      <c r="A255" s="2">
+        <v>46300.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>0</v>
+      </c>
+      <c r="C255">
+        <v>36.761</v>
+      </c>
+      <c r="D255">
+        <v>62</v>
+      </c>
+      <c r="E255" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5">
+      <c r="A256" s="2">
+        <v>46300.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>0</v>
+      </c>
+      <c r="C256">
+        <v>51.961</v>
+      </c>
+      <c r="D256">
+        <v>63</v>
+      </c>
+      <c r="E256" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5">
+      <c r="A257" s="2">
+        <v>46300.65625</v>
+      </c>
+      <c r="B257">
+        <v>0</v>
+      </c>
+      <c r="C257">
+        <v>29.416</v>
+      </c>
+      <c r="D257">
+        <v>64</v>
+      </c>
+      <c r="E257" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5">
+      <c r="A258" s="2">
+        <v>46300.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>12.692</v>
+      </c>
+      <c r="C258">
+        <v>0</v>
+      </c>
+      <c r="D258">
+        <v>65</v>
+      </c>
+      <c r="E258" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5">
+      <c r="A259" s="2">
+        <v>46300.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>0</v>
+      </c>
+      <c r="C259">
+        <v>12.456</v>
+      </c>
+      <c r="D259">
+        <v>66</v>
+      </c>
+      <c r="E259" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5">
+      <c r="A260" s="2">
+        <v>46300.6875</v>
+      </c>
+      <c r="B260">
+        <v>1.397</v>
+      </c>
+      <c r="C260">
+        <v>0</v>
+      </c>
+      <c r="D260">
+        <v>67</v>
+      </c>
+      <c r="E260" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5">
+      <c r="A261" s="2">
+        <v>46300.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>4.548</v>
+      </c>
+      <c r="C261">
+        <v>0</v>
+      </c>
+      <c r="D261">
+        <v>68</v>
+      </c>
+      <c r="E261" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5">
+      <c r="A262" s="2">
+        <v>46300.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>0</v>
+      </c>
+      <c r="C262">
+        <v>13.662</v>
+      </c>
+      <c r="D262">
+        <v>69</v>
+      </c>
+      <c r="E262" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5">
+      <c r="A263" s="2">
+        <v>46300.71875</v>
+      </c>
+      <c r="B263">
+        <v>0</v>
+      </c>
+      <c r="C263">
+        <v>0.62</v>
+      </c>
+      <c r="D263">
+        <v>70</v>
+      </c>
+      <c r="E263" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5">
+      <c r="A264" s="2">
+        <v>46300.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>0</v>
+      </c>
+      <c r="C264">
+        <v>3.959</v>
+      </c>
+      <c r="D264">
+        <v>71</v>
+      </c>
+      <c r="E264" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5">
+      <c r="A265" s="2">
+        <v>46300.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>0</v>
+      </c>
+      <c r="C265">
+        <v>4.05</v>
+      </c>
+      <c r="D265">
+        <v>72</v>
+      </c>
+      <c r="E265" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5">
+      <c r="A266" s="2">
+        <v>46300.75</v>
+      </c>
+      <c r="B266">
+        <v>0</v>
+      </c>
+      <c r="C266">
+        <v>15.144</v>
+      </c>
+      <c r="D266">
+        <v>73</v>
+      </c>
+      <c r="E266" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5">
+      <c r="A267" s="2">
+        <v>46300.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>0</v>
+      </c>
+      <c r="C267">
+        <v>12.023</v>
+      </c>
+      <c r="D267">
+        <v>74</v>
+      </c>
+      <c r="E267" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5">
+      <c r="A268" s="2">
+        <v>46300.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>0.487</v>
+      </c>
+      <c r="C268">
+        <v>0</v>
+      </c>
+      <c r="D268">
+        <v>75</v>
+      </c>
+      <c r="E268" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5">
+      <c r="A269" s="2">
+        <v>46300.78125</v>
+      </c>
+      <c r="B269">
+        <v>0</v>
+      </c>
+      <c r="C269">
+        <v>1.665</v>
+      </c>
+      <c r="D269">
+        <v>76</v>
+      </c>
+      <c r="E269" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5">
+      <c r="A270" s="2">
+        <v>46300.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>4.345</v>
+      </c>
+      <c r="C270">
+        <v>0</v>
+      </c>
+      <c r="D270">
+        <v>77</v>
+      </c>
+      <c r="E270" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5">
+      <c r="A271" s="2">
+        <v>46300.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>0</v>
+      </c>
+      <c r="C271">
+        <v>1.606</v>
+      </c>
+      <c r="D271">
+        <v>78</v>
+      </c>
+      <c r="E271" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5">
+      <c r="A272" s="2">
+        <v>46300.8125</v>
+      </c>
+      <c r="B272">
+        <v>0</v>
+      </c>
+      <c r="C272">
+        <v>0.535</v>
+      </c>
+      <c r="D272">
+        <v>79</v>
+      </c>
+      <c r="E272" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5">
+      <c r="A273" s="2">
+        <v>46300.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>1.967</v>
+      </c>
+      <c r="C273">
+        <v>0</v>
+      </c>
+      <c r="D273">
+        <v>80</v>
+      </c>
+      <c r="E273" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5">
+      <c r="A274" s="2">
+        <v>46300.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>17.301</v>
+      </c>
+      <c r="C274">
+        <v>0</v>
+      </c>
+      <c r="D274">
+        <v>81</v>
+      </c>
+      <c r="E274" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5">
+      <c r="A275" s="2">
+        <v>46300.84375</v>
+      </c>
+      <c r="B275">
+        <v>0</v>
+      </c>
+      <c r="C275">
+        <v>3.624</v>
+      </c>
+      <c r="D275">
+        <v>82</v>
+      </c>
+      <c r="E275" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5">
+      <c r="A276" s="2">
+        <v>46300.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>0</v>
+      </c>
+      <c r="C276">
+        <v>12.156</v>
+      </c>
+      <c r="D276">
+        <v>83</v>
+      </c>
+      <c r="E276" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5">
+      <c r="A277" s="2">
+        <v>46300.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>0</v>
+      </c>
+      <c r="C277">
+        <v>19.778</v>
+      </c>
+      <c r="D277">
+        <v>84</v>
+      </c>
+      <c r="E277" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5">
+      <c r="A278" s="2">
+        <v>46300.875</v>
+      </c>
+      <c r="B278">
+        <v>0</v>
+      </c>
+      <c r="C278">
+        <v>11.94</v>
+      </c>
+      <c r="D278">
+        <v>85</v>
+      </c>
+      <c r="E278" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5">
+      <c r="A279" s="2">
+        <v>46300.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>4.29</v>
+      </c>
+      <c r="C279">
+        <v>0</v>
+      </c>
+      <c r="D279">
+        <v>86</v>
+      </c>
+      <c r="E279" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5">
+      <c r="A280" s="2">
+        <v>46300.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>0</v>
+      </c>
+      <c r="C280">
+        <v>5.2</v>
+      </c>
+      <c r="D280">
+        <v>87</v>
+      </c>
+      <c r="E280" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5">
+      <c r="A281" s="2">
+        <v>46300.90625</v>
+      </c>
+      <c r="B281">
+        <v>0</v>
+      </c>
+      <c r="C281">
+        <v>4.927</v>
+      </c>
+      <c r="D281">
+        <v>88</v>
+      </c>
+      <c r="E281" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5">
+      <c r="A282" s="2">
+        <v>46300.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>14.079</v>
+      </c>
+      <c r="C282">
+        <v>0</v>
+      </c>
+      <c r="D282">
+        <v>89</v>
+      </c>
+      <c r="E282" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5">
+      <c r="A283" s="2">
+        <v>46300.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>0</v>
+      </c>
+      <c r="C283">
+        <v>0.975</v>
+      </c>
+      <c r="D283">
+        <v>90</v>
+      </c>
+      <c r="E283" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5">
+      <c r="A284" s="2">
+        <v>46300.9375</v>
+      </c>
+      <c r="B284">
+        <v>15.787</v>
+      </c>
+      <c r="C284">
+        <v>0</v>
+      </c>
+      <c r="D284">
+        <v>91</v>
+      </c>
+      <c r="E284" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5">
+      <c r="A285" s="2">
+        <v>46300.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>0</v>
+      </c>
+      <c r="C285">
+        <v>7.769</v>
+      </c>
+      <c r="D285">
+        <v>92</v>
+      </c>
+      <c r="E285" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5">
+      <c r="A286" s="2">
+        <v>46300.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>0</v>
+      </c>
+      <c r="C286">
+        <v>1.738</v>
+      </c>
+      <c r="D286">
+        <v>93</v>
+      </c>
+      <c r="E286" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5">
+      <c r="A287" s="2">
+        <v>46300.96875</v>
+      </c>
+      <c r="B287">
+        <v>6.816</v>
+      </c>
+      <c r="C287">
+        <v>0</v>
+      </c>
+      <c r="D287">
+        <v>94</v>
+      </c>
+      <c r="E287" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5">
+      <c r="A288" s="2">
+        <v>46300.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>3.66</v>
+      </c>
+      <c r="C288">
+        <v>0</v>
+      </c>
+      <c r="D288">
+        <v>95</v>
+      </c>
+      <c r="E288" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5">
+      <c r="A289" s="2">
+        <v>46300.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>0</v>
+      </c>
+      <c r="C289">
+        <v>4.787</v>
+      </c>
+      <c r="D289">
+        <v>96</v>
+      </c>
+      <c r="E289" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5">
+      <c r="A290" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B290">
+        <v>0</v>
+      </c>
+      <c r="C290">
+        <v>21.891</v>
+      </c>
+      <c r="D290">
+        <v>1</v>
+      </c>
+      <c r="E290" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5">
+      <c r="A291" s="2">
+        <v>46301.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>0</v>
+      </c>
+      <c r="C291">
+        <v>17.33</v>
+      </c>
+      <c r="D291">
+        <v>2</v>
+      </c>
+      <c r="E291" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5">
+      <c r="A292" s="2">
+        <v>46301.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>0</v>
+      </c>
+      <c r="C292">
+        <v>8.028</v>
+      </c>
+      <c r="D292">
+        <v>3</v>
+      </c>
+      <c r="E292" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5">
+      <c r="A293" s="2">
+        <v>46301.03125</v>
+      </c>
+      <c r="B293">
+        <v>0</v>
+      </c>
+      <c r="C293">
+        <v>18.087</v>
+      </c>
+      <c r="D293">
+        <v>4</v>
+      </c>
+      <c r="E293" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5">
+      <c r="A294" s="2">
+        <v>46301.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>0</v>
+      </c>
+      <c r="C294">
+        <v>10.972</v>
+      </c>
+      <c r="D294">
+        <v>5</v>
+      </c>
+      <c r="E294" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5">
+      <c r="A295" s="2">
+        <v>46301.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>0</v>
+      </c>
+      <c r="C295">
+        <v>18.786</v>
+      </c>
+      <c r="D295">
+        <v>6</v>
+      </c>
+      <c r="E295" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5">
+      <c r="A296" s="2">
+        <v>46301.0625</v>
+      </c>
+      <c r="B296">
+        <v>0</v>
+      </c>
+      <c r="C296">
+        <v>7.465</v>
+      </c>
+      <c r="D296">
+        <v>7</v>
+      </c>
+      <c r="E296" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5">
+      <c r="A297" s="2">
+        <v>46301.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>0</v>
+      </c>
+      <c r="C297">
+        <v>5.03</v>
+      </c>
+      <c r="D297">
+        <v>8</v>
+      </c>
+      <c r="E297" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5">
+      <c r="A298" s="2">
+        <v>46301.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>0</v>
+      </c>
+      <c r="C298">
+        <v>6.049</v>
+      </c>
+      <c r="D298">
+        <v>9</v>
+      </c>
+      <c r="E298" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5">
+      <c r="A299" s="2">
+        <v>46301.09375</v>
+      </c>
+      <c r="B299">
+        <v>5.893</v>
+      </c>
+      <c r="C299">
+        <v>0</v>
+      </c>
+      <c r="D299">
+        <v>10</v>
+      </c>
+      <c r="E299" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5">
+      <c r="A300" s="2">
+        <v>46301.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>1.017</v>
+      </c>
+      <c r="C300">
+        <v>0</v>
+      </c>
+      <c r="D300">
+        <v>11</v>
+      </c>
+      <c r="E300" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5">
+      <c r="A301" s="2">
+        <v>46301.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>0</v>
+      </c>
+      <c r="C301">
+        <v>7.707</v>
+      </c>
+      <c r="D301">
+        <v>12</v>
+      </c>
+      <c r="E301" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5">
+      <c r="A302" s="2">
+        <v>46301.125</v>
+      </c>
+      <c r="B302">
+        <v>0</v>
+      </c>
+      <c r="C302">
+        <v>4.961</v>
+      </c>
+      <c r="D302">
+        <v>13</v>
+      </c>
+      <c r="E302" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5">
+      <c r="A303" s="2">
+        <v>46301.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>0</v>
+      </c>
+      <c r="C303">
+        <v>10.781</v>
+      </c>
+      <c r="D303">
+        <v>14</v>
+      </c>
+      <c r="E303" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5">
+      <c r="A304" s="2">
+        <v>46301.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>0</v>
+      </c>
+      <c r="C304">
+        <v>6.045</v>
+      </c>
+      <c r="D304">
+        <v>15</v>
+      </c>
+      <c r="E304" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5">
+      <c r="A305" s="2">
+        <v>46301.15625</v>
+      </c>
+      <c r="B305">
+        <v>0</v>
+      </c>
+      <c r="C305">
+        <v>24.18</v>
+      </c>
+      <c r="D305">
+        <v>16</v>
+      </c>
+      <c r="E305" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5">
+      <c r="A306" s="2">
+        <v>46301.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>0</v>
+      </c>
+      <c r="C306">
+        <v>39.111</v>
+      </c>
+      <c r="D306">
+        <v>17</v>
+      </c>
+      <c r="E306" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5">
+      <c r="A307" s="2">
+        <v>46301.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>0</v>
+      </c>
+      <c r="C307">
+        <v>8.709</v>
+      </c>
+      <c r="D307">
+        <v>18</v>
+      </c>
+      <c r="E307" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5">
+      <c r="A308" s="2">
+        <v>46301.1875</v>
+      </c>
+      <c r="B308">
+        <v>2.808</v>
+      </c>
+      <c r="C308">
+        <v>0</v>
+      </c>
+      <c r="D308">
+        <v>19</v>
+      </c>
+      <c r="E308" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5">
+      <c r="A309" s="2">
+        <v>46301.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>5.38</v>
+      </c>
+      <c r="C309">
+        <v>0</v>
+      </c>
+      <c r="D309">
+        <v>20</v>
+      </c>
+      <c r="E309" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5">
+      <c r="A310" s="2">
+        <v>46301.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>0</v>
+      </c>
+      <c r="C310">
+        <v>6.142</v>
+      </c>
+      <c r="D310">
+        <v>21</v>
+      </c>
+      <c r="E310" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5">
+      <c r="A311" s="2">
+        <v>46301.21875</v>
+      </c>
+      <c r="B311">
+        <v>6.397</v>
+      </c>
+      <c r="C311">
+        <v>0</v>
+      </c>
+      <c r="D311">
+        <v>22</v>
+      </c>
+      <c r="E311" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5">
+      <c r="A312" s="2">
+        <v>46301.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>13.196</v>
+      </c>
+      <c r="C312">
+        <v>0</v>
+      </c>
+      <c r="D312">
+        <v>23</v>
+      </c>
+      <c r="E312" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5">
+      <c r="A313" s="2">
+        <v>46301.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>5.603</v>
+      </c>
+      <c r="C313">
+        <v>0</v>
+      </c>
+      <c r="D313">
+        <v>24</v>
+      </c>
+      <c r="E313" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5">
+      <c r="A314" s="2">
+        <v>46301.25</v>
+      </c>
+      <c r="B314">
+        <v>0</v>
+      </c>
+      <c r="C314">
+        <v>3.835</v>
+      </c>
+      <c r="D314">
+        <v>25</v>
+      </c>
+      <c r="E314" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5">
+      <c r="A315" s="2">
+        <v>46301.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>0</v>
+      </c>
+      <c r="C315">
+        <v>2.885</v>
+      </c>
+      <c r="D315">
+        <v>26</v>
+      </c>
+      <c r="E315" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5">
+      <c r="A316" s="2">
+        <v>46301.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>2.886</v>
+      </c>
+      <c r="C316">
+        <v>0</v>
+      </c>
+      <c r="D316">
+        <v>27</v>
+      </c>
+      <c r="E316" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5">
+      <c r="A317" s="2">
+        <v>46301.28125</v>
+      </c>
+      <c r="B317">
+        <v>3.547</v>
+      </c>
+      <c r="C317">
+        <v>0</v>
+      </c>
+      <c r="D317">
+        <v>28</v>
+      </c>
+      <c r="E317" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5">
+      <c r="A318" s="2">
+        <v>46301.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>0</v>
+      </c>
+      <c r="C318">
+        <v>3.342</v>
+      </c>
+      <c r="D318">
+        <v>29</v>
+      </c>
+      <c r="E318" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5">
+      <c r="A319" s="2">
+        <v>46301.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>0</v>
+      </c>
+      <c r="C319">
+        <v>6.313</v>
+      </c>
+      <c r="D319">
+        <v>30</v>
+      </c>
+      <c r="E319" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5">
+      <c r="A320" s="2">
+        <v>46301.3125</v>
+      </c>
+      <c r="B320">
+        <v>0</v>
+      </c>
+      <c r="C320">
+        <v>19.623</v>
+      </c>
+      <c r="D320">
+        <v>31</v>
+      </c>
+      <c r="E320" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5">
+      <c r="A321" s="2">
+        <v>46301.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>0</v>
+      </c>
+      <c r="C321">
+        <v>49.914</v>
+      </c>
+      <c r="D321">
+        <v>32</v>
+      </c>
+      <c r="E321" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5">
+      <c r="A322" s="2">
+        <v>46301.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>0</v>
+      </c>
+      <c r="C322">
+        <v>39.206</v>
+      </c>
+      <c r="D322">
+        <v>33</v>
+      </c>
+      <c r="E322" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5">
+      <c r="A323" s="2">
+        <v>46301.34375</v>
+      </c>
+      <c r="B323">
+        <v>0</v>
+      </c>
+      <c r="C323">
+        <v>38.631</v>
+      </c>
+      <c r="D323">
+        <v>34</v>
+      </c>
+      <c r="E323" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5">
+      <c r="A324" s="2">
+        <v>46301.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>0</v>
+      </c>
+      <c r="C324">
+        <v>23.151</v>
+      </c>
+      <c r="D324">
+        <v>35</v>
+      </c>
+      <c r="E324" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5">
+      <c r="A325" s="2">
+        <v>46301.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>0</v>
+      </c>
+      <c r="C325">
+        <v>21.83</v>
+      </c>
+      <c r="D325">
+        <v>36</v>
+      </c>
+      <c r="E325" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5">
+      <c r="A326" s="2">
+        <v>46301.375</v>
+      </c>
+      <c r="B326">
+        <v>0</v>
+      </c>
+      <c r="C326">
+        <v>12.699</v>
+      </c>
+      <c r="D326">
+        <v>37</v>
+      </c>
+      <c r="E326" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5">
+      <c r="A327" s="2">
+        <v>46301.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>0</v>
+      </c>
+      <c r="C327">
+        <v>5.342</v>
+      </c>
+      <c r="D327">
+        <v>38</v>
+      </c>
+      <c r="E327" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5">
+      <c r="A328" s="2">
+        <v>46301.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>0</v>
+      </c>
+      <c r="C328">
+        <v>7.549</v>
+      </c>
+      <c r="D328">
+        <v>39</v>
+      </c>
+      <c r="E328" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5">
+      <c r="A329" s="2">
+        <v>46301.40625</v>
+      </c>
+      <c r="B329">
+        <v>0</v>
+      </c>
+      <c r="C329">
+        <v>10.407</v>
+      </c>
+      <c r="D329">
+        <v>40</v>
+      </c>
+      <c r="E329" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5">
+      <c r="A330" s="2">
+        <v>46301.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>6.103</v>
+      </c>
+      <c r="C330">
+        <v>0</v>
+      </c>
+      <c r="D330">
+        <v>41</v>
+      </c>
+      <c r="E330" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5">
+      <c r="A331" s="2">
+        <v>46301.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>4.592</v>
+      </c>
+      <c r="C331">
+        <v>0</v>
+      </c>
+      <c r="D331">
+        <v>42</v>
+      </c>
+      <c r="E331" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5">
+      <c r="A332" s="2">
+        <v>46301.4375</v>
+      </c>
+      <c r="B332">
+        <v>4.675</v>
+      </c>
+      <c r="C332">
+        <v>0</v>
+      </c>
+      <c r="D332">
+        <v>43</v>
+      </c>
+      <c r="E332" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5">
+      <c r="A333" s="2">
+        <v>46301.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>0</v>
+      </c>
+      <c r="C333">
+        <v>12.327</v>
+      </c>
+      <c r="D333">
+        <v>44</v>
+      </c>
+      <c r="E333" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5">
+      <c r="A334" s="2">
+        <v>46301.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>0</v>
+      </c>
+      <c r="C334">
+        <v>3.006</v>
+      </c>
+      <c r="D334">
+        <v>45</v>
+      </c>
+      <c r="E334" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5">
+      <c r="A335" s="2">
+        <v>46301.46875</v>
+      </c>
+      <c r="B335">
+        <v>0</v>
+      </c>
+      <c r="C335">
+        <v>13.192</v>
+      </c>
+      <c r="D335">
+        <v>46</v>
+      </c>
+      <c r="E335" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5">
+      <c r="A336" s="2">
+        <v>46301.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>0</v>
+      </c>
+      <c r="C336">
+        <v>3.182</v>
+      </c>
+      <c r="D336">
+        <v>47</v>
+      </c>
+      <c r="E336" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5">
+      <c r="A337" s="2">
+        <v>46301.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>0</v>
+      </c>
+      <c r="C337">
+        <v>27.709</v>
+      </c>
+      <c r="D337">
+        <v>48</v>
+      </c>
+      <c r="E337" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5">
+      <c r="A338" s="2">
+        <v>46301.5</v>
+      </c>
+      <c r="B338">
+        <v>0</v>
+      </c>
+      <c r="C338">
+        <v>17.956</v>
+      </c>
+      <c r="D338">
+        <v>49</v>
+      </c>
+      <c r="E338" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5">
+      <c r="A339" s="2">
+        <v>46301.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>2.672</v>
+      </c>
+      <c r="C339">
+        <v>0</v>
+      </c>
+      <c r="D339">
+        <v>50</v>
+      </c>
+      <c r="E339" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5">
+      <c r="A340" s="2">
+        <v>46301.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>0</v>
+      </c>
+      <c r="C340">
+        <v>4.382</v>
+      </c>
+      <c r="D340">
+        <v>51</v>
+      </c>
+      <c r="E340" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5">
+      <c r="A341" s="2">
+        <v>46301.53125</v>
+      </c>
+      <c r="B341">
+        <v>0</v>
+      </c>
+      <c r="C341">
+        <v>6.526</v>
+      </c>
+      <c r="D341">
+        <v>52</v>
+      </c>
+      <c r="E341" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5">
+      <c r="A342" s="2">
+        <v>46301.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>0</v>
+      </c>
+      <c r="C342">
+        <v>3.243</v>
+      </c>
+      <c r="D342">
+        <v>53</v>
+      </c>
+      <c r="E342" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5">
+      <c r="A343" s="2">
+        <v>46301.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>0</v>
+      </c>
+      <c r="C343">
+        <v>9.228</v>
+      </c>
+      <c r="D343">
+        <v>54</v>
+      </c>
+      <c r="E343" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5">
+      <c r="A344" s="2">
+        <v>46301.5625</v>
+      </c>
+      <c r="B344">
+        <v>5.837</v>
+      </c>
+      <c r="C344">
+        <v>0</v>
+      </c>
+      <c r="D344">
+        <v>55</v>
+      </c>
+      <c r="E344" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5">
+      <c r="A345" s="2">
+        <v>46301.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="C345">
+        <v>0</v>
+      </c>
+      <c r="D345">
+        <v>56</v>
+      </c>
+      <c r="E345" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5">
+      <c r="A346" s="2">
+        <v>46301.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>0</v>
+      </c>
+      <c r="C346">
+        <v>9.666</v>
+      </c>
+      <c r="D346">
+        <v>57</v>
+      </c>
+      <c r="E346" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5">
+      <c r="A347" s="2">
+        <v>46301.59375</v>
+      </c>
+      <c r="B347">
+        <v>0</v>
+      </c>
+      <c r="C347">
+        <v>18.072</v>
+      </c>
+      <c r="D347">
+        <v>58</v>
+      </c>
+      <c r="E347" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5">
+      <c r="A348" s="2">
+        <v>46301.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>0</v>
+      </c>
+      <c r="C348">
+        <v>13.12</v>
+      </c>
+      <c r="D348">
+        <v>59</v>
+      </c>
+      <c r="E348" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5">
+      <c r="A349" s="2">
+        <v>46301.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>0</v>
+      </c>
+      <c r="C349">
+        <v>19.329</v>
+      </c>
+      <c r="D349">
+        <v>60</v>
+      </c>
+      <c r="E349" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5">
+      <c r="A350" s="2">
+        <v>46301.625</v>
+      </c>
+      <c r="B350">
+        <v>0</v>
+      </c>
+      <c r="C350">
+        <v>7.989</v>
+      </c>
+      <c r="D350">
+        <v>61</v>
+      </c>
+      <c r="E350" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5">
+      <c r="A351" s="2">
+        <v>46301.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>0</v>
+      </c>
+      <c r="C351">
+        <v>12.46</v>
+      </c>
+      <c r="D351">
+        <v>62</v>
+      </c>
+      <c r="E351" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5">
+      <c r="A352" s="2">
+        <v>46301.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>0</v>
+      </c>
+      <c r="C352">
+        <v>20.574</v>
+      </c>
+      <c r="D352">
+        <v>63</v>
+      </c>
+      <c r="E352" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5">
+      <c r="A353" s="2">
+        <v>46301.65625</v>
+      </c>
+      <c r="B353">
+        <v>0</v>
+      </c>
+      <c r="C353">
+        <v>23.095</v>
+      </c>
+      <c r="D353">
+        <v>64</v>
+      </c>
+      <c r="E353" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5">
+      <c r="A354" s="2">
+        <v>46301.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>0</v>
+      </c>
+      <c r="C354">
+        <v>28.465</v>
+      </c>
+      <c r="D354">
+        <v>65</v>
+      </c>
+      <c r="E354" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5">
+      <c r="A355" s="2">
+        <v>46301.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>0</v>
+      </c>
+      <c r="C355">
+        <v>15.676</v>
+      </c>
+      <c r="D355">
+        <v>66</v>
+      </c>
+      <c r="E355" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5">
+      <c r="A356" s="2">
+        <v>46301.6875</v>
+      </c>
+      <c r="B356">
+        <v>0</v>
+      </c>
+      <c r="C356">
+        <v>26.046</v>
+      </c>
+      <c r="D356">
+        <v>67</v>
+      </c>
+      <c r="E356" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5">
+      <c r="A357" s="2">
+        <v>46301.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>5.389</v>
+      </c>
+      <c r="C357">
+        <v>0</v>
+      </c>
+      <c r="D357">
+        <v>68</v>
+      </c>
+      <c r="E357" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5">
+      <c r="A358" s="2">
+        <v>46301.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>0</v>
+      </c>
+      <c r="C358">
+        <v>23.402</v>
+      </c>
+      <c r="D358">
+        <v>69</v>
+      </c>
+      <c r="E358" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5">
+      <c r="A359" s="2">
+        <v>46301.71875</v>
+      </c>
+      <c r="B359">
+        <v>1.523</v>
+      </c>
+      <c r="C359">
+        <v>0</v>
+      </c>
+      <c r="D359">
+        <v>70</v>
+      </c>
+      <c r="E359" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5">
+      <c r="A360" s="2">
+        <v>46301.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>0</v>
+      </c>
+      <c r="C360">
+        <v>19.416</v>
+      </c>
+      <c r="D360">
+        <v>71</v>
+      </c>
+      <c r="E360" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5">
+      <c r="A361" s="2">
+        <v>46301.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>0</v>
+      </c>
+      <c r="C361">
+        <v>33.352</v>
+      </c>
+      <c r="D361">
+        <v>72</v>
+      </c>
+      <c r="E361" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5">
+      <c r="A362" s="2">
+        <v>46301.75</v>
+      </c>
+      <c r="B362">
+        <v>0</v>
+      </c>
+      <c r="C362">
+        <v>3.915</v>
+      </c>
+      <c r="D362">
+        <v>73</v>
+      </c>
+      <c r="E362" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5">
+      <c r="A363" s="2">
+        <v>46301.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>0</v>
+      </c>
+      <c r="C363">
+        <v>2.516</v>
+      </c>
+      <c r="D363">
+        <v>74</v>
+      </c>
+      <c r="E363" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5">
+      <c r="A364" s="2">
+        <v>46301.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>0</v>
+      </c>
+      <c r="C364">
+        <v>1.3</v>
+      </c>
+      <c r="D364">
+        <v>75</v>
+      </c>
+      <c r="E364" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5">
+      <c r="A365" s="2">
+        <v>46301.78125</v>
+      </c>
+      <c r="B365">
+        <v>0</v>
+      </c>
+      <c r="C365">
+        <v>3.908</v>
+      </c>
+      <c r="D365">
+        <v>76</v>
+      </c>
+      <c r="E365" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5">
+      <c r="A366" s="2">
+        <v>46301.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>0</v>
+      </c>
+      <c r="C366">
+        <v>3.175</v>
+      </c>
+      <c r="D366">
+        <v>77</v>
+      </c>
+      <c r="E366" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5">
+      <c r="A367" s="2">
+        <v>46301.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>0</v>
+      </c>
+      <c r="C367">
+        <v>15.714</v>
+      </c>
+      <c r="D367">
+        <v>78</v>
+      </c>
+      <c r="E367" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5">
+      <c r="A368" s="2">
+        <v>46301.8125</v>
+      </c>
+      <c r="B368">
+        <v>0</v>
+      </c>
+      <c r="C368">
+        <v>31.428</v>
+      </c>
+      <c r="D368">
+        <v>79</v>
+      </c>
+      <c r="E368" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5">
+      <c r="A369" s="2">
+        <v>46301.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>0</v>
+      </c>
+      <c r="C369">
+        <v>17.611</v>
+      </c>
+      <c r="D369">
+        <v>80</v>
+      </c>
+      <c r="E369" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5">
+      <c r="A370" s="2">
+        <v>46301.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>0</v>
+      </c>
+      <c r="C370">
+        <v>13.669</v>
+      </c>
+      <c r="D370">
+        <v>81</v>
+      </c>
+      <c r="E370" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5">
+      <c r="A371" s="2">
+        <v>46301.84375</v>
+      </c>
+      <c r="B371">
+        <v>0</v>
+      </c>
+      <c r="C371">
+        <v>12.593</v>
+      </c>
+      <c r="D371">
+        <v>82</v>
+      </c>
+      <c r="E371" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5">
+      <c r="A372" s="2">
+        <v>46301.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>0</v>
+      </c>
+      <c r="C372">
+        <v>17.729</v>
+      </c>
+      <c r="D372">
+        <v>83</v>
+      </c>
+      <c r="E372" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5">
+      <c r="A373" s="2">
+        <v>46301.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>0</v>
+      </c>
+      <c r="C373">
+        <v>17.132</v>
+      </c>
+      <c r="D373">
+        <v>84</v>
+      </c>
+      <c r="E373" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5">
+      <c r="A374" s="2">
+        <v>46301.875</v>
+      </c>
+      <c r="B374">
+        <v>5.092</v>
+      </c>
+      <c r="C374">
+        <v>0</v>
+      </c>
+      <c r="D374">
+        <v>85</v>
+      </c>
+      <c r="E374" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5">
+      <c r="A375" s="2">
+        <v>46301.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>0</v>
+      </c>
+      <c r="C375">
+        <v>1.009</v>
+      </c>
+      <c r="D375">
+        <v>86</v>
+      </c>
+      <c r="E375" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5">
+      <c r="A376" s="2">
+        <v>46301.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>0</v>
+      </c>
+      <c r="C376">
+        <v>4.943</v>
+      </c>
+      <c r="D376">
+        <v>87</v>
+      </c>
+      <c r="E376" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5">
+      <c r="A377" s="2">
+        <v>46301.90625</v>
+      </c>
+      <c r="B377">
+        <v>0</v>
+      </c>
+      <c r="C377">
+        <v>1.014</v>
+      </c>
+      <c r="D377">
+        <v>88</v>
+      </c>
+      <c r="E377" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5">
+      <c r="A378" s="2">
+        <v>46301.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>5.034</v>
+      </c>
+      <c r="C378">
+        <v>0</v>
+      </c>
+      <c r="D378">
+        <v>89</v>
+      </c>
+      <c r="E378" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5">
+      <c r="A379" s="2">
+        <v>46301.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>0.463</v>
+      </c>
+      <c r="C379">
+        <v>0</v>
+      </c>
+      <c r="D379">
+        <v>90</v>
+      </c>
+      <c r="E379" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5">
+      <c r="A380" s="2">
+        <v>46301.9375</v>
+      </c>
+      <c r="B380">
+        <v>0</v>
+      </c>
+      <c r="C380">
+        <v>4.462</v>
+      </c>
+      <c r="D380">
+        <v>91</v>
+      </c>
+      <c r="E380" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5">
+      <c r="A381" s="2">
+        <v>46301.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>0</v>
+      </c>
+      <c r="C381">
+        <v>8.457000000000001</v>
+      </c>
+      <c r="D381">
+        <v>92</v>
+      </c>
+      <c r="E381" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5">
+      <c r="A382" s="2">
+        <v>46301.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>8.007</v>
+      </c>
+      <c r="C382">
+        <v>0</v>
+      </c>
+      <c r="D382">
+        <v>93</v>
+      </c>
+      <c r="E382" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="383" spans="1:5">
+      <c r="A383" s="2">
+        <v>46301.96875</v>
+      </c>
+      <c r="B383">
+        <v>0</v>
+      </c>
+      <c r="C383">
+        <v>4.53</v>
+      </c>
+      <c r="D383">
+        <v>94</v>
+      </c>
+      <c r="E383" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="384" spans="1:5">
+      <c r="A384" s="2">
+        <v>46301.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>5.125</v>
+      </c>
+      <c r="C384">
+        <v>0</v>
+      </c>
+      <c r="D384">
+        <v>95</v>
+      </c>
+      <c r="E384" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="385" spans="1:5">
+      <c r="A385" s="2">
+        <v>46301.98958333334</v>
+      </c>
+      <c r="B385">
+        <v>1.452</v>
+      </c>
+      <c r="C385">
+        <v>0</v>
+      </c>
+      <c r="D385">
+        <v>96</v>
+      </c>
+      <c r="E385" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="386" spans="1:5">
+      <c r="A386" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B386">
+        <v>6.977</v>
+      </c>
+      <c r="C386">
+        <v>0</v>
+      </c>
+      <c r="D386">
+        <v>1</v>
+      </c>
+      <c r="E386" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="387" spans="1:5">
+      <c r="A387" s="2">
+        <v>46302.01041666666</v>
+      </c>
+      <c r="B387">
+        <v>1.535</v>
+      </c>
+      <c r="C387">
+        <v>0</v>
+      </c>
+      <c r="D387">
+        <v>2</v>
+      </c>
+      <c r="E387" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="388" spans="1:5">
+      <c r="A388" s="2">
+        <v>46302.02083333334</v>
+      </c>
+      <c r="B388">
+        <v>12.375</v>
+      </c>
+      <c r="C388">
+        <v>0</v>
+      </c>
+      <c r="D388">
+        <v>3</v>
+      </c>
+      <c r="E388" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="389" spans="1:5">
+      <c r="A389" s="2">
+        <v>46302.03125</v>
+      </c>
+      <c r="B389">
+        <v>20.101</v>
+      </c>
+      <c r="C389">
+        <v>0</v>
+      </c>
+      <c r="D389">
+        <v>4</v>
+      </c>
+      <c r="E389" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="390" spans="1:5">
+      <c r="A390" s="2">
+        <v>46302.04166666666</v>
+      </c>
+      <c r="B390">
+        <v>11.95</v>
+      </c>
+      <c r="C390">
+        <v>0</v>
+      </c>
+      <c r="D390">
+        <v>5</v>
+      </c>
+      <c r="E390" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="391" spans="1:5">
+      <c r="A391" s="2">
+        <v>46302.05208333334</v>
+      </c>
+      <c r="B391">
+        <v>0</v>
+      </c>
+      <c r="C391">
+        <v>4.199</v>
+      </c>
+      <c r="D391">
+        <v>6</v>
+      </c>
+      <c r="E391" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="392" spans="1:5">
+      <c r="A392" s="2">
+        <v>46302.0625</v>
+      </c>
+      <c r="B392">
+        <v>2.957</v>
+      </c>
+      <c r="C392">
+        <v>0</v>
+      </c>
+      <c r="D392">
+        <v>7</v>
+      </c>
+      <c r="E392" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="393" spans="1:5">
+      <c r="A393" s="2">
+        <v>46302.07291666666</v>
+      </c>
+      <c r="B393">
+        <v>0</v>
+      </c>
+      <c r="C393">
+        <v>5.264</v>
+      </c>
+      <c r="D393">
+        <v>8</v>
+      </c>
+      <c r="E393" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="394" spans="1:5">
+      <c r="A394" s="2">
+        <v>46302.08333333334</v>
+      </c>
+      <c r="B394">
+        <v>0</v>
+      </c>
+      <c r="C394">
+        <v>6.761</v>
+      </c>
+      <c r="D394">
+        <v>9</v>
+      </c>
+      <c r="E394" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="395" spans="1:5">
+      <c r="A395" s="2">
+        <v>46302.09375</v>
+      </c>
+      <c r="B395">
+        <v>5.737</v>
+      </c>
+      <c r="C395">
+        <v>0</v>
+      </c>
+      <c r="D395">
+        <v>10</v>
+      </c>
+      <c r="E395" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="396" spans="1:5">
+      <c r="A396" s="2">
+        <v>46302.10416666666</v>
+      </c>
+      <c r="B396">
+        <v>0</v>
+      </c>
+      <c r="C396">
+        <v>1.812</v>
+      </c>
+      <c r="D396">
+        <v>11</v>
+      </c>
+      <c r="E396" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="397" spans="1:5">
+      <c r="A397" s="2">
+        <v>46302.11458333334</v>
+      </c>
+      <c r="B397">
+        <v>0.353</v>
+      </c>
+      <c r="C397">
+        <v>0</v>
+      </c>
+      <c r="D397">
+        <v>12</v>
+      </c>
+      <c r="E397" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="398" spans="1:5">
+      <c r="A398" s="2">
+        <v>46302.125</v>
+      </c>
+      <c r="B398">
+        <v>2.481</v>
+      </c>
+      <c r="C398">
+        <v>0</v>
+      </c>
+      <c r="D398">
+        <v>13</v>
+      </c>
+      <c r="E398" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="399" spans="1:5">
+      <c r="A399" s="2">
+        <v>46302.13541666666</v>
+      </c>
+      <c r="B399">
+        <v>5.741</v>
+      </c>
+      <c r="C399">
+        <v>0</v>
+      </c>
+      <c r="D399">
+        <v>14</v>
+      </c>
+      <c r="E399" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="400" spans="1:5">
+      <c r="A400" s="2">
+        <v>46302.14583333334</v>
+      </c>
+      <c r="B400">
+        <v>3.033</v>
+      </c>
+      <c r="C400">
+        <v>0</v>
+      </c>
+      <c r="D400">
+        <v>15</v>
+      </c>
+      <c r="E400" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="401" spans="1:5">
+      <c r="A401" s="2">
+        <v>46302.15625</v>
+      </c>
+      <c r="B401">
+        <v>5.016</v>
+      </c>
+      <c r="C401">
+        <v>0</v>
+      </c>
+      <c r="D401">
+        <v>16</v>
+      </c>
+      <c r="E401" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="402" spans="1:5">
+      <c r="A402" s="2">
+        <v>46302.16666666666</v>
+      </c>
+      <c r="B402">
+        <v>0</v>
+      </c>
+      <c r="C402">
+        <v>1.076</v>
+      </c>
+      <c r="D402">
+        <v>17</v>
+      </c>
+      <c r="E402" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="403" spans="1:5">
+      <c r="A403" s="2">
+        <v>46302.17708333334</v>
+      </c>
+      <c r="B403">
+        <v>4.179</v>
+      </c>
+      <c r="C403">
+        <v>0</v>
+      </c>
+      <c r="D403">
+        <v>18</v>
+      </c>
+      <c r="E403" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="404" spans="1:5">
+      <c r="A404" s="2">
+        <v>46302.1875</v>
+      </c>
+      <c r="B404">
+        <v>0.59</v>
+      </c>
+      <c r="C404">
+        <v>0</v>
+      </c>
+      <c r="D404">
+        <v>19</v>
+      </c>
+      <c r="E404" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="405" spans="1:5">
+      <c r="A405" s="2">
+        <v>46302.19791666666</v>
+      </c>
+      <c r="B405">
+        <v>4.79</v>
+      </c>
+      <c r="C405">
+        <v>0</v>
+      </c>
+      <c r="D405">
+        <v>20</v>
+      </c>
+      <c r="E405" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="406" spans="1:5">
+      <c r="A406" s="2">
+        <v>46302.20833333334</v>
+      </c>
+      <c r="B406">
+        <v>0</v>
+      </c>
+      <c r="C406">
+        <v>7.102</v>
+      </c>
+      <c r="D406">
+        <v>21</v>
+      </c>
+      <c r="E406" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="407" spans="1:5">
+      <c r="A407" s="2">
+        <v>46302.21875</v>
+      </c>
+      <c r="B407">
+        <v>0</v>
+      </c>
+      <c r="C407">
+        <v>1.412</v>
+      </c>
+      <c r="D407">
+        <v>22</v>
+      </c>
+      <c r="E407" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="408" spans="1:5">
+      <c r="A408" s="2">
+        <v>46302.22916666666</v>
+      </c>
+      <c r="B408">
+        <v>2.956</v>
+      </c>
+      <c r="C408">
+        <v>0</v>
+      </c>
+      <c r="D408">
+        <v>23</v>
+      </c>
+      <c r="E408" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="409" spans="1:5">
+      <c r="A409" s="2">
+        <v>46302.23958333334</v>
+      </c>
+      <c r="B409">
+        <v>0</v>
+      </c>
+      <c r="C409">
+        <v>4.013</v>
+      </c>
+      <c r="D409">
+        <v>24</v>
+      </c>
+      <c r="E409" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="410" spans="1:5">
+      <c r="A410" s="2">
+        <v>46302.25</v>
+      </c>
+      <c r="B410">
+        <v>0.199</v>
+      </c>
+      <c r="C410">
+        <v>0</v>
+      </c>
+      <c r="D410">
+        <v>25</v>
+      </c>
+      <c r="E410" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="411" spans="1:5">
+      <c r="A411" s="2">
+        <v>46302.26041666666</v>
+      </c>
+      <c r="B411">
+        <v>2.74</v>
+      </c>
+      <c r="C411">
+        <v>0</v>
+      </c>
+      <c r="D411">
+        <v>26</v>
+      </c>
+      <c r="E411" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="412" spans="1:5">
+      <c r="A412" s="2">
+        <v>46302.27083333334</v>
+      </c>
+      <c r="B412">
+        <v>0</v>
+      </c>
+      <c r="C412">
+        <v>3.653</v>
+      </c>
+      <c r="D412">
+        <v>27</v>
+      </c>
+      <c r="E412" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="413" spans="1:5">
+      <c r="A413" s="2">
+        <v>46302.28125</v>
+      </c>
+      <c r="B413">
+        <v>2.173</v>
+      </c>
+      <c r="C413">
+        <v>0</v>
+      </c>
+      <c r="D413">
+        <v>28</v>
+      </c>
+      <c r="E413" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="414" spans="1:5">
+      <c r="A414" s="2">
+        <v>46302.29166666666</v>
+      </c>
+      <c r="B414">
+        <v>3.3</v>
+      </c>
+      <c r="C414">
+        <v>0</v>
+      </c>
+      <c r="D414">
+        <v>29</v>
+      </c>
+      <c r="E414" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="415" spans="1:5">
+      <c r="A415" s="2">
+        <v>46302.30208333334</v>
+      </c>
+      <c r="B415">
+        <v>0.723</v>
+      </c>
+      <c r="C415">
+        <v>0</v>
+      </c>
+      <c r="D415">
+        <v>30</v>
+      </c>
+      <c r="E415" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="416" spans="1:5">
+      <c r="A416" s="2">
+        <v>46302.3125</v>
+      </c>
+      <c r="B416">
+        <v>0</v>
+      </c>
+      <c r="C416">
+        <v>6.92</v>
+      </c>
+      <c r="D416">
+        <v>31</v>
+      </c>
+      <c r="E416" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="417" spans="1:5">
+      <c r="A417" s="2">
+        <v>46302.32291666666</v>
+      </c>
+      <c r="B417">
+        <v>0</v>
+      </c>
+      <c r="C417">
+        <v>9.98</v>
+      </c>
+      <c r="D417">
+        <v>32</v>
+      </c>
+      <c r="E417" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="418" spans="1:5">
+      <c r="A418" s="2">
+        <v>46302.33333333334</v>
+      </c>
+      <c r="B418">
+        <v>7.894</v>
+      </c>
+      <c r="C418">
+        <v>0</v>
+      </c>
+      <c r="D418">
+        <v>33</v>
+      </c>
+      <c r="E418" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="419" spans="1:5">
+      <c r="A419" s="2">
+        <v>46302.34375</v>
+      </c>
+      <c r="B419">
+        <v>0</v>
+      </c>
+      <c r="C419">
+        <v>15.589</v>
+      </c>
+      <c r="D419">
+        <v>34</v>
+      </c>
+      <c r="E419" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="420" spans="1:5">
+      <c r="A420" s="2">
+        <v>46302.35416666666</v>
+      </c>
+      <c r="B420">
+        <v>0.596</v>
+      </c>
+      <c r="C420">
+        <v>0</v>
+      </c>
+      <c r="D420">
+        <v>35</v>
+      </c>
+      <c r="E420" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="421" spans="1:5">
+      <c r="A421" s="2">
+        <v>46302.36458333334</v>
+      </c>
+      <c r="B421">
+        <v>7.365</v>
+      </c>
+      <c r="C421">
+        <v>0</v>
+      </c>
+      <c r="D421">
+        <v>36</v>
+      </c>
+      <c r="E421" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="422" spans="1:5">
+      <c r="A422" s="2">
+        <v>46302.375</v>
+      </c>
+      <c r="B422">
+        <v>2.618</v>
+      </c>
+      <c r="C422">
+        <v>0</v>
+      </c>
+      <c r="D422">
+        <v>37</v>
+      </c>
+      <c r="E422" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="423" spans="1:5">
+      <c r="A423" s="2">
+        <v>46302.38541666666</v>
+      </c>
+      <c r="B423">
+        <v>0</v>
+      </c>
+      <c r="C423">
+        <v>7.008</v>
+      </c>
+      <c r="D423">
+        <v>38</v>
+      </c>
+      <c r="E423" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="424" spans="1:5">
+      <c r="A424" s="2">
+        <v>46302.39583333334</v>
+      </c>
+      <c r="B424">
+        <v>0</v>
+      </c>
+      <c r="C424">
+        <v>9.016</v>
+      </c>
+      <c r="D424">
+        <v>39</v>
+      </c>
+      <c r="E424" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="425" spans="1:5">
+      <c r="A425" s="2">
+        <v>46302.40625</v>
+      </c>
+      <c r="B425">
+        <v>0</v>
+      </c>
+      <c r="C425">
+        <v>15.121</v>
+      </c>
+      <c r="D425">
+        <v>40</v>
+      </c>
+      <c r="E425" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="426" spans="1:5">
+      <c r="A426" s="2">
+        <v>46302.41666666666</v>
+      </c>
+      <c r="B426">
+        <v>0</v>
+      </c>
+      <c r="C426">
+        <v>3.741</v>
+      </c>
+      <c r="D426">
+        <v>41</v>
+      </c>
+      <c r="E426" t="s">
+        <v>429</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data_fetching/Entsoe/Unintended_Deviation.xlsx
+++ b/data_fetching/Entsoe/Unintended_Deviation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="137">
   <si>
     <t>Timestamp</t>
   </si>
@@ -31,294 +31,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>07.10.20261</t>
-  </si>
-  <si>
-    <t>07.10.20262</t>
-  </si>
-  <si>
-    <t>07.10.20263</t>
-  </si>
-  <si>
-    <t>07.10.20264</t>
-  </si>
-  <si>
-    <t>07.10.20265</t>
-  </si>
-  <si>
-    <t>07.10.20266</t>
-  </si>
-  <si>
-    <t>07.10.20267</t>
-  </si>
-  <si>
-    <t>07.10.20268</t>
-  </si>
-  <si>
-    <t>07.10.20269</t>
-  </si>
-  <si>
-    <t>07.10.202610</t>
-  </si>
-  <si>
-    <t>07.10.202611</t>
-  </si>
-  <si>
-    <t>07.10.202612</t>
-  </si>
-  <si>
-    <t>07.10.202613</t>
-  </si>
-  <si>
-    <t>07.10.202614</t>
-  </si>
-  <si>
-    <t>07.10.202615</t>
-  </si>
-  <si>
-    <t>07.10.202616</t>
-  </si>
-  <si>
-    <t>07.10.202617</t>
-  </si>
-  <si>
-    <t>07.10.202618</t>
-  </si>
-  <si>
-    <t>07.10.202619</t>
-  </si>
-  <si>
-    <t>07.10.202620</t>
-  </si>
-  <si>
-    <t>07.10.202621</t>
-  </si>
-  <si>
-    <t>07.10.202622</t>
-  </si>
-  <si>
-    <t>07.10.202623</t>
-  </si>
-  <si>
-    <t>07.10.202624</t>
-  </si>
-  <si>
-    <t>07.10.202625</t>
-  </si>
-  <si>
-    <t>07.10.202626</t>
-  </si>
-  <si>
-    <t>07.10.202627</t>
-  </si>
-  <si>
-    <t>07.10.202628</t>
-  </si>
-  <si>
-    <t>07.10.202629</t>
-  </si>
-  <si>
-    <t>07.10.202630</t>
-  </si>
-  <si>
-    <t>07.10.202631</t>
-  </si>
-  <si>
-    <t>07.10.202632</t>
-  </si>
-  <si>
-    <t>07.10.202633</t>
-  </si>
-  <si>
-    <t>07.10.202634</t>
-  </si>
-  <si>
-    <t>07.10.202635</t>
-  </si>
-  <si>
-    <t>07.10.202636</t>
-  </si>
-  <si>
-    <t>07.10.202637</t>
-  </si>
-  <si>
-    <t>07.10.202638</t>
-  </si>
-  <si>
-    <t>07.10.202639</t>
-  </si>
-  <si>
-    <t>07.10.202640</t>
-  </si>
-  <si>
-    <t>07.10.202641</t>
-  </si>
-  <si>
-    <t>07.10.202642</t>
-  </si>
-  <si>
-    <t>07.10.202643</t>
-  </si>
-  <si>
-    <t>07.10.202644</t>
-  </si>
-  <si>
-    <t>07.10.202645</t>
-  </si>
-  <si>
-    <t>07.10.202646</t>
-  </si>
-  <si>
-    <t>07.10.202647</t>
-  </si>
-  <si>
-    <t>07.10.202648</t>
-  </si>
-  <si>
-    <t>07.10.202649</t>
-  </si>
-  <si>
-    <t>07.10.202650</t>
-  </si>
-  <si>
-    <t>07.10.202651</t>
-  </si>
-  <si>
-    <t>07.10.202652</t>
-  </si>
-  <si>
-    <t>07.10.202653</t>
-  </si>
-  <si>
-    <t>07.10.202654</t>
-  </si>
-  <si>
-    <t>07.10.202655</t>
-  </si>
-  <si>
-    <t>07.10.202656</t>
-  </si>
-  <si>
-    <t>07.10.202657</t>
-  </si>
-  <si>
-    <t>07.10.202658</t>
-  </si>
-  <si>
-    <t>07.10.202659</t>
-  </si>
-  <si>
-    <t>07.10.202660</t>
-  </si>
-  <si>
-    <t>07.10.202661</t>
-  </si>
-  <si>
-    <t>07.10.202662</t>
-  </si>
-  <si>
-    <t>07.10.202663</t>
-  </si>
-  <si>
-    <t>07.10.202664</t>
-  </si>
-  <si>
-    <t>07.10.202665</t>
-  </si>
-  <si>
-    <t>07.10.202666</t>
-  </si>
-  <si>
-    <t>07.10.202667</t>
-  </si>
-  <si>
-    <t>07.10.202668</t>
-  </si>
-  <si>
-    <t>07.10.202669</t>
-  </si>
-  <si>
-    <t>07.10.202670</t>
-  </si>
-  <si>
-    <t>07.10.202671</t>
-  </si>
-  <si>
-    <t>07.10.202672</t>
-  </si>
-  <si>
-    <t>07.10.202673</t>
-  </si>
-  <si>
-    <t>07.10.202674</t>
-  </si>
-  <si>
-    <t>07.10.202675</t>
-  </si>
-  <si>
-    <t>07.10.202676</t>
-  </si>
-  <si>
-    <t>07.10.202677</t>
-  </si>
-  <si>
-    <t>07.10.202678</t>
-  </si>
-  <si>
-    <t>07.10.202679</t>
-  </si>
-  <si>
-    <t>07.10.202680</t>
-  </si>
-  <si>
-    <t>07.10.202681</t>
-  </si>
-  <si>
-    <t>07.10.202682</t>
-  </si>
-  <si>
-    <t>07.10.202683</t>
-  </si>
-  <si>
-    <t>07.10.202684</t>
-  </si>
-  <si>
-    <t>07.10.202685</t>
-  </si>
-  <si>
-    <t>07.10.202686</t>
-  </si>
-  <si>
-    <t>07.10.202687</t>
-  </si>
-  <si>
-    <t>07.10.202688</t>
-  </si>
-  <si>
-    <t>07.10.202689</t>
-  </si>
-  <si>
-    <t>07.10.202690</t>
-  </si>
-  <si>
-    <t>07.10.202691</t>
-  </si>
-  <si>
-    <t>07.10.202692</t>
-  </si>
-  <si>
-    <t>07.10.202693</t>
-  </si>
-  <si>
-    <t>07.10.202694</t>
-  </si>
-  <si>
-    <t>07.10.202695</t>
-  </si>
-  <si>
-    <t>07.10.202696</t>
-  </si>
-  <si>
     <t>08.10.20261</t>
   </si>
   <si>
@@ -440,6 +152,279 @@
   </si>
   <si>
     <t>08.10.202641</t>
+  </si>
+  <si>
+    <t>08.10.202642</t>
+  </si>
+  <si>
+    <t>08.10.202643</t>
+  </si>
+  <si>
+    <t>08.10.202644</t>
+  </si>
+  <si>
+    <t>08.10.202645</t>
+  </si>
+  <si>
+    <t>08.10.202646</t>
+  </si>
+  <si>
+    <t>08.10.202647</t>
+  </si>
+  <si>
+    <t>08.10.202648</t>
+  </si>
+  <si>
+    <t>08.10.202649</t>
+  </si>
+  <si>
+    <t>08.10.202650</t>
+  </si>
+  <si>
+    <t>08.10.202651</t>
+  </si>
+  <si>
+    <t>08.10.202652</t>
+  </si>
+  <si>
+    <t>08.10.202653</t>
+  </si>
+  <si>
+    <t>08.10.202654</t>
+  </si>
+  <si>
+    <t>08.10.202655</t>
+  </si>
+  <si>
+    <t>08.10.202656</t>
+  </si>
+  <si>
+    <t>08.10.202657</t>
+  </si>
+  <si>
+    <t>08.10.202658</t>
+  </si>
+  <si>
+    <t>08.10.202659</t>
+  </si>
+  <si>
+    <t>08.10.202660</t>
+  </si>
+  <si>
+    <t>08.10.202661</t>
+  </si>
+  <si>
+    <t>08.10.202662</t>
+  </si>
+  <si>
+    <t>08.10.202663</t>
+  </si>
+  <si>
+    <t>08.10.202664</t>
+  </si>
+  <si>
+    <t>08.10.202665</t>
+  </si>
+  <si>
+    <t>08.10.202666</t>
+  </si>
+  <si>
+    <t>08.10.202667</t>
+  </si>
+  <si>
+    <t>08.10.202668</t>
+  </si>
+  <si>
+    <t>08.10.202669</t>
+  </si>
+  <si>
+    <t>08.10.202670</t>
+  </si>
+  <si>
+    <t>08.10.202671</t>
+  </si>
+  <si>
+    <t>08.10.202672</t>
+  </si>
+  <si>
+    <t>08.10.202673</t>
+  </si>
+  <si>
+    <t>08.10.202674</t>
+  </si>
+  <si>
+    <t>08.10.202675</t>
+  </si>
+  <si>
+    <t>08.10.202676</t>
+  </si>
+  <si>
+    <t>08.10.202677</t>
+  </si>
+  <si>
+    <t>08.10.202678</t>
+  </si>
+  <si>
+    <t>08.10.202679</t>
+  </si>
+  <si>
+    <t>08.10.202680</t>
+  </si>
+  <si>
+    <t>08.10.202681</t>
+  </si>
+  <si>
+    <t>08.10.202682</t>
+  </si>
+  <si>
+    <t>08.10.202683</t>
+  </si>
+  <si>
+    <t>08.10.202684</t>
+  </si>
+  <si>
+    <t>08.10.202685</t>
+  </si>
+  <si>
+    <t>08.10.202686</t>
+  </si>
+  <si>
+    <t>08.10.202687</t>
+  </si>
+  <si>
+    <t>08.10.202688</t>
+  </si>
+  <si>
+    <t>08.10.202689</t>
+  </si>
+  <si>
+    <t>08.10.202690</t>
+  </si>
+  <si>
+    <t>08.10.202691</t>
+  </si>
+  <si>
+    <t>08.10.202692</t>
+  </si>
+  <si>
+    <t>08.10.202693</t>
+  </si>
+  <si>
+    <t>08.10.202694</t>
+  </si>
+  <si>
+    <t>08.10.202695</t>
+  </si>
+  <si>
+    <t>08.10.202696</t>
+  </si>
+  <si>
+    <t>09.10.20261</t>
+  </si>
+  <si>
+    <t>09.10.20262</t>
+  </si>
+  <si>
+    <t>09.10.20263</t>
+  </si>
+  <si>
+    <t>09.10.20264</t>
+  </si>
+  <si>
+    <t>09.10.20265</t>
+  </si>
+  <si>
+    <t>09.10.20266</t>
+  </si>
+  <si>
+    <t>09.10.20267</t>
+  </si>
+  <si>
+    <t>09.10.20268</t>
+  </si>
+  <si>
+    <t>09.10.20269</t>
+  </si>
+  <si>
+    <t>09.10.202610</t>
+  </si>
+  <si>
+    <t>09.10.202611</t>
+  </si>
+  <si>
+    <t>09.10.202612</t>
+  </si>
+  <si>
+    <t>09.10.202613</t>
+  </si>
+  <si>
+    <t>09.10.202614</t>
+  </si>
+  <si>
+    <t>09.10.202615</t>
+  </si>
+  <si>
+    <t>09.10.202616</t>
+  </si>
+  <si>
+    <t>09.10.202617</t>
+  </si>
+  <si>
+    <t>09.10.202618</t>
+  </si>
+  <si>
+    <t>09.10.202619</t>
+  </si>
+  <si>
+    <t>09.10.202620</t>
+  </si>
+  <si>
+    <t>09.10.202621</t>
+  </si>
+  <si>
+    <t>09.10.202622</t>
+  </si>
+  <si>
+    <t>09.10.202623</t>
+  </si>
+  <si>
+    <t>09.10.202624</t>
+  </si>
+  <si>
+    <t>09.10.202625</t>
+  </si>
+  <si>
+    <t>09.10.202626</t>
+  </si>
+  <si>
+    <t>09.10.202627</t>
+  </si>
+  <si>
+    <t>09.10.202628</t>
+  </si>
+  <si>
+    <t>09.10.202629</t>
+  </si>
+  <si>
+    <t>09.10.202630</t>
+  </si>
+  <si>
+    <t>09.10.202631</t>
+  </si>
+  <si>
+    <t>09.10.202632</t>
+  </si>
+  <si>
+    <t>09.10.202633</t>
+  </si>
+  <si>
+    <t>09.10.202634</t>
+  </si>
+  <si>
+    <t>09.10.202635</t>
+  </si>
+  <si>
+    <t>09.10.202636</t>
   </si>
 </sst>
 </file>
@@ -801,7 +786,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E138"/>
+  <dimension ref="A1:E133"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -823,13 +808,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B2">
-        <v>6.977</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>1.654</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -840,13 +825,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46302.01041666666</v>
+        <v>46303.01041666666</v>
       </c>
       <c r="B3">
-        <v>1.535</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>4.228</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -857,10 +842,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46302.02083333334</v>
+        <v>46303.02083333334</v>
       </c>
       <c r="B4">
-        <v>12.375</v>
+        <v>6.344</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -874,10 +859,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46302.03125</v>
+        <v>46303.03125</v>
       </c>
       <c r="B5">
-        <v>20.101</v>
+        <v>5.589</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -891,13 +876,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46302.04166666666</v>
+        <v>46303.04166666666</v>
       </c>
       <c r="B6">
-        <v>11.95</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>12.776</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -908,13 +893,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46302.05208333334</v>
+        <v>46303.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="C7">
-        <v>4.199</v>
+        <v>12.904</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -925,10 +910,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46302.0625</v>
+        <v>46303.0625</v>
       </c>
       <c r="B8">
-        <v>2.957</v>
+        <v>2.344</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -942,13 +927,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46302.07291666666</v>
+        <v>46303.07291666666</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>6.376</v>
       </c>
       <c r="C9">
-        <v>5.264</v>
+        <v>0</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -959,13 +944,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46302.08333333334</v>
+        <v>46303.08333333334</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>9.398</v>
       </c>
       <c r="C10">
-        <v>6.761</v>
+        <v>0</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -976,10 +961,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46302.09375</v>
+        <v>46303.09375</v>
       </c>
       <c r="B11">
-        <v>5.737</v>
+        <v>1.594</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -993,13 +978,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46302.10416666666</v>
+        <v>46303.10416666666</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>2.241</v>
       </c>
       <c r="C12">
-        <v>1.812</v>
+        <v>0</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -1010,10 +995,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46302.11458333334</v>
+        <v>46303.11458333334</v>
       </c>
       <c r="B13">
-        <v>0.353</v>
+        <v>2.899</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1027,10 +1012,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46302.125</v>
+        <v>46303.125</v>
       </c>
       <c r="B14">
-        <v>2.481</v>
+        <v>3.793</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1044,10 +1029,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46302.13541666666</v>
+        <v>46303.13541666666</v>
       </c>
       <c r="B15">
-        <v>5.741</v>
+        <v>13.075</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1061,10 +1046,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46302.14583333334</v>
+        <v>46303.14583333334</v>
       </c>
       <c r="B16">
-        <v>3.033</v>
+        <v>4.877</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1078,13 +1063,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46302.15625</v>
+        <v>46303.15625</v>
       </c>
       <c r="B17">
-        <v>5.016</v>
+        <v>0</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="D17">
         <v>16</v>
@@ -1095,13 +1080,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46302.16666666666</v>
+        <v>46303.16666666666</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>7.273</v>
       </c>
       <c r="C18">
-        <v>1.076</v>
+        <v>0</v>
       </c>
       <c r="D18">
         <v>17</v>
@@ -1112,10 +1097,10 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46302.17708333334</v>
+        <v>46303.17708333334</v>
       </c>
       <c r="B19">
-        <v>4.179</v>
+        <v>6.235</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1129,10 +1114,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46302.1875</v>
+        <v>46303.1875</v>
       </c>
       <c r="B20">
-        <v>0.59</v>
+        <v>13.042</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1146,10 +1131,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46302.19791666666</v>
+        <v>46303.19791666666</v>
       </c>
       <c r="B21">
-        <v>4.79</v>
+        <v>13.122</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1163,13 +1148,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46302.20833333334</v>
+        <v>46303.20833333334</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>9.16</v>
       </c>
       <c r="C22">
-        <v>7.102</v>
+        <v>0</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1180,13 +1165,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46302.21875</v>
+        <v>46303.21875</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>0.896</v>
       </c>
       <c r="C23">
-        <v>1.412</v>
+        <v>0</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1197,10 +1182,10 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46302.22916666666</v>
+        <v>46303.22916666666</v>
       </c>
       <c r="B24">
-        <v>2.956</v>
+        <v>5.842</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -1214,13 +1199,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46302.23958333334</v>
+        <v>46303.23958333334</v>
       </c>
       <c r="B25">
         <v>0</v>
       </c>
       <c r="C25">
-        <v>4.013</v>
+        <v>3.217</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1231,13 +1216,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46302.25</v>
+        <v>46303.25</v>
       </c>
       <c r="B26">
-        <v>0.199</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>5.059</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1248,13 +1233,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46302.26041666666</v>
+        <v>46303.26041666666</v>
       </c>
       <c r="B27">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>4.055</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1265,13 +1250,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46302.27083333334</v>
+        <v>46303.27083333334</v>
       </c>
       <c r="B28">
         <v>0</v>
       </c>
       <c r="C28">
-        <v>3.653</v>
+        <v>9.659000000000001</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1282,13 +1267,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46302.28125</v>
+        <v>46303.28125</v>
       </c>
       <c r="B29">
-        <v>2.173</v>
+        <v>0</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>12.546</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1299,10 +1284,10 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46302.29166666666</v>
+        <v>46303.29166666666</v>
       </c>
       <c r="B30">
-        <v>3.3</v>
+        <v>11.212</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -1316,10 +1301,10 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46302.30208333334</v>
+        <v>46303.30208333334</v>
       </c>
       <c r="B31">
-        <v>0.723</v>
+        <v>3.393</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -1333,13 +1318,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46302.3125</v>
+        <v>46303.3125</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="C32">
-        <v>6.92</v>
+        <v>0</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1350,13 +1335,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46302.32291666666</v>
+        <v>46303.32291666666</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>12.293</v>
       </c>
       <c r="C33">
-        <v>9.98</v>
+        <v>0</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1367,10 +1352,10 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46302.33333333334</v>
+        <v>46303.33333333334</v>
       </c>
       <c r="B34">
-        <v>7.894</v>
+        <v>63.387</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -1384,13 +1369,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46302.34375</v>
+        <v>46303.34375</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>24.17</v>
       </c>
       <c r="C35">
-        <v>15.589</v>
+        <v>0</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1401,10 +1386,10 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46302.35416666666</v>
+        <v>46303.35416666666</v>
       </c>
       <c r="B36">
-        <v>0.596</v>
+        <v>2.755</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -1418,13 +1403,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46302.36458333334</v>
+        <v>46303.36458333334</v>
       </c>
       <c r="B37">
-        <v>7.365</v>
+        <v>0</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>34.937</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1435,13 +1420,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46302.375</v>
+        <v>46303.375</v>
       </c>
       <c r="B38">
-        <v>2.618</v>
+        <v>0</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>9.651</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1452,13 +1437,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46302.38541666666</v>
+        <v>46303.38541666666</v>
       </c>
       <c r="B39">
         <v>0</v>
       </c>
       <c r="C39">
-        <v>7.008</v>
+        <v>20.735</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1469,13 +1454,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46302.39583333334</v>
+        <v>46303.39583333334</v>
       </c>
       <c r="B40">
         <v>0</v>
       </c>
       <c r="C40">
-        <v>9.016</v>
+        <v>9.116</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1486,13 +1471,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46302.40625</v>
+        <v>46303.40625</v>
       </c>
       <c r="B41">
         <v>0</v>
       </c>
       <c r="C41">
-        <v>15.121</v>
+        <v>21.816</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1503,13 +1488,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46302.41666666666</v>
+        <v>46303.41666666666</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="C42">
-        <v>3.741</v>
+        <v>0</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1520,13 +1505,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46302.42708333334</v>
+        <v>46303.42708333334</v>
       </c>
       <c r="B43">
         <v>0</v>
       </c>
       <c r="C43">
-        <v>8.199999999999999</v>
+        <v>3.924</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1537,13 +1522,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46302.4375</v>
+        <v>46303.4375</v>
       </c>
       <c r="B44">
-        <v>0.083</v>
+        <v>0</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>5.868</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1554,13 +1539,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46302.44791666666</v>
+        <v>46303.44791666666</v>
       </c>
       <c r="B45">
         <v>0</v>
       </c>
       <c r="C45">
-        <v>18.085</v>
+        <v>23.783</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1571,13 +1556,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46302.45833333334</v>
+        <v>46303.45833333334</v>
       </c>
       <c r="B46">
-        <v>3.877</v>
+        <v>0</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>25.651</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1588,13 +1573,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46302.46875</v>
+        <v>46303.46875</v>
       </c>
       <c r="B47">
         <v>0</v>
       </c>
       <c r="C47">
-        <v>18.022</v>
+        <v>20.054</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1605,13 +1590,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46302.47916666666</v>
+        <v>46303.47916666666</v>
       </c>
       <c r="B48">
         <v>0</v>
       </c>
       <c r="C48">
-        <v>25.77</v>
+        <v>4.839</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1622,13 +1607,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46302.48958333334</v>
+        <v>46303.48958333334</v>
       </c>
       <c r="B49">
         <v>0</v>
       </c>
       <c r="C49">
-        <v>5.081</v>
+        <v>0.508</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1639,13 +1624,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46302.5</v>
+        <v>46303.5</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>0.765</v>
       </c>
       <c r="C50">
-        <v>4.666</v>
+        <v>0</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1656,13 +1641,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46302.51041666666</v>
+        <v>46303.51041666666</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>8.848000000000001</v>
       </c>
       <c r="C51">
-        <v>0.718</v>
+        <v>0</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1673,13 +1658,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46302.52083333334</v>
+        <v>46303.52083333334</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>12.258</v>
       </c>
       <c r="C52">
-        <v>0.846</v>
+        <v>0</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1690,13 +1675,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46302.53125</v>
+        <v>46303.53125</v>
       </c>
       <c r="B53">
-        <v>0</v>
+        <v>3.554</v>
       </c>
       <c r="C53">
-        <v>0.024</v>
+        <v>0</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1707,10 +1692,10 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46302.54166666666</v>
+        <v>46303.54166666666</v>
       </c>
       <c r="B54">
-        <v>3.336</v>
+        <v>0.313</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -1724,13 +1709,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46302.55208333334</v>
+        <v>46303.55208333334</v>
       </c>
       <c r="B55">
-        <v>11.143</v>
+        <v>0</v>
       </c>
       <c r="C55">
-        <v>0</v>
+        <v>10.726</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1741,13 +1726,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46302.5625</v>
+        <v>46303.5625</v>
       </c>
       <c r="B56">
         <v>0</v>
       </c>
       <c r="C56">
-        <v>0.77</v>
+        <v>10.599</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1758,13 +1743,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46302.57291666666</v>
+        <v>46303.57291666666</v>
       </c>
       <c r="B57">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>7.132</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1775,13 +1760,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46302.58333333334</v>
+        <v>46303.58333333334</v>
       </c>
       <c r="B58">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="C58">
-        <v>7.84</v>
+        <v>0</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1792,13 +1777,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46302.59375</v>
+        <v>46303.59375</v>
       </c>
       <c r="B59">
         <v>0</v>
       </c>
       <c r="C59">
-        <v>11.372</v>
+        <v>11.159</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1809,13 +1794,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46302.60416666666</v>
+        <v>46303.60416666666</v>
       </c>
       <c r="B60">
         <v>0</v>
       </c>
       <c r="C60">
-        <v>5.07</v>
+        <v>19.62</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1826,13 +1811,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46302.61458333334</v>
+        <v>46303.61458333334</v>
       </c>
       <c r="B61">
         <v>0</v>
       </c>
       <c r="C61">
-        <v>9.17</v>
+        <v>6.304</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -1843,13 +1828,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46302.625</v>
+        <v>46303.625</v>
       </c>
       <c r="B62">
         <v>0</v>
       </c>
       <c r="C62">
-        <v>14.079</v>
+        <v>42.704</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -1860,13 +1845,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46302.63541666666</v>
+        <v>46303.63541666666</v>
       </c>
       <c r="B63">
         <v>0</v>
       </c>
       <c r="C63">
-        <v>8.461</v>
+        <v>19.432</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -1877,13 +1862,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46302.64583333334</v>
+        <v>46303.64583333334</v>
       </c>
       <c r="B64">
-        <v>0</v>
+        <v>0.145</v>
       </c>
       <c r="C64">
-        <v>4.226</v>
+        <v>0</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -1894,13 +1879,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46302.65625</v>
+        <v>46303.65625</v>
       </c>
       <c r="B65">
         <v>0</v>
       </c>
       <c r="C65">
-        <v>7.412</v>
+        <v>2.54</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -1911,13 +1896,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46302.66666666666</v>
+        <v>46303.66666666666</v>
       </c>
       <c r="B66">
         <v>0</v>
       </c>
       <c r="C66">
-        <v>4.073</v>
+        <v>13.759</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -1928,13 +1913,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46302.67708333334</v>
+        <v>46303.67708333334</v>
       </c>
       <c r="B67">
         <v>0</v>
       </c>
       <c r="C67">
-        <v>4.936</v>
+        <v>1.594</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -1945,13 +1930,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46302.6875</v>
+        <v>46303.6875</v>
       </c>
       <c r="B68">
-        <v>0</v>
+        <v>6.12</v>
       </c>
       <c r="C68">
-        <v>1.548</v>
+        <v>0</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -1962,10 +1947,10 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46302.69791666666</v>
+        <v>46303.69791666666</v>
       </c>
       <c r="B69">
-        <v>2.617</v>
+        <v>12.533</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -1979,13 +1964,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46302.70833333334</v>
+        <v>46303.70833333334</v>
       </c>
       <c r="B70">
-        <v>0</v>
+        <v>2.657</v>
       </c>
       <c r="C70">
-        <v>15.794</v>
+        <v>0</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -1996,13 +1981,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46302.71875</v>
+        <v>46303.71875</v>
       </c>
       <c r="B71">
-        <v>0</v>
+        <v>18.483</v>
       </c>
       <c r="C71">
-        <v>1.969</v>
+        <v>0</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2013,13 +1998,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46302.72916666666</v>
+        <v>46303.72916666666</v>
       </c>
       <c r="B72">
-        <v>0</v>
+        <v>14.822</v>
       </c>
       <c r="C72">
-        <v>5.975</v>
+        <v>0</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2030,13 +2015,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46302.73958333334</v>
+        <v>46303.73958333334</v>
       </c>
       <c r="B73">
-        <v>0</v>
+        <v>24.355</v>
       </c>
       <c r="C73">
-        <v>16.184</v>
+        <v>0</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2047,13 +2032,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46302.75</v>
+        <v>46303.75</v>
       </c>
       <c r="B74">
-        <v>0</v>
+        <v>6.231</v>
       </c>
       <c r="C74">
-        <v>38.979</v>
+        <v>0</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2064,13 +2049,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46302.76041666666</v>
+        <v>46303.76041666666</v>
       </c>
       <c r="B75">
         <v>0</v>
       </c>
       <c r="C75">
-        <v>30.906</v>
+        <v>5.523</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2081,13 +2066,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46302.77083333334</v>
+        <v>46303.77083333334</v>
       </c>
       <c r="B76">
         <v>0</v>
       </c>
       <c r="C76">
-        <v>8.714</v>
+        <v>21.072</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2098,13 +2083,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46302.78125</v>
+        <v>46303.78125</v>
       </c>
       <c r="B77">
         <v>0</v>
       </c>
       <c r="C77">
-        <v>6.109</v>
+        <v>40.738</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2115,13 +2100,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46302.79166666666</v>
+        <v>46303.79166666666</v>
       </c>
       <c r="B78">
         <v>0</v>
       </c>
       <c r="C78">
-        <v>1.821</v>
+        <v>21.639</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2132,13 +2117,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46302.80208333334</v>
+        <v>46303.80208333334</v>
       </c>
       <c r="B79">
         <v>0</v>
       </c>
       <c r="C79">
-        <v>3.673</v>
+        <v>23.075</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2149,13 +2134,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46302.8125</v>
+        <v>46303.8125</v>
       </c>
       <c r="B80">
         <v>0</v>
       </c>
       <c r="C80">
-        <v>1.715</v>
+        <v>8.401999999999999</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2166,13 +2151,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46302.82291666666</v>
+        <v>46303.82291666666</v>
       </c>
       <c r="B81">
-        <v>11.172</v>
+        <v>0</v>
       </c>
       <c r="C81">
-        <v>0</v>
+        <v>3.026</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2183,10 +2168,10 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46302.83333333334</v>
+        <v>46303.83333333334</v>
       </c>
       <c r="B82">
-        <v>12.495</v>
+        <v>9.045999999999999</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -2200,10 +2185,10 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46302.84375</v>
+        <v>46303.84375</v>
       </c>
       <c r="B83">
-        <v>24.927</v>
+        <v>17.486</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -2217,10 +2202,10 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46302.85416666666</v>
+        <v>46303.85416666666</v>
       </c>
       <c r="B84">
-        <v>9.164999999999999</v>
+        <v>13.673</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -2234,13 +2219,13 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46302.86458333334</v>
+        <v>46303.86458333334</v>
       </c>
       <c r="B85">
-        <v>2.414</v>
+        <v>0</v>
       </c>
       <c r="C85">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="D85">
         <v>84</v>
@@ -2251,13 +2236,13 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46302.875</v>
+        <v>46303.875</v>
       </c>
       <c r="B86">
-        <v>0</v>
+        <v>4.554</v>
       </c>
       <c r="C86">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="D86">
         <v>85</v>
@@ -2268,13 +2253,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46302.88541666666</v>
+        <v>46303.88541666666</v>
       </c>
       <c r="B87">
         <v>0</v>
       </c>
       <c r="C87">
-        <v>11.31</v>
+        <v>2.605</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -2285,13 +2270,13 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46302.89583333334</v>
+        <v>46303.89583333334</v>
       </c>
       <c r="B88">
         <v>0</v>
       </c>
       <c r="C88">
-        <v>8.443</v>
+        <v>8.757</v>
       </c>
       <c r="D88">
         <v>87</v>
@@ -2302,13 +2287,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46302.90625</v>
+        <v>46303.90625</v>
       </c>
       <c r="B89">
         <v>0</v>
       </c>
       <c r="C89">
-        <v>3.357</v>
+        <v>10.737</v>
       </c>
       <c r="D89">
         <v>88</v>
@@ -2319,13 +2304,13 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46302.91666666666</v>
+        <v>46303.91666666666</v>
       </c>
       <c r="B90">
-        <v>0</v>
+        <v>2.954</v>
       </c>
       <c r="C90">
-        <v>4.769</v>
+        <v>0</v>
       </c>
       <c r="D90">
         <v>89</v>
@@ -2336,13 +2321,13 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46302.92708333334</v>
+        <v>46303.92708333334</v>
       </c>
       <c r="B91">
-        <v>0</v>
+        <v>2.251</v>
       </c>
       <c r="C91">
-        <v>4.053</v>
+        <v>0</v>
       </c>
       <c r="D91">
         <v>90</v>
@@ -2353,10 +2338,10 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46302.9375</v>
+        <v>46303.9375</v>
       </c>
       <c r="B92">
-        <v>2.361</v>
+        <v>3.624</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -2370,13 +2355,13 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46302.94791666666</v>
+        <v>46303.94791666666</v>
       </c>
       <c r="B93">
         <v>0</v>
       </c>
       <c r="C93">
-        <v>4.29</v>
+        <v>0.139</v>
       </c>
       <c r="D93">
         <v>92</v>
@@ -2387,13 +2372,13 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46302.95833333334</v>
+        <v>46303.95833333334</v>
       </c>
       <c r="B94">
-        <v>0</v>
+        <v>0.976</v>
       </c>
       <c r="C94">
-        <v>12.315</v>
+        <v>0</v>
       </c>
       <c r="D94">
         <v>93</v>
@@ -2404,13 +2389,13 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46302.96875</v>
+        <v>46303.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
       </c>
       <c r="C95">
-        <v>7.403</v>
+        <v>3.064</v>
       </c>
       <c r="D95">
         <v>94</v>
@@ -2421,13 +2406,13 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46302.97916666666</v>
+        <v>46303.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
       </c>
       <c r="C96">
-        <v>2.578</v>
+        <v>1.145</v>
       </c>
       <c r="D96">
         <v>95</v>
@@ -2438,10 +2423,10 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46302.98958333334</v>
+        <v>46303.98958333334</v>
       </c>
       <c r="B97">
-        <v>0.486</v>
+        <v>2.758</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -2455,13 +2440,13 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B98">
         <v>0</v>
       </c>
       <c r="C98">
-        <v>1.654</v>
+        <v>5.513</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -2472,13 +2457,13 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46303.01041666666</v>
+        <v>46304.01041666666</v>
       </c>
       <c r="B99">
         <v>0</v>
       </c>
       <c r="C99">
-        <v>4.228</v>
+        <v>1.911</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -2489,13 +2474,13 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46303.02083333334</v>
+        <v>46304.02083333334</v>
       </c>
       <c r="B100">
-        <v>6.344</v>
+        <v>0</v>
       </c>
       <c r="C100">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2506,13 +2491,13 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46303.03125</v>
+        <v>46304.03125</v>
       </c>
       <c r="B101">
-        <v>5.589</v>
+        <v>0</v>
       </c>
       <c r="C101">
-        <v>0</v>
+        <v>4.047</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -2523,13 +2508,13 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46303.04166666666</v>
+        <v>46304.04166666666</v>
       </c>
       <c r="B102">
-        <v>0</v>
+        <v>1.483</v>
       </c>
       <c r="C102">
-        <v>12.776</v>
+        <v>0</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -2540,13 +2525,13 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46303.05208333334</v>
+        <v>46304.05208333334</v>
       </c>
       <c r="B103">
         <v>0</v>
       </c>
       <c r="C103">
-        <v>12.904</v>
+        <v>0.537</v>
       </c>
       <c r="D103">
         <v>6</v>
@@ -2557,10 +2542,10 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46303.0625</v>
+        <v>46304.0625</v>
       </c>
       <c r="B104">
-        <v>2.344</v>
+        <v>3.306</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -2574,13 +2559,13 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46303.07291666666</v>
+        <v>46304.07291666666</v>
       </c>
       <c r="B105">
-        <v>6.376</v>
+        <v>0</v>
       </c>
       <c r="C105">
-        <v>0</v>
+        <v>2.955</v>
       </c>
       <c r="D105">
         <v>8</v>
@@ -2591,10 +2576,10 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46303.08333333334</v>
+        <v>46304.08333333334</v>
       </c>
       <c r="B106">
-        <v>9.398</v>
+        <v>3.043</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -2608,10 +2593,10 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46303.09375</v>
+        <v>46304.09375</v>
       </c>
       <c r="B107">
-        <v>1.594</v>
+        <v>3.872</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -2625,10 +2610,10 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46303.10416666666</v>
+        <v>46304.10416666666</v>
       </c>
       <c r="B108">
-        <v>2.241</v>
+        <v>0.743</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -2642,10 +2627,10 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46303.11458333334</v>
+        <v>46304.11458333334</v>
       </c>
       <c r="B109">
-        <v>2.899</v>
+        <v>0.045</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -2659,10 +2644,10 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46303.125</v>
+        <v>46304.125</v>
       </c>
       <c r="B110">
-        <v>3.793</v>
+        <v>3.994</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -2676,10 +2661,10 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46303.13541666666</v>
+        <v>46304.13541666666</v>
       </c>
       <c r="B111">
-        <v>13.075</v>
+        <v>1.176</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -2693,13 +2678,13 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46303.14583333334</v>
+        <v>46304.14583333334</v>
       </c>
       <c r="B112">
-        <v>4.877</v>
+        <v>0</v>
       </c>
       <c r="C112">
-        <v>0</v>
+        <v>0.922</v>
       </c>
       <c r="D112">
         <v>15</v>
@@ -2710,13 +2695,13 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46303.15625</v>
+        <v>46304.15625</v>
       </c>
       <c r="B113">
-        <v>0</v>
+        <v>3.012</v>
       </c>
       <c r="C113">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="D113">
         <v>16</v>
@@ -2727,13 +2712,13 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46303.16666666666</v>
+        <v>46304.16666666666</v>
       </c>
       <c r="B114">
-        <v>7.273</v>
+        <v>0</v>
       </c>
       <c r="C114">
-        <v>0</v>
+        <v>16.083</v>
       </c>
       <c r="D114">
         <v>17</v>
@@ -2744,13 +2729,13 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46303.17708333334</v>
+        <v>46304.17708333334</v>
       </c>
       <c r="B115">
-        <v>6.235</v>
+        <v>0</v>
       </c>
       <c r="C115">
-        <v>0</v>
+        <v>1.287</v>
       </c>
       <c r="D115">
         <v>18</v>
@@ -2761,13 +2746,13 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46303.1875</v>
+        <v>46304.1875</v>
       </c>
       <c r="B116">
-        <v>13.042</v>
+        <v>0</v>
       </c>
       <c r="C116">
-        <v>0</v>
+        <v>13.1</v>
       </c>
       <c r="D116">
         <v>19</v>
@@ -2778,13 +2763,13 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46303.19791666666</v>
+        <v>46304.19791666666</v>
       </c>
       <c r="B117">
-        <v>13.122</v>
+        <v>0</v>
       </c>
       <c r="C117">
-        <v>0</v>
+        <v>4.118</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -2795,13 +2780,13 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46303.20833333334</v>
+        <v>46304.20833333334</v>
       </c>
       <c r="B118">
-        <v>9.16</v>
+        <v>0</v>
       </c>
       <c r="C118">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -2812,10 +2797,10 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46303.21875</v>
+        <v>46304.21875</v>
       </c>
       <c r="B119">
-        <v>0.896</v>
+        <v>3.7</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -2829,13 +2814,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46303.22916666666</v>
+        <v>46304.22916666666</v>
       </c>
       <c r="B120">
-        <v>5.842</v>
+        <v>0</v>
       </c>
       <c r="C120">
-        <v>0</v>
+        <v>15.554</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -2846,13 +2831,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46303.23958333334</v>
+        <v>46304.23958333334</v>
       </c>
       <c r="B121">
         <v>0</v>
       </c>
       <c r="C121">
-        <v>3.217</v>
+        <v>4.965</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -2863,13 +2848,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46303.25</v>
+        <v>46304.25</v>
       </c>
       <c r="B122">
         <v>0</v>
       </c>
       <c r="C122">
-        <v>5.059</v>
+        <v>11.868</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -2880,13 +2865,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46303.26041666666</v>
+        <v>46304.26041666666</v>
       </c>
       <c r="B123">
         <v>0</v>
       </c>
       <c r="C123">
-        <v>4.055</v>
+        <v>31.386</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -2897,13 +2882,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46303.27083333334</v>
+        <v>46304.27083333334</v>
       </c>
       <c r="B124">
         <v>0</v>
       </c>
       <c r="C124">
-        <v>9.659000000000001</v>
+        <v>30.892</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -2914,13 +2899,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46303.28125</v>
+        <v>46304.28125</v>
       </c>
       <c r="B125">
         <v>0</v>
       </c>
       <c r="C125">
-        <v>12.546</v>
+        <v>6.808</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -2931,13 +2916,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46303.29166666666</v>
+        <v>46304.29166666666</v>
       </c>
       <c r="B126">
-        <v>11.212</v>
+        <v>0</v>
       </c>
       <c r="C126">
-        <v>0</v>
+        <v>11.116</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -2948,13 +2933,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46303.30208333334</v>
+        <v>46304.30208333334</v>
       </c>
       <c r="B127">
-        <v>3.393</v>
+        <v>0</v>
       </c>
       <c r="C127">
-        <v>0</v>
+        <v>2.997</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -2965,13 +2950,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46303.3125</v>
+        <v>46304.3125</v>
       </c>
       <c r="B128">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="C128">
-        <v>0</v>
+        <v>20.779</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -2982,13 +2967,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46303.32291666666</v>
+        <v>46304.32291666666</v>
       </c>
       <c r="B129">
-        <v>12.293</v>
+        <v>0</v>
       </c>
       <c r="C129">
-        <v>0</v>
+        <v>5.091</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -2999,10 +2984,10 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46303.33333333334</v>
+        <v>46304.33333333334</v>
       </c>
       <c r="B130">
-        <v>63.387</v>
+        <v>11.99</v>
       </c>
       <c r="C130">
         <v>0</v>
@@ -3016,10 +3001,10 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46303.34375</v>
+        <v>46304.34375</v>
       </c>
       <c r="B131">
-        <v>24.17</v>
+        <v>6.328</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -3033,13 +3018,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46303.35416666666</v>
+        <v>46304.35416666666</v>
       </c>
       <c r="B132">
-        <v>2.755</v>
+        <v>0</v>
       </c>
       <c r="C132">
-        <v>0</v>
+        <v>4.151</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3050,104 +3035,19 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46303.36458333334</v>
+        <v>46304.36458333334</v>
       </c>
       <c r="B133">
         <v>0</v>
       </c>
       <c r="C133">
-        <v>34.937</v>
+        <v>6.546</v>
       </c>
       <c r="D133">
         <v>36</v>
       </c>
       <c r="E133" t="s">
         <v>136</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5">
-      <c r="A134" s="2">
-        <v>46303.375</v>
-      </c>
-      <c r="B134">
-        <v>0</v>
-      </c>
-      <c r="C134">
-        <v>9.651</v>
-      </c>
-      <c r="D134">
-        <v>37</v>
-      </c>
-      <c r="E134" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5">
-      <c r="A135" s="2">
-        <v>46303.38541666666</v>
-      </c>
-      <c r="B135">
-        <v>0</v>
-      </c>
-      <c r="C135">
-        <v>20.735</v>
-      </c>
-      <c r="D135">
-        <v>38</v>
-      </c>
-      <c r="E135" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5">
-      <c r="A136" s="2">
-        <v>46303.39583333334</v>
-      </c>
-      <c r="B136">
-        <v>0</v>
-      </c>
-      <c r="C136">
-        <v>9.116</v>
-      </c>
-      <c r="D136">
-        <v>39</v>
-      </c>
-      <c r="E136" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5">
-      <c r="A137" s="2">
-        <v>46303.40625</v>
-      </c>
-      <c r="B137">
-        <v>0</v>
-      </c>
-      <c r="C137">
-        <v>21.816</v>
-      </c>
-      <c r="D137">
-        <v>40</v>
-      </c>
-      <c r="E137" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5">
-      <c r="A138" s="2">
-        <v>46303.41666666666</v>
-      </c>
-      <c r="B138">
-        <v>3.27</v>
-      </c>
-      <c r="C138">
-        <v>0</v>
-      </c>
-      <c r="D138">
-        <v>41</v>
-      </c>
-      <c r="E138" t="s">
-        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Unintended_Deviation.xlsx
+++ b/data_fetching/Entsoe/Unintended_Deviation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="331">
   <si>
     <t>Timestamp</t>
   </si>
@@ -31,294 +31,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>08.10.20261</t>
-  </si>
-  <si>
-    <t>08.10.20262</t>
-  </si>
-  <si>
-    <t>08.10.20263</t>
-  </si>
-  <si>
-    <t>08.10.20264</t>
-  </si>
-  <si>
-    <t>08.10.20265</t>
-  </si>
-  <si>
-    <t>08.10.20266</t>
-  </si>
-  <si>
-    <t>08.10.20267</t>
-  </si>
-  <si>
-    <t>08.10.20268</t>
-  </si>
-  <si>
-    <t>08.10.20269</t>
-  </si>
-  <si>
-    <t>08.10.202610</t>
-  </si>
-  <si>
-    <t>08.10.202611</t>
-  </si>
-  <si>
-    <t>08.10.202612</t>
-  </si>
-  <si>
-    <t>08.10.202613</t>
-  </si>
-  <si>
-    <t>08.10.202614</t>
-  </si>
-  <si>
-    <t>08.10.202615</t>
-  </si>
-  <si>
-    <t>08.10.202616</t>
-  </si>
-  <si>
-    <t>08.10.202617</t>
-  </si>
-  <si>
-    <t>08.10.202618</t>
-  </si>
-  <si>
-    <t>08.10.202619</t>
-  </si>
-  <si>
-    <t>08.10.202620</t>
-  </si>
-  <si>
-    <t>08.10.202621</t>
-  </si>
-  <si>
-    <t>08.10.202622</t>
-  </si>
-  <si>
-    <t>08.10.202623</t>
-  </si>
-  <si>
-    <t>08.10.202624</t>
-  </si>
-  <si>
-    <t>08.10.202625</t>
-  </si>
-  <si>
-    <t>08.10.202626</t>
-  </si>
-  <si>
-    <t>08.10.202627</t>
-  </si>
-  <si>
-    <t>08.10.202628</t>
-  </si>
-  <si>
-    <t>08.10.202629</t>
-  </si>
-  <si>
-    <t>08.10.202630</t>
-  </si>
-  <si>
-    <t>08.10.202631</t>
-  </si>
-  <si>
-    <t>08.10.202632</t>
-  </si>
-  <si>
-    <t>08.10.202633</t>
-  </si>
-  <si>
-    <t>08.10.202634</t>
-  </si>
-  <si>
-    <t>08.10.202635</t>
-  </si>
-  <si>
-    <t>08.10.202636</t>
-  </si>
-  <si>
-    <t>08.10.202637</t>
-  </si>
-  <si>
-    <t>08.10.202638</t>
-  </si>
-  <si>
-    <t>08.10.202639</t>
-  </si>
-  <si>
-    <t>08.10.202640</t>
-  </si>
-  <si>
-    <t>08.10.202641</t>
-  </si>
-  <si>
-    <t>08.10.202642</t>
-  </si>
-  <si>
-    <t>08.10.202643</t>
-  </si>
-  <si>
-    <t>08.10.202644</t>
-  </si>
-  <si>
-    <t>08.10.202645</t>
-  </si>
-  <si>
-    <t>08.10.202646</t>
-  </si>
-  <si>
-    <t>08.10.202647</t>
-  </si>
-  <si>
-    <t>08.10.202648</t>
-  </si>
-  <si>
-    <t>08.10.202649</t>
-  </si>
-  <si>
-    <t>08.10.202650</t>
-  </si>
-  <si>
-    <t>08.10.202651</t>
-  </si>
-  <si>
-    <t>08.10.202652</t>
-  </si>
-  <si>
-    <t>08.10.202653</t>
-  </si>
-  <si>
-    <t>08.10.202654</t>
-  </si>
-  <si>
-    <t>08.10.202655</t>
-  </si>
-  <si>
-    <t>08.10.202656</t>
-  </si>
-  <si>
-    <t>08.10.202657</t>
-  </si>
-  <si>
-    <t>08.10.202658</t>
-  </si>
-  <si>
-    <t>08.10.202659</t>
-  </si>
-  <si>
-    <t>08.10.202660</t>
-  </si>
-  <si>
-    <t>08.10.202661</t>
-  </si>
-  <si>
-    <t>08.10.202662</t>
-  </si>
-  <si>
-    <t>08.10.202663</t>
-  </si>
-  <si>
-    <t>08.10.202664</t>
-  </si>
-  <si>
-    <t>08.10.202665</t>
-  </si>
-  <si>
-    <t>08.10.202666</t>
-  </si>
-  <si>
-    <t>08.10.202667</t>
-  </si>
-  <si>
-    <t>08.10.202668</t>
-  </si>
-  <si>
-    <t>08.10.202669</t>
-  </si>
-  <si>
-    <t>08.10.202670</t>
-  </si>
-  <si>
-    <t>08.10.202671</t>
-  </si>
-  <si>
-    <t>08.10.202672</t>
-  </si>
-  <si>
-    <t>08.10.202673</t>
-  </si>
-  <si>
-    <t>08.10.202674</t>
-  </si>
-  <si>
-    <t>08.10.202675</t>
-  </si>
-  <si>
-    <t>08.10.202676</t>
-  </si>
-  <si>
-    <t>08.10.202677</t>
-  </si>
-  <si>
-    <t>08.10.202678</t>
-  </si>
-  <si>
-    <t>08.10.202679</t>
-  </si>
-  <si>
-    <t>08.10.202680</t>
-  </si>
-  <si>
-    <t>08.10.202681</t>
-  </si>
-  <si>
-    <t>08.10.202682</t>
-  </si>
-  <si>
-    <t>08.10.202683</t>
-  </si>
-  <si>
-    <t>08.10.202684</t>
-  </si>
-  <si>
-    <t>08.10.202685</t>
-  </si>
-  <si>
-    <t>08.10.202686</t>
-  </si>
-  <si>
-    <t>08.10.202687</t>
-  </si>
-  <si>
-    <t>08.10.202688</t>
-  </si>
-  <si>
-    <t>08.10.202689</t>
-  </si>
-  <si>
-    <t>08.10.202690</t>
-  </si>
-  <si>
-    <t>08.10.202691</t>
-  </si>
-  <si>
-    <t>08.10.202692</t>
-  </si>
-  <si>
-    <t>08.10.202693</t>
-  </si>
-  <si>
-    <t>08.10.202694</t>
-  </si>
-  <si>
-    <t>08.10.202695</t>
-  </si>
-  <si>
-    <t>08.10.202696</t>
-  </si>
-  <si>
     <t>09.10.20261</t>
   </si>
   <si>
@@ -425,6 +137,876 @@
   </si>
   <si>
     <t>09.10.202636</t>
+  </si>
+  <si>
+    <t>09.10.202637</t>
+  </si>
+  <si>
+    <t>09.10.202638</t>
+  </si>
+  <si>
+    <t>09.10.202639</t>
+  </si>
+  <si>
+    <t>09.10.202640</t>
+  </si>
+  <si>
+    <t>09.10.202641</t>
+  </si>
+  <si>
+    <t>09.10.202642</t>
+  </si>
+  <si>
+    <t>09.10.202643</t>
+  </si>
+  <si>
+    <t>09.10.202644</t>
+  </si>
+  <si>
+    <t>09.10.202645</t>
+  </si>
+  <si>
+    <t>09.10.202646</t>
+  </si>
+  <si>
+    <t>09.10.202647</t>
+  </si>
+  <si>
+    <t>09.10.202648</t>
+  </si>
+  <si>
+    <t>09.10.202649</t>
+  </si>
+  <si>
+    <t>09.10.202650</t>
+  </si>
+  <si>
+    <t>09.10.202651</t>
+  </si>
+  <si>
+    <t>09.10.202652</t>
+  </si>
+  <si>
+    <t>09.10.202653</t>
+  </si>
+  <si>
+    <t>09.10.202654</t>
+  </si>
+  <si>
+    <t>09.10.202655</t>
+  </si>
+  <si>
+    <t>09.10.202656</t>
+  </si>
+  <si>
+    <t>09.10.202657</t>
+  </si>
+  <si>
+    <t>09.10.202658</t>
+  </si>
+  <si>
+    <t>09.10.202659</t>
+  </si>
+  <si>
+    <t>09.10.202660</t>
+  </si>
+  <si>
+    <t>09.10.202661</t>
+  </si>
+  <si>
+    <t>09.10.202662</t>
+  </si>
+  <si>
+    <t>09.10.202663</t>
+  </si>
+  <si>
+    <t>09.10.202664</t>
+  </si>
+  <si>
+    <t>09.10.202665</t>
+  </si>
+  <si>
+    <t>09.10.202666</t>
+  </si>
+  <si>
+    <t>09.10.202667</t>
+  </si>
+  <si>
+    <t>09.10.202668</t>
+  </si>
+  <si>
+    <t>09.10.202669</t>
+  </si>
+  <si>
+    <t>09.10.202670</t>
+  </si>
+  <si>
+    <t>09.10.202671</t>
+  </si>
+  <si>
+    <t>09.10.202672</t>
+  </si>
+  <si>
+    <t>09.10.202673</t>
+  </si>
+  <si>
+    <t>09.10.202674</t>
+  </si>
+  <si>
+    <t>09.10.202675</t>
+  </si>
+  <si>
+    <t>09.10.202676</t>
+  </si>
+  <si>
+    <t>09.10.202677</t>
+  </si>
+  <si>
+    <t>09.10.202678</t>
+  </si>
+  <si>
+    <t>09.10.202679</t>
+  </si>
+  <si>
+    <t>09.10.202680</t>
+  </si>
+  <si>
+    <t>09.10.202681</t>
+  </si>
+  <si>
+    <t>09.10.202682</t>
+  </si>
+  <si>
+    <t>09.10.202683</t>
+  </si>
+  <si>
+    <t>09.10.202684</t>
+  </si>
+  <si>
+    <t>09.10.202685</t>
+  </si>
+  <si>
+    <t>09.10.202686</t>
+  </si>
+  <si>
+    <t>09.10.202687</t>
+  </si>
+  <si>
+    <t>09.10.202688</t>
+  </si>
+  <si>
+    <t>09.10.202689</t>
+  </si>
+  <si>
+    <t>09.10.202690</t>
+  </si>
+  <si>
+    <t>09.10.202691</t>
+  </si>
+  <si>
+    <t>09.10.202692</t>
+  </si>
+  <si>
+    <t>09.10.202693</t>
+  </si>
+  <si>
+    <t>09.10.202694</t>
+  </si>
+  <si>
+    <t>09.10.202695</t>
+  </si>
+  <si>
+    <t>09.10.202696</t>
+  </si>
+  <si>
+    <t>10.10.20261</t>
+  </si>
+  <si>
+    <t>10.10.20262</t>
+  </si>
+  <si>
+    <t>10.10.20263</t>
+  </si>
+  <si>
+    <t>10.10.20264</t>
+  </si>
+  <si>
+    <t>10.10.20265</t>
+  </si>
+  <si>
+    <t>10.10.20266</t>
+  </si>
+  <si>
+    <t>10.10.20267</t>
+  </si>
+  <si>
+    <t>10.10.20268</t>
+  </si>
+  <si>
+    <t>10.10.20269</t>
+  </si>
+  <si>
+    <t>10.10.202610</t>
+  </si>
+  <si>
+    <t>10.10.202611</t>
+  </si>
+  <si>
+    <t>10.10.202612</t>
+  </si>
+  <si>
+    <t>10.10.202613</t>
+  </si>
+  <si>
+    <t>10.10.202614</t>
+  </si>
+  <si>
+    <t>10.10.202615</t>
+  </si>
+  <si>
+    <t>10.10.202616</t>
+  </si>
+  <si>
+    <t>10.10.202617</t>
+  </si>
+  <si>
+    <t>10.10.202618</t>
+  </si>
+  <si>
+    <t>10.10.202619</t>
+  </si>
+  <si>
+    <t>10.10.202620</t>
+  </si>
+  <si>
+    <t>10.10.202621</t>
+  </si>
+  <si>
+    <t>10.10.202622</t>
+  </si>
+  <si>
+    <t>10.10.202623</t>
+  </si>
+  <si>
+    <t>10.10.202624</t>
+  </si>
+  <si>
+    <t>10.10.202625</t>
+  </si>
+  <si>
+    <t>10.10.202626</t>
+  </si>
+  <si>
+    <t>10.10.202627</t>
+  </si>
+  <si>
+    <t>10.10.202628</t>
+  </si>
+  <si>
+    <t>10.10.202629</t>
+  </si>
+  <si>
+    <t>10.10.202630</t>
+  </si>
+  <si>
+    <t>10.10.202631</t>
+  </si>
+  <si>
+    <t>10.10.202632</t>
+  </si>
+  <si>
+    <t>10.10.202633</t>
+  </si>
+  <si>
+    <t>10.10.202634</t>
+  </si>
+  <si>
+    <t>10.10.202635</t>
+  </si>
+  <si>
+    <t>10.10.202636</t>
+  </si>
+  <si>
+    <t>10.10.202637</t>
+  </si>
+  <si>
+    <t>10.10.202638</t>
+  </si>
+  <si>
+    <t>10.10.202639</t>
+  </si>
+  <si>
+    <t>10.10.202640</t>
+  </si>
+  <si>
+    <t>10.10.202641</t>
+  </si>
+  <si>
+    <t>10.10.202642</t>
+  </si>
+  <si>
+    <t>10.10.202643</t>
+  </si>
+  <si>
+    <t>10.10.202644</t>
+  </si>
+  <si>
+    <t>10.10.202645</t>
+  </si>
+  <si>
+    <t>10.10.202646</t>
+  </si>
+  <si>
+    <t>10.10.202647</t>
+  </si>
+  <si>
+    <t>10.10.202648</t>
+  </si>
+  <si>
+    <t>10.10.202649</t>
+  </si>
+  <si>
+    <t>10.10.202650</t>
+  </si>
+  <si>
+    <t>10.10.202651</t>
+  </si>
+  <si>
+    <t>10.10.202652</t>
+  </si>
+  <si>
+    <t>10.10.202653</t>
+  </si>
+  <si>
+    <t>10.10.202654</t>
+  </si>
+  <si>
+    <t>10.10.202655</t>
+  </si>
+  <si>
+    <t>10.10.202656</t>
+  </si>
+  <si>
+    <t>10.10.202657</t>
+  </si>
+  <si>
+    <t>10.10.202658</t>
+  </si>
+  <si>
+    <t>10.10.202659</t>
+  </si>
+  <si>
+    <t>10.10.202660</t>
+  </si>
+  <si>
+    <t>10.10.202661</t>
+  </si>
+  <si>
+    <t>10.10.202662</t>
+  </si>
+  <si>
+    <t>10.10.202663</t>
+  </si>
+  <si>
+    <t>10.10.202664</t>
+  </si>
+  <si>
+    <t>10.10.202665</t>
+  </si>
+  <si>
+    <t>10.10.202666</t>
+  </si>
+  <si>
+    <t>10.10.202667</t>
+  </si>
+  <si>
+    <t>10.10.202668</t>
+  </si>
+  <si>
+    <t>10.10.202669</t>
+  </si>
+  <si>
+    <t>10.10.202670</t>
+  </si>
+  <si>
+    <t>10.10.202671</t>
+  </si>
+  <si>
+    <t>10.10.202672</t>
+  </si>
+  <si>
+    <t>10.10.202673</t>
+  </si>
+  <si>
+    <t>10.10.202674</t>
+  </si>
+  <si>
+    <t>10.10.202675</t>
+  </si>
+  <si>
+    <t>10.10.202676</t>
+  </si>
+  <si>
+    <t>10.10.202677</t>
+  </si>
+  <si>
+    <t>10.10.202678</t>
+  </si>
+  <si>
+    <t>10.10.202679</t>
+  </si>
+  <si>
+    <t>10.10.202680</t>
+  </si>
+  <si>
+    <t>10.10.202681</t>
+  </si>
+  <si>
+    <t>10.10.202682</t>
+  </si>
+  <si>
+    <t>10.10.202683</t>
+  </si>
+  <si>
+    <t>10.10.202684</t>
+  </si>
+  <si>
+    <t>10.10.202685</t>
+  </si>
+  <si>
+    <t>10.10.202686</t>
+  </si>
+  <si>
+    <t>10.10.202687</t>
+  </si>
+  <si>
+    <t>10.10.202688</t>
+  </si>
+  <si>
+    <t>10.10.202689</t>
+  </si>
+  <si>
+    <t>10.10.202690</t>
+  </si>
+  <si>
+    <t>10.10.202691</t>
+  </si>
+  <si>
+    <t>10.10.202692</t>
+  </si>
+  <si>
+    <t>10.10.202693</t>
+  </si>
+  <si>
+    <t>10.10.202694</t>
+  </si>
+  <si>
+    <t>10.10.202695</t>
+  </si>
+  <si>
+    <t>10.10.202696</t>
+  </si>
+  <si>
+    <t>11.10.20261</t>
+  </si>
+  <si>
+    <t>11.10.20262</t>
+  </si>
+  <si>
+    <t>11.10.20263</t>
+  </si>
+  <si>
+    <t>11.10.20264</t>
+  </si>
+  <si>
+    <t>11.10.20265</t>
+  </si>
+  <si>
+    <t>11.10.20266</t>
+  </si>
+  <si>
+    <t>11.10.20267</t>
+  </si>
+  <si>
+    <t>11.10.20268</t>
+  </si>
+  <si>
+    <t>11.10.20269</t>
+  </si>
+  <si>
+    <t>11.10.202610</t>
+  </si>
+  <si>
+    <t>11.10.202611</t>
+  </si>
+  <si>
+    <t>11.10.202612</t>
+  </si>
+  <si>
+    <t>11.10.202613</t>
+  </si>
+  <si>
+    <t>11.10.202614</t>
+  </si>
+  <si>
+    <t>11.10.202615</t>
+  </si>
+  <si>
+    <t>11.10.202616</t>
+  </si>
+  <si>
+    <t>11.10.202617</t>
+  </si>
+  <si>
+    <t>11.10.202618</t>
+  </si>
+  <si>
+    <t>11.10.202619</t>
+  </si>
+  <si>
+    <t>11.10.202620</t>
+  </si>
+  <si>
+    <t>11.10.202621</t>
+  </si>
+  <si>
+    <t>11.10.202622</t>
+  </si>
+  <si>
+    <t>11.10.202623</t>
+  </si>
+  <si>
+    <t>11.10.202624</t>
+  </si>
+  <si>
+    <t>11.10.202625</t>
+  </si>
+  <si>
+    <t>11.10.202626</t>
+  </si>
+  <si>
+    <t>11.10.202627</t>
+  </si>
+  <si>
+    <t>11.10.202628</t>
+  </si>
+  <si>
+    <t>11.10.202629</t>
+  </si>
+  <si>
+    <t>11.10.202630</t>
+  </si>
+  <si>
+    <t>11.10.202631</t>
+  </si>
+  <si>
+    <t>11.10.202632</t>
+  </si>
+  <si>
+    <t>11.10.202633</t>
+  </si>
+  <si>
+    <t>11.10.202634</t>
+  </si>
+  <si>
+    <t>11.10.202635</t>
+  </si>
+  <si>
+    <t>11.10.202636</t>
+  </si>
+  <si>
+    <t>11.10.202637</t>
+  </si>
+  <si>
+    <t>11.10.202638</t>
+  </si>
+  <si>
+    <t>11.10.202639</t>
+  </si>
+  <si>
+    <t>11.10.202640</t>
+  </si>
+  <si>
+    <t>11.10.202641</t>
+  </si>
+  <si>
+    <t>11.10.202642</t>
+  </si>
+  <si>
+    <t>11.10.202643</t>
+  </si>
+  <si>
+    <t>11.10.202644</t>
+  </si>
+  <si>
+    <t>11.10.202645</t>
+  </si>
+  <si>
+    <t>11.10.202646</t>
+  </si>
+  <si>
+    <t>11.10.202647</t>
+  </si>
+  <si>
+    <t>11.10.202648</t>
+  </si>
+  <si>
+    <t>11.10.202649</t>
+  </si>
+  <si>
+    <t>11.10.202650</t>
+  </si>
+  <si>
+    <t>11.10.202651</t>
+  </si>
+  <si>
+    <t>11.10.202652</t>
+  </si>
+  <si>
+    <t>11.10.202653</t>
+  </si>
+  <si>
+    <t>11.10.202654</t>
+  </si>
+  <si>
+    <t>11.10.202655</t>
+  </si>
+  <si>
+    <t>11.10.202656</t>
+  </si>
+  <si>
+    <t>11.10.202657</t>
+  </si>
+  <si>
+    <t>11.10.202658</t>
+  </si>
+  <si>
+    <t>11.10.202659</t>
+  </si>
+  <si>
+    <t>11.10.202660</t>
+  </si>
+  <si>
+    <t>11.10.202661</t>
+  </si>
+  <si>
+    <t>11.10.202662</t>
+  </si>
+  <si>
+    <t>11.10.202663</t>
+  </si>
+  <si>
+    <t>11.10.202664</t>
+  </si>
+  <si>
+    <t>11.10.202665</t>
+  </si>
+  <si>
+    <t>11.10.202666</t>
+  </si>
+  <si>
+    <t>11.10.202667</t>
+  </si>
+  <si>
+    <t>11.10.202668</t>
+  </si>
+  <si>
+    <t>11.10.202669</t>
+  </si>
+  <si>
+    <t>11.10.202670</t>
+  </si>
+  <si>
+    <t>11.10.202671</t>
+  </si>
+  <si>
+    <t>11.10.202672</t>
+  </si>
+  <si>
+    <t>11.10.202673</t>
+  </si>
+  <si>
+    <t>11.10.202674</t>
+  </si>
+  <si>
+    <t>11.10.202675</t>
+  </si>
+  <si>
+    <t>11.10.202676</t>
+  </si>
+  <si>
+    <t>11.10.202677</t>
+  </si>
+  <si>
+    <t>11.10.202678</t>
+  </si>
+  <si>
+    <t>11.10.202679</t>
+  </si>
+  <si>
+    <t>11.10.202680</t>
+  </si>
+  <si>
+    <t>11.10.202681</t>
+  </si>
+  <si>
+    <t>11.10.202682</t>
+  </si>
+  <si>
+    <t>11.10.202683</t>
+  </si>
+  <si>
+    <t>11.10.202684</t>
+  </si>
+  <si>
+    <t>11.10.202685</t>
+  </si>
+  <si>
+    <t>11.10.202686</t>
+  </si>
+  <si>
+    <t>11.10.202687</t>
+  </si>
+  <si>
+    <t>11.10.202688</t>
+  </si>
+  <si>
+    <t>11.10.202689</t>
+  </si>
+  <si>
+    <t>11.10.202690</t>
+  </si>
+  <si>
+    <t>11.10.202691</t>
+  </si>
+  <si>
+    <t>11.10.202692</t>
+  </si>
+  <si>
+    <t>11.10.202693</t>
+  </si>
+  <si>
+    <t>11.10.202694</t>
+  </si>
+  <si>
+    <t>11.10.202695</t>
+  </si>
+  <si>
+    <t>11.10.202696</t>
+  </si>
+  <si>
+    <t>12.10.20261</t>
+  </si>
+  <si>
+    <t>12.10.20262</t>
+  </si>
+  <si>
+    <t>12.10.20263</t>
+  </si>
+  <si>
+    <t>12.10.20264</t>
+  </si>
+  <si>
+    <t>12.10.20265</t>
+  </si>
+  <si>
+    <t>12.10.20266</t>
+  </si>
+  <si>
+    <t>12.10.20267</t>
+  </si>
+  <si>
+    <t>12.10.20268</t>
+  </si>
+  <si>
+    <t>12.10.20269</t>
+  </si>
+  <si>
+    <t>12.10.202610</t>
+  </si>
+  <si>
+    <t>12.10.202611</t>
+  </si>
+  <si>
+    <t>12.10.202612</t>
+  </si>
+  <si>
+    <t>12.10.202613</t>
+  </si>
+  <si>
+    <t>12.10.202614</t>
+  </si>
+  <si>
+    <t>12.10.202615</t>
+  </si>
+  <si>
+    <t>12.10.202616</t>
+  </si>
+  <si>
+    <t>12.10.202617</t>
+  </si>
+  <si>
+    <t>12.10.202618</t>
+  </si>
+  <si>
+    <t>12.10.202619</t>
+  </si>
+  <si>
+    <t>12.10.202620</t>
+  </si>
+  <si>
+    <t>12.10.202621</t>
+  </si>
+  <si>
+    <t>12.10.202622</t>
+  </si>
+  <si>
+    <t>12.10.202623</t>
+  </si>
+  <si>
+    <t>12.10.202624</t>
+  </si>
+  <si>
+    <t>12.10.202625</t>
+  </si>
+  <si>
+    <t>12.10.202626</t>
+  </si>
+  <si>
+    <t>12.10.202627</t>
+  </si>
+  <si>
+    <t>12.10.202628</t>
+  </si>
+  <si>
+    <t>12.10.202629</t>
+  </si>
+  <si>
+    <t>12.10.202630</t>
+  </si>
+  <si>
+    <t>12.10.202631</t>
+  </si>
+  <si>
+    <t>12.10.202632</t>
+  </si>
+  <si>
+    <t>12.10.202633</t>
+  </si>
+  <si>
+    <t>12.10.202634</t>
+  </si>
+  <si>
+    <t>12.10.202635</t>
+  </si>
+  <si>
+    <t>12.10.202636</t>
+  </si>
+  <si>
+    <t>12.10.202637</t>
+  </si>
+  <si>
+    <t>12.10.202638</t>
   </si>
 </sst>
 </file>
@@ -786,7 +1368,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E133"/>
+  <dimension ref="A1:E327"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -808,13 +1390,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>1.654</v>
+        <v>5.513</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -825,13 +1407,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46303.01041666666</v>
+        <v>46304.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3">
-        <v>4.228</v>
+        <v>1.911</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -842,13 +1424,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46303.02083333334</v>
+        <v>46304.02083333334</v>
       </c>
       <c r="B4">
-        <v>6.344</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -859,13 +1441,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46303.03125</v>
+        <v>46304.03125</v>
       </c>
       <c r="B5">
-        <v>5.589</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>4.047</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -876,13 +1458,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46303.04166666666</v>
+        <v>46304.04166666666</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>1.483</v>
       </c>
       <c r="C6">
-        <v>12.776</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -893,13 +1475,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46303.05208333334</v>
+        <v>46304.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="C7">
-        <v>12.904</v>
+        <v>0.537</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -910,10 +1492,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46303.0625</v>
+        <v>46304.0625</v>
       </c>
       <c r="B8">
-        <v>2.344</v>
+        <v>3.306</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -927,13 +1509,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46303.07291666666</v>
+        <v>46304.07291666666</v>
       </c>
       <c r="B9">
-        <v>6.376</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>2.955</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -944,10 +1526,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46303.08333333334</v>
+        <v>46304.08333333334</v>
       </c>
       <c r="B10">
-        <v>9.398</v>
+        <v>3.043</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -961,10 +1543,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46303.09375</v>
+        <v>46304.09375</v>
       </c>
       <c r="B11">
-        <v>1.594</v>
+        <v>3.872</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -978,10 +1560,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46303.10416666666</v>
+        <v>46304.10416666666</v>
       </c>
       <c r="B12">
-        <v>2.241</v>
+        <v>0.743</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -995,10 +1577,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46303.11458333334</v>
+        <v>46304.11458333334</v>
       </c>
       <c r="B13">
-        <v>2.899</v>
+        <v>0.045</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1012,10 +1594,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46303.125</v>
+        <v>46304.125</v>
       </c>
       <c r="B14">
-        <v>3.793</v>
+        <v>3.994</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1029,10 +1611,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46303.13541666666</v>
+        <v>46304.13541666666</v>
       </c>
       <c r="B15">
-        <v>13.075</v>
+        <v>1.176</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1046,13 +1628,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46303.14583333334</v>
+        <v>46304.14583333334</v>
       </c>
       <c r="B16">
-        <v>4.877</v>
+        <v>0</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>0.922</v>
       </c>
       <c r="D16">
         <v>15</v>
@@ -1063,13 +1645,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46303.15625</v>
+        <v>46304.15625</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>3.012</v>
       </c>
       <c r="C17">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="D17">
         <v>16</v>
@@ -1080,13 +1662,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46303.16666666666</v>
+        <v>46304.16666666666</v>
       </c>
       <c r="B18">
-        <v>7.273</v>
+        <v>0</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>16.083</v>
       </c>
       <c r="D18">
         <v>17</v>
@@ -1097,13 +1679,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46303.17708333334</v>
+        <v>46304.17708333334</v>
       </c>
       <c r="B19">
-        <v>6.235</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>1.287</v>
       </c>
       <c r="D19">
         <v>18</v>
@@ -1114,13 +1696,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46303.1875</v>
+        <v>46304.1875</v>
       </c>
       <c r="B20">
-        <v>13.042</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>13.1</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1131,13 +1713,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46303.19791666666</v>
+        <v>46304.19791666666</v>
       </c>
       <c r="B21">
-        <v>13.122</v>
+        <v>0</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>4.118</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1148,13 +1730,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46303.20833333334</v>
+        <v>46304.20833333334</v>
       </c>
       <c r="B22">
-        <v>9.16</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1165,10 +1747,10 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46303.21875</v>
+        <v>46304.21875</v>
       </c>
       <c r="B23">
-        <v>0.896</v>
+        <v>3.7</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1182,13 +1764,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46303.22916666666</v>
+        <v>46304.22916666666</v>
       </c>
       <c r="B24">
-        <v>5.842</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>15.554</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1199,13 +1781,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46303.23958333334</v>
+        <v>46304.23958333334</v>
       </c>
       <c r="B25">
         <v>0</v>
       </c>
       <c r="C25">
-        <v>3.217</v>
+        <v>4.965</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1216,13 +1798,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46303.25</v>
+        <v>46304.25</v>
       </c>
       <c r="B26">
         <v>0</v>
       </c>
       <c r="C26">
-        <v>5.059</v>
+        <v>11.868</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1233,13 +1815,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46303.26041666666</v>
+        <v>46304.26041666666</v>
       </c>
       <c r="B27">
         <v>0</v>
       </c>
       <c r="C27">
-        <v>4.055</v>
+        <v>31.386</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1250,13 +1832,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46303.27083333334</v>
+        <v>46304.27083333334</v>
       </c>
       <c r="B28">
         <v>0</v>
       </c>
       <c r="C28">
-        <v>9.659000000000001</v>
+        <v>30.892</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1267,13 +1849,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46303.28125</v>
+        <v>46304.28125</v>
       </c>
       <c r="B29">
         <v>0</v>
       </c>
       <c r="C29">
-        <v>12.546</v>
+        <v>6.808</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1284,13 +1866,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46303.29166666666</v>
+        <v>46304.29166666666</v>
       </c>
       <c r="B30">
-        <v>11.212</v>
+        <v>0</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>11.116</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1301,13 +1883,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46303.30208333334</v>
+        <v>46304.30208333334</v>
       </c>
       <c r="B31">
-        <v>3.393</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>2.997</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1318,13 +1900,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46303.3125</v>
+        <v>46304.3125</v>
       </c>
       <c r="B32">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>20.779</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1335,13 +1917,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46303.32291666666</v>
+        <v>46304.32291666666</v>
       </c>
       <c r="B33">
-        <v>12.293</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>5.091</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1352,10 +1934,10 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46303.33333333334</v>
+        <v>46304.33333333334</v>
       </c>
       <c r="B34">
-        <v>63.387</v>
+        <v>11.99</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -1369,10 +1951,10 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46303.34375</v>
+        <v>46304.34375</v>
       </c>
       <c r="B35">
-        <v>24.17</v>
+        <v>6.328</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -1386,13 +1968,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46303.35416666666</v>
+        <v>46304.35416666666</v>
       </c>
       <c r="B36">
-        <v>2.755</v>
+        <v>0</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>4.151</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1403,13 +1985,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46303.36458333334</v>
+        <v>46304.36458333334</v>
       </c>
       <c r="B37">
         <v>0</v>
       </c>
       <c r="C37">
-        <v>34.937</v>
+        <v>6.546</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1420,13 +2002,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46303.375</v>
+        <v>46304.375</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>6.188</v>
       </c>
       <c r="C38">
-        <v>9.651</v>
+        <v>0</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1437,13 +2019,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46303.38541666666</v>
+        <v>46304.38541666666</v>
       </c>
       <c r="B39">
         <v>0</v>
       </c>
       <c r="C39">
-        <v>20.735</v>
+        <v>1.286</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1454,13 +2036,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46303.39583333334</v>
+        <v>46304.39583333334</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>10.508</v>
       </c>
       <c r="C40">
-        <v>9.116</v>
+        <v>0</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1471,13 +2053,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46303.40625</v>
+        <v>46304.40625</v>
       </c>
       <c r="B41">
         <v>0</v>
       </c>
       <c r="C41">
-        <v>21.816</v>
+        <v>5.339</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1488,13 +2070,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46303.41666666666</v>
+        <v>46304.41666666666</v>
       </c>
       <c r="B42">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>5.69</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1505,13 +2087,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46303.42708333334</v>
+        <v>46304.42708333334</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="C43">
-        <v>3.924</v>
+        <v>0</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1522,13 +2104,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46303.4375</v>
+        <v>46304.4375</v>
       </c>
       <c r="B44">
         <v>0</v>
       </c>
       <c r="C44">
-        <v>5.868</v>
+        <v>10.281</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1539,13 +2121,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46303.44791666666</v>
+        <v>46304.44791666666</v>
       </c>
       <c r="B45">
         <v>0</v>
       </c>
       <c r="C45">
-        <v>23.783</v>
+        <v>1.61</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1556,13 +2138,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46303.45833333334</v>
+        <v>46304.45833333334</v>
       </c>
       <c r="B46">
         <v>0</v>
       </c>
       <c r="C46">
-        <v>25.651</v>
+        <v>22.294</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1573,13 +2155,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46303.46875</v>
+        <v>46304.46875</v>
       </c>
       <c r="B47">
         <v>0</v>
       </c>
       <c r="C47">
-        <v>20.054</v>
+        <v>20.148</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1590,13 +2172,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46303.47916666666</v>
+        <v>46304.47916666666</v>
       </c>
       <c r="B48">
         <v>0</v>
       </c>
       <c r="C48">
-        <v>4.839</v>
+        <v>10.776</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1607,13 +2189,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46303.48958333334</v>
+        <v>46304.48958333334</v>
       </c>
       <c r="B49">
         <v>0</v>
       </c>
       <c r="C49">
-        <v>0.508</v>
+        <v>0.029</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1624,13 +2206,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46303.5</v>
+        <v>46304.5</v>
       </c>
       <c r="B50">
-        <v>0.765</v>
+        <v>0</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>17.904</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1641,13 +2223,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46303.51041666666</v>
+        <v>46304.51041666666</v>
       </c>
       <c r="B51">
-        <v>8.848000000000001</v>
+        <v>0</v>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>10.729</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1658,13 +2240,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46303.52083333334</v>
+        <v>46304.52083333334</v>
       </c>
       <c r="B52">
-        <v>12.258</v>
+        <v>0</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>16.708</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1675,13 +2257,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46303.53125</v>
+        <v>46304.53125</v>
       </c>
       <c r="B53">
-        <v>3.554</v>
+        <v>0</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>7.383</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1692,13 +2274,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46303.54166666666</v>
+        <v>46304.54166666666</v>
       </c>
       <c r="B54">
-        <v>0.313</v>
+        <v>0</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>18.488</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1709,13 +2291,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46303.55208333334</v>
+        <v>46304.55208333334</v>
       </c>
       <c r="B55">
         <v>0</v>
       </c>
       <c r="C55">
-        <v>10.726</v>
+        <v>39.47</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1726,13 +2308,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46303.5625</v>
+        <v>46304.5625</v>
       </c>
       <c r="B56">
         <v>0</v>
       </c>
       <c r="C56">
-        <v>10.599</v>
+        <v>48.148</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1743,13 +2325,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46303.57291666666</v>
+        <v>46304.57291666666</v>
       </c>
       <c r="B57">
         <v>0</v>
       </c>
       <c r="C57">
-        <v>7.132</v>
+        <v>20.628</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1760,10 +2342,10 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46303.58333333334</v>
+        <v>46304.58333333334</v>
       </c>
       <c r="B58">
-        <v>1.14</v>
+        <v>24.327</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -1777,13 +2359,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46303.59375</v>
+        <v>46304.59375</v>
       </c>
       <c r="B59">
-        <v>0</v>
+        <v>34.935</v>
       </c>
       <c r="C59">
-        <v>11.159</v>
+        <v>0</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1794,13 +2376,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46303.60416666666</v>
+        <v>46304.60416666666</v>
       </c>
       <c r="B60">
-        <v>0</v>
+        <v>62.725</v>
       </c>
       <c r="C60">
-        <v>19.62</v>
+        <v>0</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1811,13 +2393,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46303.61458333334</v>
+        <v>46304.61458333334</v>
       </c>
       <c r="B61">
-        <v>0</v>
+        <v>48.253</v>
       </c>
       <c r="C61">
-        <v>6.304</v>
+        <v>0</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -1828,13 +2410,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46303.625</v>
+        <v>46304.625</v>
       </c>
       <c r="B62">
-        <v>0</v>
+        <v>58.202</v>
       </c>
       <c r="C62">
-        <v>42.704</v>
+        <v>0</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -1845,13 +2427,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46303.63541666666</v>
+        <v>46304.63541666666</v>
       </c>
       <c r="B63">
-        <v>0</v>
+        <v>28.926</v>
       </c>
       <c r="C63">
-        <v>19.432</v>
+        <v>0</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -1862,13 +2444,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46303.64583333334</v>
+        <v>46304.64583333334</v>
       </c>
       <c r="B64">
-        <v>0.145</v>
+        <v>0</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>3.342</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -1879,13 +2461,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46303.65625</v>
+        <v>46304.65625</v>
       </c>
       <c r="B65">
-        <v>0</v>
+        <v>10.28</v>
       </c>
       <c r="C65">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -1896,13 +2478,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46303.66666666666</v>
+        <v>46304.66666666666</v>
       </c>
       <c r="B66">
         <v>0</v>
       </c>
       <c r="C66">
-        <v>13.759</v>
+        <v>60.936</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -1913,13 +2495,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46303.67708333334</v>
+        <v>46304.67708333334</v>
       </c>
       <c r="B67">
         <v>0</v>
       </c>
       <c r="C67">
-        <v>1.594</v>
+        <v>48.639</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -1930,13 +2512,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46303.6875</v>
+        <v>46304.6875</v>
       </c>
       <c r="B68">
-        <v>6.12</v>
+        <v>0</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>21.655</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -1947,13 +2529,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46303.69791666666</v>
+        <v>46304.69791666666</v>
       </c>
       <c r="B69">
-        <v>12.533</v>
+        <v>0</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>16.158</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -1964,13 +2546,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46303.70833333334</v>
+        <v>46304.70833333334</v>
       </c>
       <c r="B70">
-        <v>2.657</v>
+        <v>0</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>26.858</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -1981,13 +2563,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46303.71875</v>
+        <v>46304.71875</v>
       </c>
       <c r="B71">
-        <v>18.483</v>
+        <v>0</v>
       </c>
       <c r="C71">
-        <v>0</v>
+        <v>32.24</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -1998,13 +2580,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46303.72916666666</v>
+        <v>46304.72916666666</v>
       </c>
       <c r="B72">
-        <v>14.822</v>
+        <v>0</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>17.61</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2015,13 +2597,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46303.73958333334</v>
+        <v>46304.73958333334</v>
       </c>
       <c r="B73">
-        <v>24.355</v>
+        <v>0</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>0.463</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2032,13 +2614,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46303.75</v>
+        <v>46304.75</v>
       </c>
       <c r="B74">
-        <v>6.231</v>
+        <v>0</v>
       </c>
       <c r="C74">
-        <v>0</v>
+        <v>8.726000000000001</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2049,13 +2631,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46303.76041666666</v>
+        <v>46304.76041666666</v>
       </c>
       <c r="B75">
         <v>0</v>
       </c>
       <c r="C75">
-        <v>5.523</v>
+        <v>3.252</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2066,13 +2648,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46303.77083333334</v>
+        <v>46304.77083333334</v>
       </c>
       <c r="B76">
         <v>0</v>
       </c>
       <c r="C76">
-        <v>21.072</v>
+        <v>7.945</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2083,13 +2665,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46303.78125</v>
+        <v>46304.78125</v>
       </c>
       <c r="B77">
         <v>0</v>
       </c>
       <c r="C77">
-        <v>40.738</v>
+        <v>8.26</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2100,13 +2682,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46303.79166666666</v>
+        <v>46304.79166666666</v>
       </c>
       <c r="B78">
         <v>0</v>
       </c>
       <c r="C78">
-        <v>21.639</v>
+        <v>8.573</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2117,13 +2699,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46303.80208333334</v>
+        <v>46304.80208333334</v>
       </c>
       <c r="B79">
         <v>0</v>
       </c>
       <c r="C79">
-        <v>23.075</v>
+        <v>0.471</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2134,13 +2716,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46303.8125</v>
+        <v>46304.8125</v>
       </c>
       <c r="B80">
-        <v>0</v>
+        <v>8.042999999999999</v>
       </c>
       <c r="C80">
-        <v>8.401999999999999</v>
+        <v>0</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2151,13 +2733,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46303.82291666666</v>
+        <v>46304.82291666666</v>
       </c>
       <c r="B81">
-        <v>0</v>
+        <v>14.437</v>
       </c>
       <c r="C81">
-        <v>3.026</v>
+        <v>0</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2168,10 +2750,10 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46303.83333333334</v>
+        <v>46304.83333333334</v>
       </c>
       <c r="B82">
-        <v>9.045999999999999</v>
+        <v>22.771</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -2185,10 +2767,10 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46303.84375</v>
+        <v>46304.84375</v>
       </c>
       <c r="B83">
-        <v>17.486</v>
+        <v>24.865</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -2202,10 +2784,10 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46303.85416666666</v>
+        <v>46304.85416666666</v>
       </c>
       <c r="B84">
-        <v>13.673</v>
+        <v>9.885999999999999</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -2219,13 +2801,13 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46303.86458333334</v>
+        <v>46304.86458333334</v>
       </c>
       <c r="B85">
-        <v>0</v>
+        <v>6.067</v>
       </c>
       <c r="C85">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="D85">
         <v>84</v>
@@ -2236,10 +2818,10 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46303.875</v>
+        <v>46304.875</v>
       </c>
       <c r="B86">
-        <v>4.554</v>
+        <v>8.414</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -2253,13 +2835,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46303.88541666666</v>
+        <v>46304.88541666666</v>
       </c>
       <c r="B87">
-        <v>0</v>
+        <v>0.328</v>
       </c>
       <c r="C87">
-        <v>2.605</v>
+        <v>0</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -2270,13 +2852,13 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46303.89583333334</v>
+        <v>46304.89583333334</v>
       </c>
       <c r="B88">
         <v>0</v>
       </c>
       <c r="C88">
-        <v>8.757</v>
+        <v>0.08</v>
       </c>
       <c r="D88">
         <v>87</v>
@@ -2287,13 +2869,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46303.90625</v>
+        <v>46304.90625</v>
       </c>
       <c r="B89">
-        <v>0</v>
+        <v>2.662</v>
       </c>
       <c r="C89">
-        <v>10.737</v>
+        <v>0</v>
       </c>
       <c r="D89">
         <v>88</v>
@@ -2304,10 +2886,10 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46303.91666666666</v>
+        <v>46304.91666666666</v>
       </c>
       <c r="B90">
-        <v>2.954</v>
+        <v>10.895</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -2321,10 +2903,10 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46303.92708333334</v>
+        <v>46304.92708333334</v>
       </c>
       <c r="B91">
-        <v>2.251</v>
+        <v>2.909</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -2338,10 +2920,10 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46303.9375</v>
+        <v>46304.9375</v>
       </c>
       <c r="B92">
-        <v>3.624</v>
+        <v>1.981</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -2355,13 +2937,13 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46303.94791666666</v>
+        <v>46304.94791666666</v>
       </c>
       <c r="B93">
-        <v>0</v>
+        <v>13.04</v>
       </c>
       <c r="C93">
-        <v>0.139</v>
+        <v>0</v>
       </c>
       <c r="D93">
         <v>92</v>
@@ -2372,10 +2954,10 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46303.95833333334</v>
+        <v>46304.95833333334</v>
       </c>
       <c r="B94">
-        <v>0.976</v>
+        <v>9.263</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -2389,13 +2971,13 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46303.96875</v>
+        <v>46304.96875</v>
       </c>
       <c r="B95">
-        <v>0</v>
+        <v>0.926</v>
       </c>
       <c r="C95">
-        <v>3.064</v>
+        <v>0</v>
       </c>
       <c r="D95">
         <v>94</v>
@@ -2406,13 +2988,13 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46303.97916666666</v>
+        <v>46304.97916666666</v>
       </c>
       <c r="B96">
-        <v>0</v>
+        <v>1.309</v>
       </c>
       <c r="C96">
-        <v>1.145</v>
+        <v>0</v>
       </c>
       <c r="D96">
         <v>95</v>
@@ -2423,10 +3005,10 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46303.98958333334</v>
+        <v>46304.98958333334</v>
       </c>
       <c r="B97">
-        <v>2.758</v>
+        <v>15.183</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -2440,13 +3022,13 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="B98">
         <v>0</v>
       </c>
       <c r="C98">
-        <v>5.513</v>
+        <v>11.398</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -2457,13 +3039,13 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46304.01041666666</v>
+        <v>46305.01041666666</v>
       </c>
       <c r="B99">
-        <v>0</v>
+        <v>2.822</v>
       </c>
       <c r="C99">
-        <v>1.911</v>
+        <v>0</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -2474,13 +3056,13 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46304.02083333334</v>
+        <v>46305.02083333334</v>
       </c>
       <c r="B100">
-        <v>0</v>
+        <v>0.603</v>
       </c>
       <c r="C100">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2491,13 +3073,13 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46304.03125</v>
+        <v>46305.03125</v>
       </c>
       <c r="B101">
         <v>0</v>
       </c>
       <c r="C101">
-        <v>4.047</v>
+        <v>9.047000000000001</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -2508,13 +3090,13 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46304.04166666666</v>
+        <v>46305.04166666666</v>
       </c>
       <c r="B102">
-        <v>1.483</v>
+        <v>0</v>
       </c>
       <c r="C102">
-        <v>0</v>
+        <v>2.739</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -2525,13 +3107,13 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46304.05208333334</v>
+        <v>46305.05208333334</v>
       </c>
       <c r="B103">
         <v>0</v>
       </c>
       <c r="C103">
-        <v>0.537</v>
+        <v>5.015</v>
       </c>
       <c r="D103">
         <v>6</v>
@@ -2542,10 +3124,10 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46304.0625</v>
+        <v>46305.0625</v>
       </c>
       <c r="B104">
-        <v>3.306</v>
+        <v>4.355</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -2559,13 +3141,13 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46304.07291666666</v>
+        <v>46305.07291666666</v>
       </c>
       <c r="B105">
         <v>0</v>
       </c>
       <c r="C105">
-        <v>2.955</v>
+        <v>12.572</v>
       </c>
       <c r="D105">
         <v>8</v>
@@ -2576,13 +3158,13 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46304.08333333334</v>
+        <v>46305.08333333334</v>
       </c>
       <c r="B106">
-        <v>3.043</v>
+        <v>0</v>
       </c>
       <c r="C106">
-        <v>0</v>
+        <v>24.419</v>
       </c>
       <c r="D106">
         <v>9</v>
@@ -2593,13 +3175,13 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46304.09375</v>
+        <v>46305.09375</v>
       </c>
       <c r="B107">
-        <v>3.872</v>
+        <v>0</v>
       </c>
       <c r="C107">
-        <v>0</v>
+        <v>31.565</v>
       </c>
       <c r="D107">
         <v>10</v>
@@ -2610,13 +3192,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46304.10416666666</v>
+        <v>46305.10416666666</v>
       </c>
       <c r="B108">
-        <v>0.743</v>
+        <v>0</v>
       </c>
       <c r="C108">
-        <v>0</v>
+        <v>26.928</v>
       </c>
       <c r="D108">
         <v>11</v>
@@ -2627,13 +3209,13 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46304.11458333334</v>
+        <v>46305.11458333334</v>
       </c>
       <c r="B109">
-        <v>0.045</v>
+        <v>0</v>
       </c>
       <c r="C109">
-        <v>0</v>
+        <v>1.292</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -2644,13 +3226,13 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46304.125</v>
+        <v>46305.125</v>
       </c>
       <c r="B110">
-        <v>3.994</v>
+        <v>0</v>
       </c>
       <c r="C110">
-        <v>0</v>
+        <v>10.929</v>
       </c>
       <c r="D110">
         <v>13</v>
@@ -2661,13 +3243,13 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46304.13541666666</v>
+        <v>46305.13541666666</v>
       </c>
       <c r="B111">
-        <v>1.176</v>
+        <v>0</v>
       </c>
       <c r="C111">
-        <v>0</v>
+        <v>0.892</v>
       </c>
       <c r="D111">
         <v>14</v>
@@ -2678,13 +3260,13 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46304.14583333334</v>
+        <v>46305.14583333334</v>
       </c>
       <c r="B112">
-        <v>0</v>
+        <v>2.785</v>
       </c>
       <c r="C112">
-        <v>0.922</v>
+        <v>0</v>
       </c>
       <c r="D112">
         <v>15</v>
@@ -2695,10 +3277,10 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46304.15625</v>
+        <v>46305.15625</v>
       </c>
       <c r="B113">
-        <v>3.012</v>
+        <v>6.68</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -2712,13 +3294,13 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46304.16666666666</v>
+        <v>46305.16666666666</v>
       </c>
       <c r="B114">
-        <v>0</v>
+        <v>0.861</v>
       </c>
       <c r="C114">
-        <v>16.083</v>
+        <v>0</v>
       </c>
       <c r="D114">
         <v>17</v>
@@ -2729,13 +3311,13 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46304.17708333334</v>
+        <v>46305.17708333334</v>
       </c>
       <c r="B115">
         <v>0</v>
       </c>
       <c r="C115">
-        <v>1.287</v>
+        <v>3.711</v>
       </c>
       <c r="D115">
         <v>18</v>
@@ -2746,13 +3328,13 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46304.1875</v>
+        <v>46305.1875</v>
       </c>
       <c r="B116">
         <v>0</v>
       </c>
       <c r="C116">
-        <v>13.1</v>
+        <v>1.584</v>
       </c>
       <c r="D116">
         <v>19</v>
@@ -2763,13 +3345,13 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46304.19791666666</v>
+        <v>46305.19791666666</v>
       </c>
       <c r="B117">
         <v>0</v>
       </c>
       <c r="C117">
-        <v>4.118</v>
+        <v>11.789</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -2780,13 +3362,13 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46304.20833333334</v>
+        <v>46305.20833333334</v>
       </c>
       <c r="B118">
         <v>0</v>
       </c>
       <c r="C118">
-        <v>0.003</v>
+        <v>19.406</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -2797,13 +3379,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46304.21875</v>
+        <v>46305.21875</v>
       </c>
       <c r="B119">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="C119">
-        <v>0</v>
+        <v>27.382</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -2814,13 +3396,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46304.22916666666</v>
+        <v>46305.22916666666</v>
       </c>
       <c r="B120">
         <v>0</v>
       </c>
       <c r="C120">
-        <v>15.554</v>
+        <v>26.414</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -2831,13 +3413,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46304.23958333334</v>
+        <v>46305.23958333334</v>
       </c>
       <c r="B121">
         <v>0</v>
       </c>
       <c r="C121">
-        <v>4.965</v>
+        <v>20.904</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -2848,13 +3430,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46304.25</v>
+        <v>46305.25</v>
       </c>
       <c r="B122">
         <v>0</v>
       </c>
       <c r="C122">
-        <v>11.868</v>
+        <v>40.34</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -2865,13 +3447,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46304.26041666666</v>
+        <v>46305.26041666666</v>
       </c>
       <c r="B123">
         <v>0</v>
       </c>
       <c r="C123">
-        <v>31.386</v>
+        <v>65.05</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -2882,13 +3464,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46304.27083333334</v>
+        <v>46305.27083333334</v>
       </c>
       <c r="B124">
         <v>0</v>
       </c>
       <c r="C124">
-        <v>30.892</v>
+        <v>33.462</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -2899,13 +3481,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46304.28125</v>
+        <v>46305.28125</v>
       </c>
       <c r="B125">
         <v>0</v>
       </c>
       <c r="C125">
-        <v>6.808</v>
+        <v>38.526</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -2916,13 +3498,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46304.29166666666</v>
+        <v>46305.29166666666</v>
       </c>
       <c r="B126">
         <v>0</v>
       </c>
       <c r="C126">
-        <v>11.116</v>
+        <v>13.013</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -2933,13 +3515,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46304.30208333334</v>
+        <v>46305.30208333334</v>
       </c>
       <c r="B127">
         <v>0</v>
       </c>
       <c r="C127">
-        <v>2.997</v>
+        <v>12.295</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -2950,13 +3532,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46304.3125</v>
+        <v>46305.3125</v>
       </c>
       <c r="B128">
         <v>0</v>
       </c>
       <c r="C128">
-        <v>20.779</v>
+        <v>15.202</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -2967,13 +3549,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46304.32291666666</v>
+        <v>46305.32291666666</v>
       </c>
       <c r="B129">
         <v>0</v>
       </c>
       <c r="C129">
-        <v>5.091</v>
+        <v>28.213</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -2984,10 +3566,10 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46304.33333333334</v>
+        <v>46305.33333333334</v>
       </c>
       <c r="B130">
-        <v>11.99</v>
+        <v>23.27</v>
       </c>
       <c r="C130">
         <v>0</v>
@@ -3001,10 +3583,10 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46304.34375</v>
+        <v>46305.34375</v>
       </c>
       <c r="B131">
-        <v>6.328</v>
+        <v>4.063</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -3018,13 +3600,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46304.35416666666</v>
+        <v>46305.35416666666</v>
       </c>
       <c r="B132">
-        <v>0</v>
+        <v>15.931</v>
       </c>
       <c r="C132">
-        <v>4.151</v>
+        <v>0</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3035,19 +3617,3317 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46304.36458333334</v>
+        <v>46305.36458333334</v>
       </c>
       <c r="B133">
-        <v>0</v>
+        <v>12.106</v>
       </c>
       <c r="C133">
-        <v>6.546</v>
+        <v>0</v>
       </c>
       <c r="D133">
         <v>36</v>
       </c>
       <c r="E133" t="s">
         <v>136</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5">
+      <c r="A134" s="2">
+        <v>46305.375</v>
+      </c>
+      <c r="B134">
+        <v>27.374</v>
+      </c>
+      <c r="C134">
+        <v>0</v>
+      </c>
+      <c r="D134">
+        <v>37</v>
+      </c>
+      <c r="E134" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5">
+      <c r="A135" s="2">
+        <v>46305.38541666666</v>
+      </c>
+      <c r="B135">
+        <v>3.303</v>
+      </c>
+      <c r="C135">
+        <v>0</v>
+      </c>
+      <c r="D135">
+        <v>38</v>
+      </c>
+      <c r="E135" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5">
+      <c r="A136" s="2">
+        <v>46305.39583333334</v>
+      </c>
+      <c r="B136">
+        <v>0</v>
+      </c>
+      <c r="C136">
+        <v>0.842</v>
+      </c>
+      <c r="D136">
+        <v>39</v>
+      </c>
+      <c r="E136" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5">
+      <c r="A137" s="2">
+        <v>46305.40625</v>
+      </c>
+      <c r="B137">
+        <v>0</v>
+      </c>
+      <c r="C137">
+        <v>2.699</v>
+      </c>
+      <c r="D137">
+        <v>40</v>
+      </c>
+      <c r="E137" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5">
+      <c r="A138" s="2">
+        <v>46305.41666666666</v>
+      </c>
+      <c r="B138">
+        <v>0</v>
+      </c>
+      <c r="C138">
+        <v>22.095</v>
+      </c>
+      <c r="D138">
+        <v>41</v>
+      </c>
+      <c r="E138" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5">
+      <c r="A139" s="2">
+        <v>46305.42708333334</v>
+      </c>
+      <c r="B139">
+        <v>0</v>
+      </c>
+      <c r="C139">
+        <v>40.222</v>
+      </c>
+      <c r="D139">
+        <v>42</v>
+      </c>
+      <c r="E139" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5">
+      <c r="A140" s="2">
+        <v>46305.4375</v>
+      </c>
+      <c r="B140">
+        <v>0</v>
+      </c>
+      <c r="C140">
+        <v>29.787</v>
+      </c>
+      <c r="D140">
+        <v>43</v>
+      </c>
+      <c r="E140" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5">
+      <c r="A141" s="2">
+        <v>46305.44791666666</v>
+      </c>
+      <c r="B141">
+        <v>0</v>
+      </c>
+      <c r="C141">
+        <v>18.553</v>
+      </c>
+      <c r="D141">
+        <v>44</v>
+      </c>
+      <c r="E141" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
+      <c r="A142" s="2">
+        <v>46305.45833333334</v>
+      </c>
+      <c r="B142">
+        <v>42.489</v>
+      </c>
+      <c r="C142">
+        <v>0</v>
+      </c>
+      <c r="D142">
+        <v>45</v>
+      </c>
+      <c r="E142" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143" s="2">
+        <v>46305.46875</v>
+      </c>
+      <c r="B143">
+        <v>14.282</v>
+      </c>
+      <c r="C143">
+        <v>0</v>
+      </c>
+      <c r="D143">
+        <v>46</v>
+      </c>
+      <c r="E143" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="A144" s="2">
+        <v>46305.47916666666</v>
+      </c>
+      <c r="B144">
+        <v>67.43600000000001</v>
+      </c>
+      <c r="C144">
+        <v>0</v>
+      </c>
+      <c r="D144">
+        <v>47</v>
+      </c>
+      <c r="E144" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145" s="2">
+        <v>46305.48958333334</v>
+      </c>
+      <c r="B145">
+        <v>0</v>
+      </c>
+      <c r="C145">
+        <v>0.28</v>
+      </c>
+      <c r="D145">
+        <v>48</v>
+      </c>
+      <c r="E145" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5">
+      <c r="A146" s="2">
+        <v>46305.5</v>
+      </c>
+      <c r="B146">
+        <v>2.639</v>
+      </c>
+      <c r="C146">
+        <v>0</v>
+      </c>
+      <c r="D146">
+        <v>49</v>
+      </c>
+      <c r="E146" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5">
+      <c r="A147" s="2">
+        <v>46305.51041666666</v>
+      </c>
+      <c r="B147">
+        <v>11.546</v>
+      </c>
+      <c r="C147">
+        <v>0</v>
+      </c>
+      <c r="D147">
+        <v>50</v>
+      </c>
+      <c r="E147" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5">
+      <c r="A148" s="2">
+        <v>46305.52083333334</v>
+      </c>
+      <c r="B148">
+        <v>6.099</v>
+      </c>
+      <c r="C148">
+        <v>0</v>
+      </c>
+      <c r="D148">
+        <v>51</v>
+      </c>
+      <c r="E148" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5">
+      <c r="A149" s="2">
+        <v>46305.53125</v>
+      </c>
+      <c r="B149">
+        <v>3.693</v>
+      </c>
+      <c r="C149">
+        <v>0</v>
+      </c>
+      <c r="D149">
+        <v>52</v>
+      </c>
+      <c r="E149" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5">
+      <c r="A150" s="2">
+        <v>46305.54166666666</v>
+      </c>
+      <c r="B150">
+        <v>5.214</v>
+      </c>
+      <c r="C150">
+        <v>0</v>
+      </c>
+      <c r="D150">
+        <v>53</v>
+      </c>
+      <c r="E150" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5">
+      <c r="A151" s="2">
+        <v>46305.55208333334</v>
+      </c>
+      <c r="B151">
+        <v>24.058</v>
+      </c>
+      <c r="C151">
+        <v>0</v>
+      </c>
+      <c r="D151">
+        <v>54</v>
+      </c>
+      <c r="E151" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5">
+      <c r="A152" s="2">
+        <v>46305.5625</v>
+      </c>
+      <c r="B152">
+        <v>26.908</v>
+      </c>
+      <c r="C152">
+        <v>0</v>
+      </c>
+      <c r="D152">
+        <v>55</v>
+      </c>
+      <c r="E152" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5">
+      <c r="A153" s="2">
+        <v>46305.57291666666</v>
+      </c>
+      <c r="B153">
+        <v>18.017</v>
+      </c>
+      <c r="C153">
+        <v>0</v>
+      </c>
+      <c r="D153">
+        <v>56</v>
+      </c>
+      <c r="E153" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5">
+      <c r="A154" s="2">
+        <v>46305.58333333334</v>
+      </c>
+      <c r="B154">
+        <v>20.723</v>
+      </c>
+      <c r="C154">
+        <v>0</v>
+      </c>
+      <c r="D154">
+        <v>57</v>
+      </c>
+      <c r="E154" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5">
+      <c r="A155" s="2">
+        <v>46305.59375</v>
+      </c>
+      <c r="B155">
+        <v>13.704</v>
+      </c>
+      <c r="C155">
+        <v>0</v>
+      </c>
+      <c r="D155">
+        <v>58</v>
+      </c>
+      <c r="E155" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5">
+      <c r="A156" s="2">
+        <v>46305.60416666666</v>
+      </c>
+      <c r="B156">
+        <v>2.234</v>
+      </c>
+      <c r="C156">
+        <v>0</v>
+      </c>
+      <c r="D156">
+        <v>59</v>
+      </c>
+      <c r="E156" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5">
+      <c r="A157" s="2">
+        <v>46305.61458333334</v>
+      </c>
+      <c r="B157">
+        <v>0.473</v>
+      </c>
+      <c r="C157">
+        <v>0</v>
+      </c>
+      <c r="D157">
+        <v>60</v>
+      </c>
+      <c r="E157" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5">
+      <c r="A158" s="2">
+        <v>46305.625</v>
+      </c>
+      <c r="B158">
+        <v>0</v>
+      </c>
+      <c r="C158">
+        <v>3.652</v>
+      </c>
+      <c r="D158">
+        <v>61</v>
+      </c>
+      <c r="E158" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5">
+      <c r="A159" s="2">
+        <v>46305.63541666666</v>
+      </c>
+      <c r="B159">
+        <v>6.588</v>
+      </c>
+      <c r="C159">
+        <v>0</v>
+      </c>
+      <c r="D159">
+        <v>62</v>
+      </c>
+      <c r="E159" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5">
+      <c r="A160" s="2">
+        <v>46305.64583333334</v>
+      </c>
+      <c r="B160">
+        <v>9.493</v>
+      </c>
+      <c r="C160">
+        <v>0</v>
+      </c>
+      <c r="D160">
+        <v>63</v>
+      </c>
+      <c r="E160" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5">
+      <c r="A161" s="2">
+        <v>46305.65625</v>
+      </c>
+      <c r="B161">
+        <v>13.195</v>
+      </c>
+      <c r="C161">
+        <v>0</v>
+      </c>
+      <c r="D161">
+        <v>64</v>
+      </c>
+      <c r="E161" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5">
+      <c r="A162" s="2">
+        <v>46305.66666666666</v>
+      </c>
+      <c r="B162">
+        <v>2.883</v>
+      </c>
+      <c r="C162">
+        <v>0</v>
+      </c>
+      <c r="D162">
+        <v>65</v>
+      </c>
+      <c r="E162" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5">
+      <c r="A163" s="2">
+        <v>46305.67708333334</v>
+      </c>
+      <c r="B163">
+        <v>0</v>
+      </c>
+      <c r="C163">
+        <v>0.198</v>
+      </c>
+      <c r="D163">
+        <v>66</v>
+      </c>
+      <c r="E163" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5">
+      <c r="A164" s="2">
+        <v>46305.6875</v>
+      </c>
+      <c r="B164">
+        <v>1.477</v>
+      </c>
+      <c r="C164">
+        <v>0</v>
+      </c>
+      <c r="D164">
+        <v>67</v>
+      </c>
+      <c r="E164" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5">
+      <c r="A165" s="2">
+        <v>46305.69791666666</v>
+      </c>
+      <c r="B165">
+        <v>0</v>
+      </c>
+      <c r="C165">
+        <v>1.605</v>
+      </c>
+      <c r="D165">
+        <v>68</v>
+      </c>
+      <c r="E165" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5">
+      <c r="A166" s="2">
+        <v>46305.70833333334</v>
+      </c>
+      <c r="B166">
+        <v>2.801</v>
+      </c>
+      <c r="C166">
+        <v>0</v>
+      </c>
+      <c r="D166">
+        <v>69</v>
+      </c>
+      <c r="E166" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5">
+      <c r="A167" s="2">
+        <v>46305.71875</v>
+      </c>
+      <c r="B167">
+        <v>1.869</v>
+      </c>
+      <c r="C167">
+        <v>0</v>
+      </c>
+      <c r="D167">
+        <v>70</v>
+      </c>
+      <c r="E167" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5">
+      <c r="A168" s="2">
+        <v>46305.72916666666</v>
+      </c>
+      <c r="B168">
+        <v>0</v>
+      </c>
+      <c r="C168">
+        <v>6.375</v>
+      </c>
+      <c r="D168">
+        <v>71</v>
+      </c>
+      <c r="E168" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5">
+      <c r="A169" s="2">
+        <v>46305.73958333334</v>
+      </c>
+      <c r="B169">
+        <v>0</v>
+      </c>
+      <c r="C169">
+        <v>1.074</v>
+      </c>
+      <c r="D169">
+        <v>72</v>
+      </c>
+      <c r="E169" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5">
+      <c r="A170" s="2">
+        <v>46305.75</v>
+      </c>
+      <c r="B170">
+        <v>8.614000000000001</v>
+      </c>
+      <c r="C170">
+        <v>0</v>
+      </c>
+      <c r="D170">
+        <v>73</v>
+      </c>
+      <c r="E170" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5">
+      <c r="A171" s="2">
+        <v>46305.76041666666</v>
+      </c>
+      <c r="B171">
+        <v>0</v>
+      </c>
+      <c r="C171">
+        <v>5.933</v>
+      </c>
+      <c r="D171">
+        <v>74</v>
+      </c>
+      <c r="E171" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5">
+      <c r="A172" s="2">
+        <v>46305.77083333334</v>
+      </c>
+      <c r="B172">
+        <v>0</v>
+      </c>
+      <c r="C172">
+        <v>4.56</v>
+      </c>
+      <c r="D172">
+        <v>75</v>
+      </c>
+      <c r="E172" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5">
+      <c r="A173" s="2">
+        <v>46305.78125</v>
+      </c>
+      <c r="B173">
+        <v>0</v>
+      </c>
+      <c r="C173">
+        <v>0.636</v>
+      </c>
+      <c r="D173">
+        <v>76</v>
+      </c>
+      <c r="E173" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5">
+      <c r="A174" s="2">
+        <v>46305.79166666666</v>
+      </c>
+      <c r="B174">
+        <v>0</v>
+      </c>
+      <c r="C174">
+        <v>2.764</v>
+      </c>
+      <c r="D174">
+        <v>77</v>
+      </c>
+      <c r="E174" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5">
+      <c r="A175" s="2">
+        <v>46305.80208333334</v>
+      </c>
+      <c r="B175">
+        <v>0</v>
+      </c>
+      <c r="C175">
+        <v>15.303</v>
+      </c>
+      <c r="D175">
+        <v>78</v>
+      </c>
+      <c r="E175" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5">
+      <c r="A176" s="2">
+        <v>46305.8125</v>
+      </c>
+      <c r="B176">
+        <v>2.537</v>
+      </c>
+      <c r="C176">
+        <v>0</v>
+      </c>
+      <c r="D176">
+        <v>79</v>
+      </c>
+      <c r="E176" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5">
+      <c r="A177" s="2">
+        <v>46305.82291666666</v>
+      </c>
+      <c r="B177">
+        <v>2.751</v>
+      </c>
+      <c r="C177">
+        <v>0</v>
+      </c>
+      <c r="D177">
+        <v>80</v>
+      </c>
+      <c r="E177" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5">
+      <c r="A178" s="2">
+        <v>46305.83333333334</v>
+      </c>
+      <c r="B178">
+        <v>9.423999999999999</v>
+      </c>
+      <c r="C178">
+        <v>0</v>
+      </c>
+      <c r="D178">
+        <v>81</v>
+      </c>
+      <c r="E178" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5">
+      <c r="A179" s="2">
+        <v>46305.84375</v>
+      </c>
+      <c r="B179">
+        <v>0.427</v>
+      </c>
+      <c r="C179">
+        <v>0</v>
+      </c>
+      <c r="D179">
+        <v>82</v>
+      </c>
+      <c r="E179" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5">
+      <c r="A180" s="2">
+        <v>46305.85416666666</v>
+      </c>
+      <c r="B180">
+        <v>0</v>
+      </c>
+      <c r="C180">
+        <v>0.369</v>
+      </c>
+      <c r="D180">
+        <v>83</v>
+      </c>
+      <c r="E180" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5">
+      <c r="A181" s="2">
+        <v>46305.86458333334</v>
+      </c>
+      <c r="B181">
+        <v>4.419</v>
+      </c>
+      <c r="C181">
+        <v>0</v>
+      </c>
+      <c r="D181">
+        <v>84</v>
+      </c>
+      <c r="E181" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5">
+      <c r="A182" s="2">
+        <v>46305.875</v>
+      </c>
+      <c r="B182">
+        <v>2.01</v>
+      </c>
+      <c r="C182">
+        <v>0</v>
+      </c>
+      <c r="D182">
+        <v>85</v>
+      </c>
+      <c r="E182" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5">
+      <c r="A183" s="2">
+        <v>46305.88541666666</v>
+      </c>
+      <c r="B183">
+        <v>6.271</v>
+      </c>
+      <c r="C183">
+        <v>0</v>
+      </c>
+      <c r="D183">
+        <v>86</v>
+      </c>
+      <c r="E183" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5">
+      <c r="A184" s="2">
+        <v>46305.89583333334</v>
+      </c>
+      <c r="B184">
+        <v>4.3</v>
+      </c>
+      <c r="C184">
+        <v>0</v>
+      </c>
+      <c r="D184">
+        <v>87</v>
+      </c>
+      <c r="E184" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5">
+      <c r="A185" s="2">
+        <v>46305.90625</v>
+      </c>
+      <c r="B185">
+        <v>2.982</v>
+      </c>
+      <c r="C185">
+        <v>0</v>
+      </c>
+      <c r="D185">
+        <v>88</v>
+      </c>
+      <c r="E185" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5">
+      <c r="A186" s="2">
+        <v>46305.91666666666</v>
+      </c>
+      <c r="B186">
+        <v>5.427</v>
+      </c>
+      <c r="C186">
+        <v>0</v>
+      </c>
+      <c r="D186">
+        <v>89</v>
+      </c>
+      <c r="E186" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5">
+      <c r="A187" s="2">
+        <v>46305.92708333334</v>
+      </c>
+      <c r="B187">
+        <v>3.408</v>
+      </c>
+      <c r="C187">
+        <v>0</v>
+      </c>
+      <c r="D187">
+        <v>90</v>
+      </c>
+      <c r="E187" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5">
+      <c r="A188" s="2">
+        <v>46305.9375</v>
+      </c>
+      <c r="B188">
+        <v>0</v>
+      </c>
+      <c r="C188">
+        <v>11.603</v>
+      </c>
+      <c r="D188">
+        <v>91</v>
+      </c>
+      <c r="E188" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5">
+      <c r="A189" s="2">
+        <v>46305.94791666666</v>
+      </c>
+      <c r="B189">
+        <v>0</v>
+      </c>
+      <c r="C189">
+        <v>3.841</v>
+      </c>
+      <c r="D189">
+        <v>92</v>
+      </c>
+      <c r="E189" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5">
+      <c r="A190" s="2">
+        <v>46305.95833333334</v>
+      </c>
+      <c r="B190">
+        <v>4.302</v>
+      </c>
+      <c r="C190">
+        <v>0</v>
+      </c>
+      <c r="D190">
+        <v>93</v>
+      </c>
+      <c r="E190" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5">
+      <c r="A191" s="2">
+        <v>46305.96875</v>
+      </c>
+      <c r="B191">
+        <v>0</v>
+      </c>
+      <c r="C191">
+        <v>0.579</v>
+      </c>
+      <c r="D191">
+        <v>94</v>
+      </c>
+      <c r="E191" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5">
+      <c r="A192" s="2">
+        <v>46305.97916666666</v>
+      </c>
+      <c r="B192">
+        <v>0</v>
+      </c>
+      <c r="C192">
+        <v>1.949</v>
+      </c>
+      <c r="D192">
+        <v>95</v>
+      </c>
+      <c r="E192" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5">
+      <c r="A193" s="2">
+        <v>46305.98958333334</v>
+      </c>
+      <c r="B193">
+        <v>1.982</v>
+      </c>
+      <c r="C193">
+        <v>0</v>
+      </c>
+      <c r="D193">
+        <v>96</v>
+      </c>
+      <c r="E193" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5">
+      <c r="A194" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B194">
+        <v>20.367</v>
+      </c>
+      <c r="C194">
+        <v>0</v>
+      </c>
+      <c r="D194">
+        <v>1</v>
+      </c>
+      <c r="E194" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5">
+      <c r="A195" s="2">
+        <v>46306.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>0</v>
+      </c>
+      <c r="C195">
+        <v>5.513</v>
+      </c>
+      <c r="D195">
+        <v>2</v>
+      </c>
+      <c r="E195" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5">
+      <c r="A196" s="2">
+        <v>46306.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>0</v>
+      </c>
+      <c r="C196">
+        <v>6.443</v>
+      </c>
+      <c r="D196">
+        <v>3</v>
+      </c>
+      <c r="E196" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="A197" s="2">
+        <v>46306.03125</v>
+      </c>
+      <c r="B197">
+        <v>7.328</v>
+      </c>
+      <c r="C197">
+        <v>0</v>
+      </c>
+      <c r="D197">
+        <v>4</v>
+      </c>
+      <c r="E197" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="A198" s="2">
+        <v>46306.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>14.707</v>
+      </c>
+      <c r="C198">
+        <v>0</v>
+      </c>
+      <c r="D198">
+        <v>5</v>
+      </c>
+      <c r="E198" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5">
+      <c r="A199" s="2">
+        <v>46306.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>10.809</v>
+      </c>
+      <c r="C199">
+        <v>0</v>
+      </c>
+      <c r="D199">
+        <v>6</v>
+      </c>
+      <c r="E199" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="A200" s="2">
+        <v>46306.0625</v>
+      </c>
+      <c r="B200">
+        <v>3.165</v>
+      </c>
+      <c r="C200">
+        <v>0</v>
+      </c>
+      <c r="D200">
+        <v>7</v>
+      </c>
+      <c r="E200" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5">
+      <c r="A201" s="2">
+        <v>46306.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>6.323</v>
+      </c>
+      <c r="C201">
+        <v>0</v>
+      </c>
+      <c r="D201">
+        <v>8</v>
+      </c>
+      <c r="E201" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5">
+      <c r="A202" s="2">
+        <v>46306.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>31.575</v>
+      </c>
+      <c r="C202">
+        <v>0</v>
+      </c>
+      <c r="D202">
+        <v>9</v>
+      </c>
+      <c r="E202" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5">
+      <c r="A203" s="2">
+        <v>46306.09375</v>
+      </c>
+      <c r="B203">
+        <v>27.284</v>
+      </c>
+      <c r="C203">
+        <v>0</v>
+      </c>
+      <c r="D203">
+        <v>10</v>
+      </c>
+      <c r="E203" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5">
+      <c r="A204" s="2">
+        <v>46306.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>28.613</v>
+      </c>
+      <c r="C204">
+        <v>0</v>
+      </c>
+      <c r="D204">
+        <v>11</v>
+      </c>
+      <c r="E204" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5">
+      <c r="A205" s="2">
+        <v>46306.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>4.624</v>
+      </c>
+      <c r="C205">
+        <v>0</v>
+      </c>
+      <c r="D205">
+        <v>12</v>
+      </c>
+      <c r="E205" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5">
+      <c r="A206" s="2">
+        <v>46306.125</v>
+      </c>
+      <c r="B206">
+        <v>25.54</v>
+      </c>
+      <c r="C206">
+        <v>0</v>
+      </c>
+      <c r="D206">
+        <v>13</v>
+      </c>
+      <c r="E206" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5">
+      <c r="A207" s="2">
+        <v>46306.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>25.113</v>
+      </c>
+      <c r="C207">
+        <v>0</v>
+      </c>
+      <c r="D207">
+        <v>14</v>
+      </c>
+      <c r="E207" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5">
+      <c r="A208" s="2">
+        <v>46306.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>22.839</v>
+      </c>
+      <c r="C208">
+        <v>0</v>
+      </c>
+      <c r="D208">
+        <v>15</v>
+      </c>
+      <c r="E208" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5">
+      <c r="A209" s="2">
+        <v>46306.15625</v>
+      </c>
+      <c r="B209">
+        <v>29.582</v>
+      </c>
+      <c r="C209">
+        <v>0</v>
+      </c>
+      <c r="D209">
+        <v>16</v>
+      </c>
+      <c r="E209" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5">
+      <c r="A210" s="2">
+        <v>46306.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>6.056</v>
+      </c>
+      <c r="C210">
+        <v>0</v>
+      </c>
+      <c r="D210">
+        <v>17</v>
+      </c>
+      <c r="E210" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5">
+      <c r="A211" s="2">
+        <v>46306.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>6.621</v>
+      </c>
+      <c r="C211">
+        <v>0</v>
+      </c>
+      <c r="D211">
+        <v>18</v>
+      </c>
+      <c r="E211" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5">
+      <c r="A212" s="2">
+        <v>46306.1875</v>
+      </c>
+      <c r="B212">
+        <v>16.762</v>
+      </c>
+      <c r="C212">
+        <v>0</v>
+      </c>
+      <c r="D212">
+        <v>19</v>
+      </c>
+      <c r="E212" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5">
+      <c r="A213" s="2">
+        <v>46306.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>58.404</v>
+      </c>
+      <c r="C213">
+        <v>0</v>
+      </c>
+      <c r="D213">
+        <v>20</v>
+      </c>
+      <c r="E213" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5">
+      <c r="A214" s="2">
+        <v>46306.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>35.592</v>
+      </c>
+      <c r="C214">
+        <v>0</v>
+      </c>
+      <c r="D214">
+        <v>21</v>
+      </c>
+      <c r="E214" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5">
+      <c r="A215" s="2">
+        <v>46306.21875</v>
+      </c>
+      <c r="B215">
+        <v>16.32</v>
+      </c>
+      <c r="C215">
+        <v>0</v>
+      </c>
+      <c r="D215">
+        <v>22</v>
+      </c>
+      <c r="E215" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5">
+      <c r="A216" s="2">
+        <v>46306.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>35.144</v>
+      </c>
+      <c r="C216">
+        <v>0</v>
+      </c>
+      <c r="D216">
+        <v>23</v>
+      </c>
+      <c r="E216" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5">
+      <c r="A217" s="2">
+        <v>46306.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>38.092</v>
+      </c>
+      <c r="C217">
+        <v>0</v>
+      </c>
+      <c r="D217">
+        <v>24</v>
+      </c>
+      <c r="E217" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5">
+      <c r="A218" s="2">
+        <v>46306.25</v>
+      </c>
+      <c r="B218">
+        <v>57.784</v>
+      </c>
+      <c r="C218">
+        <v>0</v>
+      </c>
+      <c r="D218">
+        <v>25</v>
+      </c>
+      <c r="E218" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5">
+      <c r="A219" s="2">
+        <v>46306.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>38.725</v>
+      </c>
+      <c r="C219">
+        <v>0</v>
+      </c>
+      <c r="D219">
+        <v>26</v>
+      </c>
+      <c r="E219" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5">
+      <c r="A220" s="2">
+        <v>46306.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>2.333</v>
+      </c>
+      <c r="C220">
+        <v>0</v>
+      </c>
+      <c r="D220">
+        <v>27</v>
+      </c>
+      <c r="E220" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5">
+      <c r="A221" s="2">
+        <v>46306.28125</v>
+      </c>
+      <c r="B221">
+        <v>16.739</v>
+      </c>
+      <c r="C221">
+        <v>0</v>
+      </c>
+      <c r="D221">
+        <v>28</v>
+      </c>
+      <c r="E221" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5">
+      <c r="A222" s="2">
+        <v>46306.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>21.808</v>
+      </c>
+      <c r="C222">
+        <v>0</v>
+      </c>
+      <c r="D222">
+        <v>29</v>
+      </c>
+      <c r="E222" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5">
+      <c r="A223" s="2">
+        <v>46306.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>8.227</v>
+      </c>
+      <c r="C223">
+        <v>0</v>
+      </c>
+      <c r="D223">
+        <v>30</v>
+      </c>
+      <c r="E223" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5">
+      <c r="A224" s="2">
+        <v>46306.3125</v>
+      </c>
+      <c r="B224">
+        <v>0</v>
+      </c>
+      <c r="C224">
+        <v>6.114</v>
+      </c>
+      <c r="D224">
+        <v>31</v>
+      </c>
+      <c r="E224" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5">
+      <c r="A225" s="2">
+        <v>46306.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>0</v>
+      </c>
+      <c r="C225">
+        <v>43.364</v>
+      </c>
+      <c r="D225">
+        <v>32</v>
+      </c>
+      <c r="E225" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5">
+      <c r="A226" s="2">
+        <v>46306.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>0</v>
+      </c>
+      <c r="C226">
+        <v>20.573</v>
+      </c>
+      <c r="D226">
+        <v>33</v>
+      </c>
+      <c r="E226" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5">
+      <c r="A227" s="2">
+        <v>46306.34375</v>
+      </c>
+      <c r="B227">
+        <v>0</v>
+      </c>
+      <c r="C227">
+        <v>26.01</v>
+      </c>
+      <c r="D227">
+        <v>34</v>
+      </c>
+      <c r="E227" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5">
+      <c r="A228" s="2">
+        <v>46306.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>31.225</v>
+      </c>
+      <c r="C228">
+        <v>0</v>
+      </c>
+      <c r="D228">
+        <v>35</v>
+      </c>
+      <c r="E228" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5">
+      <c r="A229" s="2">
+        <v>46306.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>3.976</v>
+      </c>
+      <c r="C229">
+        <v>0</v>
+      </c>
+      <c r="D229">
+        <v>36</v>
+      </c>
+      <c r="E229" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5">
+      <c r="A230" s="2">
+        <v>46306.375</v>
+      </c>
+      <c r="B230">
+        <v>19.674</v>
+      </c>
+      <c r="C230">
+        <v>0</v>
+      </c>
+      <c r="D230">
+        <v>37</v>
+      </c>
+      <c r="E230" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5">
+      <c r="A231" s="2">
+        <v>46306.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>8.032</v>
+      </c>
+      <c r="C231">
+        <v>0</v>
+      </c>
+      <c r="D231">
+        <v>38</v>
+      </c>
+      <c r="E231" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5">
+      <c r="A232" s="2">
+        <v>46306.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>0</v>
+      </c>
+      <c r="C232">
+        <v>1.341</v>
+      </c>
+      <c r="D232">
+        <v>39</v>
+      </c>
+      <c r="E232" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5">
+      <c r="A233" s="2">
+        <v>46306.40625</v>
+      </c>
+      <c r="B233">
+        <v>0</v>
+      </c>
+      <c r="C233">
+        <v>28.543</v>
+      </c>
+      <c r="D233">
+        <v>40</v>
+      </c>
+      <c r="E233" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5">
+      <c r="A234" s="2">
+        <v>46306.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>0</v>
+      </c>
+      <c r="C234">
+        <v>37.787</v>
+      </c>
+      <c r="D234">
+        <v>41</v>
+      </c>
+      <c r="E234" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5">
+      <c r="A235" s="2">
+        <v>46306.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>0</v>
+      </c>
+      <c r="C235">
+        <v>42.789</v>
+      </c>
+      <c r="D235">
+        <v>42</v>
+      </c>
+      <c r="E235" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5">
+      <c r="A236" s="2">
+        <v>46306.4375</v>
+      </c>
+      <c r="B236">
+        <v>0</v>
+      </c>
+      <c r="C236">
+        <v>9.513</v>
+      </c>
+      <c r="D236">
+        <v>43</v>
+      </c>
+      <c r="E236" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5">
+      <c r="A237" s="2">
+        <v>46306.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>0</v>
+      </c>
+      <c r="C237">
+        <v>15.33</v>
+      </c>
+      <c r="D237">
+        <v>44</v>
+      </c>
+      <c r="E237" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5">
+      <c r="A238" s="2">
+        <v>46306.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>11.266</v>
+      </c>
+      <c r="C238">
+        <v>0</v>
+      </c>
+      <c r="D238">
+        <v>45</v>
+      </c>
+      <c r="E238" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5">
+      <c r="A239" s="2">
+        <v>46306.46875</v>
+      </c>
+      <c r="B239">
+        <v>13.648</v>
+      </c>
+      <c r="C239">
+        <v>0</v>
+      </c>
+      <c r="D239">
+        <v>46</v>
+      </c>
+      <c r="E239" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5">
+      <c r="A240" s="2">
+        <v>46306.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>8.629</v>
+      </c>
+      <c r="C240">
+        <v>0</v>
+      </c>
+      <c r="D240">
+        <v>47</v>
+      </c>
+      <c r="E240" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5">
+      <c r="A241" s="2">
+        <v>46306.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>20.337</v>
+      </c>
+      <c r="C241">
+        <v>0</v>
+      </c>
+      <c r="D241">
+        <v>48</v>
+      </c>
+      <c r="E241" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5">
+      <c r="A242" s="2">
+        <v>46306.5</v>
+      </c>
+      <c r="B242">
+        <v>5.578</v>
+      </c>
+      <c r="C242">
+        <v>0</v>
+      </c>
+      <c r="D242">
+        <v>49</v>
+      </c>
+      <c r="E242" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5">
+      <c r="A243" s="2">
+        <v>46306.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>11.741</v>
+      </c>
+      <c r="C243">
+        <v>0</v>
+      </c>
+      <c r="D243">
+        <v>50</v>
+      </c>
+      <c r="E243" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5">
+      <c r="A244" s="2">
+        <v>46306.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>0</v>
+      </c>
+      <c r="C244">
+        <v>3.902</v>
+      </c>
+      <c r="D244">
+        <v>51</v>
+      </c>
+      <c r="E244" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5">
+      <c r="A245" s="2">
+        <v>46306.53125</v>
+      </c>
+      <c r="B245">
+        <v>0</v>
+      </c>
+      <c r="C245">
+        <v>9.750999999999999</v>
+      </c>
+      <c r="D245">
+        <v>52</v>
+      </c>
+      <c r="E245" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5">
+      <c r="A246" s="2">
+        <v>46306.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>0</v>
+      </c>
+      <c r="C246">
+        <v>7.77</v>
+      </c>
+      <c r="D246">
+        <v>53</v>
+      </c>
+      <c r="E246" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5">
+      <c r="A247" s="2">
+        <v>46306.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>0</v>
+      </c>
+      <c r="C247">
+        <v>8.599</v>
+      </c>
+      <c r="D247">
+        <v>54</v>
+      </c>
+      <c r="E247" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5">
+      <c r="A248" s="2">
+        <v>46306.5625</v>
+      </c>
+      <c r="B248">
+        <v>2.716</v>
+      </c>
+      <c r="C248">
+        <v>0</v>
+      </c>
+      <c r="D248">
+        <v>55</v>
+      </c>
+      <c r="E248" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5">
+      <c r="A249" s="2">
+        <v>46306.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>18.233</v>
+      </c>
+      <c r="C249">
+        <v>0</v>
+      </c>
+      <c r="D249">
+        <v>56</v>
+      </c>
+      <c r="E249" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5">
+      <c r="A250" s="2">
+        <v>46306.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>5.036</v>
+      </c>
+      <c r="C250">
+        <v>0</v>
+      </c>
+      <c r="D250">
+        <v>57</v>
+      </c>
+      <c r="E250" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5">
+      <c r="A251" s="2">
+        <v>46306.59375</v>
+      </c>
+      <c r="B251">
+        <v>8.757999999999999</v>
+      </c>
+      <c r="C251">
+        <v>0</v>
+      </c>
+      <c r="D251">
+        <v>58</v>
+      </c>
+      <c r="E251" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5">
+      <c r="A252" s="2">
+        <v>46306.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>14.316</v>
+      </c>
+      <c r="C252">
+        <v>0</v>
+      </c>
+      <c r="D252">
+        <v>59</v>
+      </c>
+      <c r="E252" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5">
+      <c r="A253" s="2">
+        <v>46306.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>20.24</v>
+      </c>
+      <c r="C253">
+        <v>0</v>
+      </c>
+      <c r="D253">
+        <v>60</v>
+      </c>
+      <c r="E253" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5">
+      <c r="A254" s="2">
+        <v>46306.625</v>
+      </c>
+      <c r="B254">
+        <v>32.014</v>
+      </c>
+      <c r="C254">
+        <v>0</v>
+      </c>
+      <c r="D254">
+        <v>61</v>
+      </c>
+      <c r="E254" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5">
+      <c r="A255" s="2">
+        <v>46306.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>17.852</v>
+      </c>
+      <c r="C255">
+        <v>0</v>
+      </c>
+      <c r="D255">
+        <v>62</v>
+      </c>
+      <c r="E255" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5">
+      <c r="A256" s="2">
+        <v>46306.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>4.992</v>
+      </c>
+      <c r="C256">
+        <v>0</v>
+      </c>
+      <c r="D256">
+        <v>63</v>
+      </c>
+      <c r="E256" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5">
+      <c r="A257" s="2">
+        <v>46306.65625</v>
+      </c>
+      <c r="B257">
+        <v>12.3</v>
+      </c>
+      <c r="C257">
+        <v>0</v>
+      </c>
+      <c r="D257">
+        <v>64</v>
+      </c>
+      <c r="E257" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5">
+      <c r="A258" s="2">
+        <v>46306.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>0</v>
+      </c>
+      <c r="C258">
+        <v>11.252</v>
+      </c>
+      <c r="D258">
+        <v>65</v>
+      </c>
+      <c r="E258" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5">
+      <c r="A259" s="2">
+        <v>46306.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>0</v>
+      </c>
+      <c r="C259">
+        <v>24.259</v>
+      </c>
+      <c r="D259">
+        <v>66</v>
+      </c>
+      <c r="E259" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5">
+      <c r="A260" s="2">
+        <v>46306.6875</v>
+      </c>
+      <c r="B260">
+        <v>0</v>
+      </c>
+      <c r="C260">
+        <v>1.126</v>
+      </c>
+      <c r="D260">
+        <v>67</v>
+      </c>
+      <c r="E260" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5">
+      <c r="A261" s="2">
+        <v>46306.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>0</v>
+      </c>
+      <c r="C261">
+        <v>27.619</v>
+      </c>
+      <c r="D261">
+        <v>68</v>
+      </c>
+      <c r="E261" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5">
+      <c r="A262" s="2">
+        <v>46306.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>0</v>
+      </c>
+      <c r="C262">
+        <v>35.353</v>
+      </c>
+      <c r="D262">
+        <v>69</v>
+      </c>
+      <c r="E262" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5">
+      <c r="A263" s="2">
+        <v>46306.71875</v>
+      </c>
+      <c r="B263">
+        <v>0</v>
+      </c>
+      <c r="C263">
+        <v>52.603</v>
+      </c>
+      <c r="D263">
+        <v>70</v>
+      </c>
+      <c r="E263" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5">
+      <c r="A264" s="2">
+        <v>46306.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>0</v>
+      </c>
+      <c r="C264">
+        <v>7.384</v>
+      </c>
+      <c r="D264">
+        <v>71</v>
+      </c>
+      <c r="E264" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5">
+      <c r="A265" s="2">
+        <v>46306.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>8.079000000000001</v>
+      </c>
+      <c r="C265">
+        <v>0</v>
+      </c>
+      <c r="D265">
+        <v>72</v>
+      </c>
+      <c r="E265" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5">
+      <c r="A266" s="2">
+        <v>46306.75</v>
+      </c>
+      <c r="B266">
+        <v>0</v>
+      </c>
+      <c r="C266">
+        <v>9.481999999999999</v>
+      </c>
+      <c r="D266">
+        <v>73</v>
+      </c>
+      <c r="E266" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5">
+      <c r="A267" s="2">
+        <v>46306.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>7.466</v>
+      </c>
+      <c r="C267">
+        <v>0</v>
+      </c>
+      <c r="D267">
+        <v>74</v>
+      </c>
+      <c r="E267" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5">
+      <c r="A268" s="2">
+        <v>46306.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>0</v>
+      </c>
+      <c r="C268">
+        <v>6.308</v>
+      </c>
+      <c r="D268">
+        <v>75</v>
+      </c>
+      <c r="E268" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5">
+      <c r="A269" s="2">
+        <v>46306.78125</v>
+      </c>
+      <c r="B269">
+        <v>0</v>
+      </c>
+      <c r="C269">
+        <v>10.203</v>
+      </c>
+      <c r="D269">
+        <v>76</v>
+      </c>
+      <c r="E269" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5">
+      <c r="A270" s="2">
+        <v>46306.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>0</v>
+      </c>
+      <c r="C270">
+        <v>7.69</v>
+      </c>
+      <c r="D270">
+        <v>77</v>
+      </c>
+      <c r="E270" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5">
+      <c r="A271" s="2">
+        <v>46306.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>0</v>
+      </c>
+      <c r="C271">
+        <v>42.952</v>
+      </c>
+      <c r="D271">
+        <v>78</v>
+      </c>
+      <c r="E271" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5">
+      <c r="A272" s="2">
+        <v>46306.8125</v>
+      </c>
+      <c r="B272">
+        <v>0</v>
+      </c>
+      <c r="C272">
+        <v>37.923</v>
+      </c>
+      <c r="D272">
+        <v>79</v>
+      </c>
+      <c r="E272" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5">
+      <c r="A273" s="2">
+        <v>46306.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>0</v>
+      </c>
+      <c r="C273">
+        <v>16.476</v>
+      </c>
+      <c r="D273">
+        <v>80</v>
+      </c>
+      <c r="E273" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5">
+      <c r="A274" s="2">
+        <v>46306.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>0</v>
+      </c>
+      <c r="C274">
+        <v>25.594</v>
+      </c>
+      <c r="D274">
+        <v>81</v>
+      </c>
+      <c r="E274" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5">
+      <c r="A275" s="2">
+        <v>46306.84375</v>
+      </c>
+      <c r="B275">
+        <v>0</v>
+      </c>
+      <c r="C275">
+        <v>1.553</v>
+      </c>
+      <c r="D275">
+        <v>82</v>
+      </c>
+      <c r="E275" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5">
+      <c r="A276" s="2">
+        <v>46306.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>0.305</v>
+      </c>
+      <c r="C276">
+        <v>0</v>
+      </c>
+      <c r="D276">
+        <v>83</v>
+      </c>
+      <c r="E276" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5">
+      <c r="A277" s="2">
+        <v>46306.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>3.389</v>
+      </c>
+      <c r="C277">
+        <v>0</v>
+      </c>
+      <c r="D277">
+        <v>84</v>
+      </c>
+      <c r="E277" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5">
+      <c r="A278" s="2">
+        <v>46306.875</v>
+      </c>
+      <c r="B278">
+        <v>0</v>
+      </c>
+      <c r="C278">
+        <v>12.472</v>
+      </c>
+      <c r="D278">
+        <v>85</v>
+      </c>
+      <c r="E278" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5">
+      <c r="A279" s="2">
+        <v>46306.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>0</v>
+      </c>
+      <c r="C279">
+        <v>30.919</v>
+      </c>
+      <c r="D279">
+        <v>86</v>
+      </c>
+      <c r="E279" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5">
+      <c r="A280" s="2">
+        <v>46306.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>0</v>
+      </c>
+      <c r="C280">
+        <v>20.713</v>
+      </c>
+      <c r="D280">
+        <v>87</v>
+      </c>
+      <c r="E280" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5">
+      <c r="A281" s="2">
+        <v>46306.90625</v>
+      </c>
+      <c r="B281">
+        <v>0</v>
+      </c>
+      <c r="C281">
+        <v>9.093</v>
+      </c>
+      <c r="D281">
+        <v>88</v>
+      </c>
+      <c r="E281" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5">
+      <c r="A282" s="2">
+        <v>46306.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>0</v>
+      </c>
+      <c r="C282">
+        <v>23.696</v>
+      </c>
+      <c r="D282">
+        <v>89</v>
+      </c>
+      <c r="E282" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5">
+      <c r="A283" s="2">
+        <v>46306.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>0</v>
+      </c>
+      <c r="C283">
+        <v>15.229</v>
+      </c>
+      <c r="D283">
+        <v>90</v>
+      </c>
+      <c r="E283" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5">
+      <c r="A284" s="2">
+        <v>46306.9375</v>
+      </c>
+      <c r="B284">
+        <v>0</v>
+      </c>
+      <c r="C284">
+        <v>23.52</v>
+      </c>
+      <c r="D284">
+        <v>91</v>
+      </c>
+      <c r="E284" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5">
+      <c r="A285" s="2">
+        <v>46306.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>0</v>
+      </c>
+      <c r="C285">
+        <v>13.892</v>
+      </c>
+      <c r="D285">
+        <v>92</v>
+      </c>
+      <c r="E285" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5">
+      <c r="A286" s="2">
+        <v>46306.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>8.289</v>
+      </c>
+      <c r="C286">
+        <v>0</v>
+      </c>
+      <c r="D286">
+        <v>93</v>
+      </c>
+      <c r="E286" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5">
+      <c r="A287" s="2">
+        <v>46306.96875</v>
+      </c>
+      <c r="B287">
+        <v>24.791</v>
+      </c>
+      <c r="C287">
+        <v>0</v>
+      </c>
+      <c r="D287">
+        <v>94</v>
+      </c>
+      <c r="E287" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5">
+      <c r="A288" s="2">
+        <v>46306.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>29</v>
+      </c>
+      <c r="C288">
+        <v>0</v>
+      </c>
+      <c r="D288">
+        <v>95</v>
+      </c>
+      <c r="E288" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5">
+      <c r="A289" s="2">
+        <v>46306.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>17.511</v>
+      </c>
+      <c r="C289">
+        <v>0</v>
+      </c>
+      <c r="D289">
+        <v>96</v>
+      </c>
+      <c r="E289" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5">
+      <c r="A290" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B290">
+        <v>41.739</v>
+      </c>
+      <c r="C290">
+        <v>0</v>
+      </c>
+      <c r="D290">
+        <v>1</v>
+      </c>
+      <c r="E290" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5">
+      <c r="A291" s="2">
+        <v>46307.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>37.362</v>
+      </c>
+      <c r="C291">
+        <v>0</v>
+      </c>
+      <c r="D291">
+        <v>2</v>
+      </c>
+      <c r="E291" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5">
+      <c r="A292" s="2">
+        <v>46307.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>15.562</v>
+      </c>
+      <c r="C292">
+        <v>0</v>
+      </c>
+      <c r="D292">
+        <v>3</v>
+      </c>
+      <c r="E292" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5">
+      <c r="A293" s="2">
+        <v>46307.03125</v>
+      </c>
+      <c r="B293">
+        <v>0</v>
+      </c>
+      <c r="C293">
+        <v>12.639</v>
+      </c>
+      <c r="D293">
+        <v>4</v>
+      </c>
+      <c r="E293" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5">
+      <c r="A294" s="2">
+        <v>46307.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>0</v>
+      </c>
+      <c r="C294">
+        <v>44.241</v>
+      </c>
+      <c r="D294">
+        <v>5</v>
+      </c>
+      <c r="E294" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5">
+      <c r="A295" s="2">
+        <v>46307.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>0</v>
+      </c>
+      <c r="C295">
+        <v>32.15</v>
+      </c>
+      <c r="D295">
+        <v>6</v>
+      </c>
+      <c r="E295" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5">
+      <c r="A296" s="2">
+        <v>46307.0625</v>
+      </c>
+      <c r="B296">
+        <v>0</v>
+      </c>
+      <c r="C296">
+        <v>63.479</v>
+      </c>
+      <c r="D296">
+        <v>7</v>
+      </c>
+      <c r="E296" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5">
+      <c r="A297" s="2">
+        <v>46307.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>0</v>
+      </c>
+      <c r="C297">
+        <v>46.497</v>
+      </c>
+      <c r="D297">
+        <v>8</v>
+      </c>
+      <c r="E297" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5">
+      <c r="A298" s="2">
+        <v>46307.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>0</v>
+      </c>
+      <c r="C298">
+        <v>39.79</v>
+      </c>
+      <c r="D298">
+        <v>9</v>
+      </c>
+      <c r="E298" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5">
+      <c r="A299" s="2">
+        <v>46307.09375</v>
+      </c>
+      <c r="B299">
+        <v>0</v>
+      </c>
+      <c r="C299">
+        <v>4.764</v>
+      </c>
+      <c r="D299">
+        <v>10</v>
+      </c>
+      <c r="E299" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5">
+      <c r="A300" s="2">
+        <v>46307.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>0</v>
+      </c>
+      <c r="C300">
+        <v>29.876</v>
+      </c>
+      <c r="D300">
+        <v>11</v>
+      </c>
+      <c r="E300" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5">
+      <c r="A301" s="2">
+        <v>46307.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>0</v>
+      </c>
+      <c r="C301">
+        <v>1.517</v>
+      </c>
+      <c r="D301">
+        <v>12</v>
+      </c>
+      <c r="E301" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5">
+      <c r="A302" s="2">
+        <v>46307.125</v>
+      </c>
+      <c r="B302">
+        <v>0</v>
+      </c>
+      <c r="C302">
+        <v>9.895</v>
+      </c>
+      <c r="D302">
+        <v>13</v>
+      </c>
+      <c r="E302" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5">
+      <c r="A303" s="2">
+        <v>46307.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>0</v>
+      </c>
+      <c r="C303">
+        <v>4.904</v>
+      </c>
+      <c r="D303">
+        <v>14</v>
+      </c>
+      <c r="E303" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5">
+      <c r="A304" s="2">
+        <v>46307.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>0</v>
+      </c>
+      <c r="C304">
+        <v>9.33</v>
+      </c>
+      <c r="D304">
+        <v>15</v>
+      </c>
+      <c r="E304" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5">
+      <c r="A305" s="2">
+        <v>46307.15625</v>
+      </c>
+      <c r="B305">
+        <v>0</v>
+      </c>
+      <c r="C305">
+        <v>18.528</v>
+      </c>
+      <c r="D305">
+        <v>16</v>
+      </c>
+      <c r="E305" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5">
+      <c r="A306" s="2">
+        <v>46307.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>0</v>
+      </c>
+      <c r="C306">
+        <v>17.647</v>
+      </c>
+      <c r="D306">
+        <v>17</v>
+      </c>
+      <c r="E306" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5">
+      <c r="A307" s="2">
+        <v>46307.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>7.32</v>
+      </c>
+      <c r="C307">
+        <v>0</v>
+      </c>
+      <c r="D307">
+        <v>18</v>
+      </c>
+      <c r="E307" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5">
+      <c r="A308" s="2">
+        <v>46307.1875</v>
+      </c>
+      <c r="B308">
+        <v>7.408</v>
+      </c>
+      <c r="C308">
+        <v>0</v>
+      </c>
+      <c r="D308">
+        <v>19</v>
+      </c>
+      <c r="E308" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5">
+      <c r="A309" s="2">
+        <v>46307.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>9.288</v>
+      </c>
+      <c r="C309">
+        <v>0</v>
+      </c>
+      <c r="D309">
+        <v>20</v>
+      </c>
+      <c r="E309" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5">
+      <c r="A310" s="2">
+        <v>46307.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>0</v>
+      </c>
+      <c r="C310">
+        <v>16.441</v>
+      </c>
+      <c r="D310">
+        <v>21</v>
+      </c>
+      <c r="E310" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5">
+      <c r="A311" s="2">
+        <v>46307.21875</v>
+      </c>
+      <c r="B311">
+        <v>0</v>
+      </c>
+      <c r="C311">
+        <v>12.119</v>
+      </c>
+      <c r="D311">
+        <v>22</v>
+      </c>
+      <c r="E311" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5">
+      <c r="A312" s="2">
+        <v>46307.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>2.722</v>
+      </c>
+      <c r="C312">
+        <v>0</v>
+      </c>
+      <c r="D312">
+        <v>23</v>
+      </c>
+      <c r="E312" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5">
+      <c r="A313" s="2">
+        <v>46307.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>18.189</v>
+      </c>
+      <c r="C313">
+        <v>0</v>
+      </c>
+      <c r="D313">
+        <v>24</v>
+      </c>
+      <c r="E313" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5">
+      <c r="A314" s="2">
+        <v>46307.25</v>
+      </c>
+      <c r="B314">
+        <v>14.215</v>
+      </c>
+      <c r="C314">
+        <v>0</v>
+      </c>
+      <c r="D314">
+        <v>25</v>
+      </c>
+      <c r="E314" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5">
+      <c r="A315" s="2">
+        <v>46307.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>0</v>
+      </c>
+      <c r="C315">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="D315">
+        <v>26</v>
+      </c>
+      <c r="E315" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5">
+      <c r="A316" s="2">
+        <v>46307.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>0.956</v>
+      </c>
+      <c r="C316">
+        <v>0</v>
+      </c>
+      <c r="D316">
+        <v>27</v>
+      </c>
+      <c r="E316" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5">
+      <c r="A317" s="2">
+        <v>46307.28125</v>
+      </c>
+      <c r="B317">
+        <v>0.539</v>
+      </c>
+      <c r="C317">
+        <v>0</v>
+      </c>
+      <c r="D317">
+        <v>28</v>
+      </c>
+      <c r="E317" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5">
+      <c r="A318" s="2">
+        <v>46307.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>25.391</v>
+      </c>
+      <c r="C318">
+        <v>0</v>
+      </c>
+      <c r="D318">
+        <v>29</v>
+      </c>
+      <c r="E318" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5">
+      <c r="A319" s="2">
+        <v>46307.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>26.804</v>
+      </c>
+      <c r="C319">
+        <v>0</v>
+      </c>
+      <c r="D319">
+        <v>30</v>
+      </c>
+      <c r="E319" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5">
+      <c r="A320" s="2">
+        <v>46307.3125</v>
+      </c>
+      <c r="B320">
+        <v>0</v>
+      </c>
+      <c r="C320">
+        <v>10.199</v>
+      </c>
+      <c r="D320">
+        <v>31</v>
+      </c>
+      <c r="E320" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5">
+      <c r="A321" s="2">
+        <v>46307.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>0</v>
+      </c>
+      <c r="C321">
+        <v>11.496</v>
+      </c>
+      <c r="D321">
+        <v>32</v>
+      </c>
+      <c r="E321" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5">
+      <c r="A322" s="2">
+        <v>46307.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>0</v>
+      </c>
+      <c r="C322">
+        <v>37.359</v>
+      </c>
+      <c r="D322">
+        <v>33</v>
+      </c>
+      <c r="E322" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5">
+      <c r="A323" s="2">
+        <v>46307.34375</v>
+      </c>
+      <c r="B323">
+        <v>0</v>
+      </c>
+      <c r="C323">
+        <v>23.519</v>
+      </c>
+      <c r="D323">
+        <v>34</v>
+      </c>
+      <c r="E323" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5">
+      <c r="A324" s="2">
+        <v>46307.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>0</v>
+      </c>
+      <c r="C324">
+        <v>9.746</v>
+      </c>
+      <c r="D324">
+        <v>35</v>
+      </c>
+      <c r="E324" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5">
+      <c r="A325" s="2">
+        <v>46307.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>0</v>
+      </c>
+      <c r="C325">
+        <v>19.181</v>
+      </c>
+      <c r="D325">
+        <v>36</v>
+      </c>
+      <c r="E325" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5">
+      <c r="A326" s="2">
+        <v>46307.375</v>
+      </c>
+      <c r="B326">
+        <v>0</v>
+      </c>
+      <c r="C326">
+        <v>4.991</v>
+      </c>
+      <c r="D326">
+        <v>37</v>
+      </c>
+      <c r="E326" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5">
+      <c r="A327" s="2">
+        <v>46307.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>9.313000000000001</v>
+      </c>
+      <c r="C327">
+        <v>0</v>
+      </c>
+      <c r="D327">
+        <v>38</v>
+      </c>
+      <c r="E327" t="s">
+        <v>330</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Unintended_Deviation.xlsx
+++ b/data_fetching/Entsoe/Unintended_Deviation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="160">
   <si>
     <t>Timestamp</t>
   </si>
@@ -31,294 +31,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>12.10.20261</t>
-  </si>
-  <si>
-    <t>12.10.20262</t>
-  </si>
-  <si>
-    <t>12.10.20263</t>
-  </si>
-  <si>
-    <t>12.10.20264</t>
-  </si>
-  <si>
-    <t>12.10.20265</t>
-  </si>
-  <si>
-    <t>12.10.20266</t>
-  </si>
-  <si>
-    <t>12.10.20267</t>
-  </si>
-  <si>
-    <t>12.10.20268</t>
-  </si>
-  <si>
-    <t>12.10.20269</t>
-  </si>
-  <si>
-    <t>12.10.202610</t>
-  </si>
-  <si>
-    <t>12.10.202611</t>
-  </si>
-  <si>
-    <t>12.10.202612</t>
-  </si>
-  <si>
-    <t>12.10.202613</t>
-  </si>
-  <si>
-    <t>12.10.202614</t>
-  </si>
-  <si>
-    <t>12.10.202615</t>
-  </si>
-  <si>
-    <t>12.10.202616</t>
-  </si>
-  <si>
-    <t>12.10.202617</t>
-  </si>
-  <si>
-    <t>12.10.202618</t>
-  </si>
-  <si>
-    <t>12.10.202619</t>
-  </si>
-  <si>
-    <t>12.10.202620</t>
-  </si>
-  <si>
-    <t>12.10.202621</t>
-  </si>
-  <si>
-    <t>12.10.202622</t>
-  </si>
-  <si>
-    <t>12.10.202623</t>
-  </si>
-  <si>
-    <t>12.10.202624</t>
-  </si>
-  <si>
-    <t>12.10.202625</t>
-  </si>
-  <si>
-    <t>12.10.202626</t>
-  </si>
-  <si>
-    <t>12.10.202627</t>
-  </si>
-  <si>
-    <t>12.10.202628</t>
-  </si>
-  <si>
-    <t>12.10.202629</t>
-  </si>
-  <si>
-    <t>12.10.202630</t>
-  </si>
-  <si>
-    <t>12.10.202631</t>
-  </si>
-  <si>
-    <t>12.10.202632</t>
-  </si>
-  <si>
-    <t>12.10.202633</t>
-  </si>
-  <si>
-    <t>12.10.202634</t>
-  </si>
-  <si>
-    <t>12.10.202635</t>
-  </si>
-  <si>
-    <t>12.10.202636</t>
-  </si>
-  <si>
-    <t>12.10.202637</t>
-  </si>
-  <si>
-    <t>12.10.202638</t>
-  </si>
-  <si>
-    <t>12.10.202639</t>
-  </si>
-  <si>
-    <t>12.10.202640</t>
-  </si>
-  <si>
-    <t>12.10.202641</t>
-  </si>
-  <si>
-    <t>12.10.202642</t>
-  </si>
-  <si>
-    <t>12.10.202643</t>
-  </si>
-  <si>
-    <t>12.10.202644</t>
-  </si>
-  <si>
-    <t>12.10.202645</t>
-  </si>
-  <si>
-    <t>12.10.202646</t>
-  </si>
-  <si>
-    <t>12.10.202647</t>
-  </si>
-  <si>
-    <t>12.10.202648</t>
-  </si>
-  <si>
-    <t>12.10.202649</t>
-  </si>
-  <si>
-    <t>12.10.202650</t>
-  </si>
-  <si>
-    <t>12.10.202651</t>
-  </si>
-  <si>
-    <t>12.10.202652</t>
-  </si>
-  <si>
-    <t>12.10.202653</t>
-  </si>
-  <si>
-    <t>12.10.202654</t>
-  </si>
-  <si>
-    <t>12.10.202655</t>
-  </si>
-  <si>
-    <t>12.10.202656</t>
-  </si>
-  <si>
-    <t>12.10.202657</t>
-  </si>
-  <si>
-    <t>12.10.202658</t>
-  </si>
-  <si>
-    <t>12.10.202659</t>
-  </si>
-  <si>
-    <t>12.10.202660</t>
-  </si>
-  <si>
-    <t>12.10.202661</t>
-  </si>
-  <si>
-    <t>12.10.202662</t>
-  </si>
-  <si>
-    <t>12.10.202663</t>
-  </si>
-  <si>
-    <t>12.10.202664</t>
-  </si>
-  <si>
-    <t>12.10.202665</t>
-  </si>
-  <si>
-    <t>12.10.202666</t>
-  </si>
-  <si>
-    <t>12.10.202667</t>
-  </si>
-  <si>
-    <t>12.10.202668</t>
-  </si>
-  <si>
-    <t>12.10.202669</t>
-  </si>
-  <si>
-    <t>12.10.202670</t>
-  </si>
-  <si>
-    <t>12.10.202671</t>
-  </si>
-  <si>
-    <t>12.10.202672</t>
-  </si>
-  <si>
-    <t>12.10.202673</t>
-  </si>
-  <si>
-    <t>12.10.202674</t>
-  </si>
-  <si>
-    <t>12.10.202675</t>
-  </si>
-  <si>
-    <t>12.10.202676</t>
-  </si>
-  <si>
-    <t>12.10.202677</t>
-  </si>
-  <si>
-    <t>12.10.202678</t>
-  </si>
-  <si>
-    <t>12.10.202679</t>
-  </si>
-  <si>
-    <t>12.10.202680</t>
-  </si>
-  <si>
-    <t>12.10.202681</t>
-  </si>
-  <si>
-    <t>12.10.202682</t>
-  </si>
-  <si>
-    <t>12.10.202683</t>
-  </si>
-  <si>
-    <t>12.10.202684</t>
-  </si>
-  <si>
-    <t>12.10.202685</t>
-  </si>
-  <si>
-    <t>12.10.202686</t>
-  </si>
-  <si>
-    <t>12.10.202687</t>
-  </si>
-  <si>
-    <t>12.10.202688</t>
-  </si>
-  <si>
-    <t>12.10.202689</t>
-  </si>
-  <si>
-    <t>12.10.202690</t>
-  </si>
-  <si>
-    <t>12.10.202691</t>
-  </si>
-  <si>
-    <t>12.10.202692</t>
-  </si>
-  <si>
-    <t>12.10.202693</t>
-  </si>
-  <si>
-    <t>12.10.202694</t>
-  </si>
-  <si>
-    <t>12.10.202695</t>
-  </si>
-  <si>
-    <t>12.10.202696</t>
-  </si>
-  <si>
     <t>13.10.20261</t>
   </si>
   <si>
@@ -482,6 +194,306 @@
   </si>
   <si>
     <t>13.10.202655</t>
+  </si>
+  <si>
+    <t>13.10.202656</t>
+  </si>
+  <si>
+    <t>13.10.202657</t>
+  </si>
+  <si>
+    <t>13.10.202658</t>
+  </si>
+  <si>
+    <t>13.10.202659</t>
+  </si>
+  <si>
+    <t>13.10.202660</t>
+  </si>
+  <si>
+    <t>13.10.202661</t>
+  </si>
+  <si>
+    <t>13.10.202662</t>
+  </si>
+  <si>
+    <t>13.10.202663</t>
+  </si>
+  <si>
+    <t>13.10.202664</t>
+  </si>
+  <si>
+    <t>13.10.202665</t>
+  </si>
+  <si>
+    <t>13.10.202666</t>
+  </si>
+  <si>
+    <t>13.10.202667</t>
+  </si>
+  <si>
+    <t>13.10.202668</t>
+  </si>
+  <si>
+    <t>13.10.202669</t>
+  </si>
+  <si>
+    <t>13.10.202670</t>
+  </si>
+  <si>
+    <t>13.10.202671</t>
+  </si>
+  <si>
+    <t>13.10.202672</t>
+  </si>
+  <si>
+    <t>13.10.202673</t>
+  </si>
+  <si>
+    <t>13.10.202674</t>
+  </si>
+  <si>
+    <t>13.10.202675</t>
+  </si>
+  <si>
+    <t>13.10.202676</t>
+  </si>
+  <si>
+    <t>13.10.202677</t>
+  </si>
+  <si>
+    <t>13.10.202678</t>
+  </si>
+  <si>
+    <t>13.10.202679</t>
+  </si>
+  <si>
+    <t>13.10.202680</t>
+  </si>
+  <si>
+    <t>13.10.202681</t>
+  </si>
+  <si>
+    <t>13.10.202682</t>
+  </si>
+  <si>
+    <t>13.10.202683</t>
+  </si>
+  <si>
+    <t>13.10.202684</t>
+  </si>
+  <si>
+    <t>13.10.202685</t>
+  </si>
+  <si>
+    <t>13.10.202686</t>
+  </si>
+  <si>
+    <t>13.10.202687</t>
+  </si>
+  <si>
+    <t>13.10.202688</t>
+  </si>
+  <si>
+    <t>13.10.202689</t>
+  </si>
+  <si>
+    <t>13.10.202690</t>
+  </si>
+  <si>
+    <t>13.10.202691</t>
+  </si>
+  <si>
+    <t>13.10.202692</t>
+  </si>
+  <si>
+    <t>13.10.202693</t>
+  </si>
+  <si>
+    <t>13.10.202694</t>
+  </si>
+  <si>
+    <t>13.10.202695</t>
+  </si>
+  <si>
+    <t>13.10.202696</t>
+  </si>
+  <si>
+    <t>14.10.20261</t>
+  </si>
+  <si>
+    <t>14.10.20262</t>
+  </si>
+  <si>
+    <t>14.10.20263</t>
+  </si>
+  <si>
+    <t>14.10.20264</t>
+  </si>
+  <si>
+    <t>14.10.20265</t>
+  </si>
+  <si>
+    <t>14.10.20266</t>
+  </si>
+  <si>
+    <t>14.10.20267</t>
+  </si>
+  <si>
+    <t>14.10.20268</t>
+  </si>
+  <si>
+    <t>14.10.20269</t>
+  </si>
+  <si>
+    <t>14.10.202610</t>
+  </si>
+  <si>
+    <t>14.10.202611</t>
+  </si>
+  <si>
+    <t>14.10.202612</t>
+  </si>
+  <si>
+    <t>14.10.202613</t>
+  </si>
+  <si>
+    <t>14.10.202614</t>
+  </si>
+  <si>
+    <t>14.10.202615</t>
+  </si>
+  <si>
+    <t>14.10.202616</t>
+  </si>
+  <si>
+    <t>14.10.202617</t>
+  </si>
+  <si>
+    <t>14.10.202618</t>
+  </si>
+  <si>
+    <t>14.10.202619</t>
+  </si>
+  <si>
+    <t>14.10.202620</t>
+  </si>
+  <si>
+    <t>14.10.202621</t>
+  </si>
+  <si>
+    <t>14.10.202622</t>
+  </si>
+  <si>
+    <t>14.10.202623</t>
+  </si>
+  <si>
+    <t>14.10.202624</t>
+  </si>
+  <si>
+    <t>14.10.202625</t>
+  </si>
+  <si>
+    <t>14.10.202626</t>
+  </si>
+  <si>
+    <t>14.10.202627</t>
+  </si>
+  <si>
+    <t>14.10.202628</t>
+  </si>
+  <si>
+    <t>14.10.202629</t>
+  </si>
+  <si>
+    <t>14.10.202630</t>
+  </si>
+  <si>
+    <t>14.10.202631</t>
+  </si>
+  <si>
+    <t>14.10.202632</t>
+  </si>
+  <si>
+    <t>14.10.202633</t>
+  </si>
+  <si>
+    <t>14.10.202634</t>
+  </si>
+  <si>
+    <t>14.10.202635</t>
+  </si>
+  <si>
+    <t>14.10.202636</t>
+  </si>
+  <si>
+    <t>14.10.202637</t>
+  </si>
+  <si>
+    <t>14.10.202638</t>
+  </si>
+  <si>
+    <t>14.10.202639</t>
+  </si>
+  <si>
+    <t>14.10.202640</t>
+  </si>
+  <si>
+    <t>14.10.202641</t>
+  </si>
+  <si>
+    <t>14.10.202642</t>
+  </si>
+  <si>
+    <t>14.10.202643</t>
+  </si>
+  <si>
+    <t>14.10.202644</t>
+  </si>
+  <si>
+    <t>14.10.202645</t>
+  </si>
+  <si>
+    <t>14.10.202646</t>
+  </si>
+  <si>
+    <t>14.10.202647</t>
+  </si>
+  <si>
+    <t>14.10.202648</t>
+  </si>
+  <si>
+    <t>14.10.202649</t>
+  </si>
+  <si>
+    <t>14.10.202650</t>
+  </si>
+  <si>
+    <t>14.10.202651</t>
+  </si>
+  <si>
+    <t>14.10.202652</t>
+  </si>
+  <si>
+    <t>14.10.202653</t>
+  </si>
+  <si>
+    <t>14.10.202654</t>
+  </si>
+  <si>
+    <t>14.10.202655</t>
+  </si>
+  <si>
+    <t>14.10.202656</t>
+  </si>
+  <si>
+    <t>14.10.202657</t>
+  </si>
+  <si>
+    <t>14.10.202658</t>
+  </si>
+  <si>
+    <t>14.10.202659</t>
   </si>
 </sst>
 </file>
@@ -843,7 +855,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E152"/>
+  <dimension ref="A1:E156"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -865,13 +877,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B2">
-        <v>41.739</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>52.203</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -882,13 +894,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46307.01041666666</v>
+        <v>46308.01041666666</v>
       </c>
       <c r="B3">
-        <v>37.362</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>56.666</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -899,13 +911,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46307.02083333334</v>
+        <v>46308.02083333334</v>
       </c>
       <c r="B4">
-        <v>15.562</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>13.726</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -916,13 +928,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46307.03125</v>
+        <v>46308.03125</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>0.351</v>
       </c>
       <c r="C5">
-        <v>12.639</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -933,13 +945,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46307.04166666666</v>
+        <v>46308.04166666666</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="C6">
-        <v>44.241</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -950,13 +962,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46307.05208333334</v>
+        <v>46308.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="C7">
-        <v>32.15</v>
+        <v>4.399</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -967,13 +979,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46307.0625</v>
+        <v>46308.0625</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>1.858</v>
       </c>
       <c r="C8">
-        <v>63.479</v>
+        <v>0</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -984,13 +996,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46307.07291666666</v>
+        <v>46308.07291666666</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>2.136</v>
       </c>
       <c r="C9">
-        <v>46.497</v>
+        <v>0</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -1001,13 +1013,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46307.08333333334</v>
+        <v>46308.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="C10">
-        <v>39.79</v>
+        <v>4.468</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -1018,13 +1030,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46307.09375</v>
+        <v>46308.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
       <c r="C11">
-        <v>4.764</v>
+        <v>0.399</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1035,13 +1047,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46307.10416666666</v>
+        <v>46308.10416666666</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>0.289</v>
       </c>
       <c r="C12">
-        <v>29.876</v>
+        <v>0</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -1052,13 +1064,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46307.11458333334</v>
+        <v>46308.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
       <c r="C13">
-        <v>1.517</v>
+        <v>3.642</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -1069,13 +1081,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46307.125</v>
+        <v>46308.125</v>
       </c>
       <c r="B14">
         <v>0</v>
       </c>
       <c r="C14">
-        <v>9.895</v>
+        <v>0.258</v>
       </c>
       <c r="D14">
         <v>13</v>
@@ -1086,13 +1098,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46307.13541666666</v>
+        <v>46308.13541666666</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>6.798</v>
       </c>
       <c r="C15">
-        <v>4.904</v>
+        <v>0</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -1103,13 +1115,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46307.14583333334</v>
+        <v>46308.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
       <c r="C16">
-        <v>9.33</v>
+        <v>3.6</v>
       </c>
       <c r="D16">
         <v>15</v>
@@ -1120,13 +1132,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46307.15625</v>
+        <v>46308.15625</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>0.739</v>
       </c>
       <c r="C17">
-        <v>18.528</v>
+        <v>0</v>
       </c>
       <c r="D17">
         <v>16</v>
@@ -1137,13 +1149,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46307.16666666666</v>
+        <v>46308.16666666666</v>
       </c>
       <c r="B18">
         <v>0</v>
       </c>
       <c r="C18">
-        <v>17.647</v>
+        <v>12.938</v>
       </c>
       <c r="D18">
         <v>17</v>
@@ -1154,13 +1166,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46307.17708333334</v>
+        <v>46308.17708333334</v>
       </c>
       <c r="B19">
-        <v>7.32</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>4.755</v>
       </c>
       <c r="D19">
         <v>18</v>
@@ -1171,13 +1183,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46307.1875</v>
+        <v>46308.1875</v>
       </c>
       <c r="B20">
-        <v>7.408</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>2.947</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1188,13 +1200,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46307.19791666666</v>
+        <v>46308.19791666666</v>
       </c>
       <c r="B21">
-        <v>9.288</v>
+        <v>0</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>1.212</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1205,13 +1217,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46307.20833333334</v>
+        <v>46308.20833333334</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>2.321</v>
       </c>
       <c r="C22">
-        <v>16.441</v>
+        <v>0</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1222,13 +1234,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46307.21875</v>
+        <v>46308.21875</v>
       </c>
       <c r="B23">
         <v>0</v>
       </c>
       <c r="C23">
-        <v>12.119</v>
+        <v>3.332</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1239,13 +1251,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46307.22916666666</v>
+        <v>46308.22916666666</v>
       </c>
       <c r="B24">
-        <v>2.722</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>12.979</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1256,13 +1268,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46307.23958333334</v>
+        <v>46308.23958333334</v>
       </c>
       <c r="B25">
-        <v>18.189</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>21.126</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1273,13 +1285,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46307.25</v>
+        <v>46308.25</v>
       </c>
       <c r="B26">
-        <v>14.215</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>20.931</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1290,13 +1302,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46307.26041666666</v>
+        <v>46308.26041666666</v>
       </c>
       <c r="B27">
         <v>0</v>
       </c>
       <c r="C27">
-        <v>0.08799999999999999</v>
+        <v>30.171</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1307,13 +1319,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46307.27083333334</v>
+        <v>46308.27083333334</v>
       </c>
       <c r="B28">
-        <v>0.956</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>20.179</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1324,13 +1336,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46307.28125</v>
+        <v>46308.28125</v>
       </c>
       <c r="B29">
-        <v>0.539</v>
+        <v>0</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>22.334</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1341,13 +1353,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46307.29166666666</v>
+        <v>46308.29166666666</v>
       </c>
       <c r="B30">
-        <v>25.391</v>
+        <v>0</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>42.17</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1358,13 +1370,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46307.30208333334</v>
+        <v>46308.30208333334</v>
       </c>
       <c r="B31">
-        <v>26.804</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>40.354</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1375,13 +1387,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46307.3125</v>
+        <v>46308.3125</v>
       </c>
       <c r="B32">
         <v>0</v>
       </c>
       <c r="C32">
-        <v>10.199</v>
+        <v>35.58</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1392,13 +1404,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46307.32291666666</v>
+        <v>46308.32291666666</v>
       </c>
       <c r="B33">
         <v>0</v>
       </c>
       <c r="C33">
-        <v>11.496</v>
+        <v>56.221</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1409,13 +1421,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46307.33333333334</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="B34">
         <v>0</v>
       </c>
       <c r="C34">
-        <v>37.359</v>
+        <v>47.666</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1426,13 +1438,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46307.34375</v>
+        <v>46308.34375</v>
       </c>
       <c r="B35">
         <v>0</v>
       </c>
       <c r="C35">
-        <v>23.519</v>
+        <v>26.563</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1443,13 +1455,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46307.35416666666</v>
+        <v>46308.35416666666</v>
       </c>
       <c r="B36">
         <v>0</v>
       </c>
       <c r="C36">
-        <v>9.746</v>
+        <v>45.978</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1460,13 +1472,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46307.36458333334</v>
+        <v>46308.36458333334</v>
       </c>
       <c r="B37">
         <v>0</v>
       </c>
       <c r="C37">
-        <v>19.181</v>
+        <v>45.673</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1477,13 +1489,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46307.375</v>
+        <v>46308.375</v>
       </c>
       <c r="B38">
         <v>0</v>
       </c>
       <c r="C38">
-        <v>4.991</v>
+        <v>16.499</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1494,10 +1506,10 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46307.38541666666</v>
+        <v>46308.38541666666</v>
       </c>
       <c r="B39">
-        <v>9.313000000000001</v>
+        <v>1.565</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -1511,13 +1523,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46307.39583333334</v>
+        <v>46308.39583333334</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="C40">
-        <v>0.552</v>
+        <v>0</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1528,13 +1540,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46307.40625</v>
+        <v>46308.40625</v>
       </c>
       <c r="B41">
-        <v>15.281</v>
+        <v>0</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1545,10 +1557,10 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46307.41666666666</v>
+        <v>46308.41666666666</v>
       </c>
       <c r="B42">
-        <v>30.943</v>
+        <v>30.067</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -1562,10 +1574,10 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46307.42708333334</v>
+        <v>46308.42708333334</v>
       </c>
       <c r="B43">
-        <v>32.849</v>
+        <v>20.258</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -1579,10 +1591,10 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46307.4375</v>
+        <v>46308.4375</v>
       </c>
       <c r="B44">
-        <v>26.879</v>
+        <v>2.324</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -1596,13 +1608,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46307.44791666666</v>
+        <v>46308.44791666666</v>
       </c>
       <c r="B45">
-        <v>9.763</v>
+        <v>0</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>9.682</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1613,13 +1625,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46307.45833333334</v>
+        <v>46308.45833333334</v>
       </c>
       <c r="B46">
-        <v>2.252</v>
+        <v>0</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1630,13 +1642,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46307.46875</v>
+        <v>46308.46875</v>
       </c>
       <c r="B47">
-        <v>14.252</v>
+        <v>0</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>36.9</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1647,13 +1659,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46307.47916666666</v>
+        <v>46308.47916666666</v>
       </c>
       <c r="B48">
         <v>0</v>
       </c>
       <c r="C48">
-        <v>7.702</v>
+        <v>51.204</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1664,13 +1676,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46307.48958333334</v>
+        <v>46308.48958333334</v>
       </c>
       <c r="B49">
         <v>0</v>
       </c>
       <c r="C49">
-        <v>12.01</v>
+        <v>55.287</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1681,13 +1693,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46307.5</v>
+        <v>46308.5</v>
       </c>
       <c r="B50">
-        <v>3.953</v>
+        <v>0</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>25.074</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1698,13 +1710,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46307.51041666666</v>
+        <v>46308.51041666666</v>
       </c>
       <c r="B51">
         <v>0</v>
       </c>
       <c r="C51">
-        <v>19.175</v>
+        <v>1.389</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1715,13 +1727,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46307.52083333334</v>
+        <v>46308.52083333334</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>2.193</v>
       </c>
       <c r="C52">
-        <v>20.765</v>
+        <v>0</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1732,13 +1744,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46307.53125</v>
+        <v>46308.53125</v>
       </c>
       <c r="B53">
-        <v>0</v>
+        <v>8.349</v>
       </c>
       <c r="C53">
-        <v>33.168</v>
+        <v>0</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1749,13 +1761,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46307.54166666666</v>
+        <v>46308.54166666666</v>
       </c>
       <c r="B54">
-        <v>0</v>
+        <v>4.439</v>
       </c>
       <c r="C54">
-        <v>40.767</v>
+        <v>0</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1766,10 +1778,10 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46307.55208333334</v>
+        <v>46308.55208333334</v>
       </c>
       <c r="B55">
-        <v>7.668</v>
+        <v>4.571</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -1783,13 +1795,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46307.5625</v>
+        <v>46308.5625</v>
       </c>
       <c r="B56">
-        <v>0</v>
+        <v>9.584</v>
       </c>
       <c r="C56">
-        <v>7.372</v>
+        <v>0</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1800,13 +1812,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46307.57291666666</v>
+        <v>46308.57291666666</v>
       </c>
       <c r="B57">
-        <v>0</v>
+        <v>39.599</v>
       </c>
       <c r="C57">
-        <v>14.173</v>
+        <v>0</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1817,13 +1829,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46307.58333333334</v>
+        <v>46308.58333333334</v>
       </c>
       <c r="B58">
-        <v>0</v>
+        <v>14.705</v>
       </c>
       <c r="C58">
-        <v>14.875</v>
+        <v>0</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1834,13 +1846,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46307.59375</v>
+        <v>46308.59375</v>
       </c>
       <c r="B59">
         <v>0</v>
       </c>
       <c r="C59">
-        <v>20.57</v>
+        <v>4.44</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1851,13 +1863,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46307.60416666666</v>
+        <v>46308.60416666666</v>
       </c>
       <c r="B60">
-        <v>0</v>
+        <v>12.749</v>
       </c>
       <c r="C60">
-        <v>1.131</v>
+        <v>0</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1868,13 +1880,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46307.61458333334</v>
+        <v>46308.61458333334</v>
       </c>
       <c r="B61">
-        <v>6.18</v>
+        <v>0</v>
       </c>
       <c r="C61">
-        <v>0</v>
+        <v>1.426</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -1885,13 +1897,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46307.625</v>
+        <v>46308.625</v>
       </c>
       <c r="B62">
-        <v>19.806</v>
+        <v>0</v>
       </c>
       <c r="C62">
-        <v>0</v>
+        <v>12.257</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -1902,13 +1914,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46307.63541666666</v>
+        <v>46308.63541666666</v>
       </c>
       <c r="B63">
-        <v>25.934</v>
+        <v>0</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>34.849</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -1919,13 +1931,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46307.64583333334</v>
+        <v>46308.64583333334</v>
       </c>
       <c r="B64">
-        <v>27.675</v>
+        <v>0</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>18.889</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -1936,10 +1948,10 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46307.65625</v>
+        <v>46308.65625</v>
       </c>
       <c r="B65">
-        <v>47.666</v>
+        <v>3.829</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -1953,13 +1965,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46307.66666666666</v>
+        <v>46308.66666666666</v>
       </c>
       <c r="B66">
-        <v>4.295</v>
+        <v>0</v>
       </c>
       <c r="C66">
-        <v>0</v>
+        <v>42.513</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -1970,13 +1982,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46307.67708333334</v>
+        <v>46308.67708333334</v>
       </c>
       <c r="B67">
         <v>0</v>
       </c>
       <c r="C67">
-        <v>6.767</v>
+        <v>19.376</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -1987,10 +1999,10 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46307.6875</v>
+        <v>46308.6875</v>
       </c>
       <c r="B68">
-        <v>3.589</v>
+        <v>0.704</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -2004,10 +2016,10 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46307.69791666666</v>
+        <v>46308.69791666666</v>
       </c>
       <c r="B69">
-        <v>26.265</v>
+        <v>6.896</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -2021,10 +2033,10 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46307.70833333334</v>
+        <v>46308.70833333334</v>
       </c>
       <c r="B70">
-        <v>18.808</v>
+        <v>30.056</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -2038,10 +2050,10 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46307.71875</v>
+        <v>46308.71875</v>
       </c>
       <c r="B71">
-        <v>17.07</v>
+        <v>8.423999999999999</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -2055,10 +2067,10 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46307.72916666666</v>
+        <v>46308.72916666666</v>
       </c>
       <c r="B72">
-        <v>20.434</v>
+        <v>0.439</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -2072,13 +2084,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46307.73958333334</v>
+        <v>46308.73958333334</v>
       </c>
       <c r="B73">
-        <v>3.735</v>
+        <v>0</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>1.966</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2089,10 +2101,10 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46307.75</v>
+        <v>46308.75</v>
       </c>
       <c r="B74">
-        <v>14.665</v>
+        <v>4.635</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -2106,13 +2118,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46307.76041666666</v>
+        <v>46308.76041666666</v>
       </c>
       <c r="B75">
-        <v>7.312</v>
+        <v>0</v>
       </c>
       <c r="C75">
-        <v>0</v>
+        <v>4.672</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2123,13 +2135,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46307.77083333334</v>
+        <v>46308.77083333334</v>
       </c>
       <c r="B76">
         <v>0</v>
       </c>
       <c r="C76">
-        <v>4.826</v>
+        <v>18.316</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2140,13 +2152,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46307.78125</v>
+        <v>46308.78125</v>
       </c>
       <c r="B77">
         <v>0</v>
       </c>
       <c r="C77">
-        <v>5.586</v>
+        <v>1.806</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2157,13 +2169,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46307.79166666666</v>
+        <v>46308.79166666666</v>
       </c>
       <c r="B78">
         <v>0</v>
       </c>
       <c r="C78">
-        <v>14.685</v>
+        <v>0.239</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2174,13 +2186,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46307.80208333334</v>
+        <v>46308.80208333334</v>
       </c>
       <c r="B79">
         <v>0</v>
       </c>
       <c r="C79">
-        <v>15.793</v>
+        <v>8.91</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2191,13 +2203,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46307.8125</v>
+        <v>46308.8125</v>
       </c>
       <c r="B80">
         <v>0</v>
       </c>
       <c r="C80">
-        <v>1.393</v>
+        <v>16.24</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2208,13 +2220,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46307.82291666666</v>
+        <v>46308.82291666666</v>
       </c>
       <c r="B81">
         <v>0</v>
       </c>
       <c r="C81">
-        <v>9.347</v>
+        <v>4.147</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2225,13 +2237,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46307.83333333334</v>
+        <v>46308.83333333334</v>
       </c>
       <c r="B82">
-        <v>0</v>
+        <v>0.597</v>
       </c>
       <c r="C82">
-        <v>20.267</v>
+        <v>0</v>
       </c>
       <c r="D82">
         <v>81</v>
@@ -2242,13 +2254,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46307.84375</v>
+        <v>46308.84375</v>
       </c>
       <c r="B83">
-        <v>0</v>
+        <v>3.857</v>
       </c>
       <c r="C83">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="D83">
         <v>82</v>
@@ -2259,13 +2271,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46307.85416666666</v>
+        <v>46308.85416666666</v>
       </c>
       <c r="B84">
         <v>0</v>
       </c>
       <c r="C84">
-        <v>36.155</v>
+        <v>3.876</v>
       </c>
       <c r="D84">
         <v>83</v>
@@ -2276,13 +2288,13 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46307.86458333334</v>
+        <v>46308.86458333334</v>
       </c>
       <c r="B85">
         <v>0</v>
       </c>
       <c r="C85">
-        <v>30.817</v>
+        <v>2.67</v>
       </c>
       <c r="D85">
         <v>84</v>
@@ -2293,13 +2305,13 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46307.875</v>
+        <v>46308.875</v>
       </c>
       <c r="B86">
         <v>0</v>
       </c>
       <c r="C86">
-        <v>24.205</v>
+        <v>0.169</v>
       </c>
       <c r="D86">
         <v>85</v>
@@ -2310,13 +2322,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46307.88541666666</v>
+        <v>46308.88541666666</v>
       </c>
       <c r="B87">
-        <v>0</v>
+        <v>7.099</v>
       </c>
       <c r="C87">
-        <v>10.33</v>
+        <v>0</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -2327,13 +2339,13 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46307.89583333334</v>
+        <v>46308.89583333334</v>
       </c>
       <c r="B88">
-        <v>0</v>
+        <v>0.778</v>
       </c>
       <c r="C88">
-        <v>17.256</v>
+        <v>0</v>
       </c>
       <c r="D88">
         <v>87</v>
@@ -2344,13 +2356,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46307.90625</v>
+        <v>46308.90625</v>
       </c>
       <c r="B89">
-        <v>0</v>
+        <v>1.714</v>
       </c>
       <c r="C89">
-        <v>4.954</v>
+        <v>0</v>
       </c>
       <c r="D89">
         <v>88</v>
@@ -2361,10 +2373,10 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46307.91666666666</v>
+        <v>46308.91666666666</v>
       </c>
       <c r="B90">
-        <v>6.369</v>
+        <v>27.533</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -2378,10 +2390,10 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46307.92708333334</v>
+        <v>46308.92708333334</v>
       </c>
       <c r="B91">
-        <v>6.54</v>
+        <v>14.588</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -2395,10 +2407,10 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46307.9375</v>
+        <v>46308.9375</v>
       </c>
       <c r="B92">
-        <v>17.956</v>
+        <v>19.153</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -2412,10 +2424,10 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46307.94791666666</v>
+        <v>46308.94791666666</v>
       </c>
       <c r="B93">
-        <v>23.582</v>
+        <v>25.217</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -2429,10 +2441,10 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46307.95833333334</v>
+        <v>46308.95833333334</v>
       </c>
       <c r="B94">
-        <v>7.529</v>
+        <v>15.016</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -2446,10 +2458,10 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46307.96875</v>
+        <v>46308.96875</v>
       </c>
       <c r="B95">
-        <v>0.534</v>
+        <v>20.487</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -2463,13 +2475,13 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46307.97916666666</v>
+        <v>46308.97916666666</v>
       </c>
       <c r="B96">
-        <v>0</v>
+        <v>15.579</v>
       </c>
       <c r="C96">
-        <v>17.467</v>
+        <v>0</v>
       </c>
       <c r="D96">
         <v>95</v>
@@ -2480,13 +2492,13 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46307.98958333334</v>
+        <v>46308.98958333334</v>
       </c>
       <c r="B97">
-        <v>0</v>
+        <v>16.545</v>
       </c>
       <c r="C97">
-        <v>44.878</v>
+        <v>0</v>
       </c>
       <c r="D97">
         <v>96</v>
@@ -2497,13 +2509,13 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B98">
-        <v>0</v>
+        <v>9.323</v>
       </c>
       <c r="C98">
-        <v>52.203</v>
+        <v>0</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -2514,13 +2526,13 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46308.01041666666</v>
+        <v>46309.01041666666</v>
       </c>
       <c r="B99">
         <v>0</v>
       </c>
       <c r="C99">
-        <v>56.666</v>
+        <v>7.101</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -2531,13 +2543,13 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46308.02083333334</v>
+        <v>46309.02083333334</v>
       </c>
       <c r="B100">
-        <v>0</v>
+        <v>2.382</v>
       </c>
       <c r="C100">
-        <v>13.726</v>
+        <v>0</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2548,10 +2560,10 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46308.03125</v>
+        <v>46309.03125</v>
       </c>
       <c r="B101">
-        <v>0.351</v>
+        <v>0.553</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -2565,13 +2577,13 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46308.04166666666</v>
+        <v>46309.04166666666</v>
       </c>
       <c r="B102">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="C102">
-        <v>0</v>
+        <v>13.429</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -2582,13 +2594,13 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46308.05208333334</v>
+        <v>46309.05208333334</v>
       </c>
       <c r="B103">
-        <v>0</v>
+        <v>11.19</v>
       </c>
       <c r="C103">
-        <v>4.399</v>
+        <v>0</v>
       </c>
       <c r="D103">
         <v>6</v>
@@ -2599,13 +2611,13 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46308.0625</v>
+        <v>46309.0625</v>
       </c>
       <c r="B104">
-        <v>1.858</v>
+        <v>0</v>
       </c>
       <c r="C104">
-        <v>0</v>
+        <v>4.901</v>
       </c>
       <c r="D104">
         <v>7</v>
@@ -2616,10 +2628,10 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46308.07291666666</v>
+        <v>46309.07291666666</v>
       </c>
       <c r="B105">
-        <v>2.136</v>
+        <v>10.86</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -2633,13 +2645,13 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46308.08333333334</v>
+        <v>46309.08333333334</v>
       </c>
       <c r="B106">
-        <v>0</v>
+        <v>1.216</v>
       </c>
       <c r="C106">
-        <v>4.468</v>
+        <v>0</v>
       </c>
       <c r="D106">
         <v>9</v>
@@ -2650,13 +2662,13 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46308.09375</v>
+        <v>46309.09375</v>
       </c>
       <c r="B107">
         <v>0</v>
       </c>
       <c r="C107">
-        <v>0.399</v>
+        <v>4.002</v>
       </c>
       <c r="D107">
         <v>10</v>
@@ -2667,13 +2679,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46308.10416666666</v>
+        <v>46309.10416666666</v>
       </c>
       <c r="B108">
-        <v>0.289</v>
+        <v>0</v>
       </c>
       <c r="C108">
-        <v>0</v>
+        <v>13.241</v>
       </c>
       <c r="D108">
         <v>11</v>
@@ -2684,13 +2696,13 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46308.11458333334</v>
+        <v>46309.11458333334</v>
       </c>
       <c r="B109">
         <v>0</v>
       </c>
       <c r="C109">
-        <v>3.642</v>
+        <v>16.765</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -2701,13 +2713,13 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46308.125</v>
+        <v>46309.125</v>
       </c>
       <c r="B110">
         <v>0</v>
       </c>
       <c r="C110">
-        <v>0.258</v>
+        <v>13.021</v>
       </c>
       <c r="D110">
         <v>13</v>
@@ -2718,13 +2730,13 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46308.13541666666</v>
+        <v>46309.13541666666</v>
       </c>
       <c r="B111">
-        <v>6.798</v>
+        <v>0</v>
       </c>
       <c r="C111">
-        <v>0</v>
+        <v>5.827</v>
       </c>
       <c r="D111">
         <v>14</v>
@@ -2735,13 +2747,13 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46308.14583333334</v>
+        <v>46309.14583333334</v>
       </c>
       <c r="B112">
-        <v>0</v>
+        <v>3.709</v>
       </c>
       <c r="C112">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="D112">
         <v>15</v>
@@ -2752,13 +2764,13 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46308.15625</v>
+        <v>46309.15625</v>
       </c>
       <c r="B113">
-        <v>0.739</v>
+        <v>0</v>
       </c>
       <c r="C113">
-        <v>0</v>
+        <v>4.938</v>
       </c>
       <c r="D113">
         <v>16</v>
@@ -2769,13 +2781,13 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46308.16666666666</v>
+        <v>46309.16666666666</v>
       </c>
       <c r="B114">
-        <v>0</v>
+        <v>0.773</v>
       </c>
       <c r="C114">
-        <v>12.938</v>
+        <v>0</v>
       </c>
       <c r="D114">
         <v>17</v>
@@ -2786,13 +2798,13 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46308.17708333334</v>
+        <v>46309.17708333334</v>
       </c>
       <c r="B115">
         <v>0</v>
       </c>
       <c r="C115">
-        <v>4.755</v>
+        <v>1.891</v>
       </c>
       <c r="D115">
         <v>18</v>
@@ -2803,13 +2815,13 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46308.1875</v>
+        <v>46309.1875</v>
       </c>
       <c r="B116">
         <v>0</v>
       </c>
       <c r="C116">
-        <v>2.947</v>
+        <v>0.324</v>
       </c>
       <c r="D116">
         <v>19</v>
@@ -2820,13 +2832,13 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46308.19791666666</v>
+        <v>46309.19791666666</v>
       </c>
       <c r="B117">
         <v>0</v>
       </c>
       <c r="C117">
-        <v>1.212</v>
+        <v>7.461</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -2837,10 +2849,10 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46308.20833333334</v>
+        <v>46309.20833333334</v>
       </c>
       <c r="B118">
-        <v>2.321</v>
+        <v>6.507</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -2854,13 +2866,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46308.21875</v>
+        <v>46309.21875</v>
       </c>
       <c r="B119">
         <v>0</v>
       </c>
       <c r="C119">
-        <v>3.332</v>
+        <v>0.397</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -2871,13 +2883,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46308.22916666666</v>
+        <v>46309.22916666666</v>
       </c>
       <c r="B120">
         <v>0</v>
       </c>
       <c r="C120">
-        <v>12.979</v>
+        <v>2.455</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -2888,13 +2900,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46308.23958333334</v>
+        <v>46309.23958333334</v>
       </c>
       <c r="B121">
-        <v>0</v>
+        <v>5.169</v>
       </c>
       <c r="C121">
-        <v>21.126</v>
+        <v>0</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -2905,13 +2917,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46308.25</v>
+        <v>46309.25</v>
       </c>
       <c r="B122">
-        <v>0</v>
+        <v>4.592</v>
       </c>
       <c r="C122">
-        <v>20.931</v>
+        <v>0</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -2922,13 +2934,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46308.26041666666</v>
+        <v>46309.26041666666</v>
       </c>
       <c r="B123">
         <v>0</v>
       </c>
       <c r="C123">
-        <v>30.171</v>
+        <v>1.781</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -2939,13 +2951,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46308.27083333334</v>
+        <v>46309.27083333334</v>
       </c>
       <c r="B124">
         <v>0</v>
       </c>
       <c r="C124">
-        <v>20.179</v>
+        <v>0.973</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -2956,13 +2968,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46308.28125</v>
+        <v>46309.28125</v>
       </c>
       <c r="B125">
-        <v>0</v>
+        <v>0.089</v>
       </c>
       <c r="C125">
-        <v>22.334</v>
+        <v>0</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -2973,13 +2985,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46308.29166666666</v>
+        <v>46309.29166666666</v>
       </c>
       <c r="B126">
         <v>0</v>
       </c>
       <c r="C126">
-        <v>42.17</v>
+        <v>6.42</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -2990,13 +3002,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46308.30208333334</v>
+        <v>46309.30208333334</v>
       </c>
       <c r="B127">
         <v>0</v>
       </c>
       <c r="C127">
-        <v>40.354</v>
+        <v>20.596</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3007,13 +3019,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46308.3125</v>
+        <v>46309.3125</v>
       </c>
       <c r="B128">
         <v>0</v>
       </c>
       <c r="C128">
-        <v>35.58</v>
+        <v>68.239</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3024,13 +3036,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46308.32291666666</v>
+        <v>46309.32291666666</v>
       </c>
       <c r="B129">
         <v>0</v>
       </c>
       <c r="C129">
-        <v>56.221</v>
+        <v>64.032</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3041,13 +3053,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46308.33333333334</v>
+        <v>46309.33333333334</v>
       </c>
       <c r="B130">
         <v>0</v>
       </c>
       <c r="C130">
-        <v>47.666</v>
+        <v>89.249</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3058,13 +3070,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46308.34375</v>
+        <v>46309.34375</v>
       </c>
       <c r="B131">
         <v>0</v>
       </c>
       <c r="C131">
-        <v>26.563</v>
+        <v>63.26</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3075,13 +3087,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46308.35416666666</v>
+        <v>46309.35416666666</v>
       </c>
       <c r="B132">
         <v>0</v>
       </c>
       <c r="C132">
-        <v>45.978</v>
+        <v>51.333</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3092,13 +3104,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46308.36458333334</v>
+        <v>46309.36458333334</v>
       </c>
       <c r="B133">
         <v>0</v>
       </c>
       <c r="C133">
-        <v>45.673</v>
+        <v>15.149</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3109,13 +3121,13 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46308.375</v>
+        <v>46309.375</v>
       </c>
       <c r="B134">
         <v>0</v>
       </c>
       <c r="C134">
-        <v>16.499</v>
+        <v>43.528</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3126,10 +3138,10 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46308.38541666666</v>
+        <v>46309.38541666666</v>
       </c>
       <c r="B135">
-        <v>1.565</v>
+        <v>12.215</v>
       </c>
       <c r="C135">
         <v>0</v>
@@ -3143,13 +3155,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46308.39583333334</v>
+        <v>46309.39583333334</v>
       </c>
       <c r="B136">
-        <v>0.8070000000000001</v>
+        <v>0</v>
       </c>
       <c r="C136">
-        <v>0</v>
+        <v>13.791</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3160,13 +3172,13 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46308.40625</v>
+        <v>46309.40625</v>
       </c>
       <c r="B137">
-        <v>0</v>
+        <v>3.181</v>
       </c>
       <c r="C137">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3177,10 +3189,10 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46308.41666666666</v>
+        <v>46309.41666666666</v>
       </c>
       <c r="B138">
-        <v>30.067</v>
+        <v>16.409</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -3194,13 +3206,13 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46308.42708333334</v>
+        <v>46309.42708333334</v>
       </c>
       <c r="B139">
-        <v>20.258</v>
+        <v>0</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>6.93</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3211,10 +3223,10 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46308.4375</v>
+        <v>46309.4375</v>
       </c>
       <c r="B140">
-        <v>2.324</v>
+        <v>3.265</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -3228,13 +3240,13 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46308.44791666666</v>
+        <v>46309.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
       </c>
       <c r="C141">
-        <v>9.682</v>
+        <v>13.22</v>
       </c>
       <c r="D141">
         <v>44</v>
@@ -3245,13 +3257,13 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46308.45833333334</v>
+        <v>46309.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
       </c>
       <c r="C142">
-        <v>4.36</v>
+        <v>11.572</v>
       </c>
       <c r="D142">
         <v>45</v>
@@ -3262,13 +3274,13 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46308.46875</v>
+        <v>46309.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
       </c>
       <c r="C143">
-        <v>36.9</v>
+        <v>12.526</v>
       </c>
       <c r="D143">
         <v>46</v>
@@ -3279,13 +3291,13 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46308.47916666666</v>
+        <v>46309.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
       </c>
       <c r="C144">
-        <v>51.204</v>
+        <v>24.279</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -3296,13 +3308,13 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46308.48958333334</v>
+        <v>46309.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
       </c>
       <c r="C145">
-        <v>55.287</v>
+        <v>8.775</v>
       </c>
       <c r="D145">
         <v>48</v>
@@ -3313,13 +3325,13 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46308.5</v>
+        <v>46309.5</v>
       </c>
       <c r="B146">
         <v>0</v>
       </c>
       <c r="C146">
-        <v>25.074</v>
+        <v>1.403</v>
       </c>
       <c r="D146">
         <v>49</v>
@@ -3330,13 +3342,13 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46308.51041666666</v>
+        <v>46309.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
       </c>
       <c r="C147">
-        <v>1.389</v>
+        <v>12.758</v>
       </c>
       <c r="D147">
         <v>50</v>
@@ -3347,13 +3359,13 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46308.52083333334</v>
+        <v>46309.52083333334</v>
       </c>
       <c r="B148">
-        <v>2.193</v>
+        <v>0</v>
       </c>
       <c r="C148">
-        <v>0</v>
+        <v>18.097</v>
       </c>
       <c r="D148">
         <v>51</v>
@@ -3364,13 +3376,13 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46308.53125</v>
+        <v>46309.53125</v>
       </c>
       <c r="B149">
-        <v>8.349</v>
+        <v>0</v>
       </c>
       <c r="C149">
-        <v>0</v>
+        <v>1.611</v>
       </c>
       <c r="D149">
         <v>52</v>
@@ -3381,13 +3393,13 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46308.54166666666</v>
+        <v>46309.54166666666</v>
       </c>
       <c r="B150">
-        <v>4.439</v>
+        <v>0</v>
       </c>
       <c r="C150">
-        <v>0</v>
+        <v>26.253</v>
       </c>
       <c r="D150">
         <v>53</v>
@@ -3398,13 +3410,13 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46308.55208333334</v>
+        <v>46309.55208333334</v>
       </c>
       <c r="B151">
-        <v>4.571</v>
+        <v>0</v>
       </c>
       <c r="C151">
-        <v>0</v>
+        <v>18.962</v>
       </c>
       <c r="D151">
         <v>54</v>
@@ -3415,19 +3427,87 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46308.5625</v>
+        <v>46309.5625</v>
       </c>
       <c r="B152">
-        <v>9.584</v>
+        <v>0</v>
       </c>
       <c r="C152">
-        <v>0</v>
+        <v>17.686</v>
       </c>
       <c r="D152">
         <v>55</v>
       </c>
       <c r="E152" t="s">
         <v>155</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5">
+      <c r="A153" s="2">
+        <v>46309.57291666666</v>
+      </c>
+      <c r="B153">
+        <v>0</v>
+      </c>
+      <c r="C153">
+        <v>8.269</v>
+      </c>
+      <c r="D153">
+        <v>56</v>
+      </c>
+      <c r="E153" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5">
+      <c r="A154" s="2">
+        <v>46309.58333333334</v>
+      </c>
+      <c r="B154">
+        <v>5.261</v>
+      </c>
+      <c r="C154">
+        <v>0</v>
+      </c>
+      <c r="D154">
+        <v>57</v>
+      </c>
+      <c r="E154" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5">
+      <c r="A155" s="2">
+        <v>46309.59375</v>
+      </c>
+      <c r="B155">
+        <v>0</v>
+      </c>
+      <c r="C155">
+        <v>9.859</v>
+      </c>
+      <c r="D155">
+        <v>58</v>
+      </c>
+      <c r="E155" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5">
+      <c r="A156" s="2">
+        <v>46309.60416666666</v>
+      </c>
+      <c r="B156">
+        <v>0</v>
+      </c>
+      <c r="C156">
+        <v>25.536</v>
+      </c>
+      <c r="D156">
+        <v>59</v>
+      </c>
+      <c r="E156" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Unintended_Deviation.xlsx
+++ b/data_fetching/Entsoe/Unintended_Deviation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="153">
   <si>
     <t>Timestamp</t>
   </si>
@@ -31,469 +31,448 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>13.10.20261</t>
-  </si>
-  <si>
-    <t>13.10.20262</t>
-  </si>
-  <si>
-    <t>13.10.20263</t>
-  </si>
-  <si>
-    <t>13.10.20264</t>
-  </si>
-  <si>
-    <t>13.10.20265</t>
-  </si>
-  <si>
-    <t>13.10.20266</t>
-  </si>
-  <si>
-    <t>13.10.20267</t>
-  </si>
-  <si>
-    <t>13.10.20268</t>
-  </si>
-  <si>
-    <t>13.10.20269</t>
-  </si>
-  <si>
-    <t>13.10.202610</t>
-  </si>
-  <si>
-    <t>13.10.202611</t>
-  </si>
-  <si>
-    <t>13.10.202612</t>
-  </si>
-  <si>
-    <t>13.10.202613</t>
-  </si>
-  <si>
-    <t>13.10.202614</t>
-  </si>
-  <si>
-    <t>13.10.202615</t>
-  </si>
-  <si>
-    <t>13.10.202616</t>
-  </si>
-  <si>
-    <t>13.10.202617</t>
-  </si>
-  <si>
-    <t>13.10.202618</t>
-  </si>
-  <si>
-    <t>13.10.202619</t>
-  </si>
-  <si>
-    <t>13.10.202620</t>
-  </si>
-  <si>
-    <t>13.10.202621</t>
-  </si>
-  <si>
-    <t>13.10.202622</t>
-  </si>
-  <si>
-    <t>13.10.202623</t>
-  </si>
-  <si>
-    <t>13.10.202624</t>
-  </si>
-  <si>
-    <t>13.10.202625</t>
-  </si>
-  <si>
-    <t>13.10.202626</t>
-  </si>
-  <si>
-    <t>13.10.202627</t>
-  </si>
-  <si>
-    <t>13.10.202628</t>
-  </si>
-  <si>
-    <t>13.10.202629</t>
-  </si>
-  <si>
-    <t>13.10.202630</t>
-  </si>
-  <si>
-    <t>13.10.202631</t>
-  </si>
-  <si>
-    <t>13.10.202632</t>
-  </si>
-  <si>
-    <t>13.10.202633</t>
-  </si>
-  <si>
-    <t>13.10.202634</t>
-  </si>
-  <si>
-    <t>13.10.202635</t>
-  </si>
-  <si>
-    <t>13.10.202636</t>
-  </si>
-  <si>
-    <t>13.10.202637</t>
-  </si>
-  <si>
-    <t>13.10.202638</t>
-  </si>
-  <si>
-    <t>13.10.202639</t>
-  </si>
-  <si>
-    <t>13.10.202640</t>
-  </si>
-  <si>
-    <t>13.10.202641</t>
-  </si>
-  <si>
-    <t>13.10.202642</t>
-  </si>
-  <si>
-    <t>13.10.202643</t>
-  </si>
-  <si>
-    <t>13.10.202644</t>
-  </si>
-  <si>
-    <t>13.10.202645</t>
-  </si>
-  <si>
-    <t>13.10.202646</t>
-  </si>
-  <si>
-    <t>13.10.202647</t>
-  </si>
-  <si>
-    <t>13.10.202648</t>
-  </si>
-  <si>
-    <t>13.10.202649</t>
-  </si>
-  <si>
-    <t>13.10.202650</t>
-  </si>
-  <si>
-    <t>13.10.202651</t>
-  </si>
-  <si>
-    <t>13.10.202652</t>
-  </si>
-  <si>
-    <t>13.10.202653</t>
-  </si>
-  <si>
-    <t>13.10.202654</t>
-  </si>
-  <si>
-    <t>13.10.202655</t>
-  </si>
-  <si>
-    <t>13.10.202656</t>
-  </si>
-  <si>
-    <t>13.10.202657</t>
-  </si>
-  <si>
-    <t>13.10.202658</t>
-  </si>
-  <si>
-    <t>13.10.202659</t>
-  </si>
-  <si>
-    <t>13.10.202660</t>
-  </si>
-  <si>
-    <t>13.10.202661</t>
-  </si>
-  <si>
-    <t>13.10.202662</t>
-  </si>
-  <si>
-    <t>13.10.202663</t>
-  </si>
-  <si>
-    <t>13.10.202664</t>
-  </si>
-  <si>
-    <t>13.10.202665</t>
-  </si>
-  <si>
-    <t>13.10.202666</t>
-  </si>
-  <si>
-    <t>13.10.202667</t>
-  </si>
-  <si>
-    <t>13.10.202668</t>
-  </si>
-  <si>
-    <t>13.10.202669</t>
-  </si>
-  <si>
-    <t>13.10.202670</t>
-  </si>
-  <si>
-    <t>13.10.202671</t>
-  </si>
-  <si>
-    <t>13.10.202672</t>
-  </si>
-  <si>
-    <t>13.10.202673</t>
-  </si>
-  <si>
-    <t>13.10.202674</t>
-  </si>
-  <si>
-    <t>13.10.202675</t>
-  </si>
-  <si>
-    <t>13.10.202676</t>
-  </si>
-  <si>
-    <t>13.10.202677</t>
-  </si>
-  <si>
-    <t>13.10.202678</t>
-  </si>
-  <si>
-    <t>13.10.202679</t>
-  </si>
-  <si>
-    <t>13.10.202680</t>
-  </si>
-  <si>
-    <t>13.10.202681</t>
-  </si>
-  <si>
-    <t>13.10.202682</t>
-  </si>
-  <si>
-    <t>13.10.202683</t>
-  </si>
-  <si>
-    <t>13.10.202684</t>
-  </si>
-  <si>
-    <t>13.10.202685</t>
-  </si>
-  <si>
-    <t>13.10.202686</t>
-  </si>
-  <si>
-    <t>13.10.202687</t>
-  </si>
-  <si>
-    <t>13.10.202688</t>
-  </si>
-  <si>
-    <t>13.10.202689</t>
-  </si>
-  <si>
-    <t>13.10.202690</t>
-  </si>
-  <si>
-    <t>13.10.202691</t>
-  </si>
-  <si>
-    <t>13.10.202692</t>
-  </si>
-  <si>
-    <t>13.10.202693</t>
-  </si>
-  <si>
-    <t>13.10.202694</t>
-  </si>
-  <si>
-    <t>13.10.202695</t>
-  </si>
-  <si>
-    <t>13.10.202696</t>
-  </si>
-  <si>
-    <t>14.10.20261</t>
-  </si>
-  <si>
-    <t>14.10.20262</t>
-  </si>
-  <si>
-    <t>14.10.20263</t>
-  </si>
-  <si>
-    <t>14.10.20264</t>
-  </si>
-  <si>
-    <t>14.10.20265</t>
-  </si>
-  <si>
-    <t>14.10.20266</t>
-  </si>
-  <si>
-    <t>14.10.20267</t>
-  </si>
-  <si>
-    <t>14.10.20268</t>
-  </si>
-  <si>
-    <t>14.10.20269</t>
-  </si>
-  <si>
-    <t>14.10.202610</t>
-  </si>
-  <si>
-    <t>14.10.202611</t>
-  </si>
-  <si>
-    <t>14.10.202612</t>
-  </si>
-  <si>
-    <t>14.10.202613</t>
-  </si>
-  <si>
-    <t>14.10.202614</t>
-  </si>
-  <si>
-    <t>14.10.202615</t>
-  </si>
-  <si>
-    <t>14.10.202616</t>
-  </si>
-  <si>
-    <t>14.10.202617</t>
-  </si>
-  <si>
-    <t>14.10.202618</t>
-  </si>
-  <si>
-    <t>14.10.202619</t>
-  </si>
-  <si>
-    <t>14.10.202620</t>
-  </si>
-  <si>
-    <t>14.10.202621</t>
-  </si>
-  <si>
-    <t>14.10.202622</t>
-  </si>
-  <si>
-    <t>14.10.202623</t>
-  </si>
-  <si>
-    <t>14.10.202624</t>
-  </si>
-  <si>
-    <t>14.10.202625</t>
-  </si>
-  <si>
-    <t>14.10.202626</t>
-  </si>
-  <si>
-    <t>14.10.202627</t>
-  </si>
-  <si>
-    <t>14.10.202628</t>
-  </si>
-  <si>
-    <t>14.10.202629</t>
-  </si>
-  <si>
-    <t>14.10.202630</t>
-  </si>
-  <si>
-    <t>14.10.202631</t>
-  </si>
-  <si>
-    <t>14.10.202632</t>
-  </si>
-  <si>
-    <t>14.10.202633</t>
-  </si>
-  <si>
-    <t>14.10.202634</t>
-  </si>
-  <si>
-    <t>14.10.202635</t>
-  </si>
-  <si>
-    <t>14.10.202636</t>
-  </si>
-  <si>
-    <t>14.10.202637</t>
-  </si>
-  <si>
-    <t>14.10.202638</t>
-  </si>
-  <si>
-    <t>14.10.202639</t>
-  </si>
-  <si>
-    <t>14.10.202640</t>
-  </si>
-  <si>
-    <t>14.10.202641</t>
-  </si>
-  <si>
-    <t>14.10.202642</t>
-  </si>
-  <si>
-    <t>14.10.202643</t>
-  </si>
-  <si>
-    <t>14.10.202644</t>
-  </si>
-  <si>
-    <t>14.10.202645</t>
-  </si>
-  <si>
-    <t>14.10.202646</t>
-  </si>
-  <si>
-    <t>14.10.202647</t>
-  </si>
-  <si>
-    <t>14.10.202648</t>
-  </si>
-  <si>
-    <t>14.10.202649</t>
-  </si>
-  <si>
-    <t>14.10.202650</t>
-  </si>
-  <si>
-    <t>14.10.202651</t>
-  </si>
-  <si>
-    <t>14.10.202652</t>
-  </si>
-  <si>
-    <t>14.10.202653</t>
-  </si>
-  <si>
-    <t>14.10.202654</t>
-  </si>
-  <si>
-    <t>14.10.202655</t>
-  </si>
-  <si>
-    <t>14.10.202656</t>
-  </si>
-  <si>
-    <t>14.10.202657</t>
-  </si>
-  <si>
-    <t>14.10.202658</t>
-  </si>
-  <si>
-    <t>14.10.202659</t>
+    <t>15.10.20261</t>
+  </si>
+  <si>
+    <t>15.10.20262</t>
+  </si>
+  <si>
+    <t>15.10.20263</t>
+  </si>
+  <si>
+    <t>15.10.20264</t>
+  </si>
+  <si>
+    <t>15.10.20265</t>
+  </si>
+  <si>
+    <t>15.10.20266</t>
+  </si>
+  <si>
+    <t>15.10.20267</t>
+  </si>
+  <si>
+    <t>15.10.20268</t>
+  </si>
+  <si>
+    <t>15.10.20269</t>
+  </si>
+  <si>
+    <t>15.10.202610</t>
+  </si>
+  <si>
+    <t>15.10.202611</t>
+  </si>
+  <si>
+    <t>15.10.202612</t>
+  </si>
+  <si>
+    <t>15.10.202613</t>
+  </si>
+  <si>
+    <t>15.10.202614</t>
+  </si>
+  <si>
+    <t>15.10.202615</t>
+  </si>
+  <si>
+    <t>15.10.202616</t>
+  </si>
+  <si>
+    <t>15.10.202617</t>
+  </si>
+  <si>
+    <t>15.10.202618</t>
+  </si>
+  <si>
+    <t>15.10.202619</t>
+  </si>
+  <si>
+    <t>15.10.202620</t>
+  </si>
+  <si>
+    <t>15.10.202621</t>
+  </si>
+  <si>
+    <t>15.10.202622</t>
+  </si>
+  <si>
+    <t>15.10.202623</t>
+  </si>
+  <si>
+    <t>15.10.202624</t>
+  </si>
+  <si>
+    <t>15.10.202625</t>
+  </si>
+  <si>
+    <t>15.10.202626</t>
+  </si>
+  <si>
+    <t>15.10.202627</t>
+  </si>
+  <si>
+    <t>15.10.202628</t>
+  </si>
+  <si>
+    <t>15.10.202629</t>
+  </si>
+  <si>
+    <t>15.10.202630</t>
+  </si>
+  <si>
+    <t>15.10.202631</t>
+  </si>
+  <si>
+    <t>15.10.202632</t>
+  </si>
+  <si>
+    <t>15.10.202633</t>
+  </si>
+  <si>
+    <t>15.10.202634</t>
+  </si>
+  <si>
+    <t>15.10.202635</t>
+  </si>
+  <si>
+    <t>15.10.202636</t>
+  </si>
+  <si>
+    <t>15.10.202637</t>
+  </si>
+  <si>
+    <t>15.10.202638</t>
+  </si>
+  <si>
+    <t>15.10.202639</t>
+  </si>
+  <si>
+    <t>15.10.202640</t>
+  </si>
+  <si>
+    <t>15.10.202641</t>
+  </si>
+  <si>
+    <t>15.10.202642</t>
+  </si>
+  <si>
+    <t>15.10.202643</t>
+  </si>
+  <si>
+    <t>15.10.202644</t>
+  </si>
+  <si>
+    <t>15.10.202645</t>
+  </si>
+  <si>
+    <t>15.10.202646</t>
+  </si>
+  <si>
+    <t>15.10.202647</t>
+  </si>
+  <si>
+    <t>15.10.202648</t>
+  </si>
+  <si>
+    <t>15.10.202649</t>
+  </si>
+  <si>
+    <t>15.10.202650</t>
+  </si>
+  <si>
+    <t>15.10.202651</t>
+  </si>
+  <si>
+    <t>15.10.202652</t>
+  </si>
+  <si>
+    <t>15.10.202653</t>
+  </si>
+  <si>
+    <t>15.10.202654</t>
+  </si>
+  <si>
+    <t>15.10.202655</t>
+  </si>
+  <si>
+    <t>15.10.202656</t>
+  </si>
+  <si>
+    <t>15.10.202657</t>
+  </si>
+  <si>
+    <t>15.10.202658</t>
+  </si>
+  <si>
+    <t>15.10.202659</t>
+  </si>
+  <si>
+    <t>15.10.202660</t>
+  </si>
+  <si>
+    <t>15.10.202661</t>
+  </si>
+  <si>
+    <t>15.10.202662</t>
+  </si>
+  <si>
+    <t>15.10.202663</t>
+  </si>
+  <si>
+    <t>15.10.202664</t>
+  </si>
+  <si>
+    <t>15.10.202665</t>
+  </si>
+  <si>
+    <t>15.10.202666</t>
+  </si>
+  <si>
+    <t>15.10.202667</t>
+  </si>
+  <si>
+    <t>15.10.202668</t>
+  </si>
+  <si>
+    <t>15.10.202669</t>
+  </si>
+  <si>
+    <t>15.10.202670</t>
+  </si>
+  <si>
+    <t>15.10.202671</t>
+  </si>
+  <si>
+    <t>15.10.202672</t>
+  </si>
+  <si>
+    <t>15.10.202673</t>
+  </si>
+  <si>
+    <t>15.10.202674</t>
+  </si>
+  <si>
+    <t>15.10.202675</t>
+  </si>
+  <si>
+    <t>15.10.202676</t>
+  </si>
+  <si>
+    <t>15.10.202677</t>
+  </si>
+  <si>
+    <t>15.10.202678</t>
+  </si>
+  <si>
+    <t>15.10.202679</t>
+  </si>
+  <si>
+    <t>15.10.202680</t>
+  </si>
+  <si>
+    <t>15.10.202681</t>
+  </si>
+  <si>
+    <t>15.10.202682</t>
+  </si>
+  <si>
+    <t>15.10.202683</t>
+  </si>
+  <si>
+    <t>15.10.202684</t>
+  </si>
+  <si>
+    <t>15.10.202685</t>
+  </si>
+  <si>
+    <t>15.10.202686</t>
+  </si>
+  <si>
+    <t>15.10.202687</t>
+  </si>
+  <si>
+    <t>15.10.202688</t>
+  </si>
+  <si>
+    <t>15.10.202689</t>
+  </si>
+  <si>
+    <t>15.10.202690</t>
+  </si>
+  <si>
+    <t>15.10.202691</t>
+  </si>
+  <si>
+    <t>15.10.202692</t>
+  </si>
+  <si>
+    <t>15.10.202693</t>
+  </si>
+  <si>
+    <t>15.10.202694</t>
+  </si>
+  <si>
+    <t>15.10.202695</t>
+  </si>
+  <si>
+    <t>15.10.202696</t>
+  </si>
+  <si>
+    <t>16.10.20261</t>
+  </si>
+  <si>
+    <t>16.10.20262</t>
+  </si>
+  <si>
+    <t>16.10.20263</t>
+  </si>
+  <si>
+    <t>16.10.20264</t>
+  </si>
+  <si>
+    <t>16.10.20265</t>
+  </si>
+  <si>
+    <t>16.10.20266</t>
+  </si>
+  <si>
+    <t>16.10.20267</t>
+  </si>
+  <si>
+    <t>16.10.20268</t>
+  </si>
+  <si>
+    <t>16.10.20269</t>
+  </si>
+  <si>
+    <t>16.10.202610</t>
+  </si>
+  <si>
+    <t>16.10.202611</t>
+  </si>
+  <si>
+    <t>16.10.202612</t>
+  </si>
+  <si>
+    <t>16.10.202613</t>
+  </si>
+  <si>
+    <t>16.10.202614</t>
+  </si>
+  <si>
+    <t>16.10.202615</t>
+  </si>
+  <si>
+    <t>16.10.202616</t>
+  </si>
+  <si>
+    <t>16.10.202617</t>
+  </si>
+  <si>
+    <t>16.10.202618</t>
+  </si>
+  <si>
+    <t>16.10.202619</t>
+  </si>
+  <si>
+    <t>16.10.202620</t>
+  </si>
+  <si>
+    <t>16.10.202621</t>
+  </si>
+  <si>
+    <t>16.10.202622</t>
+  </si>
+  <si>
+    <t>16.10.202623</t>
+  </si>
+  <si>
+    <t>16.10.202624</t>
+  </si>
+  <si>
+    <t>16.10.202625</t>
+  </si>
+  <si>
+    <t>16.10.202626</t>
+  </si>
+  <si>
+    <t>16.10.202627</t>
+  </si>
+  <si>
+    <t>16.10.202628</t>
+  </si>
+  <si>
+    <t>16.10.202629</t>
+  </si>
+  <si>
+    <t>16.10.202630</t>
+  </si>
+  <si>
+    <t>16.10.202631</t>
+  </si>
+  <si>
+    <t>16.10.202632</t>
+  </si>
+  <si>
+    <t>16.10.202633</t>
+  </si>
+  <si>
+    <t>16.10.202634</t>
+  </si>
+  <si>
+    <t>16.10.202635</t>
+  </si>
+  <si>
+    <t>16.10.202636</t>
+  </si>
+  <si>
+    <t>16.10.202637</t>
+  </si>
+  <si>
+    <t>16.10.202638</t>
+  </si>
+  <si>
+    <t>16.10.202639</t>
+  </si>
+  <si>
+    <t>16.10.202640</t>
+  </si>
+  <si>
+    <t>16.10.202641</t>
+  </si>
+  <si>
+    <t>16.10.202642</t>
+  </si>
+  <si>
+    <t>16.10.202643</t>
+  </si>
+  <si>
+    <t>16.10.202644</t>
+  </si>
+  <si>
+    <t>16.10.202645</t>
+  </si>
+  <si>
+    <t>16.10.202646</t>
+  </si>
+  <si>
+    <t>16.10.202647</t>
+  </si>
+  <si>
+    <t>16.10.202648</t>
+  </si>
+  <si>
+    <t>16.10.202649</t>
+  </si>
+  <si>
+    <t>16.10.202650</t>
+  </si>
+  <si>
+    <t>16.10.202651</t>
+  </si>
+  <si>
+    <t>16.10.202652</t>
   </si>
 </sst>
 </file>
@@ -855,7 +834,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E156"/>
+  <dimension ref="A1:E149"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -877,13 +856,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>52.203</v>
+        <v>2.128</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -894,13 +873,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46308.01041666666</v>
+        <v>46310.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3">
-        <v>56.666</v>
+        <v>0.356</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -911,13 +890,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46308.02083333334</v>
+        <v>46310.02083333334</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="C4">
-        <v>13.726</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -928,10 +907,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46308.03125</v>
+        <v>46310.03125</v>
       </c>
       <c r="B5">
-        <v>0.351</v>
+        <v>4.163</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -945,13 +924,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46308.04166666666</v>
+        <v>46310.04166666666</v>
       </c>
       <c r="B6">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>6.935</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -962,13 +941,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46308.05208333334</v>
+        <v>46310.05208333334</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="C7">
-        <v>4.399</v>
+        <v>0</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -979,13 +958,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46308.0625</v>
+        <v>46310.0625</v>
       </c>
       <c r="B8">
-        <v>1.858</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>20.863</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -996,13 +975,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46308.07291666666</v>
+        <v>46310.07291666666</v>
       </c>
       <c r="B9">
-        <v>2.136</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>24.981</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -1013,13 +992,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46308.08333333334</v>
+        <v>46310.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="C10">
-        <v>4.468</v>
+        <v>26.959</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -1030,13 +1009,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46308.09375</v>
+        <v>46310.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
       <c r="C11">
-        <v>0.399</v>
+        <v>7.623</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1047,10 +1026,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46308.10416666666</v>
+        <v>46310.10416666666</v>
       </c>
       <c r="B12">
-        <v>0.289</v>
+        <v>1.493</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1064,13 +1043,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46308.11458333334</v>
+        <v>46310.11458333334</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>9.102</v>
       </c>
       <c r="C13">
-        <v>3.642</v>
+        <v>0</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -1081,13 +1060,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46308.125</v>
+        <v>46310.125</v>
       </c>
       <c r="B14">
         <v>0</v>
       </c>
       <c r="C14">
-        <v>0.258</v>
+        <v>9.996</v>
       </c>
       <c r="D14">
         <v>13</v>
@@ -1098,13 +1077,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46308.13541666666</v>
+        <v>46310.13541666666</v>
       </c>
       <c r="B15">
-        <v>6.798</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>8.052</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -1115,13 +1094,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46308.14583333334</v>
+        <v>46310.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
       <c r="C16">
-        <v>3.6</v>
+        <v>45.465</v>
       </c>
       <c r="D16">
         <v>15</v>
@@ -1132,13 +1111,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46308.15625</v>
+        <v>46310.15625</v>
       </c>
       <c r="B17">
-        <v>0.739</v>
+        <v>0</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>57.276</v>
       </c>
       <c r="D17">
         <v>16</v>
@@ -1149,13 +1128,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46308.16666666666</v>
+        <v>46310.16666666666</v>
       </c>
       <c r="B18">
         <v>0</v>
       </c>
       <c r="C18">
-        <v>12.938</v>
+        <v>73.40300000000001</v>
       </c>
       <c r="D18">
         <v>17</v>
@@ -1166,13 +1145,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46308.17708333334</v>
+        <v>46310.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
       </c>
       <c r="C19">
-        <v>4.755</v>
+        <v>37.355</v>
       </c>
       <c r="D19">
         <v>18</v>
@@ -1183,13 +1162,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46308.1875</v>
+        <v>46310.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
       </c>
       <c r="C20">
-        <v>2.947</v>
+        <v>27.617</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1200,13 +1179,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46308.19791666666</v>
+        <v>46310.19791666666</v>
       </c>
       <c r="B21">
         <v>0</v>
       </c>
       <c r="C21">
-        <v>1.212</v>
+        <v>0.352</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1217,10 +1196,10 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46308.20833333334</v>
+        <v>46310.20833333334</v>
       </c>
       <c r="B22">
-        <v>2.321</v>
+        <v>0.988</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1234,13 +1213,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46308.21875</v>
+        <v>46310.21875</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>4.352</v>
       </c>
       <c r="C23">
-        <v>3.332</v>
+        <v>0</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1251,13 +1230,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46308.22916666666</v>
+        <v>46310.22916666666</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>10.114</v>
       </c>
       <c r="C24">
-        <v>12.979</v>
+        <v>0</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1268,13 +1247,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46308.23958333334</v>
+        <v>46310.23958333334</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>5.071</v>
       </c>
       <c r="C25">
-        <v>21.126</v>
+        <v>0</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1285,13 +1264,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46308.25</v>
+        <v>46310.25</v>
       </c>
       <c r="B26">
         <v>0</v>
       </c>
       <c r="C26">
-        <v>20.931</v>
+        <v>12.704</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1302,13 +1281,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46308.26041666666</v>
+        <v>46310.26041666666</v>
       </c>
       <c r="B27">
         <v>0</v>
       </c>
       <c r="C27">
-        <v>30.171</v>
+        <v>0.201</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1319,13 +1298,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46308.27083333334</v>
+        <v>46310.27083333334</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>0.409</v>
       </c>
       <c r="C28">
-        <v>20.179</v>
+        <v>0</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1336,13 +1315,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46308.28125</v>
+        <v>46310.28125</v>
       </c>
       <c r="B29">
         <v>0</v>
       </c>
       <c r="C29">
-        <v>22.334</v>
+        <v>14.538</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1353,13 +1332,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46308.29166666666</v>
+        <v>46310.29166666666</v>
       </c>
       <c r="B30">
         <v>0</v>
       </c>
       <c r="C30">
-        <v>42.17</v>
+        <v>2.777</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1370,13 +1349,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46308.30208333334</v>
+        <v>46310.30208333334</v>
       </c>
       <c r="B31">
         <v>0</v>
       </c>
       <c r="C31">
-        <v>40.354</v>
+        <v>1.284</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1387,13 +1366,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46308.3125</v>
+        <v>46310.3125</v>
       </c>
       <c r="B32">
         <v>0</v>
       </c>
       <c r="C32">
-        <v>35.58</v>
+        <v>7.604</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1404,13 +1383,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46308.32291666666</v>
+        <v>46310.32291666666</v>
       </c>
       <c r="B33">
         <v>0</v>
       </c>
       <c r="C33">
-        <v>56.221</v>
+        <v>4.907</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1421,13 +1400,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46308.33333333334</v>
+        <v>46310.33333333334</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>38.175</v>
       </c>
       <c r="C34">
-        <v>47.666</v>
+        <v>0</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1438,13 +1417,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46308.34375</v>
+        <v>46310.34375</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>28.32</v>
       </c>
       <c r="C35">
-        <v>26.563</v>
+        <v>0</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1455,13 +1434,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46308.35416666666</v>
+        <v>46310.35416666666</v>
       </c>
       <c r="B36">
         <v>0</v>
       </c>
       <c r="C36">
-        <v>45.978</v>
+        <v>5.469</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1472,13 +1451,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46308.36458333334</v>
+        <v>46310.36458333334</v>
       </c>
       <c r="B37">
         <v>0</v>
       </c>
       <c r="C37">
-        <v>45.673</v>
+        <v>84.718</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1489,13 +1468,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46308.375</v>
+        <v>46310.375</v>
       </c>
       <c r="B38">
         <v>0</v>
       </c>
       <c r="C38">
-        <v>16.499</v>
+        <v>21.523</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1506,13 +1485,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46308.38541666666</v>
+        <v>46310.38541666666</v>
       </c>
       <c r="B39">
-        <v>1.565</v>
+        <v>0</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>39.967</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1523,13 +1502,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46308.39583333334</v>
+        <v>46310.39583333334</v>
       </c>
       <c r="B40">
-        <v>0.8070000000000001</v>
+        <v>0</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>48.369</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1540,13 +1519,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46308.40625</v>
+        <v>46310.40625</v>
       </c>
       <c r="B41">
         <v>0</v>
       </c>
       <c r="C41">
-        <v>8</v>
+        <v>24.259</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1557,10 +1536,10 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46308.41666666666</v>
+        <v>46310.41666666666</v>
       </c>
       <c r="B42">
-        <v>30.067</v>
+        <v>23.09</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -1574,10 +1553,10 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46308.42708333334</v>
+        <v>46310.42708333334</v>
       </c>
       <c r="B43">
-        <v>20.258</v>
+        <v>3.54</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -1591,10 +1570,10 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46308.4375</v>
+        <v>46310.4375</v>
       </c>
       <c r="B44">
-        <v>2.324</v>
+        <v>36.457</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -1608,13 +1587,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46308.44791666666</v>
+        <v>46310.44791666666</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>24.58</v>
       </c>
       <c r="C45">
-        <v>9.682</v>
+        <v>0</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1625,13 +1604,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46308.45833333334</v>
+        <v>46310.45833333334</v>
       </c>
       <c r="B46">
         <v>0</v>
       </c>
       <c r="C46">
-        <v>4.36</v>
+        <v>19.452</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1642,13 +1621,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46308.46875</v>
+        <v>46310.46875</v>
       </c>
       <c r="B47">
         <v>0</v>
       </c>
       <c r="C47">
-        <v>36.9</v>
+        <v>73.947</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1659,13 +1638,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46308.47916666666</v>
+        <v>46310.47916666666</v>
       </c>
       <c r="B48">
         <v>0</v>
       </c>
       <c r="C48">
-        <v>51.204</v>
+        <v>82.11499999999999</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1676,13 +1655,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46308.48958333334</v>
+        <v>46310.48958333334</v>
       </c>
       <c r="B49">
         <v>0</v>
       </c>
       <c r="C49">
-        <v>55.287</v>
+        <v>100.383</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1693,13 +1672,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46308.5</v>
+        <v>46310.5</v>
       </c>
       <c r="B50">
         <v>0</v>
       </c>
       <c r="C50">
-        <v>25.074</v>
+        <v>117.97</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1710,13 +1689,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46308.51041666666</v>
+        <v>46310.51041666666</v>
       </c>
       <c r="B51">
         <v>0</v>
       </c>
       <c r="C51">
-        <v>1.389</v>
+        <v>90.91500000000001</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1727,13 +1706,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46308.52083333334</v>
+        <v>46310.52083333334</v>
       </c>
       <c r="B52">
-        <v>2.193</v>
+        <v>0</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>81.226</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1744,10 +1723,10 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46308.53125</v>
+        <v>46310.53125</v>
       </c>
       <c r="B53">
-        <v>8.349</v>
+        <v>3.207</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -1761,13 +1740,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46308.54166666666</v>
+        <v>46310.54166666666</v>
       </c>
       <c r="B54">
-        <v>4.439</v>
+        <v>0</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>50.311</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1778,13 +1757,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46308.55208333334</v>
+        <v>46310.55208333334</v>
       </c>
       <c r="B55">
-        <v>4.571</v>
+        <v>0</v>
       </c>
       <c r="C55">
-        <v>0</v>
+        <v>21.332</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1795,10 +1774,10 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46308.5625</v>
+        <v>46310.5625</v>
       </c>
       <c r="B56">
-        <v>9.584</v>
+        <v>6.435</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -1812,13 +1791,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46308.57291666666</v>
+        <v>46310.57291666666</v>
       </c>
       <c r="B57">
-        <v>39.599</v>
+        <v>0</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>1.614</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1829,13 +1808,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46308.58333333334</v>
+        <v>46310.58333333334</v>
       </c>
       <c r="B58">
-        <v>14.705</v>
+        <v>0</v>
       </c>
       <c r="C58">
-        <v>0</v>
+        <v>17.306</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1846,13 +1825,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46308.59375</v>
+        <v>46310.59375</v>
       </c>
       <c r="B59">
         <v>0</v>
       </c>
       <c r="C59">
-        <v>4.44</v>
+        <v>3.185</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1863,13 +1842,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46308.60416666666</v>
+        <v>46310.60416666666</v>
       </c>
       <c r="B60">
-        <v>12.749</v>
+        <v>0</v>
       </c>
       <c r="C60">
-        <v>0</v>
+        <v>11.519</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1880,13 +1859,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46308.61458333334</v>
+        <v>46310.61458333334</v>
       </c>
       <c r="B61">
         <v>0</v>
       </c>
       <c r="C61">
-        <v>1.426</v>
+        <v>12.44</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -1897,13 +1876,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46308.625</v>
+        <v>46310.625</v>
       </c>
       <c r="B62">
         <v>0</v>
       </c>
       <c r="C62">
-        <v>12.257</v>
+        <v>102.132</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -1914,13 +1893,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46308.63541666666</v>
+        <v>46310.63541666666</v>
       </c>
       <c r="B63">
         <v>0</v>
       </c>
       <c r="C63">
-        <v>34.849</v>
+        <v>74.789</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -1931,13 +1910,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46308.64583333334</v>
+        <v>46310.64583333334</v>
       </c>
       <c r="B64">
         <v>0</v>
       </c>
       <c r="C64">
-        <v>18.889</v>
+        <v>4.546</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -1948,10 +1927,10 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46308.65625</v>
+        <v>46310.65625</v>
       </c>
       <c r="B65">
-        <v>3.829</v>
+        <v>1.153</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -1965,13 +1944,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46308.66666666666</v>
+        <v>46310.66666666666</v>
       </c>
       <c r="B66">
         <v>0</v>
       </c>
       <c r="C66">
-        <v>42.513</v>
+        <v>67.863</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -1982,13 +1961,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46308.67708333334</v>
+        <v>46310.67708333334</v>
       </c>
       <c r="B67">
         <v>0</v>
       </c>
       <c r="C67">
-        <v>19.376</v>
+        <v>25.511</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -1999,10 +1978,10 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46308.6875</v>
+        <v>46310.6875</v>
       </c>
       <c r="B68">
-        <v>0.704</v>
+        <v>1.249</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -2016,10 +1995,10 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46308.69791666666</v>
+        <v>46310.69791666666</v>
       </c>
       <c r="B69">
-        <v>6.896</v>
+        <v>3.732</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -2033,13 +2012,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46308.70833333334</v>
+        <v>46310.70833333334</v>
       </c>
       <c r="B70">
-        <v>30.056</v>
+        <v>0</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>4.279</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2050,10 +2029,10 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46308.71875</v>
+        <v>46310.71875</v>
       </c>
       <c r="B71">
-        <v>8.423999999999999</v>
+        <v>2.091</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -2067,10 +2046,10 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46308.72916666666</v>
+        <v>46310.72916666666</v>
       </c>
       <c r="B72">
-        <v>0.439</v>
+        <v>1.341</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -2084,13 +2063,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46308.73958333334</v>
+        <v>46310.73958333334</v>
       </c>
       <c r="B73">
         <v>0</v>
       </c>
       <c r="C73">
-        <v>1.966</v>
+        <v>28.857</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2101,13 +2080,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46308.75</v>
+        <v>46310.75</v>
       </c>
       <c r="B74">
-        <v>4.635</v>
+        <v>0</v>
       </c>
       <c r="C74">
-        <v>0</v>
+        <v>3.883</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2118,13 +2097,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46308.76041666666</v>
+        <v>46310.76041666666</v>
       </c>
       <c r="B75">
         <v>0</v>
       </c>
       <c r="C75">
-        <v>4.672</v>
+        <v>17.422</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2135,13 +2114,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46308.77083333334</v>
+        <v>46310.77083333334</v>
       </c>
       <c r="B76">
         <v>0</v>
       </c>
       <c r="C76">
-        <v>18.316</v>
+        <v>19.232</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2152,13 +2131,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46308.78125</v>
+        <v>46310.78125</v>
       </c>
       <c r="B77">
         <v>0</v>
       </c>
       <c r="C77">
-        <v>1.806</v>
+        <v>19.015</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2169,13 +2148,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46308.79166666666</v>
+        <v>46310.79166666666</v>
       </c>
       <c r="B78">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="C78">
-        <v>0.239</v>
+        <v>0</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2186,13 +2165,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46308.80208333334</v>
+        <v>46310.80208333334</v>
       </c>
       <c r="B79">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="C79">
-        <v>8.91</v>
+        <v>0</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2203,13 +2182,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46308.8125</v>
+        <v>46310.8125</v>
       </c>
       <c r="B80">
         <v>0</v>
       </c>
       <c r="C80">
-        <v>16.24</v>
+        <v>1.71</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2220,13 +2199,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46308.82291666666</v>
+        <v>46310.82291666666</v>
       </c>
       <c r="B81">
         <v>0</v>
       </c>
       <c r="C81">
-        <v>4.147</v>
+        <v>7.554</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2237,13 +2216,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46308.83333333334</v>
+        <v>46310.83333333334</v>
       </c>
       <c r="B82">
-        <v>0.597</v>
+        <v>0</v>
       </c>
       <c r="C82">
-        <v>0</v>
+        <v>11.572</v>
       </c>
       <c r="D82">
         <v>81</v>
@@ -2254,13 +2233,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46308.84375</v>
+        <v>46310.84375</v>
       </c>
       <c r="B83">
-        <v>3.857</v>
+        <v>0</v>
       </c>
       <c r="C83">
-        <v>0</v>
+        <v>12.08</v>
       </c>
       <c r="D83">
         <v>82</v>
@@ -2271,13 +2250,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46308.85416666666</v>
+        <v>46310.85416666666</v>
       </c>
       <c r="B84">
         <v>0</v>
       </c>
       <c r="C84">
-        <v>3.876</v>
+        <v>12.366</v>
       </c>
       <c r="D84">
         <v>83</v>
@@ -2288,13 +2267,13 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46308.86458333334</v>
+        <v>46310.86458333334</v>
       </c>
       <c r="B85">
         <v>0</v>
       </c>
       <c r="C85">
-        <v>2.67</v>
+        <v>10.285</v>
       </c>
       <c r="D85">
         <v>84</v>
@@ -2305,13 +2284,13 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46308.875</v>
+        <v>46310.875</v>
       </c>
       <c r="B86">
-        <v>0</v>
+        <v>0.884</v>
       </c>
       <c r="C86">
-        <v>0.169</v>
+        <v>0</v>
       </c>
       <c r="D86">
         <v>85</v>
@@ -2322,13 +2301,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46308.88541666666</v>
+        <v>46310.88541666666</v>
       </c>
       <c r="B87">
-        <v>7.099</v>
+        <v>0</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>8.755000000000001</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -2339,13 +2318,13 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46308.89583333334</v>
+        <v>46310.89583333334</v>
       </c>
       <c r="B88">
-        <v>0.778</v>
+        <v>0</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>4.896</v>
       </c>
       <c r="D88">
         <v>87</v>
@@ -2356,13 +2335,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46308.90625</v>
+        <v>46310.90625</v>
       </c>
       <c r="B89">
-        <v>1.714</v>
+        <v>0</v>
       </c>
       <c r="C89">
-        <v>0</v>
+        <v>2.672</v>
       </c>
       <c r="D89">
         <v>88</v>
@@ -2373,13 +2352,13 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46308.91666666666</v>
+        <v>46310.91666666666</v>
       </c>
       <c r="B90">
-        <v>27.533</v>
+        <v>0</v>
       </c>
       <c r="C90">
-        <v>0</v>
+        <v>1.791</v>
       </c>
       <c r="D90">
         <v>89</v>
@@ -2390,13 +2369,13 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46308.92708333334</v>
+        <v>46310.92708333334</v>
       </c>
       <c r="B91">
-        <v>14.588</v>
+        <v>0</v>
       </c>
       <c r="C91">
-        <v>0</v>
+        <v>10.493</v>
       </c>
       <c r="D91">
         <v>90</v>
@@ -2407,13 +2386,13 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46308.9375</v>
+        <v>46310.9375</v>
       </c>
       <c r="B92">
-        <v>19.153</v>
+        <v>0</v>
       </c>
       <c r="C92">
-        <v>0</v>
+        <v>10.442</v>
       </c>
       <c r="D92">
         <v>91</v>
@@ -2424,13 +2403,13 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46308.94791666666</v>
+        <v>46310.94791666666</v>
       </c>
       <c r="B93">
-        <v>25.217</v>
+        <v>0</v>
       </c>
       <c r="C93">
-        <v>0</v>
+        <v>13.611</v>
       </c>
       <c r="D93">
         <v>92</v>
@@ -2441,13 +2420,13 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46308.95833333334</v>
+        <v>46310.95833333334</v>
       </c>
       <c r="B94">
-        <v>15.016</v>
+        <v>0</v>
       </c>
       <c r="C94">
-        <v>0</v>
+        <v>27.883</v>
       </c>
       <c r="D94">
         <v>93</v>
@@ -2458,13 +2437,13 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46308.96875</v>
+        <v>46310.96875</v>
       </c>
       <c r="B95">
-        <v>20.487</v>
+        <v>0</v>
       </c>
       <c r="C95">
-        <v>0</v>
+        <v>48.913</v>
       </c>
       <c r="D95">
         <v>94</v>
@@ -2475,13 +2454,13 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46308.97916666666</v>
+        <v>46310.97916666666</v>
       </c>
       <c r="B96">
-        <v>15.579</v>
+        <v>0</v>
       </c>
       <c r="C96">
-        <v>0</v>
+        <v>67.48099999999999</v>
       </c>
       <c r="D96">
         <v>95</v>
@@ -2492,13 +2471,13 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46308.98958333334</v>
+        <v>46310.98958333334</v>
       </c>
       <c r="B97">
-        <v>16.545</v>
+        <v>0</v>
       </c>
       <c r="C97">
-        <v>0</v>
+        <v>69.908</v>
       </c>
       <c r="D97">
         <v>96</v>
@@ -2509,13 +2488,13 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="B98">
-        <v>9.323</v>
+        <v>0</v>
       </c>
       <c r="C98">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -2526,13 +2505,13 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46309.01041666666</v>
+        <v>46311.01041666666</v>
       </c>
       <c r="B99">
-        <v>0</v>
+        <v>2.078</v>
       </c>
       <c r="C99">
-        <v>7.101</v>
+        <v>0</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -2543,10 +2522,10 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46309.02083333334</v>
+        <v>46311.02083333334</v>
       </c>
       <c r="B100">
-        <v>2.382</v>
+        <v>7.16</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -2560,13 +2539,13 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46309.03125</v>
+        <v>46311.03125</v>
       </c>
       <c r="B101">
-        <v>0.553</v>
+        <v>0</v>
       </c>
       <c r="C101">
-        <v>0</v>
+        <v>19.13</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -2577,13 +2556,13 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46309.04166666666</v>
+        <v>46311.04166666666</v>
       </c>
       <c r="B102">
         <v>0</v>
       </c>
       <c r="C102">
-        <v>13.429</v>
+        <v>14.824</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -2594,13 +2573,13 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46309.05208333334</v>
+        <v>46311.05208333334</v>
       </c>
       <c r="B103">
-        <v>11.19</v>
+        <v>0</v>
       </c>
       <c r="C103">
-        <v>0</v>
+        <v>19.408</v>
       </c>
       <c r="D103">
         <v>6</v>
@@ -2611,13 +2590,13 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46309.0625</v>
+        <v>46311.0625</v>
       </c>
       <c r="B104">
         <v>0</v>
       </c>
       <c r="C104">
-        <v>4.901</v>
+        <v>50.849</v>
       </c>
       <c r="D104">
         <v>7</v>
@@ -2628,13 +2607,13 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46309.07291666666</v>
+        <v>46311.07291666666</v>
       </c>
       <c r="B105">
-        <v>10.86</v>
+        <v>0</v>
       </c>
       <c r="C105">
-        <v>0</v>
+        <v>58.876</v>
       </c>
       <c r="D105">
         <v>8</v>
@@ -2645,13 +2624,13 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46309.08333333334</v>
+        <v>46311.08333333334</v>
       </c>
       <c r="B106">
-        <v>1.216</v>
+        <v>0</v>
       </c>
       <c r="C106">
-        <v>0</v>
+        <v>61.243</v>
       </c>
       <c r="D106">
         <v>9</v>
@@ -2662,13 +2641,13 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46309.09375</v>
+        <v>46311.09375</v>
       </c>
       <c r="B107">
         <v>0</v>
       </c>
       <c r="C107">
-        <v>4.002</v>
+        <v>38.248</v>
       </c>
       <c r="D107">
         <v>10</v>
@@ -2679,13 +2658,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46309.10416666666</v>
+        <v>46311.10416666666</v>
       </c>
       <c r="B108">
         <v>0</v>
       </c>
       <c r="C108">
-        <v>13.241</v>
+        <v>23.273</v>
       </c>
       <c r="D108">
         <v>11</v>
@@ -2696,13 +2675,13 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46309.11458333334</v>
+        <v>46311.11458333334</v>
       </c>
       <c r="B109">
         <v>0</v>
       </c>
       <c r="C109">
-        <v>16.765</v>
+        <v>17.911</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -2713,13 +2692,13 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46309.125</v>
+        <v>46311.125</v>
       </c>
       <c r="B110">
         <v>0</v>
       </c>
       <c r="C110">
-        <v>13.021</v>
+        <v>3.485</v>
       </c>
       <c r="D110">
         <v>13</v>
@@ -2730,13 +2709,13 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46309.13541666666</v>
+        <v>46311.13541666666</v>
       </c>
       <c r="B111">
         <v>0</v>
       </c>
       <c r="C111">
-        <v>5.827</v>
+        <v>1.05</v>
       </c>
       <c r="D111">
         <v>14</v>
@@ -2747,13 +2726,13 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46309.14583333334</v>
+        <v>46311.14583333334</v>
       </c>
       <c r="B112">
-        <v>3.709</v>
+        <v>0</v>
       </c>
       <c r="C112">
-        <v>0</v>
+        <v>5.218</v>
       </c>
       <c r="D112">
         <v>15</v>
@@ -2764,13 +2743,13 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46309.15625</v>
+        <v>46311.15625</v>
       </c>
       <c r="B113">
         <v>0</v>
       </c>
       <c r="C113">
-        <v>4.938</v>
+        <v>3.726</v>
       </c>
       <c r="D113">
         <v>16</v>
@@ -2781,13 +2760,13 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46309.16666666666</v>
+        <v>46311.16666666666</v>
       </c>
       <c r="B114">
-        <v>0.773</v>
+        <v>0</v>
       </c>
       <c r="C114">
-        <v>0</v>
+        <v>21.998</v>
       </c>
       <c r="D114">
         <v>17</v>
@@ -2798,13 +2777,13 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46309.17708333334</v>
+        <v>46311.17708333334</v>
       </c>
       <c r="B115">
         <v>0</v>
       </c>
       <c r="C115">
-        <v>1.891</v>
+        <v>15.091</v>
       </c>
       <c r="D115">
         <v>18</v>
@@ -2815,13 +2794,13 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46309.1875</v>
+        <v>46311.1875</v>
       </c>
       <c r="B116">
         <v>0</v>
       </c>
       <c r="C116">
-        <v>0.324</v>
+        <v>17.98</v>
       </c>
       <c r="D116">
         <v>19</v>
@@ -2832,13 +2811,13 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46309.19791666666</v>
+        <v>46311.19791666666</v>
       </c>
       <c r="B117">
         <v>0</v>
       </c>
       <c r="C117">
-        <v>7.461</v>
+        <v>22.354</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -2849,13 +2828,13 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46309.20833333334</v>
+        <v>46311.20833333334</v>
       </c>
       <c r="B118">
-        <v>6.507</v>
+        <v>0</v>
       </c>
       <c r="C118">
-        <v>0</v>
+        <v>14.426</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -2866,13 +2845,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46309.21875</v>
+        <v>46311.21875</v>
       </c>
       <c r="B119">
         <v>0</v>
       </c>
       <c r="C119">
-        <v>0.397</v>
+        <v>17.198</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -2883,13 +2862,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46309.22916666666</v>
+        <v>46311.22916666666</v>
       </c>
       <c r="B120">
         <v>0</v>
       </c>
       <c r="C120">
-        <v>2.455</v>
+        <v>29.306</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -2900,13 +2879,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46309.23958333334</v>
+        <v>46311.23958333334</v>
       </c>
       <c r="B121">
-        <v>5.169</v>
+        <v>0</v>
       </c>
       <c r="C121">
-        <v>0</v>
+        <v>26.822</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -2917,13 +2896,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46309.25</v>
+        <v>46311.25</v>
       </c>
       <c r="B122">
-        <v>4.592</v>
+        <v>0</v>
       </c>
       <c r="C122">
-        <v>0</v>
+        <v>47.562</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -2934,13 +2913,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46309.26041666666</v>
+        <v>46311.26041666666</v>
       </c>
       <c r="B123">
         <v>0</v>
       </c>
       <c r="C123">
-        <v>1.781</v>
+        <v>45.549</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -2951,13 +2930,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46309.27083333334</v>
+        <v>46311.27083333334</v>
       </c>
       <c r="B124">
         <v>0</v>
       </c>
       <c r="C124">
-        <v>0.973</v>
+        <v>48.151</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -2968,13 +2947,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46309.28125</v>
+        <v>46311.28125</v>
       </c>
       <c r="B125">
-        <v>0.089</v>
+        <v>0</v>
       </c>
       <c r="C125">
-        <v>0</v>
+        <v>38.357</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -2985,13 +2964,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46309.29166666666</v>
+        <v>46311.29166666666</v>
       </c>
       <c r="B126">
         <v>0</v>
       </c>
       <c r="C126">
-        <v>6.42</v>
+        <v>19.174</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3002,13 +2981,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46309.30208333334</v>
+        <v>46311.30208333334</v>
       </c>
       <c r="B127">
         <v>0</v>
       </c>
       <c r="C127">
-        <v>20.596</v>
+        <v>10.373</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3019,13 +2998,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46309.3125</v>
+        <v>46311.3125</v>
       </c>
       <c r="B128">
         <v>0</v>
       </c>
       <c r="C128">
-        <v>68.239</v>
+        <v>14.853</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3036,13 +3015,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46309.32291666666</v>
+        <v>46311.32291666666</v>
       </c>
       <c r="B129">
         <v>0</v>
       </c>
       <c r="C129">
-        <v>64.032</v>
+        <v>10.907</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3053,13 +3032,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46309.33333333334</v>
+        <v>46311.33333333334</v>
       </c>
       <c r="B130">
-        <v>0</v>
+        <v>2.168</v>
       </c>
       <c r="C130">
-        <v>89.249</v>
+        <v>0</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3070,13 +3049,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46309.34375</v>
+        <v>46311.34375</v>
       </c>
       <c r="B131">
         <v>0</v>
       </c>
       <c r="C131">
-        <v>63.26</v>
+        <v>3.243</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3087,13 +3066,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46309.35416666666</v>
+        <v>46311.35416666666</v>
       </c>
       <c r="B132">
         <v>0</v>
       </c>
       <c r="C132">
-        <v>51.333</v>
+        <v>2.646</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3104,13 +3083,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46309.36458333334</v>
+        <v>46311.36458333334</v>
       </c>
       <c r="B133">
         <v>0</v>
       </c>
       <c r="C133">
-        <v>15.149</v>
+        <v>34.86</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3121,13 +3100,13 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46309.375</v>
+        <v>46311.375</v>
       </c>
       <c r="B134">
         <v>0</v>
       </c>
       <c r="C134">
-        <v>43.528</v>
+        <v>14.449</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3138,13 +3117,13 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46309.38541666666</v>
+        <v>46311.38541666666</v>
       </c>
       <c r="B135">
-        <v>12.215</v>
+        <v>0</v>
       </c>
       <c r="C135">
-        <v>0</v>
+        <v>45.214</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3155,13 +3134,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46309.39583333334</v>
+        <v>46311.39583333334</v>
       </c>
       <c r="B136">
         <v>0</v>
       </c>
       <c r="C136">
-        <v>13.791</v>
+        <v>57.997</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3172,13 +3151,13 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46309.40625</v>
+        <v>46311.40625</v>
       </c>
       <c r="B137">
-        <v>3.181</v>
+        <v>0</v>
       </c>
       <c r="C137">
-        <v>0</v>
+        <v>9.391</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3189,10 +3168,10 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46309.41666666666</v>
+        <v>46311.41666666666</v>
       </c>
       <c r="B138">
-        <v>16.409</v>
+        <v>51.307</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -3206,13 +3185,13 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46309.42708333334</v>
+        <v>46311.42708333334</v>
       </c>
       <c r="B139">
-        <v>0</v>
+        <v>0.031</v>
       </c>
       <c r="C139">
-        <v>6.93</v>
+        <v>0</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3223,13 +3202,13 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46309.4375</v>
+        <v>46311.4375</v>
       </c>
       <c r="B140">
-        <v>3.265</v>
+        <v>0</v>
       </c>
       <c r="C140">
-        <v>0</v>
+        <v>3.168</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3240,13 +3219,13 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46309.44791666666</v>
+        <v>46311.44791666666</v>
       </c>
       <c r="B141">
-        <v>0</v>
+        <v>17.875</v>
       </c>
       <c r="C141">
-        <v>13.22</v>
+        <v>0</v>
       </c>
       <c r="D141">
         <v>44</v>
@@ -3257,13 +3236,13 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46309.45833333334</v>
+        <v>46311.45833333334</v>
       </c>
       <c r="B142">
-        <v>0</v>
+        <v>16.02</v>
       </c>
       <c r="C142">
-        <v>11.572</v>
+        <v>0</v>
       </c>
       <c r="D142">
         <v>45</v>
@@ -3274,13 +3253,13 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46309.46875</v>
+        <v>46311.46875</v>
       </c>
       <c r="B143">
-        <v>0</v>
+        <v>4.897</v>
       </c>
       <c r="C143">
-        <v>12.526</v>
+        <v>0</v>
       </c>
       <c r="D143">
         <v>46</v>
@@ -3291,13 +3270,13 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46309.47916666666</v>
+        <v>46311.47916666666</v>
       </c>
       <c r="B144">
-        <v>0</v>
+        <v>5.367</v>
       </c>
       <c r="C144">
-        <v>24.279</v>
+        <v>0</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -3308,13 +3287,13 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46309.48958333334</v>
+        <v>46311.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
       </c>
       <c r="C145">
-        <v>8.775</v>
+        <v>23.791</v>
       </c>
       <c r="D145">
         <v>48</v>
@@ -3325,13 +3304,13 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46309.5</v>
+        <v>46311.5</v>
       </c>
       <c r="B146">
         <v>0</v>
       </c>
       <c r="C146">
-        <v>1.403</v>
+        <v>40.405</v>
       </c>
       <c r="D146">
         <v>49</v>
@@ -3342,13 +3321,13 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46309.51041666666</v>
+        <v>46311.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
       </c>
       <c r="C147">
-        <v>12.758</v>
+        <v>24.179</v>
       </c>
       <c r="D147">
         <v>50</v>
@@ -3359,13 +3338,13 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46309.52083333334</v>
+        <v>46311.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
       </c>
       <c r="C148">
-        <v>18.097</v>
+        <v>4.868</v>
       </c>
       <c r="D148">
         <v>51</v>
@@ -3376,138 +3355,19 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46309.53125</v>
+        <v>46311.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
       </c>
       <c r="C149">
-        <v>1.611</v>
+        <v>1.386</v>
       </c>
       <c r="D149">
         <v>52</v>
       </c>
       <c r="E149" t="s">
         <v>152</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5">
-      <c r="A150" s="2">
-        <v>46309.54166666666</v>
-      </c>
-      <c r="B150">
-        <v>0</v>
-      </c>
-      <c r="C150">
-        <v>26.253</v>
-      </c>
-      <c r="D150">
-        <v>53</v>
-      </c>
-      <c r="E150" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5">
-      <c r="A151" s="2">
-        <v>46309.55208333334</v>
-      </c>
-      <c r="B151">
-        <v>0</v>
-      </c>
-      <c r="C151">
-        <v>18.962</v>
-      </c>
-      <c r="D151">
-        <v>54</v>
-      </c>
-      <c r="E151" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5">
-      <c r="A152" s="2">
-        <v>46309.5625</v>
-      </c>
-      <c r="B152">
-        <v>0</v>
-      </c>
-      <c r="C152">
-        <v>17.686</v>
-      </c>
-      <c r="D152">
-        <v>55</v>
-      </c>
-      <c r="E152" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5">
-      <c r="A153" s="2">
-        <v>46309.57291666666</v>
-      </c>
-      <c r="B153">
-        <v>0</v>
-      </c>
-      <c r="C153">
-        <v>8.269</v>
-      </c>
-      <c r="D153">
-        <v>56</v>
-      </c>
-      <c r="E153" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5">
-      <c r="A154" s="2">
-        <v>46309.58333333334</v>
-      </c>
-      <c r="B154">
-        <v>5.261</v>
-      </c>
-      <c r="C154">
-        <v>0</v>
-      </c>
-      <c r="D154">
-        <v>57</v>
-      </c>
-      <c r="E154" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5">
-      <c r="A155" s="2">
-        <v>46309.59375</v>
-      </c>
-      <c r="B155">
-        <v>0</v>
-      </c>
-      <c r="C155">
-        <v>9.859</v>
-      </c>
-      <c r="D155">
-        <v>58</v>
-      </c>
-      <c r="E155" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5">
-      <c r="A156" s="2">
-        <v>46309.60416666666</v>
-      </c>
-      <c r="B156">
-        <v>0</v>
-      </c>
-      <c r="C156">
-        <v>25.536</v>
-      </c>
-      <c r="D156">
-        <v>59</v>
-      </c>
-      <c r="E156" t="s">
-        <v>159</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Unintended_Deviation.xlsx
+++ b/data_fetching/Entsoe/Unintended_Deviation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="130">
   <si>
     <t>Timestamp</t>
   </si>
@@ -31,448 +31,379 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>15.10.20261</t>
-  </si>
-  <si>
-    <t>15.10.20262</t>
-  </si>
-  <si>
-    <t>15.10.20263</t>
-  </si>
-  <si>
-    <t>15.10.20264</t>
-  </si>
-  <si>
-    <t>15.10.20265</t>
-  </si>
-  <si>
-    <t>15.10.20266</t>
-  </si>
-  <si>
-    <t>15.10.20267</t>
-  </si>
-  <si>
-    <t>15.10.20268</t>
-  </si>
-  <si>
-    <t>15.10.20269</t>
-  </si>
-  <si>
-    <t>15.10.202610</t>
-  </si>
-  <si>
-    <t>15.10.202611</t>
-  </si>
-  <si>
-    <t>15.10.202612</t>
-  </si>
-  <si>
-    <t>15.10.202613</t>
-  </si>
-  <si>
-    <t>15.10.202614</t>
-  </si>
-  <si>
-    <t>15.10.202615</t>
-  </si>
-  <si>
-    <t>15.10.202616</t>
-  </si>
-  <si>
-    <t>15.10.202617</t>
-  </si>
-  <si>
-    <t>15.10.202618</t>
-  </si>
-  <si>
-    <t>15.10.202619</t>
-  </si>
-  <si>
-    <t>15.10.202620</t>
-  </si>
-  <si>
-    <t>15.10.202621</t>
-  </si>
-  <si>
-    <t>15.10.202622</t>
-  </si>
-  <si>
-    <t>15.10.202623</t>
-  </si>
-  <si>
-    <t>15.10.202624</t>
-  </si>
-  <si>
-    <t>15.10.202625</t>
-  </si>
-  <si>
-    <t>15.10.202626</t>
-  </si>
-  <si>
-    <t>15.10.202627</t>
-  </si>
-  <si>
-    <t>15.10.202628</t>
-  </si>
-  <si>
-    <t>15.10.202629</t>
-  </si>
-  <si>
-    <t>15.10.202630</t>
-  </si>
-  <si>
-    <t>15.10.202631</t>
-  </si>
-  <si>
-    <t>15.10.202632</t>
-  </si>
-  <si>
-    <t>15.10.202633</t>
-  </si>
-  <si>
-    <t>15.10.202634</t>
-  </si>
-  <si>
-    <t>15.10.202635</t>
-  </si>
-  <si>
-    <t>15.10.202636</t>
-  </si>
-  <si>
-    <t>15.10.202637</t>
-  </si>
-  <si>
-    <t>15.10.202638</t>
-  </si>
-  <si>
-    <t>15.10.202639</t>
-  </si>
-  <si>
-    <t>15.10.202640</t>
-  </si>
-  <si>
-    <t>15.10.202641</t>
-  </si>
-  <si>
-    <t>15.10.202642</t>
-  </si>
-  <si>
-    <t>15.10.202643</t>
-  </si>
-  <si>
-    <t>15.10.202644</t>
-  </si>
-  <si>
-    <t>15.10.202645</t>
-  </si>
-  <si>
-    <t>15.10.202646</t>
-  </si>
-  <si>
-    <t>15.10.202647</t>
-  </si>
-  <si>
-    <t>15.10.202648</t>
-  </si>
-  <si>
-    <t>15.10.202649</t>
-  </si>
-  <si>
-    <t>15.10.202650</t>
-  </si>
-  <si>
-    <t>15.10.202651</t>
-  </si>
-  <si>
-    <t>15.10.202652</t>
-  </si>
-  <si>
-    <t>15.10.202653</t>
-  </si>
-  <si>
-    <t>15.10.202654</t>
-  </si>
-  <si>
-    <t>15.10.202655</t>
-  </si>
-  <si>
-    <t>15.10.202656</t>
-  </si>
-  <si>
-    <t>15.10.202657</t>
-  </si>
-  <si>
-    <t>15.10.202658</t>
-  </si>
-  <si>
-    <t>15.10.202659</t>
-  </si>
-  <si>
-    <t>15.10.202660</t>
-  </si>
-  <si>
-    <t>15.10.202661</t>
-  </si>
-  <si>
-    <t>15.10.202662</t>
-  </si>
-  <si>
-    <t>15.10.202663</t>
-  </si>
-  <si>
-    <t>15.10.202664</t>
-  </si>
-  <si>
-    <t>15.10.202665</t>
-  </si>
-  <si>
-    <t>15.10.202666</t>
-  </si>
-  <si>
-    <t>15.10.202667</t>
-  </si>
-  <si>
-    <t>15.10.202668</t>
-  </si>
-  <si>
-    <t>15.10.202669</t>
-  </si>
-  <si>
-    <t>15.10.202670</t>
-  </si>
-  <si>
-    <t>15.10.202671</t>
-  </si>
-  <si>
-    <t>15.10.202672</t>
-  </si>
-  <si>
-    <t>15.10.202673</t>
-  </si>
-  <si>
-    <t>15.10.202674</t>
-  </si>
-  <si>
-    <t>15.10.202675</t>
-  </si>
-  <si>
-    <t>15.10.202676</t>
-  </si>
-  <si>
-    <t>15.10.202677</t>
-  </si>
-  <si>
-    <t>15.10.202678</t>
-  </si>
-  <si>
-    <t>15.10.202679</t>
-  </si>
-  <si>
-    <t>15.10.202680</t>
-  </si>
-  <si>
-    <t>15.10.202681</t>
-  </si>
-  <si>
-    <t>15.10.202682</t>
-  </si>
-  <si>
-    <t>15.10.202683</t>
-  </si>
-  <si>
-    <t>15.10.202684</t>
-  </si>
-  <si>
-    <t>15.10.202685</t>
-  </si>
-  <si>
-    <t>15.10.202686</t>
-  </si>
-  <si>
-    <t>15.10.202687</t>
-  </si>
-  <si>
-    <t>15.10.202688</t>
-  </si>
-  <si>
-    <t>15.10.202689</t>
-  </si>
-  <si>
-    <t>15.10.202690</t>
-  </si>
-  <si>
-    <t>15.10.202691</t>
-  </si>
-  <si>
-    <t>15.10.202692</t>
-  </si>
-  <si>
-    <t>15.10.202693</t>
-  </si>
-  <si>
-    <t>15.10.202694</t>
-  </si>
-  <si>
-    <t>15.10.202695</t>
-  </si>
-  <si>
-    <t>15.10.202696</t>
-  </si>
-  <si>
-    <t>16.10.20261</t>
-  </si>
-  <si>
-    <t>16.10.20262</t>
-  </si>
-  <si>
-    <t>16.10.20263</t>
-  </si>
-  <si>
-    <t>16.10.20264</t>
-  </si>
-  <si>
-    <t>16.10.20265</t>
-  </si>
-  <si>
-    <t>16.10.20266</t>
-  </si>
-  <si>
-    <t>16.10.20267</t>
-  </si>
-  <si>
-    <t>16.10.20268</t>
-  </si>
-  <si>
-    <t>16.10.20269</t>
-  </si>
-  <si>
-    <t>16.10.202610</t>
-  </si>
-  <si>
-    <t>16.10.202611</t>
-  </si>
-  <si>
-    <t>16.10.202612</t>
-  </si>
-  <si>
-    <t>16.10.202613</t>
-  </si>
-  <si>
-    <t>16.10.202614</t>
-  </si>
-  <si>
-    <t>16.10.202615</t>
-  </si>
-  <si>
-    <t>16.10.202616</t>
-  </si>
-  <si>
-    <t>16.10.202617</t>
-  </si>
-  <si>
-    <t>16.10.202618</t>
-  </si>
-  <si>
-    <t>16.10.202619</t>
-  </si>
-  <si>
-    <t>16.10.202620</t>
-  </si>
-  <si>
-    <t>16.10.202621</t>
-  </si>
-  <si>
-    <t>16.10.202622</t>
-  </si>
-  <si>
-    <t>16.10.202623</t>
-  </si>
-  <si>
-    <t>16.10.202624</t>
-  </si>
-  <si>
-    <t>16.10.202625</t>
-  </si>
-  <si>
-    <t>16.10.202626</t>
-  </si>
-  <si>
-    <t>16.10.202627</t>
-  </si>
-  <si>
-    <t>16.10.202628</t>
-  </si>
-  <si>
-    <t>16.10.202629</t>
-  </si>
-  <si>
-    <t>16.10.202630</t>
-  </si>
-  <si>
-    <t>16.10.202631</t>
-  </si>
-  <si>
-    <t>16.10.202632</t>
-  </si>
-  <si>
-    <t>16.10.202633</t>
-  </si>
-  <si>
-    <t>16.10.202634</t>
-  </si>
-  <si>
-    <t>16.10.202635</t>
-  </si>
-  <si>
-    <t>16.10.202636</t>
-  </si>
-  <si>
-    <t>16.10.202637</t>
-  </si>
-  <si>
-    <t>16.10.202638</t>
-  </si>
-  <si>
-    <t>16.10.202639</t>
-  </si>
-  <si>
-    <t>16.10.202640</t>
-  </si>
-  <si>
-    <t>16.10.202641</t>
-  </si>
-  <si>
-    <t>16.10.202642</t>
-  </si>
-  <si>
-    <t>16.10.202643</t>
-  </si>
-  <si>
-    <t>16.10.202644</t>
-  </si>
-  <si>
-    <t>16.10.202645</t>
-  </si>
-  <si>
-    <t>16.10.202646</t>
-  </si>
-  <si>
-    <t>16.10.202647</t>
-  </si>
-  <si>
-    <t>16.10.202648</t>
-  </si>
-  <si>
-    <t>16.10.202649</t>
-  </si>
-  <si>
-    <t>16.10.202650</t>
-  </si>
-  <si>
-    <t>16.10.202651</t>
-  </si>
-  <si>
-    <t>16.10.202652</t>
+    <t>20.10.20261</t>
+  </si>
+  <si>
+    <t>20.10.20262</t>
+  </si>
+  <si>
+    <t>20.10.20263</t>
+  </si>
+  <si>
+    <t>20.10.20264</t>
+  </si>
+  <si>
+    <t>20.10.20265</t>
+  </si>
+  <si>
+    <t>20.10.20266</t>
+  </si>
+  <si>
+    <t>20.10.20267</t>
+  </si>
+  <si>
+    <t>20.10.20268</t>
+  </si>
+  <si>
+    <t>20.10.20269</t>
+  </si>
+  <si>
+    <t>20.10.202610</t>
+  </si>
+  <si>
+    <t>20.10.202611</t>
+  </si>
+  <si>
+    <t>20.10.202612</t>
+  </si>
+  <si>
+    <t>20.10.202613</t>
+  </si>
+  <si>
+    <t>20.10.202614</t>
+  </si>
+  <si>
+    <t>20.10.202615</t>
+  </si>
+  <si>
+    <t>20.10.202616</t>
+  </si>
+  <si>
+    <t>20.10.202617</t>
+  </si>
+  <si>
+    <t>20.10.202618</t>
+  </si>
+  <si>
+    <t>20.10.202619</t>
+  </si>
+  <si>
+    <t>20.10.202620</t>
+  </si>
+  <si>
+    <t>20.10.202621</t>
+  </si>
+  <si>
+    <t>20.10.202622</t>
+  </si>
+  <si>
+    <t>20.10.202623</t>
+  </si>
+  <si>
+    <t>20.10.202624</t>
+  </si>
+  <si>
+    <t>20.10.202625</t>
+  </si>
+  <si>
+    <t>20.10.202626</t>
+  </si>
+  <si>
+    <t>20.10.202627</t>
+  </si>
+  <si>
+    <t>20.10.202628</t>
+  </si>
+  <si>
+    <t>20.10.202629</t>
+  </si>
+  <si>
+    <t>20.10.202630</t>
+  </si>
+  <si>
+    <t>20.10.202631</t>
+  </si>
+  <si>
+    <t>20.10.202632</t>
+  </si>
+  <si>
+    <t>20.10.202633</t>
+  </si>
+  <si>
+    <t>20.10.202634</t>
+  </si>
+  <si>
+    <t>20.10.202635</t>
+  </si>
+  <si>
+    <t>20.10.202636</t>
+  </si>
+  <si>
+    <t>20.10.202637</t>
+  </si>
+  <si>
+    <t>20.10.202638</t>
+  </si>
+  <si>
+    <t>20.10.202639</t>
+  </si>
+  <si>
+    <t>20.10.202640</t>
+  </si>
+  <si>
+    <t>20.10.202641</t>
+  </si>
+  <si>
+    <t>20.10.202642</t>
+  </si>
+  <si>
+    <t>20.10.202643</t>
+  </si>
+  <si>
+    <t>20.10.202644</t>
+  </si>
+  <si>
+    <t>20.10.202645</t>
+  </si>
+  <si>
+    <t>20.10.202646</t>
+  </si>
+  <si>
+    <t>20.10.202647</t>
+  </si>
+  <si>
+    <t>20.10.202648</t>
+  </si>
+  <si>
+    <t>20.10.202649</t>
+  </si>
+  <si>
+    <t>20.10.202650</t>
+  </si>
+  <si>
+    <t>20.10.202651</t>
+  </si>
+  <si>
+    <t>20.10.202652</t>
+  </si>
+  <si>
+    <t>20.10.202653</t>
+  </si>
+  <si>
+    <t>20.10.202654</t>
+  </si>
+  <si>
+    <t>20.10.202655</t>
+  </si>
+  <si>
+    <t>20.10.202656</t>
+  </si>
+  <si>
+    <t>20.10.202657</t>
+  </si>
+  <si>
+    <t>20.10.202658</t>
+  </si>
+  <si>
+    <t>20.10.202659</t>
+  </si>
+  <si>
+    <t>20.10.202660</t>
+  </si>
+  <si>
+    <t>20.10.202661</t>
+  </si>
+  <si>
+    <t>20.10.202662</t>
+  </si>
+  <si>
+    <t>20.10.202663</t>
+  </si>
+  <si>
+    <t>20.10.202664</t>
+  </si>
+  <si>
+    <t>20.10.202665</t>
+  </si>
+  <si>
+    <t>20.10.202666</t>
+  </si>
+  <si>
+    <t>20.10.202667</t>
+  </si>
+  <si>
+    <t>20.10.202668</t>
+  </si>
+  <si>
+    <t>20.10.202669</t>
+  </si>
+  <si>
+    <t>20.10.202670</t>
+  </si>
+  <si>
+    <t>20.10.202671</t>
+  </si>
+  <si>
+    <t>20.10.202672</t>
+  </si>
+  <si>
+    <t>20.10.202673</t>
+  </si>
+  <si>
+    <t>20.10.202674</t>
+  </si>
+  <si>
+    <t>20.10.202675</t>
+  </si>
+  <si>
+    <t>20.10.202676</t>
+  </si>
+  <si>
+    <t>20.10.202677</t>
+  </si>
+  <si>
+    <t>20.10.202678</t>
+  </si>
+  <si>
+    <t>20.10.202679</t>
+  </si>
+  <si>
+    <t>20.10.202680</t>
+  </si>
+  <si>
+    <t>20.10.202681</t>
+  </si>
+  <si>
+    <t>20.10.202682</t>
+  </si>
+  <si>
+    <t>20.10.202683</t>
+  </si>
+  <si>
+    <t>20.10.202684</t>
+  </si>
+  <si>
+    <t>20.10.202685</t>
+  </si>
+  <si>
+    <t>20.10.202686</t>
+  </si>
+  <si>
+    <t>20.10.202687</t>
+  </si>
+  <si>
+    <t>20.10.202688</t>
+  </si>
+  <si>
+    <t>20.10.202689</t>
+  </si>
+  <si>
+    <t>21.10.202690</t>
+  </si>
+  <si>
+    <t>21.10.202691</t>
+  </si>
+  <si>
+    <t>21.10.202692</t>
+  </si>
+  <si>
+    <t>21.10.202693</t>
+  </si>
+  <si>
+    <t>21.10.202694</t>
+  </si>
+  <si>
+    <t>21.10.202695</t>
+  </si>
+  <si>
+    <t>21.10.202696</t>
+  </si>
+  <si>
+    <t>21.10.20261</t>
+  </si>
+  <si>
+    <t>21.10.20262</t>
+  </si>
+  <si>
+    <t>21.10.20263</t>
+  </si>
+  <si>
+    <t>21.10.20264</t>
+  </si>
+  <si>
+    <t>21.10.20265</t>
+  </si>
+  <si>
+    <t>21.10.20266</t>
+  </si>
+  <si>
+    <t>21.10.20267</t>
+  </si>
+  <si>
+    <t>21.10.20268</t>
+  </si>
+  <si>
+    <t>21.10.20269</t>
+  </si>
+  <si>
+    <t>21.10.202610</t>
+  </si>
+  <si>
+    <t>21.10.202611</t>
+  </si>
+  <si>
+    <t>21.10.202612</t>
+  </si>
+  <si>
+    <t>21.10.202613</t>
+  </si>
+  <si>
+    <t>21.10.202614</t>
+  </si>
+  <si>
+    <t>21.10.202615</t>
+  </si>
+  <si>
+    <t>21.10.202616</t>
+  </si>
+  <si>
+    <t>21.10.202617</t>
+  </si>
+  <si>
+    <t>21.10.202618</t>
+  </si>
+  <si>
+    <t>21.10.202619</t>
+  </si>
+  <si>
+    <t>21.10.202620</t>
+  </si>
+  <si>
+    <t>21.10.202621</t>
+  </si>
+  <si>
+    <t>21.10.202622</t>
+  </si>
+  <si>
+    <t>21.10.202623</t>
+  </si>
+  <si>
+    <t>21.10.202624</t>
+  </si>
+  <si>
+    <t>21.10.202625</t>
+  </si>
+  <si>
+    <t>21.10.202626</t>
+  </si>
+  <si>
+    <t>21.10.202627</t>
+  </si>
+  <si>
+    <t>21.10.202628</t>
+  </si>
+  <si>
+    <t>21.10.202629</t>
   </si>
 </sst>
 </file>
@@ -834,7 +765,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E149"/>
+  <dimension ref="A1:E126"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -856,13 +787,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46310</v>
+        <v>46315</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>2.128</v>
+        <v>25.853</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -873,13 +804,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46310.01041666666</v>
+        <v>46315.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.356</v>
+        <v>18.867</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -890,13 +821,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46310.02083333334</v>
+        <v>46315.02083333334</v>
       </c>
       <c r="B4">
-        <v>0.9370000000000001</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>29.959</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -907,13 +838,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46310.03125</v>
+        <v>46315.03125</v>
       </c>
       <c r="B5">
-        <v>4.163</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>8.731999999999999</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -924,13 +855,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46310.04166666666</v>
+        <v>46315.04166666666</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>13.071</v>
       </c>
       <c r="C6">
-        <v>6.935</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -941,10 +872,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46310.05208333334</v>
+        <v>46315.05208333334</v>
       </c>
       <c r="B7">
-        <v>0.72</v>
+        <v>11.253</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -958,13 +889,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46310.0625</v>
+        <v>46315.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
       <c r="C8">
-        <v>20.863</v>
+        <v>1.667</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -975,13 +906,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46310.07291666666</v>
+        <v>46315.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="C9">
-        <v>24.981</v>
+        <v>4.057</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -992,13 +923,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46310.08333333334</v>
+        <v>46315.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="C10">
-        <v>26.959</v>
+        <v>17.794</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -1009,13 +940,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46310.09375</v>
+        <v>46315.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
       <c r="C11">
-        <v>7.623</v>
+        <v>24.679</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1026,13 +957,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46310.10416666666</v>
+        <v>46315.10416666666</v>
       </c>
       <c r="B12">
-        <v>1.493</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>32.909</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -1043,13 +974,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46310.11458333334</v>
+        <v>46315.11458333334</v>
       </c>
       <c r="B13">
-        <v>9.102</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>17.648</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -1060,13 +991,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46310.125</v>
+        <v>46315.125</v>
       </c>
       <c r="B14">
         <v>0</v>
       </c>
       <c r="C14">
-        <v>9.996</v>
+        <v>26.123</v>
       </c>
       <c r="D14">
         <v>13</v>
@@ -1077,13 +1008,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46310.13541666666</v>
+        <v>46315.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
       </c>
       <c r="C15">
-        <v>8.052</v>
+        <v>27.786</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -1094,13 +1025,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46310.14583333334</v>
+        <v>46315.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
       <c r="C16">
-        <v>45.465</v>
+        <v>5.629</v>
       </c>
       <c r="D16">
         <v>15</v>
@@ -1111,13 +1042,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46310.15625</v>
+        <v>46315.15625</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>2.971</v>
       </c>
       <c r="C17">
-        <v>57.276</v>
+        <v>0</v>
       </c>
       <c r="D17">
         <v>16</v>
@@ -1128,13 +1059,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46310.16666666666</v>
+        <v>46315.16666666666</v>
       </c>
       <c r="B18">
         <v>0</v>
       </c>
       <c r="C18">
-        <v>73.40300000000001</v>
+        <v>6.218</v>
       </c>
       <c r="D18">
         <v>17</v>
@@ -1145,13 +1076,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46310.17708333334</v>
+        <v>46315.17708333334</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>6.664</v>
       </c>
       <c r="C19">
-        <v>37.355</v>
+        <v>0</v>
       </c>
       <c r="D19">
         <v>18</v>
@@ -1162,13 +1093,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46310.1875</v>
+        <v>46315.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
       </c>
       <c r="C20">
-        <v>27.617</v>
+        <v>4.066</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1179,13 +1110,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46310.19791666666</v>
+        <v>46315.19791666666</v>
       </c>
       <c r="B21">
         <v>0</v>
       </c>
       <c r="C21">
-        <v>0.352</v>
+        <v>0.884</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1196,13 +1127,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46310.20833333334</v>
+        <v>46315.20833333334</v>
       </c>
       <c r="B22">
-        <v>0.988</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>21.313</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1213,13 +1144,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46310.21875</v>
+        <v>46315.21875</v>
       </c>
       <c r="B23">
-        <v>4.352</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>15.415</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1230,13 +1161,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46310.22916666666</v>
+        <v>46315.22916666666</v>
       </c>
       <c r="B24">
-        <v>10.114</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>19.668</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1247,13 +1178,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46310.23958333334</v>
+        <v>46315.23958333334</v>
       </c>
       <c r="B25">
-        <v>5.071</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>14.49</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1264,13 +1195,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46310.25</v>
+        <v>46315.25</v>
       </c>
       <c r="B26">
         <v>0</v>
       </c>
       <c r="C26">
-        <v>12.704</v>
+        <v>11.811</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1281,13 +1212,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46310.26041666666</v>
+        <v>46315.26041666666</v>
       </c>
       <c r="B27">
         <v>0</v>
       </c>
       <c r="C27">
-        <v>0.201</v>
+        <v>23.613</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1298,13 +1229,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46310.27083333334</v>
+        <v>46315.27083333334</v>
       </c>
       <c r="B28">
-        <v>0.409</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>1.943</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1315,13 +1246,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46310.28125</v>
+        <v>46315.28125</v>
       </c>
       <c r="B29">
         <v>0</v>
       </c>
       <c r="C29">
-        <v>14.538</v>
+        <v>7.535</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1332,13 +1263,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46310.29166666666</v>
+        <v>46315.29166666666</v>
       </c>
       <c r="B30">
         <v>0</v>
       </c>
       <c r="C30">
-        <v>2.777</v>
+        <v>43.613</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1349,13 +1280,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46310.30208333334</v>
+        <v>46315.30208333334</v>
       </c>
       <c r="B31">
         <v>0</v>
       </c>
       <c r="C31">
-        <v>1.284</v>
+        <v>24.36</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1366,13 +1297,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46310.3125</v>
+        <v>46315.3125</v>
       </c>
       <c r="B32">
         <v>0</v>
       </c>
       <c r="C32">
-        <v>7.604</v>
+        <v>9.092000000000001</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1383,13 +1314,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46310.32291666666</v>
+        <v>46315.32291666666</v>
       </c>
       <c r="B33">
         <v>0</v>
       </c>
       <c r="C33">
-        <v>4.907</v>
+        <v>14.346</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1400,13 +1331,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46310.33333333334</v>
+        <v>46315.33333333334</v>
       </c>
       <c r="B34">
-        <v>38.175</v>
+        <v>0</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>11.081</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1417,13 +1348,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46310.34375</v>
+        <v>46315.34375</v>
       </c>
       <c r="B35">
-        <v>28.32</v>
+        <v>0</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>9.18</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1434,13 +1365,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46310.35416666666</v>
+        <v>46315.35416666666</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>5.574</v>
       </c>
       <c r="C36">
-        <v>5.469</v>
+        <v>0</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1451,13 +1382,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46310.36458333334</v>
+        <v>46315.36458333334</v>
       </c>
       <c r="B37">
         <v>0</v>
       </c>
       <c r="C37">
-        <v>84.718</v>
+        <v>5.254</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1468,13 +1399,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46310.375</v>
+        <v>46315.375</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="C38">
-        <v>21.523</v>
+        <v>0</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1485,13 +1416,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46310.38541666666</v>
+        <v>46315.38541666666</v>
       </c>
       <c r="B39">
         <v>0</v>
       </c>
       <c r="C39">
-        <v>39.967</v>
+        <v>9.105</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1502,13 +1433,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46310.39583333334</v>
+        <v>46315.39583333334</v>
       </c>
       <c r="B40">
         <v>0</v>
       </c>
       <c r="C40">
-        <v>48.369</v>
+        <v>20.163</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1519,13 +1450,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46310.40625</v>
+        <v>46315.40625</v>
       </c>
       <c r="B41">
         <v>0</v>
       </c>
       <c r="C41">
-        <v>24.259</v>
+        <v>64.35299999999999</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1536,13 +1467,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46310.41666666666</v>
+        <v>46315.41666666666</v>
       </c>
       <c r="B42">
-        <v>23.09</v>
+        <v>0</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>64.845</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1553,13 +1484,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46310.42708333334</v>
+        <v>46315.42708333334</v>
       </c>
       <c r="B43">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>88.642</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1570,13 +1501,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46310.4375</v>
+        <v>46315.4375</v>
       </c>
       <c r="B44">
-        <v>36.457</v>
+        <v>0</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>85.386</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1587,13 +1518,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46310.44791666666</v>
+        <v>46315.44791666666</v>
       </c>
       <c r="B45">
-        <v>24.58</v>
+        <v>0</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>103.861</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1604,13 +1535,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46310.45833333334</v>
+        <v>46315.45833333334</v>
       </c>
       <c r="B46">
         <v>0</v>
       </c>
       <c r="C46">
-        <v>19.452</v>
+        <v>80.343</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1621,13 +1552,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46310.46875</v>
+        <v>46315.46875</v>
       </c>
       <c r="B47">
         <v>0</v>
       </c>
       <c r="C47">
-        <v>73.947</v>
+        <v>52.609</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1638,13 +1569,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46310.47916666666</v>
+        <v>46315.47916666666</v>
       </c>
       <c r="B48">
         <v>0</v>
       </c>
       <c r="C48">
-        <v>82.11499999999999</v>
+        <v>119.871</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1655,13 +1586,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46310.48958333334</v>
+        <v>46315.48958333334</v>
       </c>
       <c r="B49">
         <v>0</v>
       </c>
       <c r="C49">
-        <v>100.383</v>
+        <v>115.371</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1672,13 +1603,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46310.5</v>
+        <v>46315.5</v>
       </c>
       <c r="B50">
         <v>0</v>
       </c>
       <c r="C50">
-        <v>117.97</v>
+        <v>40.496</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1689,13 +1620,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46310.51041666666</v>
+        <v>46315.51041666666</v>
       </c>
       <c r="B51">
         <v>0</v>
       </c>
       <c r="C51">
-        <v>90.91500000000001</v>
+        <v>5.9</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1706,13 +1637,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46310.52083333334</v>
+        <v>46315.52083333334</v>
       </c>
       <c r="B52">
         <v>0</v>
       </c>
       <c r="C52">
-        <v>81.226</v>
+        <v>1.711</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1723,13 +1654,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46310.53125</v>
+        <v>46315.53125</v>
       </c>
       <c r="B53">
-        <v>3.207</v>
+        <v>0</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>16.319</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1740,13 +1671,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46310.54166666666</v>
+        <v>46315.54166666666</v>
       </c>
       <c r="B54">
         <v>0</v>
       </c>
       <c r="C54">
-        <v>50.311</v>
+        <v>50.767</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1757,13 +1688,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46310.55208333334</v>
+        <v>46315.55208333334</v>
       </c>
       <c r="B55">
         <v>0</v>
       </c>
       <c r="C55">
-        <v>21.332</v>
+        <v>40.117</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1774,13 +1705,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46310.5625</v>
+        <v>46315.5625</v>
       </c>
       <c r="B56">
-        <v>6.435</v>
+        <v>0</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>24.472</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1791,13 +1722,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46310.57291666666</v>
+        <v>46315.57291666666</v>
       </c>
       <c r="B57">
         <v>0</v>
       </c>
       <c r="C57">
-        <v>1.614</v>
+        <v>18.968</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1808,13 +1739,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46310.58333333334</v>
+        <v>46315.58333333334</v>
       </c>
       <c r="B58">
         <v>0</v>
       </c>
       <c r="C58">
-        <v>17.306</v>
+        <v>47.469</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1825,13 +1756,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46310.59375</v>
+        <v>46315.59375</v>
       </c>
       <c r="B59">
         <v>0</v>
       </c>
       <c r="C59">
-        <v>3.185</v>
+        <v>22.789</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1842,13 +1773,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46310.60416666666</v>
+        <v>46315.60416666666</v>
       </c>
       <c r="B60">
         <v>0</v>
       </c>
       <c r="C60">
-        <v>11.519</v>
+        <v>3.124</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1859,13 +1790,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46310.61458333334</v>
+        <v>46315.61458333334</v>
       </c>
       <c r="B61">
         <v>0</v>
       </c>
       <c r="C61">
-        <v>12.44</v>
+        <v>5.42</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -1876,13 +1807,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46310.625</v>
+        <v>46315.625</v>
       </c>
       <c r="B62">
         <v>0</v>
       </c>
       <c r="C62">
-        <v>102.132</v>
+        <v>12.727</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -1893,13 +1824,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46310.63541666666</v>
+        <v>46315.63541666666</v>
       </c>
       <c r="B63">
         <v>0</v>
       </c>
       <c r="C63">
-        <v>74.789</v>
+        <v>5.358</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -1910,13 +1841,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46310.64583333334</v>
+        <v>46315.64583333334</v>
       </c>
       <c r="B64">
-        <v>0</v>
+        <v>1.016</v>
       </c>
       <c r="C64">
-        <v>4.546</v>
+        <v>0</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -1927,10 +1858,10 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46310.65625</v>
+        <v>46315.65625</v>
       </c>
       <c r="B65">
-        <v>1.153</v>
+        <v>0.455</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -1944,13 +1875,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46310.66666666666</v>
+        <v>46315.66666666666</v>
       </c>
       <c r="B66">
         <v>0</v>
       </c>
       <c r="C66">
-        <v>67.863</v>
+        <v>14.033</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -1961,13 +1892,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46310.67708333334</v>
+        <v>46315.67708333334</v>
       </c>
       <c r="B67">
         <v>0</v>
       </c>
       <c r="C67">
-        <v>25.511</v>
+        <v>0.784</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -1978,13 +1909,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46310.6875</v>
+        <v>46315.6875</v>
       </c>
       <c r="B68">
-        <v>1.249</v>
+        <v>0</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>0.803</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -1995,13 +1926,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46310.69791666666</v>
+        <v>46315.69791666666</v>
       </c>
       <c r="B69">
-        <v>3.732</v>
+        <v>0</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>1.436</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2012,13 +1943,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46310.70833333334</v>
+        <v>46315.70833333334</v>
       </c>
       <c r="B70">
         <v>0</v>
       </c>
       <c r="C70">
-        <v>4.279</v>
+        <v>32.592</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2029,13 +1960,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46310.71875</v>
+        <v>46315.71875</v>
       </c>
       <c r="B71">
-        <v>2.091</v>
+        <v>0</v>
       </c>
       <c r="C71">
-        <v>0</v>
+        <v>21.931</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2046,10 +1977,10 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46310.72916666666</v>
+        <v>46315.80208333334</v>
       </c>
       <c r="B72">
-        <v>1.341</v>
+        <v>0.362</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -2063,13 +1994,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46310.73958333334</v>
+        <v>46315.8125</v>
       </c>
       <c r="B73">
         <v>0</v>
       </c>
       <c r="C73">
-        <v>28.857</v>
+        <v>4.431</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2080,13 +2011,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46310.75</v>
+        <v>46315.82291666666</v>
       </c>
       <c r="B74">
-        <v>0</v>
+        <v>5.378</v>
       </c>
       <c r="C74">
-        <v>3.883</v>
+        <v>0</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2097,13 +2028,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46310.76041666666</v>
+        <v>46315.83333333334</v>
       </c>
       <c r="B75">
-        <v>0</v>
+        <v>5.561</v>
       </c>
       <c r="C75">
-        <v>17.422</v>
+        <v>0</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2114,13 +2045,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46310.77083333334</v>
+        <v>46315.84375</v>
       </c>
       <c r="B76">
         <v>0</v>
       </c>
       <c r="C76">
-        <v>19.232</v>
+        <v>14.77</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2131,13 +2062,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46310.78125</v>
+        <v>46315.85416666666</v>
       </c>
       <c r="B77">
         <v>0</v>
       </c>
       <c r="C77">
-        <v>19.015</v>
+        <v>32.764</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2148,10 +2079,10 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46310.79166666666</v>
+        <v>46315.86458333334</v>
       </c>
       <c r="B78">
-        <v>3.26</v>
+        <v>1.453</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -2165,10 +2096,10 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46310.80208333334</v>
+        <v>46315.875</v>
       </c>
       <c r="B79">
-        <v>4.95</v>
+        <v>2.886</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -2182,13 +2113,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46310.8125</v>
+        <v>46315.88541666666</v>
       </c>
       <c r="B80">
-        <v>0</v>
+        <v>1.298</v>
       </c>
       <c r="C80">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2199,13 +2130,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46310.82291666666</v>
+        <v>46315.89583333334</v>
       </c>
       <c r="B81">
-        <v>0</v>
+        <v>21.215</v>
       </c>
       <c r="C81">
-        <v>7.554</v>
+        <v>0</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2216,13 +2147,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46310.83333333334</v>
+        <v>46315.90625</v>
       </c>
       <c r="B82">
-        <v>0</v>
+        <v>13.924</v>
       </c>
       <c r="C82">
-        <v>11.572</v>
+        <v>0</v>
       </c>
       <c r="D82">
         <v>81</v>
@@ -2233,13 +2164,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46310.84375</v>
+        <v>46315.91666666666</v>
       </c>
       <c r="B83">
         <v>0</v>
       </c>
       <c r="C83">
-        <v>12.08</v>
+        <v>2.962</v>
       </c>
       <c r="D83">
         <v>82</v>
@@ -2250,13 +2181,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46310.85416666666</v>
+        <v>46315.92708333334</v>
       </c>
       <c r="B84">
         <v>0</v>
       </c>
       <c r="C84">
-        <v>12.366</v>
+        <v>13.819</v>
       </c>
       <c r="D84">
         <v>83</v>
@@ -2267,13 +2198,13 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46310.86458333334</v>
+        <v>46315.9375</v>
       </c>
       <c r="B85">
         <v>0</v>
       </c>
       <c r="C85">
-        <v>10.285</v>
+        <v>9.584</v>
       </c>
       <c r="D85">
         <v>84</v>
@@ -2284,13 +2215,13 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46310.875</v>
+        <v>46315.94791666666</v>
       </c>
       <c r="B86">
-        <v>0.884</v>
+        <v>0</v>
       </c>
       <c r="C86">
-        <v>0</v>
+        <v>5.592</v>
       </c>
       <c r="D86">
         <v>85</v>
@@ -2301,13 +2232,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46310.88541666666</v>
+        <v>46315.95833333334</v>
       </c>
       <c r="B87">
         <v>0</v>
       </c>
       <c r="C87">
-        <v>8.755000000000001</v>
+        <v>37.41</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -2318,13 +2249,13 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46310.89583333334</v>
+        <v>46315.96875</v>
       </c>
       <c r="B88">
         <v>0</v>
       </c>
       <c r="C88">
-        <v>4.896</v>
+        <v>11.919</v>
       </c>
       <c r="D88">
         <v>87</v>
@@ -2335,13 +2266,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46310.90625</v>
+        <v>46315.97916666666</v>
       </c>
       <c r="B89">
         <v>0</v>
       </c>
       <c r="C89">
-        <v>2.672</v>
+        <v>12.966</v>
       </c>
       <c r="D89">
         <v>88</v>
@@ -2352,13 +2283,13 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46310.91666666666</v>
+        <v>46315.98958333334</v>
       </c>
       <c r="B90">
         <v>0</v>
       </c>
       <c r="C90">
-        <v>1.791</v>
+        <v>14.772</v>
       </c>
       <c r="D90">
         <v>89</v>
@@ -2369,13 +2300,13 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46310.92708333334</v>
+        <v>46316</v>
       </c>
       <c r="B91">
-        <v>0</v>
+        <v>1.056</v>
       </c>
       <c r="C91">
-        <v>10.493</v>
+        <v>0</v>
       </c>
       <c r="D91">
         <v>90</v>
@@ -2386,13 +2317,13 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46310.9375</v>
+        <v>46316.01041666666</v>
       </c>
       <c r="B92">
         <v>0</v>
       </c>
       <c r="C92">
-        <v>10.442</v>
+        <v>6.774</v>
       </c>
       <c r="D92">
         <v>91</v>
@@ -2403,13 +2334,13 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46310.94791666666</v>
+        <v>46316.02083333334</v>
       </c>
       <c r="B93">
-        <v>0</v>
+        <v>5.612</v>
       </c>
       <c r="C93">
-        <v>13.611</v>
+        <v>0</v>
       </c>
       <c r="D93">
         <v>92</v>
@@ -2420,13 +2351,13 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46310.95833333334</v>
+        <v>46316.03125</v>
       </c>
       <c r="B94">
-        <v>0</v>
+        <v>7.792</v>
       </c>
       <c r="C94">
-        <v>27.883</v>
+        <v>0</v>
       </c>
       <c r="D94">
         <v>93</v>
@@ -2437,13 +2368,13 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46310.96875</v>
+        <v>46316.04166666666</v>
       </c>
       <c r="B95">
         <v>0</v>
       </c>
       <c r="C95">
-        <v>48.913</v>
+        <v>7.879</v>
       </c>
       <c r="D95">
         <v>94</v>
@@ -2454,13 +2385,13 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46310.97916666666</v>
+        <v>46316.05208333334</v>
       </c>
       <c r="B96">
-        <v>0</v>
+        <v>14.325</v>
       </c>
       <c r="C96">
-        <v>67.48099999999999</v>
+        <v>0</v>
       </c>
       <c r="D96">
         <v>95</v>
@@ -2471,13 +2402,13 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46310.98958333334</v>
+        <v>46316.0625</v>
       </c>
       <c r="B97">
         <v>0</v>
       </c>
       <c r="C97">
-        <v>69.908</v>
+        <v>1.844</v>
       </c>
       <c r="D97">
         <v>96</v>
@@ -2488,13 +2419,13 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46311</v>
+        <v>46316.07291666666</v>
       </c>
       <c r="B98">
-        <v>0</v>
+        <v>7.829</v>
       </c>
       <c r="C98">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -2505,13 +2436,13 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46311.01041666666</v>
+        <v>46316.08333333334</v>
       </c>
       <c r="B99">
-        <v>2.078</v>
+        <v>0</v>
       </c>
       <c r="C99">
-        <v>0</v>
+        <v>3.538</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -2522,13 +2453,13 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46311.02083333334</v>
+        <v>46316.09375</v>
       </c>
       <c r="B100">
-        <v>7.16</v>
+        <v>0</v>
       </c>
       <c r="C100">
-        <v>0</v>
+        <v>18.872</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2539,13 +2470,13 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46311.03125</v>
+        <v>46316.10416666666</v>
       </c>
       <c r="B101">
         <v>0</v>
       </c>
       <c r="C101">
-        <v>19.13</v>
+        <v>3.946</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -2556,13 +2487,13 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46311.04166666666</v>
+        <v>46316.11458333334</v>
       </c>
       <c r="B102">
         <v>0</v>
       </c>
       <c r="C102">
-        <v>14.824</v>
+        <v>17.291</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -2573,13 +2504,13 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46311.05208333334</v>
+        <v>46316.125</v>
       </c>
       <c r="B103">
         <v>0</v>
       </c>
       <c r="C103">
-        <v>19.408</v>
+        <v>12.676</v>
       </c>
       <c r="D103">
         <v>6</v>
@@ -2590,13 +2521,13 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46311.0625</v>
+        <v>46316.13541666666</v>
       </c>
       <c r="B104">
-        <v>0</v>
+        <v>4.809</v>
       </c>
       <c r="C104">
-        <v>50.849</v>
+        <v>0</v>
       </c>
       <c r="D104">
         <v>7</v>
@@ -2607,13 +2538,13 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46311.07291666666</v>
+        <v>46316.14583333334</v>
       </c>
       <c r="B105">
         <v>0</v>
       </c>
       <c r="C105">
-        <v>58.876</v>
+        <v>10.912</v>
       </c>
       <c r="D105">
         <v>8</v>
@@ -2624,13 +2555,13 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46311.08333333334</v>
+        <v>46316.15625</v>
       </c>
       <c r="B106">
         <v>0</v>
       </c>
       <c r="C106">
-        <v>61.243</v>
+        <v>30.798</v>
       </c>
       <c r="D106">
         <v>9</v>
@@ -2641,13 +2572,13 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46311.09375</v>
+        <v>46316.16666666666</v>
       </c>
       <c r="B107">
         <v>0</v>
       </c>
       <c r="C107">
-        <v>38.248</v>
+        <v>3.317</v>
       </c>
       <c r="D107">
         <v>10</v>
@@ -2658,13 +2589,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46311.10416666666</v>
+        <v>46316.17708333334</v>
       </c>
       <c r="B108">
         <v>0</v>
       </c>
       <c r="C108">
-        <v>23.273</v>
+        <v>46.085</v>
       </c>
       <c r="D108">
         <v>11</v>
@@ -2675,13 +2606,13 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46311.11458333334</v>
+        <v>46316.1875</v>
       </c>
       <c r="B109">
         <v>0</v>
       </c>
       <c r="C109">
-        <v>17.911</v>
+        <v>40.261</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -2692,13 +2623,13 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46311.125</v>
+        <v>46316.19791666666</v>
       </c>
       <c r="B110">
         <v>0</v>
       </c>
       <c r="C110">
-        <v>3.485</v>
+        <v>64.42400000000001</v>
       </c>
       <c r="D110">
         <v>13</v>
@@ -2709,13 +2640,13 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46311.13541666666</v>
+        <v>46316.20833333334</v>
       </c>
       <c r="B111">
         <v>0</v>
       </c>
       <c r="C111">
-        <v>1.05</v>
+        <v>52.461</v>
       </c>
       <c r="D111">
         <v>14</v>
@@ -2726,13 +2657,13 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46311.14583333334</v>
+        <v>46316.21875</v>
       </c>
       <c r="B112">
         <v>0</v>
       </c>
       <c r="C112">
-        <v>5.218</v>
+        <v>44.586</v>
       </c>
       <c r="D112">
         <v>15</v>
@@ -2743,13 +2674,13 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46311.15625</v>
+        <v>46316.22916666666</v>
       </c>
       <c r="B113">
-        <v>0</v>
+        <v>4.047</v>
       </c>
       <c r="C113">
-        <v>3.726</v>
+        <v>0</v>
       </c>
       <c r="D113">
         <v>16</v>
@@ -2760,13 +2691,13 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46311.16666666666</v>
+        <v>46316.23958333334</v>
       </c>
       <c r="B114">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="C114">
-        <v>21.998</v>
+        <v>0</v>
       </c>
       <c r="D114">
         <v>17</v>
@@ -2777,13 +2708,13 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46311.17708333334</v>
+        <v>46316.25</v>
       </c>
       <c r="B115">
         <v>0</v>
       </c>
       <c r="C115">
-        <v>15.091</v>
+        <v>8.286</v>
       </c>
       <c r="D115">
         <v>18</v>
@@ -2794,13 +2725,13 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46311.1875</v>
+        <v>46316.26041666666</v>
       </c>
       <c r="B116">
         <v>0</v>
       </c>
       <c r="C116">
-        <v>17.98</v>
+        <v>0.772</v>
       </c>
       <c r="D116">
         <v>19</v>
@@ -2811,13 +2742,13 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46311.19791666666</v>
+        <v>46316.27083333334</v>
       </c>
       <c r="B117">
         <v>0</v>
       </c>
       <c r="C117">
-        <v>22.354</v>
+        <v>0.035</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -2828,13 +2759,13 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46311.20833333334</v>
+        <v>46316.28125</v>
       </c>
       <c r="B118">
         <v>0</v>
       </c>
       <c r="C118">
-        <v>14.426</v>
+        <v>0.172</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -2845,13 +2776,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46311.21875</v>
+        <v>46316.29166666666</v>
       </c>
       <c r="B119">
         <v>0</v>
       </c>
       <c r="C119">
-        <v>17.198</v>
+        <v>7.529</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -2862,13 +2793,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46311.22916666666</v>
+        <v>46316.30208333334</v>
       </c>
       <c r="B120">
         <v>0</v>
       </c>
       <c r="C120">
-        <v>29.306</v>
+        <v>1.264</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -2879,13 +2810,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46311.23958333334</v>
+        <v>46316.3125</v>
       </c>
       <c r="B121">
         <v>0</v>
       </c>
       <c r="C121">
-        <v>26.822</v>
+        <v>9.667999999999999</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -2896,13 +2827,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46311.25</v>
+        <v>46316.32291666666</v>
       </c>
       <c r="B122">
-        <v>0</v>
+        <v>9.747999999999999</v>
       </c>
       <c r="C122">
-        <v>47.562</v>
+        <v>0</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -2913,13 +2844,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46311.26041666666</v>
+        <v>46316.33333333334</v>
       </c>
       <c r="B123">
-        <v>0</v>
+        <v>17.773</v>
       </c>
       <c r="C123">
-        <v>45.549</v>
+        <v>0</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -2930,13 +2861,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46311.27083333334</v>
+        <v>46316.34375</v>
       </c>
       <c r="B124">
-        <v>0</v>
+        <v>19.478</v>
       </c>
       <c r="C124">
-        <v>48.151</v>
+        <v>0</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -2947,13 +2878,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46311.28125</v>
+        <v>46316.35416666666</v>
       </c>
       <c r="B125">
-        <v>0</v>
+        <v>13.631</v>
       </c>
       <c r="C125">
-        <v>38.357</v>
+        <v>0</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -2964,410 +2895,19 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46311.29166666666</v>
+        <v>46316.36458333334</v>
       </c>
       <c r="B126">
-        <v>0</v>
+        <v>12.595</v>
       </c>
       <c r="C126">
-        <v>19.174</v>
+        <v>0</v>
       </c>
       <c r="D126">
         <v>29</v>
       </c>
       <c r="E126" t="s">
         <v>129</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5">
-      <c r="A127" s="2">
-        <v>46311.30208333334</v>
-      </c>
-      <c r="B127">
-        <v>0</v>
-      </c>
-      <c r="C127">
-        <v>10.373</v>
-      </c>
-      <c r="D127">
-        <v>30</v>
-      </c>
-      <c r="E127" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5">
-      <c r="A128" s="2">
-        <v>46311.3125</v>
-      </c>
-      <c r="B128">
-        <v>0</v>
-      </c>
-      <c r="C128">
-        <v>14.853</v>
-      </c>
-      <c r="D128">
-        <v>31</v>
-      </c>
-      <c r="E128" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5">
-      <c r="A129" s="2">
-        <v>46311.32291666666</v>
-      </c>
-      <c r="B129">
-        <v>0</v>
-      </c>
-      <c r="C129">
-        <v>10.907</v>
-      </c>
-      <c r="D129">
-        <v>32</v>
-      </c>
-      <c r="E129" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5">
-      <c r="A130" s="2">
-        <v>46311.33333333334</v>
-      </c>
-      <c r="B130">
-        <v>2.168</v>
-      </c>
-      <c r="C130">
-        <v>0</v>
-      </c>
-      <c r="D130">
-        <v>33</v>
-      </c>
-      <c r="E130" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5">
-      <c r="A131" s="2">
-        <v>46311.34375</v>
-      </c>
-      <c r="B131">
-        <v>0</v>
-      </c>
-      <c r="C131">
-        <v>3.243</v>
-      </c>
-      <c r="D131">
-        <v>34</v>
-      </c>
-      <c r="E131" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5">
-      <c r="A132" s="2">
-        <v>46311.35416666666</v>
-      </c>
-      <c r="B132">
-        <v>0</v>
-      </c>
-      <c r="C132">
-        <v>2.646</v>
-      </c>
-      <c r="D132">
-        <v>35</v>
-      </c>
-      <c r="E132" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5">
-      <c r="A133" s="2">
-        <v>46311.36458333334</v>
-      </c>
-      <c r="B133">
-        <v>0</v>
-      </c>
-      <c r="C133">
-        <v>34.86</v>
-      </c>
-      <c r="D133">
-        <v>36</v>
-      </c>
-      <c r="E133" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5">
-      <c r="A134" s="2">
-        <v>46311.375</v>
-      </c>
-      <c r="B134">
-        <v>0</v>
-      </c>
-      <c r="C134">
-        <v>14.449</v>
-      </c>
-      <c r="D134">
-        <v>37</v>
-      </c>
-      <c r="E134" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5">
-      <c r="A135" s="2">
-        <v>46311.38541666666</v>
-      </c>
-      <c r="B135">
-        <v>0</v>
-      </c>
-      <c r="C135">
-        <v>45.214</v>
-      </c>
-      <c r="D135">
-        <v>38</v>
-      </c>
-      <c r="E135" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5">
-      <c r="A136" s="2">
-        <v>46311.39583333334</v>
-      </c>
-      <c r="B136">
-        <v>0</v>
-      </c>
-      <c r="C136">
-        <v>57.997</v>
-      </c>
-      <c r="D136">
-        <v>39</v>
-      </c>
-      <c r="E136" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5">
-      <c r="A137" s="2">
-        <v>46311.40625</v>
-      </c>
-      <c r="B137">
-        <v>0</v>
-      </c>
-      <c r="C137">
-        <v>9.391</v>
-      </c>
-      <c r="D137">
-        <v>40</v>
-      </c>
-      <c r="E137" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5">
-      <c r="A138" s="2">
-        <v>46311.41666666666</v>
-      </c>
-      <c r="B138">
-        <v>51.307</v>
-      </c>
-      <c r="C138">
-        <v>0</v>
-      </c>
-      <c r="D138">
-        <v>41</v>
-      </c>
-      <c r="E138" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5">
-      <c r="A139" s="2">
-        <v>46311.42708333334</v>
-      </c>
-      <c r="B139">
-        <v>0.031</v>
-      </c>
-      <c r="C139">
-        <v>0</v>
-      </c>
-      <c r="D139">
-        <v>42</v>
-      </c>
-      <c r="E139" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5">
-      <c r="A140" s="2">
-        <v>46311.4375</v>
-      </c>
-      <c r="B140">
-        <v>0</v>
-      </c>
-      <c r="C140">
-        <v>3.168</v>
-      </c>
-      <c r="D140">
-        <v>43</v>
-      </c>
-      <c r="E140" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5">
-      <c r="A141" s="2">
-        <v>46311.44791666666</v>
-      </c>
-      <c r="B141">
-        <v>17.875</v>
-      </c>
-      <c r="C141">
-        <v>0</v>
-      </c>
-      <c r="D141">
-        <v>44</v>
-      </c>
-      <c r="E141" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5">
-      <c r="A142" s="2">
-        <v>46311.45833333334</v>
-      </c>
-      <c r="B142">
-        <v>16.02</v>
-      </c>
-      <c r="C142">
-        <v>0</v>
-      </c>
-      <c r="D142">
-        <v>45</v>
-      </c>
-      <c r="E142" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5">
-      <c r="A143" s="2">
-        <v>46311.46875</v>
-      </c>
-      <c r="B143">
-        <v>4.897</v>
-      </c>
-      <c r="C143">
-        <v>0</v>
-      </c>
-      <c r="D143">
-        <v>46</v>
-      </c>
-      <c r="E143" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5">
-      <c r="A144" s="2">
-        <v>46311.47916666666</v>
-      </c>
-      <c r="B144">
-        <v>5.367</v>
-      </c>
-      <c r="C144">
-        <v>0</v>
-      </c>
-      <c r="D144">
-        <v>47</v>
-      </c>
-      <c r="E144" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5">
-      <c r="A145" s="2">
-        <v>46311.48958333334</v>
-      </c>
-      <c r="B145">
-        <v>0</v>
-      </c>
-      <c r="C145">
-        <v>23.791</v>
-      </c>
-      <c r="D145">
-        <v>48</v>
-      </c>
-      <c r="E145" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5">
-      <c r="A146" s="2">
-        <v>46311.5</v>
-      </c>
-      <c r="B146">
-        <v>0</v>
-      </c>
-      <c r="C146">
-        <v>40.405</v>
-      </c>
-      <c r="D146">
-        <v>49</v>
-      </c>
-      <c r="E146" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5">
-      <c r="A147" s="2">
-        <v>46311.51041666666</v>
-      </c>
-      <c r="B147">
-        <v>0</v>
-      </c>
-      <c r="C147">
-        <v>24.179</v>
-      </c>
-      <c r="D147">
-        <v>50</v>
-      </c>
-      <c r="E147" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5">
-      <c r="A148" s="2">
-        <v>46311.52083333334</v>
-      </c>
-      <c r="B148">
-        <v>0</v>
-      </c>
-      <c r="C148">
-        <v>4.868</v>
-      </c>
-      <c r="D148">
-        <v>51</v>
-      </c>
-      <c r="E148" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5">
-      <c r="A149" s="2">
-        <v>46311.53125</v>
-      </c>
-      <c r="B149">
-        <v>0</v>
-      </c>
-      <c r="C149">
-        <v>1.386</v>
-      </c>
-      <c r="D149">
-        <v>52</v>
-      </c>
-      <c r="E149" t="s">
-        <v>152</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Unintended_Deviation.xlsx
+++ b/data_fetching/Entsoe/Unintended_Deviation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="131">
   <si>
     <t>Timestamp</t>
   </si>
@@ -31,379 +31,382 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>20.10.20261</t>
-  </si>
-  <si>
-    <t>20.10.20262</t>
-  </si>
-  <si>
-    <t>20.10.20263</t>
-  </si>
-  <si>
-    <t>20.10.20264</t>
-  </si>
-  <si>
-    <t>20.10.20265</t>
-  </si>
-  <si>
-    <t>20.10.20266</t>
-  </si>
-  <si>
-    <t>20.10.20267</t>
-  </si>
-  <si>
-    <t>20.10.20268</t>
-  </si>
-  <si>
-    <t>20.10.20269</t>
-  </si>
-  <si>
-    <t>20.10.202610</t>
-  </si>
-  <si>
-    <t>20.10.202611</t>
-  </si>
-  <si>
-    <t>20.10.202612</t>
-  </si>
-  <si>
-    <t>20.10.202613</t>
-  </si>
-  <si>
-    <t>20.10.202614</t>
-  </si>
-  <si>
-    <t>20.10.202615</t>
-  </si>
-  <si>
-    <t>20.10.202616</t>
-  </si>
-  <si>
-    <t>20.10.202617</t>
-  </si>
-  <si>
-    <t>20.10.202618</t>
-  </si>
-  <si>
-    <t>20.10.202619</t>
-  </si>
-  <si>
-    <t>20.10.202620</t>
-  </si>
-  <si>
-    <t>20.10.202621</t>
-  </si>
-  <si>
-    <t>20.10.202622</t>
-  </si>
-  <si>
-    <t>20.10.202623</t>
-  </si>
-  <si>
-    <t>20.10.202624</t>
-  </si>
-  <si>
-    <t>20.10.202625</t>
-  </si>
-  <si>
-    <t>20.10.202626</t>
-  </si>
-  <si>
-    <t>20.10.202627</t>
-  </si>
-  <si>
-    <t>20.10.202628</t>
-  </si>
-  <si>
-    <t>20.10.202629</t>
-  </si>
-  <si>
-    <t>20.10.202630</t>
-  </si>
-  <si>
-    <t>20.10.202631</t>
-  </si>
-  <si>
-    <t>20.10.202632</t>
-  </si>
-  <si>
-    <t>20.10.202633</t>
-  </si>
-  <si>
-    <t>20.10.202634</t>
-  </si>
-  <si>
-    <t>20.10.202635</t>
-  </si>
-  <si>
-    <t>20.10.202636</t>
-  </si>
-  <si>
-    <t>20.10.202637</t>
-  </si>
-  <si>
-    <t>20.10.202638</t>
-  </si>
-  <si>
-    <t>20.10.202639</t>
-  </si>
-  <si>
-    <t>20.10.202640</t>
-  </si>
-  <si>
-    <t>20.10.202641</t>
-  </si>
-  <si>
-    <t>20.10.202642</t>
-  </si>
-  <si>
-    <t>20.10.202643</t>
-  </si>
-  <si>
-    <t>20.10.202644</t>
-  </si>
-  <si>
-    <t>20.10.202645</t>
-  </si>
-  <si>
-    <t>20.10.202646</t>
-  </si>
-  <si>
-    <t>20.10.202647</t>
-  </si>
-  <si>
-    <t>20.10.202648</t>
-  </si>
-  <si>
-    <t>20.10.202649</t>
-  </si>
-  <si>
-    <t>20.10.202650</t>
-  </si>
-  <si>
-    <t>20.10.202651</t>
-  </si>
-  <si>
-    <t>20.10.202652</t>
-  </si>
-  <si>
-    <t>20.10.202653</t>
-  </si>
-  <si>
-    <t>20.10.202654</t>
-  </si>
-  <si>
-    <t>20.10.202655</t>
-  </si>
-  <si>
-    <t>20.10.202656</t>
-  </si>
-  <si>
-    <t>20.10.202657</t>
-  </si>
-  <si>
-    <t>20.10.202658</t>
-  </si>
-  <si>
-    <t>20.10.202659</t>
-  </si>
-  <si>
-    <t>20.10.202660</t>
-  </si>
-  <si>
-    <t>20.10.202661</t>
-  </si>
-  <si>
-    <t>20.10.202662</t>
-  </si>
-  <si>
-    <t>20.10.202663</t>
-  </si>
-  <si>
-    <t>20.10.202664</t>
-  </si>
-  <si>
-    <t>20.10.202665</t>
-  </si>
-  <si>
-    <t>20.10.202666</t>
-  </si>
-  <si>
-    <t>20.10.202667</t>
-  </si>
-  <si>
-    <t>20.10.202668</t>
-  </si>
-  <si>
-    <t>20.10.202669</t>
-  </si>
-  <si>
-    <t>20.10.202670</t>
-  </si>
-  <si>
-    <t>20.10.202671</t>
-  </si>
-  <si>
-    <t>20.10.202672</t>
-  </si>
-  <si>
-    <t>20.10.202673</t>
-  </si>
-  <si>
-    <t>20.10.202674</t>
-  </si>
-  <si>
-    <t>20.10.202675</t>
-  </si>
-  <si>
-    <t>20.10.202676</t>
-  </si>
-  <si>
-    <t>20.10.202677</t>
-  </si>
-  <si>
-    <t>20.10.202678</t>
-  </si>
-  <si>
-    <t>20.10.202679</t>
-  </si>
-  <si>
-    <t>20.10.202680</t>
-  </si>
-  <si>
-    <t>20.10.202681</t>
-  </si>
-  <si>
-    <t>20.10.202682</t>
-  </si>
-  <si>
-    <t>20.10.202683</t>
-  </si>
-  <si>
-    <t>20.10.202684</t>
-  </si>
-  <si>
-    <t>20.10.202685</t>
-  </si>
-  <si>
-    <t>20.10.202686</t>
-  </si>
-  <si>
-    <t>20.10.202687</t>
-  </si>
-  <si>
-    <t>20.10.202688</t>
-  </si>
-  <si>
-    <t>20.10.202689</t>
-  </si>
-  <si>
-    <t>21.10.202690</t>
-  </si>
-  <si>
-    <t>21.10.202691</t>
-  </si>
-  <si>
-    <t>21.10.202692</t>
-  </si>
-  <si>
-    <t>21.10.202693</t>
-  </si>
-  <si>
-    <t>21.10.202694</t>
-  </si>
-  <si>
-    <t>21.10.202695</t>
-  </si>
-  <si>
-    <t>21.10.202696</t>
-  </si>
-  <si>
-    <t>21.10.20261</t>
-  </si>
-  <si>
-    <t>21.10.20262</t>
-  </si>
-  <si>
-    <t>21.10.20263</t>
-  </si>
-  <si>
-    <t>21.10.20264</t>
-  </si>
-  <si>
-    <t>21.10.20265</t>
-  </si>
-  <si>
-    <t>21.10.20266</t>
-  </si>
-  <si>
-    <t>21.10.20267</t>
-  </si>
-  <si>
-    <t>21.10.20268</t>
-  </si>
-  <si>
-    <t>21.10.20269</t>
-  </si>
-  <si>
-    <t>21.10.202610</t>
-  </si>
-  <si>
-    <t>21.10.202611</t>
-  </si>
-  <si>
-    <t>21.10.202612</t>
-  </si>
-  <si>
-    <t>21.10.202613</t>
-  </si>
-  <si>
-    <t>21.10.202614</t>
-  </si>
-  <si>
-    <t>21.10.202615</t>
-  </si>
-  <si>
-    <t>21.10.202616</t>
-  </si>
-  <si>
-    <t>21.10.202617</t>
-  </si>
-  <si>
-    <t>21.10.202618</t>
-  </si>
-  <si>
-    <t>21.10.202619</t>
-  </si>
-  <si>
-    <t>21.10.202620</t>
-  </si>
-  <si>
-    <t>21.10.202621</t>
-  </si>
-  <si>
-    <t>21.10.202622</t>
-  </si>
-  <si>
-    <t>21.10.202623</t>
-  </si>
-  <si>
-    <t>21.10.202624</t>
-  </si>
-  <si>
-    <t>21.10.202625</t>
-  </si>
-  <si>
-    <t>21.10.202626</t>
-  </si>
-  <si>
-    <t>21.10.202627</t>
-  </si>
-  <si>
-    <t>21.10.202628</t>
-  </si>
-  <si>
-    <t>21.10.202629</t>
+    <t>24.10.20261</t>
+  </si>
+  <si>
+    <t>24.10.20262</t>
+  </si>
+  <si>
+    <t>24.10.20263</t>
+  </si>
+  <si>
+    <t>24.10.20264</t>
+  </si>
+  <si>
+    <t>24.10.20265</t>
+  </si>
+  <si>
+    <t>24.10.20266</t>
+  </si>
+  <si>
+    <t>24.10.20267</t>
+  </si>
+  <si>
+    <t>24.10.20268</t>
+  </si>
+  <si>
+    <t>24.10.20269</t>
+  </si>
+  <si>
+    <t>24.10.202610</t>
+  </si>
+  <si>
+    <t>24.10.202611</t>
+  </si>
+  <si>
+    <t>24.10.202612</t>
+  </si>
+  <si>
+    <t>24.10.202613</t>
+  </si>
+  <si>
+    <t>24.10.202614</t>
+  </si>
+  <si>
+    <t>24.10.202615</t>
+  </si>
+  <si>
+    <t>24.10.202616</t>
+  </si>
+  <si>
+    <t>24.10.202617</t>
+  </si>
+  <si>
+    <t>24.10.202618</t>
+  </si>
+  <si>
+    <t>24.10.202619</t>
+  </si>
+  <si>
+    <t>24.10.202620</t>
+  </si>
+  <si>
+    <t>24.10.202621</t>
+  </si>
+  <si>
+    <t>24.10.202622</t>
+  </si>
+  <si>
+    <t>24.10.202623</t>
+  </si>
+  <si>
+    <t>24.10.202624</t>
+  </si>
+  <si>
+    <t>24.10.202625</t>
+  </si>
+  <si>
+    <t>24.10.202626</t>
+  </si>
+  <si>
+    <t>24.10.202627</t>
+  </si>
+  <si>
+    <t>24.10.202628</t>
+  </si>
+  <si>
+    <t>24.10.202629</t>
+  </si>
+  <si>
+    <t>24.10.202630</t>
+  </si>
+  <si>
+    <t>24.10.202631</t>
+  </si>
+  <si>
+    <t>24.10.202632</t>
+  </si>
+  <si>
+    <t>24.10.202633</t>
+  </si>
+  <si>
+    <t>24.10.202634</t>
+  </si>
+  <si>
+    <t>24.10.202635</t>
+  </si>
+  <si>
+    <t>24.10.202636</t>
+  </si>
+  <si>
+    <t>24.10.202637</t>
+  </si>
+  <si>
+    <t>24.10.202638</t>
+  </si>
+  <si>
+    <t>24.10.202639</t>
+  </si>
+  <si>
+    <t>24.10.202640</t>
+  </si>
+  <si>
+    <t>24.10.202641</t>
+  </si>
+  <si>
+    <t>24.10.202642</t>
+  </si>
+  <si>
+    <t>24.10.202643</t>
+  </si>
+  <si>
+    <t>24.10.202644</t>
+  </si>
+  <si>
+    <t>24.10.202645</t>
+  </si>
+  <si>
+    <t>24.10.202646</t>
+  </si>
+  <si>
+    <t>24.10.202647</t>
+  </si>
+  <si>
+    <t>24.10.202648</t>
+  </si>
+  <si>
+    <t>24.10.202649</t>
+  </si>
+  <si>
+    <t>24.10.202650</t>
+  </si>
+  <si>
+    <t>24.10.202651</t>
+  </si>
+  <si>
+    <t>24.10.202652</t>
+  </si>
+  <si>
+    <t>24.10.202653</t>
+  </si>
+  <si>
+    <t>24.10.202654</t>
+  </si>
+  <si>
+    <t>24.10.202655</t>
+  </si>
+  <si>
+    <t>24.10.202656</t>
+  </si>
+  <si>
+    <t>24.10.202657</t>
+  </si>
+  <si>
+    <t>24.10.202658</t>
+  </si>
+  <si>
+    <t>24.10.202659</t>
+  </si>
+  <si>
+    <t>24.10.202660</t>
+  </si>
+  <si>
+    <t>24.10.202661</t>
+  </si>
+  <si>
+    <t>24.10.202662</t>
+  </si>
+  <si>
+    <t>24.10.202663</t>
+  </si>
+  <si>
+    <t>24.10.202664</t>
+  </si>
+  <si>
+    <t>24.10.202665</t>
+  </si>
+  <si>
+    <t>24.10.202666</t>
+  </si>
+  <si>
+    <t>24.10.202667</t>
+  </si>
+  <si>
+    <t>24.10.202668</t>
+  </si>
+  <si>
+    <t>24.10.202669</t>
+  </si>
+  <si>
+    <t>24.10.202670</t>
+  </si>
+  <si>
+    <t>24.10.202671</t>
+  </si>
+  <si>
+    <t>24.10.202672</t>
+  </si>
+  <si>
+    <t>24.10.202673</t>
+  </si>
+  <si>
+    <t>24.10.202674</t>
+  </si>
+  <si>
+    <t>24.10.202675</t>
+  </si>
+  <si>
+    <t>24.10.202676</t>
+  </si>
+  <si>
+    <t>24.10.202677</t>
+  </si>
+  <si>
+    <t>24.10.202678</t>
+  </si>
+  <si>
+    <t>24.10.202679</t>
+  </si>
+  <si>
+    <t>24.10.202680</t>
+  </si>
+  <si>
+    <t>24.10.202681</t>
+  </si>
+  <si>
+    <t>24.10.202682</t>
+  </si>
+  <si>
+    <t>24.10.202683</t>
+  </si>
+  <si>
+    <t>24.10.202684</t>
+  </si>
+  <si>
+    <t>24.10.202685</t>
+  </si>
+  <si>
+    <t>24.10.202686</t>
+  </si>
+  <si>
+    <t>24.10.202687</t>
+  </si>
+  <si>
+    <t>24.10.202688</t>
+  </si>
+  <si>
+    <t>24.10.202689</t>
+  </si>
+  <si>
+    <t>24.10.202690</t>
+  </si>
+  <si>
+    <t>24.10.202691</t>
+  </si>
+  <si>
+    <t>24.10.202692</t>
+  </si>
+  <si>
+    <t>24.10.202693</t>
+  </si>
+  <si>
+    <t>24.10.202694</t>
+  </si>
+  <si>
+    <t>24.10.202695</t>
+  </si>
+  <si>
+    <t>24.10.202696</t>
+  </si>
+  <si>
+    <t>25.10.20261</t>
+  </si>
+  <si>
+    <t>25.10.20262</t>
+  </si>
+  <si>
+    <t>25.10.20263</t>
+  </si>
+  <si>
+    <t>25.10.20264</t>
+  </si>
+  <si>
+    <t>25.10.20265</t>
+  </si>
+  <si>
+    <t>25.10.20266</t>
+  </si>
+  <si>
+    <t>25.10.20267</t>
+  </si>
+  <si>
+    <t>25.10.20268</t>
+  </si>
+  <si>
+    <t>25.10.20269</t>
+  </si>
+  <si>
+    <t>25.10.202610</t>
+  </si>
+  <si>
+    <t>25.10.202611</t>
+  </si>
+  <si>
+    <t>25.10.202612</t>
+  </si>
+  <si>
+    <t>25.10.202613</t>
+  </si>
+  <si>
+    <t>25.10.202614</t>
+  </si>
+  <si>
+    <t>25.10.202615</t>
+  </si>
+  <si>
+    <t>25.10.202616</t>
+  </si>
+  <si>
+    <t>25.10.202617</t>
+  </si>
+  <si>
+    <t>25.10.202618</t>
+  </si>
+  <si>
+    <t>25.10.202619</t>
+  </si>
+  <si>
+    <t>25.10.202620</t>
+  </si>
+  <si>
+    <t>25.10.202621</t>
+  </si>
+  <si>
+    <t>25.10.202622</t>
+  </si>
+  <si>
+    <t>25.10.202623</t>
+  </si>
+  <si>
+    <t>25.10.202624</t>
+  </si>
+  <si>
+    <t>25.10.202625</t>
+  </si>
+  <si>
+    <t>25.10.202626</t>
+  </si>
+  <si>
+    <t>25.10.202627</t>
+  </si>
+  <si>
+    <t>25.10.202628</t>
+  </si>
+  <si>
+    <t>25.10.202629</t>
+  </si>
+  <si>
+    <t>25.10.202630</t>
   </si>
 </sst>
 </file>
@@ -765,7 +768,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E126"/>
+  <dimension ref="A1:E127"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -787,13 +790,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46315</v>
+        <v>46319</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>25.853</v>
+        <v>25.14</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -804,13 +807,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46315.01041666666</v>
+        <v>46319.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3">
-        <v>18.867</v>
+        <v>52.45</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -821,13 +824,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46315.02083333334</v>
+        <v>46319.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
       <c r="C4">
-        <v>29.959</v>
+        <v>47.821</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -838,13 +841,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46315.03125</v>
+        <v>46319.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
       </c>
       <c r="C5">
-        <v>8.731999999999999</v>
+        <v>30.096</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -855,13 +858,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46315.04166666666</v>
+        <v>46319.04166666666</v>
       </c>
       <c r="B6">
-        <v>13.071</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>33.711</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -872,13 +875,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46315.05208333334</v>
+        <v>46319.05208333334</v>
       </c>
       <c r="B7">
-        <v>11.253</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>19.346</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -889,13 +892,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46315.0625</v>
+        <v>46319.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
       <c r="C8">
-        <v>1.667</v>
+        <v>10.55</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -906,13 +909,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46315.07291666666</v>
+        <v>46319.07291666666</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="C9">
-        <v>4.057</v>
+        <v>0</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -923,13 +926,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46315.08333333334</v>
+        <v>46319.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="C10">
-        <v>17.794</v>
+        <v>2.941</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -940,13 +943,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46315.09375</v>
+        <v>46319.09375</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>4.585</v>
       </c>
       <c r="C11">
-        <v>24.679</v>
+        <v>0</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -957,13 +960,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46315.10416666666</v>
+        <v>46319.10416666666</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="C12">
-        <v>32.909</v>
+        <v>0</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -974,13 +977,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46315.11458333334</v>
+        <v>46319.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
       <c r="C13">
-        <v>17.648</v>
+        <v>1.542</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -991,13 +994,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46315.125</v>
+        <v>46319.125</v>
       </c>
       <c r="B14">
         <v>0</v>
       </c>
       <c r="C14">
-        <v>26.123</v>
+        <v>14.406</v>
       </c>
       <c r="D14">
         <v>13</v>
@@ -1008,13 +1011,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46315.13541666666</v>
+        <v>46319.13541666666</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>5.429</v>
       </c>
       <c r="C15">
-        <v>27.786</v>
+        <v>0</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -1025,13 +1028,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46315.14583333334</v>
+        <v>46319.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
       <c r="C16">
-        <v>5.629</v>
+        <v>4.095</v>
       </c>
       <c r="D16">
         <v>15</v>
@@ -1042,13 +1045,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46315.15625</v>
+        <v>46319.15625</v>
       </c>
       <c r="B17">
-        <v>2.971</v>
+        <v>0</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>15.926</v>
       </c>
       <c r="D17">
         <v>16</v>
@@ -1059,13 +1062,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46315.16666666666</v>
+        <v>46319.16666666666</v>
       </c>
       <c r="B18">
         <v>0</v>
       </c>
       <c r="C18">
-        <v>6.218</v>
+        <v>50.198</v>
       </c>
       <c r="D18">
         <v>17</v>
@@ -1076,13 +1079,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46315.17708333334</v>
+        <v>46319.17708333334</v>
       </c>
       <c r="B19">
-        <v>6.664</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>12.626</v>
       </c>
       <c r="D19">
         <v>18</v>
@@ -1093,13 +1096,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46315.1875</v>
+        <v>46319.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
       </c>
       <c r="C20">
-        <v>4.066</v>
+        <v>3.581</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1110,13 +1113,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46315.19791666666</v>
+        <v>46319.19791666666</v>
       </c>
       <c r="B21">
         <v>0</v>
       </c>
       <c r="C21">
-        <v>0.884</v>
+        <v>11.394</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1127,13 +1130,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46315.20833333334</v>
+        <v>46319.20833333334</v>
       </c>
       <c r="B22">
         <v>0</v>
       </c>
       <c r="C22">
-        <v>21.313</v>
+        <v>8.856</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1144,13 +1147,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46315.21875</v>
+        <v>46319.21875</v>
       </c>
       <c r="B23">
         <v>0</v>
       </c>
       <c r="C23">
-        <v>15.415</v>
+        <v>28.619</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1161,13 +1164,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46315.22916666666</v>
+        <v>46319.22916666666</v>
       </c>
       <c r="B24">
         <v>0</v>
       </c>
       <c r="C24">
-        <v>19.668</v>
+        <v>21.459</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1178,13 +1181,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46315.23958333334</v>
+        <v>46319.23958333334</v>
       </c>
       <c r="B25">
         <v>0</v>
       </c>
       <c r="C25">
-        <v>14.49</v>
+        <v>4.301</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1195,13 +1198,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46315.25</v>
+        <v>46319.25</v>
       </c>
       <c r="B26">
         <v>0</v>
       </c>
       <c r="C26">
-        <v>11.811</v>
+        <v>20.667</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1212,13 +1215,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46315.26041666666</v>
+        <v>46319.26041666666</v>
       </c>
       <c r="B27">
         <v>0</v>
       </c>
       <c r="C27">
-        <v>23.613</v>
+        <v>8.840999999999999</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1229,13 +1232,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46315.27083333334</v>
+        <v>46319.27083333334</v>
       </c>
       <c r="B28">
         <v>0</v>
       </c>
       <c r="C28">
-        <v>1.943</v>
+        <v>6.203</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1246,13 +1249,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46315.28125</v>
+        <v>46319.28125</v>
       </c>
       <c r="B29">
         <v>0</v>
       </c>
       <c r="C29">
-        <v>7.535</v>
+        <v>4.531</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1263,13 +1266,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46315.29166666666</v>
+        <v>46319.29166666666</v>
       </c>
       <c r="B30">
         <v>0</v>
       </c>
       <c r="C30">
-        <v>43.613</v>
+        <v>11.928</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1280,13 +1283,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46315.30208333334</v>
+        <v>46319.30208333334</v>
       </c>
       <c r="B31">
         <v>0</v>
       </c>
       <c r="C31">
-        <v>24.36</v>
+        <v>6.495</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1297,13 +1300,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46315.3125</v>
+        <v>46319.3125</v>
       </c>
       <c r="B32">
         <v>0</v>
       </c>
       <c r="C32">
-        <v>9.092000000000001</v>
+        <v>17.866</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1314,13 +1317,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46315.32291666666</v>
+        <v>46319.32291666666</v>
       </c>
       <c r="B33">
         <v>0</v>
       </c>
       <c r="C33">
-        <v>14.346</v>
+        <v>37.788</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1331,13 +1334,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46315.33333333334</v>
+        <v>46319.33333333334</v>
       </c>
       <c r="B34">
         <v>0</v>
       </c>
       <c r="C34">
-        <v>11.081</v>
+        <v>17.334</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1348,13 +1351,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46315.34375</v>
+        <v>46319.34375</v>
       </c>
       <c r="B35">
         <v>0</v>
       </c>
       <c r="C35">
-        <v>9.18</v>
+        <v>37.638</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1365,13 +1368,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46315.35416666666</v>
+        <v>46319.35416666666</v>
       </c>
       <c r="B36">
-        <v>5.574</v>
+        <v>0</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>17.995</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1382,13 +1385,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46315.36458333334</v>
+        <v>46319.36458333334</v>
       </c>
       <c r="B37">
         <v>0</v>
       </c>
       <c r="C37">
-        <v>5.254</v>
+        <v>10.441</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1399,10 +1402,10 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46315.375</v>
+        <v>46319.375</v>
       </c>
       <c r="B38">
-        <v>2.67</v>
+        <v>45.932</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -1416,13 +1419,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46315.38541666666</v>
+        <v>46319.38541666666</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>45.283</v>
       </c>
       <c r="C39">
-        <v>9.105</v>
+        <v>0</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1433,13 +1436,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46315.39583333334</v>
+        <v>46319.39583333334</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>19.473</v>
       </c>
       <c r="C40">
-        <v>20.163</v>
+        <v>0</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1450,13 +1453,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46315.40625</v>
+        <v>46319.40625</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>0.574</v>
       </c>
       <c r="C41">
-        <v>64.35299999999999</v>
+        <v>0</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1467,13 +1470,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46315.41666666666</v>
+        <v>46319.41666666666</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>13.485</v>
       </c>
       <c r="C42">
-        <v>64.845</v>
+        <v>0</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1484,13 +1487,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46315.42708333334</v>
+        <v>46319.42708333334</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>3.057</v>
       </c>
       <c r="C43">
-        <v>88.642</v>
+        <v>0</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1501,13 +1504,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46315.4375</v>
+        <v>46319.4375</v>
       </c>
       <c r="B44">
         <v>0</v>
       </c>
       <c r="C44">
-        <v>85.386</v>
+        <v>18.741</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1518,13 +1521,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46315.44791666666</v>
+        <v>46319.44791666666</v>
       </c>
       <c r="B45">
         <v>0</v>
       </c>
       <c r="C45">
-        <v>103.861</v>
+        <v>63.861</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1535,13 +1538,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46315.45833333334</v>
+        <v>46319.45833333334</v>
       </c>
       <c r="B46">
         <v>0</v>
       </c>
       <c r="C46">
-        <v>80.343</v>
+        <v>53.622</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1552,13 +1555,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46315.46875</v>
+        <v>46319.46875</v>
       </c>
       <c r="B47">
         <v>0</v>
       </c>
       <c r="C47">
-        <v>52.609</v>
+        <v>44.403</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1569,13 +1572,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46315.47916666666</v>
+        <v>46319.47916666666</v>
       </c>
       <c r="B48">
         <v>0</v>
       </c>
       <c r="C48">
-        <v>119.871</v>
+        <v>9.236000000000001</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1586,13 +1589,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46315.48958333334</v>
+        <v>46319.48958333334</v>
       </c>
       <c r="B49">
         <v>0</v>
       </c>
       <c r="C49">
-        <v>115.371</v>
+        <v>2.41</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1603,13 +1606,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46315.5</v>
+        <v>46319.5</v>
       </c>
       <c r="B50">
         <v>0</v>
       </c>
       <c r="C50">
-        <v>40.496</v>
+        <v>4.553</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1620,13 +1623,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46315.51041666666</v>
+        <v>46319.51041666666</v>
       </c>
       <c r="B51">
         <v>0</v>
       </c>
       <c r="C51">
-        <v>5.9</v>
+        <v>2.724</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1637,13 +1640,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46315.52083333334</v>
+        <v>46319.52083333334</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>0.141</v>
       </c>
       <c r="C52">
-        <v>1.711</v>
+        <v>0</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1654,13 +1657,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46315.53125</v>
+        <v>46319.53125</v>
       </c>
       <c r="B53">
-        <v>0</v>
+        <v>4.727</v>
       </c>
       <c r="C53">
-        <v>16.319</v>
+        <v>0</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1671,13 +1674,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46315.54166666666</v>
+        <v>46319.54166666666</v>
       </c>
       <c r="B54">
-        <v>0</v>
+        <v>22.378</v>
       </c>
       <c r="C54">
-        <v>50.767</v>
+        <v>0</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1688,13 +1691,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46315.55208333334</v>
+        <v>46319.55208333334</v>
       </c>
       <c r="B55">
-        <v>0</v>
+        <v>8.669</v>
       </c>
       <c r="C55">
-        <v>40.117</v>
+        <v>0</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1705,13 +1708,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46315.5625</v>
+        <v>46319.5625</v>
       </c>
       <c r="B56">
-        <v>0</v>
+        <v>8.625999999999999</v>
       </c>
       <c r="C56">
-        <v>24.472</v>
+        <v>0</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1722,13 +1725,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46315.57291666666</v>
+        <v>46319.57291666666</v>
       </c>
       <c r="B57">
         <v>0</v>
       </c>
       <c r="C57">
-        <v>18.968</v>
+        <v>2.306</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1739,13 +1742,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46315.58333333334</v>
+        <v>46319.58333333334</v>
       </c>
       <c r="B58">
         <v>0</v>
       </c>
       <c r="C58">
-        <v>47.469</v>
+        <v>1.755</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1756,13 +1759,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46315.59375</v>
+        <v>46319.59375</v>
       </c>
       <c r="B59">
-        <v>0</v>
+        <v>0.489</v>
       </c>
       <c r="C59">
-        <v>22.789</v>
+        <v>0</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1773,13 +1776,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46315.60416666666</v>
+        <v>46319.60416666666</v>
       </c>
       <c r="B60">
         <v>0</v>
       </c>
       <c r="C60">
-        <v>3.124</v>
+        <v>13.868</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1790,13 +1793,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46315.61458333334</v>
+        <v>46319.61458333334</v>
       </c>
       <c r="B61">
         <v>0</v>
       </c>
       <c r="C61">
-        <v>5.42</v>
+        <v>26.108</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -1807,13 +1810,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46315.625</v>
+        <v>46319.625</v>
       </c>
       <c r="B62">
         <v>0</v>
       </c>
       <c r="C62">
-        <v>12.727</v>
+        <v>39.749</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -1824,13 +1827,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46315.63541666666</v>
+        <v>46319.63541666666</v>
       </c>
       <c r="B63">
         <v>0</v>
       </c>
       <c r="C63">
-        <v>5.358</v>
+        <v>14.388</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -1841,13 +1844,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46315.64583333334</v>
+        <v>46319.64583333334</v>
       </c>
       <c r="B64">
-        <v>1.016</v>
+        <v>0</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>0.947</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -1858,10 +1861,10 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46315.65625</v>
+        <v>46319.65625</v>
       </c>
       <c r="B65">
-        <v>0.455</v>
+        <v>4.283</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -1875,13 +1878,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46315.66666666666</v>
+        <v>46319.66666666666</v>
       </c>
       <c r="B66">
         <v>0</v>
       </c>
       <c r="C66">
-        <v>14.033</v>
+        <v>21.856</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -1892,13 +1895,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46315.67708333334</v>
+        <v>46319.67708333334</v>
       </c>
       <c r="B67">
-        <v>0</v>
+        <v>6.114</v>
       </c>
       <c r="C67">
-        <v>0.784</v>
+        <v>0</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -1909,13 +1912,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46315.6875</v>
+        <v>46319.6875</v>
       </c>
       <c r="B68">
         <v>0</v>
       </c>
       <c r="C68">
-        <v>0.803</v>
+        <v>8.9</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -1926,13 +1929,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46315.69791666666</v>
+        <v>46319.69791666666</v>
       </c>
       <c r="B69">
-        <v>0</v>
+        <v>0.144</v>
       </c>
       <c r="C69">
-        <v>1.436</v>
+        <v>0</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -1943,13 +1946,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46315.70833333334</v>
+        <v>46319.70833333334</v>
       </c>
       <c r="B70">
         <v>0</v>
       </c>
       <c r="C70">
-        <v>32.592</v>
+        <v>24.823</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -1960,13 +1963,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46315.71875</v>
+        <v>46319.71875</v>
       </c>
       <c r="B71">
         <v>0</v>
       </c>
       <c r="C71">
-        <v>21.931</v>
+        <v>0.359</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -1977,10 +1980,10 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46315.80208333334</v>
+        <v>46319.72916666666</v>
       </c>
       <c r="B72">
-        <v>0.362</v>
+        <v>3.144</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -1994,13 +1997,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46315.8125</v>
+        <v>46319.73958333334</v>
       </c>
       <c r="B73">
         <v>0</v>
       </c>
       <c r="C73">
-        <v>4.431</v>
+        <v>2.011</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2011,10 +2014,10 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46315.82291666666</v>
+        <v>46319.75</v>
       </c>
       <c r="B74">
-        <v>5.378</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -2028,13 +2031,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46315.83333333334</v>
+        <v>46319.76041666666</v>
       </c>
       <c r="B75">
-        <v>5.561</v>
+        <v>0</v>
       </c>
       <c r="C75">
-        <v>0</v>
+        <v>2.459</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2045,13 +2048,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46315.84375</v>
+        <v>46319.77083333334</v>
       </c>
       <c r="B76">
-        <v>0</v>
+        <v>1.692</v>
       </c>
       <c r="C76">
-        <v>14.77</v>
+        <v>0</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2062,13 +2065,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46315.85416666666</v>
+        <v>46319.78125</v>
       </c>
       <c r="B77">
-        <v>0</v>
+        <v>3.301</v>
       </c>
       <c r="C77">
-        <v>32.764</v>
+        <v>0</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2079,10 +2082,10 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46315.86458333334</v>
+        <v>46319.79166666666</v>
       </c>
       <c r="B78">
-        <v>1.453</v>
+        <v>10.53</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -2096,10 +2099,10 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46315.875</v>
+        <v>46319.80208333334</v>
       </c>
       <c r="B79">
-        <v>2.886</v>
+        <v>16.061</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -2113,10 +2116,10 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46315.88541666666</v>
+        <v>46319.8125</v>
       </c>
       <c r="B80">
-        <v>1.298</v>
+        <v>4.704</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -2130,10 +2133,10 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46315.89583333334</v>
+        <v>46319.82291666666</v>
       </c>
       <c r="B81">
-        <v>21.215</v>
+        <v>14.441</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -2147,10 +2150,10 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46315.90625</v>
+        <v>46319.83333333334</v>
       </c>
       <c r="B82">
-        <v>13.924</v>
+        <v>4.689</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -2164,13 +2167,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46315.91666666666</v>
+        <v>46319.84375</v>
       </c>
       <c r="B83">
-        <v>0</v>
+        <v>1.718</v>
       </c>
       <c r="C83">
-        <v>2.962</v>
+        <v>0</v>
       </c>
       <c r="D83">
         <v>82</v>
@@ -2181,13 +2184,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46315.92708333334</v>
+        <v>46319.85416666666</v>
       </c>
       <c r="B84">
-        <v>0</v>
+        <v>3.713</v>
       </c>
       <c r="C84">
-        <v>13.819</v>
+        <v>0</v>
       </c>
       <c r="D84">
         <v>83</v>
@@ -2198,13 +2201,13 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46315.9375</v>
+        <v>46319.86458333334</v>
       </c>
       <c r="B85">
-        <v>0</v>
+        <v>2.414</v>
       </c>
       <c r="C85">
-        <v>9.584</v>
+        <v>0</v>
       </c>
       <c r="D85">
         <v>84</v>
@@ -2215,13 +2218,13 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46315.94791666666</v>
+        <v>46319.875</v>
       </c>
       <c r="B86">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="C86">
-        <v>5.592</v>
+        <v>0</v>
       </c>
       <c r="D86">
         <v>85</v>
@@ -2232,13 +2235,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46315.95833333334</v>
+        <v>46319.88541666666</v>
       </c>
       <c r="B87">
-        <v>0</v>
+        <v>2.792</v>
       </c>
       <c r="C87">
-        <v>37.41</v>
+        <v>0</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -2249,13 +2252,13 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46315.96875</v>
+        <v>46319.89583333334</v>
       </c>
       <c r="B88">
         <v>0</v>
       </c>
       <c r="C88">
-        <v>11.919</v>
+        <v>0.862</v>
       </c>
       <c r="D88">
         <v>87</v>
@@ -2266,13 +2269,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46315.97916666666</v>
+        <v>46319.90625</v>
       </c>
       <c r="B89">
-        <v>0</v>
+        <v>4.804</v>
       </c>
       <c r="C89">
-        <v>12.966</v>
+        <v>0</v>
       </c>
       <c r="D89">
         <v>88</v>
@@ -2283,13 +2286,13 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46315.98958333334</v>
+        <v>46319.91666666666</v>
       </c>
       <c r="B90">
-        <v>0</v>
+        <v>4.558</v>
       </c>
       <c r="C90">
-        <v>14.772</v>
+        <v>0</v>
       </c>
       <c r="D90">
         <v>89</v>
@@ -2300,13 +2303,13 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46316</v>
+        <v>46319.92708333334</v>
       </c>
       <c r="B91">
-        <v>1.056</v>
+        <v>0</v>
       </c>
       <c r="C91">
-        <v>0</v>
+        <v>0.206</v>
       </c>
       <c r="D91">
         <v>90</v>
@@ -2317,13 +2320,13 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46316.01041666666</v>
+        <v>46319.9375</v>
       </c>
       <c r="B92">
         <v>0</v>
       </c>
       <c r="C92">
-        <v>6.774</v>
+        <v>0.13</v>
       </c>
       <c r="D92">
         <v>91</v>
@@ -2334,10 +2337,10 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46316.02083333334</v>
+        <v>46319.94791666666</v>
       </c>
       <c r="B93">
-        <v>5.612</v>
+        <v>8.085000000000001</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -2351,10 +2354,10 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46316.03125</v>
+        <v>46319.95833333334</v>
       </c>
       <c r="B94">
-        <v>7.792</v>
+        <v>9.961</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -2368,13 +2371,13 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46316.04166666666</v>
+        <v>46319.96875</v>
       </c>
       <c r="B95">
-        <v>0</v>
+        <v>4.299</v>
       </c>
       <c r="C95">
-        <v>7.879</v>
+        <v>0</v>
       </c>
       <c r="D95">
         <v>94</v>
@@ -2385,10 +2388,10 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46316.05208333334</v>
+        <v>46319.97916666666</v>
       </c>
       <c r="B96">
-        <v>14.325</v>
+        <v>18.527</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -2402,13 +2405,13 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46316.0625</v>
+        <v>46319.98958333334</v>
       </c>
       <c r="B97">
-        <v>0</v>
+        <v>23.573</v>
       </c>
       <c r="C97">
-        <v>1.844</v>
+        <v>0</v>
       </c>
       <c r="D97">
         <v>96</v>
@@ -2419,10 +2422,10 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46316.07291666666</v>
+        <v>46320</v>
       </c>
       <c r="B98">
-        <v>7.829</v>
+        <v>11.896</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -2436,13 +2439,13 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46316.08333333334</v>
+        <v>46320.01041666666</v>
       </c>
       <c r="B99">
-        <v>0</v>
+        <v>3.522</v>
       </c>
       <c r="C99">
-        <v>3.538</v>
+        <v>0</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -2453,13 +2456,13 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46316.09375</v>
+        <v>46320.02083333334</v>
       </c>
       <c r="B100">
-        <v>0</v>
+        <v>24.958</v>
       </c>
       <c r="C100">
-        <v>18.872</v>
+        <v>0</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2470,13 +2473,13 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46316.10416666666</v>
+        <v>46320.03125</v>
       </c>
       <c r="B101">
-        <v>0</v>
+        <v>17.236</v>
       </c>
       <c r="C101">
-        <v>3.946</v>
+        <v>0</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -2487,13 +2490,13 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46316.11458333334</v>
+        <v>46320.04166666666</v>
       </c>
       <c r="B102">
-        <v>0</v>
+        <v>2.958</v>
       </c>
       <c r="C102">
-        <v>17.291</v>
+        <v>0</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -2504,13 +2507,13 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46316.125</v>
+        <v>46320.05208333334</v>
       </c>
       <c r="B103">
-        <v>0</v>
+        <v>15.418</v>
       </c>
       <c r="C103">
-        <v>12.676</v>
+        <v>0</v>
       </c>
       <c r="D103">
         <v>6</v>
@@ -2521,10 +2524,10 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46316.13541666666</v>
+        <v>46320.0625</v>
       </c>
       <c r="B104">
-        <v>4.809</v>
+        <v>28.012</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -2538,13 +2541,13 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46316.14583333334</v>
+        <v>46320.08333333334</v>
       </c>
       <c r="B105">
-        <v>0</v>
+        <v>12.882</v>
       </c>
       <c r="C105">
-        <v>10.912</v>
+        <v>0</v>
       </c>
       <c r="D105">
         <v>8</v>
@@ -2555,13 +2558,13 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46316.15625</v>
+        <v>46320.09375</v>
       </c>
       <c r="B106">
-        <v>0</v>
+        <v>11.694</v>
       </c>
       <c r="C106">
-        <v>30.798</v>
+        <v>0</v>
       </c>
       <c r="D106">
         <v>9</v>
@@ -2572,13 +2575,13 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46316.16666666666</v>
+        <v>46320.10416666666</v>
       </c>
       <c r="B107">
-        <v>0</v>
+        <v>7.827</v>
       </c>
       <c r="C107">
-        <v>3.317</v>
+        <v>0</v>
       </c>
       <c r="D107">
         <v>10</v>
@@ -2589,13 +2592,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46316.17708333334</v>
+        <v>46320.11458333334</v>
       </c>
       <c r="B108">
-        <v>0</v>
+        <v>8.221</v>
       </c>
       <c r="C108">
-        <v>46.085</v>
+        <v>0</v>
       </c>
       <c r="D108">
         <v>11</v>
@@ -2606,13 +2609,13 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46316.1875</v>
+        <v>46320.125</v>
       </c>
       <c r="B109">
-        <v>0</v>
+        <v>3.257</v>
       </c>
       <c r="C109">
-        <v>40.261</v>
+        <v>0</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -2623,13 +2626,13 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46316.19791666666</v>
+        <v>46320.13541666666</v>
       </c>
       <c r="B110">
-        <v>0</v>
+        <v>1.395</v>
       </c>
       <c r="C110">
-        <v>64.42400000000001</v>
+        <v>0</v>
       </c>
       <c r="D110">
         <v>13</v>
@@ -2640,13 +2643,13 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46316.20833333334</v>
+        <v>46320.14583333334</v>
       </c>
       <c r="B111">
         <v>0</v>
       </c>
       <c r="C111">
-        <v>52.461</v>
+        <v>2.902</v>
       </c>
       <c r="D111">
         <v>14</v>
@@ -2657,13 +2660,13 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46316.21875</v>
+        <v>46320.15625</v>
       </c>
       <c r="B112">
-        <v>0</v>
+        <v>2.823</v>
       </c>
       <c r="C112">
-        <v>44.586</v>
+        <v>0</v>
       </c>
       <c r="D112">
         <v>15</v>
@@ -2674,13 +2677,13 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46316.22916666666</v>
+        <v>46320.16666666666</v>
       </c>
       <c r="B113">
-        <v>4.047</v>
+        <v>0</v>
       </c>
       <c r="C113">
-        <v>0</v>
+        <v>2.243</v>
       </c>
       <c r="D113">
         <v>16</v>
@@ -2691,10 +2694,10 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46316.23958333334</v>
+        <v>46320.17708333334</v>
       </c>
       <c r="B114">
-        <v>1.83</v>
+        <v>3.83</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -2708,13 +2711,13 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46316.25</v>
+        <v>46320.1875</v>
       </c>
       <c r="B115">
-        <v>0</v>
+        <v>7.457</v>
       </c>
       <c r="C115">
-        <v>8.286</v>
+        <v>0</v>
       </c>
       <c r="D115">
         <v>18</v>
@@ -2725,13 +2728,13 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46316.26041666666</v>
+        <v>46320.19791666666</v>
       </c>
       <c r="B116">
-        <v>0</v>
+        <v>6.421</v>
       </c>
       <c r="C116">
-        <v>0.772</v>
+        <v>0</v>
       </c>
       <c r="D116">
         <v>19</v>
@@ -2742,13 +2745,13 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46316.27083333334</v>
+        <v>46320.20833333334</v>
       </c>
       <c r="B117">
-        <v>0</v>
+        <v>2.718</v>
       </c>
       <c r="C117">
-        <v>0.035</v>
+        <v>0</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -2759,13 +2762,13 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46316.28125</v>
+        <v>46320.21875</v>
       </c>
       <c r="B118">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="C118">
-        <v>0.172</v>
+        <v>0</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -2776,13 +2779,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46316.29166666666</v>
+        <v>46320.22916666666</v>
       </c>
       <c r="B119">
-        <v>0</v>
+        <v>2.714</v>
       </c>
       <c r="C119">
-        <v>7.529</v>
+        <v>0</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -2793,13 +2796,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46316.30208333334</v>
+        <v>46320.23958333334</v>
       </c>
       <c r="B120">
         <v>0</v>
       </c>
       <c r="C120">
-        <v>1.264</v>
+        <v>3.434</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -2810,13 +2813,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46316.3125</v>
+        <v>46320.25</v>
       </c>
       <c r="B121">
         <v>0</v>
       </c>
       <c r="C121">
-        <v>9.667999999999999</v>
+        <v>0.016</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -2827,10 +2830,10 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46316.32291666666</v>
+        <v>46320.26041666666</v>
       </c>
       <c r="B122">
-        <v>9.747999999999999</v>
+        <v>12.899</v>
       </c>
       <c r="C122">
         <v>0</v>
@@ -2844,13 +2847,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46316.33333333334</v>
+        <v>46320.27083333334</v>
       </c>
       <c r="B123">
-        <v>17.773</v>
+        <v>0</v>
       </c>
       <c r="C123">
-        <v>0</v>
+        <v>2.079</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -2861,13 +2864,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46316.34375</v>
+        <v>46320.28125</v>
       </c>
       <c r="B124">
-        <v>19.478</v>
+        <v>0</v>
       </c>
       <c r="C124">
-        <v>0</v>
+        <v>40.242</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -2878,13 +2881,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46316.35416666666</v>
+        <v>46320.32291666666</v>
       </c>
       <c r="B125">
-        <v>13.631</v>
+        <v>0</v>
       </c>
       <c r="C125">
-        <v>0</v>
+        <v>13.18</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -2895,19 +2898,36 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46316.36458333334</v>
+        <v>46320.33333333334</v>
       </c>
       <c r="B126">
-        <v>12.595</v>
+        <v>0</v>
       </c>
       <c r="C126">
-        <v>0</v>
+        <v>13.599</v>
       </c>
       <c r="D126">
         <v>29</v>
       </c>
       <c r="E126" t="s">
         <v>129</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5">
+      <c r="A127" s="2">
+        <v>46320.34375</v>
+      </c>
+      <c r="B127">
+        <v>2.601</v>
+      </c>
+      <c r="C127">
+        <v>0</v>
+      </c>
+      <c r="D127">
+        <v>30</v>
+      </c>
+      <c r="E127" t="s">
+        <v>130</v>
       </c>
     </row>
   </sheetData>
